--- a/test/casedb/integration/case_access/test_case_access.xlsx
+++ b/test/casedb/integration/case_access/test_case_access.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivo_v\Documents\gen-epix-api\test\casedb\integration\case_access\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B9378B-E48A-436A-BD3C-CC50223717A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DE2C17-DA4F-4801-9D69-A2C766C910BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="20057" tabRatio="913" firstSheet="2" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="20057" tabRatio="913" firstSheet="2" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Organization" sheetId="17" r:id="rId1"/>
@@ -19,33 +19,37 @@
     <sheet name="UserInvitation" sheetId="19" r:id="rId4"/>
     <sheet name="Dim" sheetId="14" r:id="rId5"/>
     <sheet name="Col" sheetId="13" r:id="rId6"/>
-    <sheet name="CaseType" sheetId="8" r:id="rId7"/>
-    <sheet name="CaseTypeSetCategory" sheetId="7" r:id="rId8"/>
-    <sheet name="CaseTypeSet" sheetId="6" r:id="rId9"/>
-    <sheet name="CaseTypeSetMember" sheetId="12" r:id="rId10"/>
-    <sheet name="CaseTypeCol" sheetId="11" r:id="rId11"/>
-    <sheet name="CaseTypeColSet" sheetId="10" r:id="rId12"/>
-    <sheet name="CaseTypeColSetMember" sheetId="9" r:id="rId13"/>
-    <sheet name="OrganizationAdminPolicy" sheetId="2" r:id="rId14"/>
-    <sheet name="CaseCrudCommand" sheetId="24" r:id="rId15"/>
-    <sheet name="OrganizationAccessCasePolicy" sheetId="20" r:id="rId16"/>
-    <sheet name="UserAccessCasePolicy" sheetId="21" r:id="rId17"/>
-    <sheet name="UserShareCasePolicy" sheetId="23" r:id="rId18"/>
-    <sheet name="OrganizationShareCasePolicy" sheetId="22" r:id="rId19"/>
-    <sheet name="_DataCollectionRelation" sheetId="18" r:id="rId20"/>
-    <sheet name="_OrganizationCasePolicy" sheetId="3" r:id="rId21"/>
-    <sheet name="_UserCasePolicy" sheetId="4" r:id="rId22"/>
-    <sheet name="_OrganizationDataCollectionPoli" sheetId="5" r:id="rId23"/>
-    <sheet name="_UserDataCollectionPolicy" sheetId="1" r:id="rId24"/>
+    <sheet name="Disease" sheetId="25" r:id="rId7"/>
+    <sheet name="EtiologicalAgent" sheetId="26" r:id="rId8"/>
+    <sheet name="CaseType" sheetId="8" r:id="rId9"/>
+    <sheet name="CaseTypeSetCategory" sheetId="7" r:id="rId10"/>
+    <sheet name="CaseTypeSet" sheetId="6" r:id="rId11"/>
+    <sheet name="CaseTypeSetMember" sheetId="12" r:id="rId12"/>
+    <sheet name="CaseTypeCol" sheetId="11" r:id="rId13"/>
+    <sheet name="CaseTypeColSet" sheetId="10" r:id="rId14"/>
+    <sheet name="CaseTypeColSetMember" sheetId="9" r:id="rId15"/>
+    <sheet name="OrganizationAdminPolicy" sheetId="2" r:id="rId16"/>
+    <sheet name="CaseCrudCommand" sheetId="24" r:id="rId17"/>
+    <sheet name="OrganizationAccessCasePolicy" sheetId="20" r:id="rId18"/>
+    <sheet name="UserAccessCasePolicy" sheetId="21" r:id="rId19"/>
+    <sheet name="UserShareCasePolicy" sheetId="23" r:id="rId20"/>
+    <sheet name="OrganizationShareCasePolicy" sheetId="22" r:id="rId21"/>
+    <sheet name="_DataCollectionRelation" sheetId="18" r:id="rId22"/>
+    <sheet name="_OrganizationCasePolicy" sheetId="3" r:id="rId23"/>
+    <sheet name="_UserCasePolicy" sheetId="4" r:id="rId24"/>
+    <sheet name="_OrganizationDataCollectionPoli" sheetId="5" r:id="rId25"/>
+    <sheet name="_UserDataCollectionPolicy" sheetId="1" r:id="rId26"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">_OrganizationDataCollectionPoli!$A$1:$M$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">_UserDataCollectionPolicy!$A$1:$L$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">CaseTypeSetMember!$A$1:$G$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">OrganizationAccessCasePolicy!$A$1:$U$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">UserAccessCasePolicy!$A$1:$V$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">_OrganizationDataCollectionPoli!$A$1:$M$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">_UserDataCollectionPolicy!$A$1:$L$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">CaseCrudCommand!$A$1:$AT$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">CaseTypeSetMember!$A$1:$G$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">OrganizationAccessCasePolicy!$A$1:$U$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">UserAccessCasePolicy!$A$1:$V$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -85,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2599" uniqueCount="935">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2571" uniqueCount="974">
   <si>
     <t>id</t>
   </si>
@@ -2643,15 +2647,6 @@
     <t>case.content.case_type_col_value1</t>
   </si>
   <si>
-    <t>case.content.case_type_col_code1</t>
-  </si>
-  <si>
-    <t>case.content.case_type_col_code3</t>
-  </si>
-  <si>
-    <t>case.content.case_type_col_code2</t>
-  </si>
-  <si>
     <t>is_allowed</t>
   </si>
   <si>
@@ -2838,9 +2833,6 @@
     <t>dm.case.case_type.code</t>
   </si>
   <si>
-    <t>case.created_in_data_collection.name</t>
-  </si>
-  <si>
     <t>CREATE</t>
   </si>
   <si>
@@ -2853,12 +2845,6 @@
     <t>a</t>
   </si>
   <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
     <t>dm.case.case_type.cols_match</t>
   </si>
   <si>
@@ -2890,6 +2876,141 @@
   </si>
   <si>
     <t>dm.roles.is_org_user</t>
+  </si>
+  <si>
+    <t>dm.organization_access_case_policy.case_type_set.contains_case_type</t>
+  </si>
+  <si>
+    <t>dm.user_access_case_policy.case_type_set.contains_case_type</t>
+  </si>
+  <si>
+    <t>dm.case.content.case_type_col_code1</t>
+  </si>
+  <si>
+    <t>dm.case.created_in_data_collection.name</t>
+  </si>
+  <si>
+    <t>dm.case.content.case_type_col_code2</t>
+  </si>
+  <si>
+    <t>dm.case.content.case_type_col_code3</t>
+  </si>
+  <si>
+    <t>dm.organization_access_case_policy.read_case_type_col_set.contains_col1</t>
+  </si>
+  <si>
+    <t>dm.organization_access_case_policy.write_case_type_col_set.contains_col1</t>
+  </si>
+  <si>
+    <t>dm.organization_access_case_policy.read_case_type_col_set.contains_col2</t>
+  </si>
+  <si>
+    <t>dm.organization_access_case_policy.write_case_type_col_set.contains_col2</t>
+  </si>
+  <si>
+    <t>dm.organization_access_case_policy.read_case_type_col_set.contains_col3</t>
+  </si>
+  <si>
+    <t>dm.organization_access_case_policy.write_case_type_col_set.contains_col3</t>
+  </si>
+  <si>
+    <t>dm.user_access_case_policy.read_case_type_col_set.contains_col1</t>
+  </si>
+  <si>
+    <t>dm.user_access_case_policy.write_case_type_col_set.contains_col1</t>
+  </si>
+  <si>
+    <t>dm.user_access_case_policy.read_case_type_col_set.contains_col2</t>
+  </si>
+  <si>
+    <t>dm.user_access_case_policy.write_case_type_col_set.contains_col2</t>
+  </si>
+  <si>
+    <t>dm.user_access_case_policy.read_case_type_col_set.contains_col3</t>
+  </si>
+  <si>
+    <t>dm.user_access_case_policy.write_case_type_col_set.contains_col3</t>
+  </si>
+  <si>
+    <t>icd_code</t>
+  </si>
+  <si>
+    <t>disease1</t>
+  </si>
+  <si>
+    <t>disease2</t>
+  </si>
+  <si>
+    <t>disease3</t>
+  </si>
+  <si>
+    <t>disease4</t>
+  </si>
+  <si>
+    <t>disease5</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>etiological_agent1</t>
+  </si>
+  <si>
+    <t>etiological_agent2</t>
+  </si>
+  <si>
+    <t>etiological_agent3</t>
+  </si>
+  <si>
+    <t>etiological_agent4</t>
+  </si>
+  <si>
+    <t>etiological_agent5</t>
+  </si>
+  <si>
+    <t>dm.disease.name</t>
+  </si>
+  <si>
+    <t>dm.etiological_agent.name</t>
+  </si>
+  <si>
+    <t>ORGANISM</t>
+  </si>
+  <si>
+    <t>case.content.case_type_col_value2</t>
+  </si>
+  <si>
+    <t>case.content.case_type_col_value3</t>
+  </si>
+  <si>
+    <t>CASES_CREATE</t>
+  </si>
+  <si>
+    <t>0198221b-5adb-d596-0352-8ae2fe336894</t>
+  </si>
+  <si>
+    <t>0198221b-5adb-068a-e2eb-3e3da27aaf5c</t>
+  </si>
+  <si>
+    <t>0198221b-5adb-ea6d-fc5c-e1198ac9e42f</t>
+  </si>
+  <si>
+    <t>0198221b-5adb-2258-c194-eab8a8e94b90</t>
+  </si>
+  <si>
+    <t>0198221b-5adb-f506-672a-860dee7d4d46</t>
+  </si>
+  <si>
+    <t>0198221b-5adb-97fb-41db-bca5efc1bbb6</t>
+  </si>
+  <si>
+    <t>0198221b-5adb-ac88-8aac-4b199ae92773</t>
+  </si>
+  <si>
+    <t>0198221b-5adb-bbaa-606d-fc0c31bc55ee</t>
+  </si>
+  <si>
+    <t>user.name</t>
   </si>
 </sst>
 </file>
@@ -2931,7 +3052,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2952,6 +3073,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3018,7 +3145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3064,6 +3191,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3462,6 +3590,366 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="34.23046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.07421875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.53515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.84375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="35.84375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.07421875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.07421875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.23046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.61328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.53515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>840</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E2" s="6" t="str">
+        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D2,CaseTypeSetCategory!$A:$A,0))</f>
+        <v>case_type_set_category1</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E3" s="6" t="str">
+        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D3,CaseTypeSetCategory!$A:$A,0))</f>
+        <v>case_type_set_category1</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>304</v>
+      </c>
+      <c r="D4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E4" s="6" t="str">
+        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D4,CaseTypeSetCategory!$A:$A,0))</f>
+        <v>case_type_set_category1</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" t="s">
+        <v>305</v>
+      </c>
+      <c r="D5" t="s">
+        <v>302</v>
+      </c>
+      <c r="E5" s="6" t="str">
+        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D5,CaseTypeSetCategory!$A:$A,0))</f>
+        <v>case_type_set_category1</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" t="s">
+        <v>306</v>
+      </c>
+      <c r="D6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E6" s="6" t="str">
+        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D6,CaseTypeSetCategory!$A:$A,0))</f>
+        <v>case_type_set_category1</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B7" t="s">
+        <v>308</v>
+      </c>
+      <c r="D7" t="s">
+        <v>302</v>
+      </c>
+      <c r="E7" s="6" t="str">
+        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D7,CaseTypeSetCategory!$A:$A,0))</f>
+        <v>case_type_set_category1</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>309</v>
+      </c>
+      <c r="B8" t="s">
+        <v>310</v>
+      </c>
+      <c r="D8" t="s">
+        <v>302</v>
+      </c>
+      <c r="E8" s="6" t="str">
+        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D8,CaseTypeSetCategory!$A:$A,0))</f>
+        <v>case_type_set_category1</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>311</v>
+      </c>
+      <c r="B9" t="s">
+        <v>312</v>
+      </c>
+      <c r="D9" t="s">
+        <v>302</v>
+      </c>
+      <c r="E9" s="6" t="str">
+        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D9,CaseTypeSetCategory!$A:$A,0))</f>
+        <v>case_type_set_category1</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>313</v>
+      </c>
+      <c r="B10" t="s">
+        <v>314</v>
+      </c>
+      <c r="D10" t="s">
+        <v>302</v>
+      </c>
+      <c r="E10" s="6" t="str">
+        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D10,CaseTypeSetCategory!$A:$A,0))</f>
+        <v>case_type_set_category1</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>315</v>
+      </c>
+      <c r="B11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D11" t="s">
+        <v>302</v>
+      </c>
+      <c r="E11" s="6" t="str">
+        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D11,CaseTypeSetCategory!$A:$A,0))</f>
+        <v>case_type_set_category1</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>317</v>
+      </c>
+      <c r="B12" t="s">
+        <v>318</v>
+      </c>
+      <c r="D12" t="s">
+        <v>302</v>
+      </c>
+      <c r="E12" s="6" t="str">
+        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D12,CaseTypeSetCategory!$A:$A,0))</f>
+        <v>case_type_set_category1</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>319</v>
+      </c>
+      <c r="B13" t="s">
+        <v>320</v>
+      </c>
+      <c r="D13" t="s">
+        <v>302</v>
+      </c>
+      <c r="E13" s="6" t="str">
+        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D13,CaseTypeSetCategory!$A:$A,0))</f>
+        <v>case_type_set_category1</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>321</v>
+      </c>
+      <c r="B14" t="s">
+        <v>322</v>
+      </c>
+      <c r="D14" t="s">
+        <v>302</v>
+      </c>
+      <c r="E14" s="6" t="str">
+        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D14,CaseTypeSetCategory!$A:$A,0))</f>
+        <v>case_type_set_category1</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>323</v>
+      </c>
+      <c r="B15" t="s">
+        <v>324</v>
+      </c>
+      <c r="D15" t="s">
+        <v>302</v>
+      </c>
+      <c r="E15" s="6" t="str">
+        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D15,CaseTypeSetCategory!$A:$A,0))</f>
+        <v>case_type_set_category1</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>325</v>
+      </c>
+      <c r="B16" t="s">
+        <v>326</v>
+      </c>
+      <c r="D16" t="s">
+        <v>302</v>
+      </c>
+      <c r="E16" s="6" t="str">
+        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D16,CaseTypeSetCategory!$A:$A,0))</f>
+        <v>case_type_set_category1</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:H26"/>
@@ -3500,7 +3988,7 @@
         <v>532</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
@@ -4020,7 +4508,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:T46"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -4879,7 +5367,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C46"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -5399,7 +5887,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -5437,7 +5925,7 @@
         <v>355</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
@@ -6480,7 +6968,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -6628,44 +7116,60 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E0C7C33-6768-4AAE-A57E-F80585DED472}">
-  <dimension ref="A1:AF29"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AT33"/>
+  <sheetFormatPr defaultColWidth="5.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="5.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="35.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.15234375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.69140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.53515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="8.921875" style="6" customWidth="1"/>
-    <col min="9" max="9" width="39.4609375" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="42.765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.921875" style="6" customWidth="1"/>
-    <col min="12" max="12" width="32.69140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="36" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.53515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35.3828125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="33.53515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.15234375" style="6" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="26.53515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.4609375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="34.53515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="32.84375" style="6" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.69140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.23046875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="34.765625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="29.921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="30.3046875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="34.84375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="29.921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="30.3046875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="34.69140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="29.921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="30.3046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.765625" style="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.61328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.23046875" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="62.84375" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="41.69140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="45" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.4609375" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="56.15234375" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="34.921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="38.23046875" style="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="36.15234375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="33.53515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.3828125" style="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="28.765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.69140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="34.53515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="38.3828125" style="6" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.921875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.4609375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="34.765625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="32.53515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="35.3828125" style="6" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="66.15234375" style="6" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="66.765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="59.3828125" style="6" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="60.07421875" style="6" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="29.61328125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="32.53515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="35.3828125" style="6" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="66.15234375" style="6" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="66.765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="59.3828125" style="6" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="60.07421875" style="6" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="29.61328125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="32.53515625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="35.3828125" style="6" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="66.15234375" style="6" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="66.765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="59.3828125" style="6" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="60.07421875" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>841</v>
       </c>
@@ -6676,99 +7180,141 @@
         <v>844</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>819</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>925</v>
-      </c>
-      <c r="F1" t="s">
+        <v>973</v>
+      </c>
+      <c r="E1" t="s">
         <v>842</v>
       </c>
+      <c r="F1" s="19" t="s">
+        <v>852</v>
+      </c>
       <c r="G1" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>923</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>920</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>929</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>926</v>
-      </c>
-      <c r="I1" s="6" t="s">
+      <c r="K1" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>854</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>922</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>930</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="P1" s="6" t="s">
         <v>856</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>857</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>928</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>858</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>859</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>855</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>843</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>845</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="S1" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>918</v>
+      </c>
+      <c r="U1" t="s">
+        <v>846</v>
+      </c>
+      <c r="V1" t="s">
+        <v>847</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="X1" t="s">
+        <v>848</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>849</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>850</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>851</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>931</v>
+      </c>
+      <c r="AC1" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="AD1" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="AE1" s="6" t="s">
+        <v>941</v>
+      </c>
+      <c r="AF1" s="6" t="s">
+        <v>942</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>915</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>962</v>
+      </c>
+      <c r="AI1" s="6" t="s">
+        <v>933</v>
+      </c>
+      <c r="AJ1" s="6" t="s">
+        <v>937</v>
+      </c>
+      <c r="AK1" s="6" t="s">
+        <v>938</v>
+      </c>
+      <c r="AL1" s="6" t="s">
+        <v>943</v>
+      </c>
+      <c r="AM1" s="6" t="s">
+        <v>944</v>
+      </c>
+      <c r="AN1" t="s">
         <v>916</v>
       </c>
-      <c r="R1" s="6" t="s">
-        <v>924</v>
-      </c>
-      <c r="S1" t="s">
-        <v>846</v>
-      </c>
-      <c r="T1" t="s">
-        <v>847</v>
-      </c>
-      <c r="U1" s="6" t="s">
-        <v>917</v>
-      </c>
-      <c r="V1" t="s">
-        <v>848</v>
-      </c>
-      <c r="W1" t="s">
-        <v>849</v>
-      </c>
-      <c r="X1" t="s">
-        <v>850</v>
-      </c>
-      <c r="Y1" s="6" t="s">
-        <v>852</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>851</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>919</v>
-      </c>
-      <c r="AB1" s="6" t="s">
-        <v>854</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>851</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>920</v>
-      </c>
-      <c r="AE1" s="6" t="s">
-        <v>853</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AO1" t="s">
+        <v>963</v>
+      </c>
+      <c r="AP1" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="AQ1" s="6" t="s">
+        <v>939</v>
+      </c>
+      <c r="AR1" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="AS1" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="AT1" s="6" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="2" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="C2" t="s">
         <v>658</v>
@@ -6777,106 +7323,150 @@
         <f>INDEX(User!$C:$C,MATCH($C2,User!$A:$A,0))</f>
         <v>root1_1</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" t="s">
+        <v>914</v>
+      </c>
+      <c r="F2" s="19" t="b">
+        <f>IF($E2="CREATE",$H2,IF($E2="CASES_CREATE",OR($H2,AND($J2,$K2,$N2,$O2,$AD2,AF2,$AK2,$AM2,$AR2,$AT2)),"TBD"))</f>
+        <v>1</v>
+      </c>
+      <c r="G2" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C2,User!$A:$A,0))</f>
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
       </c>
-      <c r="F2" t="s">
-        <v>918</v>
-      </c>
-      <c r="G2" s="6" t="b">
+      <c r="H2" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C2,User!$A:$A,0))</f>
         <v>1</v>
       </c>
-      <c r="H2" s="6">
-        <f>IF(ISNA(MATCH($E2&amp;"|"&amp;$T2,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E2&amp;"|"&amp;$T2,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I2" s="6">
+        <f>IF(ISNA(MATCH($G2&amp;"|"&amp;$V2,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G2&amp;"|"&amp;$V2,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v>2</v>
       </c>
-      <c r="I2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I2" ca="1">IF($H2="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H2),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H2)&amp;"|"&amp;$P2,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
       <c r="J2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J2" ca="1">IF($H2="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H2),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H2)&amp;"|"&amp;$P2,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="K2" s="6" t="str">
-        <f>IF(ISNA(MATCH($C2&amp;"|"&amp;$T2,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C2&amp;"|"&amp;$T2,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="J2" ca="1">IF($I2="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I2)&amp;"|"&amp;$R2,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="K2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K2" ca="1">IF($I2="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I2),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I2)&amp;"|"&amp;$R2,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="L2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L2" ca="1">IF($I2="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I2),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I2)&amp;"|"&amp;$R2,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M2" s="6" t="str">
+        <f>IF(ISNA(MATCH($C2&amp;"|"&amp;$V2,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C2&amp;"|"&amp;$V2,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L2" ca="1">IF($K2="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K2),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K2)&amp;"|"&amp;$P2,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M2" ca="1">IF($K2="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K2),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K2)&amp;"|"&amp;$P2,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N2" s="6" t="b">
-        <f ca="1">IF($F2="CREATE",OR($G2,AND($I2,$L2)),"TBD")</f>
-        <v>1</v>
-      </c>
-      <c r="O2" t="s">
-        <v>862</v>
-      </c>
-      <c r="P2" t="s">
+      <c r="N2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N2" ca="1">IF($M2="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M2)&amp;"|"&amp;$R2,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O2" ca="1">IF($M2="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M2),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M2)&amp;"|"&amp;$R2,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P2" ca="1">IF($M2="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M2),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M2)&amp;"|"&amp;$R2,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>859</v>
+      </c>
+      <c r="R2" t="s">
         <v>334</v>
       </c>
-      <c r="Q2" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P2,CaseType!$A:$A,0))</f>
+      <c r="S2" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R2,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R2" s="6" t="b">
-        <f>AND(IF($X2="",TRUE,$P2=INDEX(CaseTypeCol!$B:$B,MATCH($X2,CaseTypeCol!$A:$A,0))),IF($AA2="",TRUE,$P2=INDEX(CaseTypeCol!$B:$B,MATCH($AA2,CaseTypeCol!$A:$A,0))),IF($AD2="",TRUE,$P2=INDEX(CaseTypeCol!$B:$B,MATCH($AD2,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="T2" s="6" t="b">
+        <f>AND(IF($Z2="",TRUE,$R2=INDEX(CaseTypeCol!$B:$B,MATCH($Z2,CaseTypeCol!$A:$A,0))),IF($AG2="",TRUE,$R2=INDEX(CaseTypeCol!$B:$B,MATCH($AG2,CaseTypeCol!$A:$A,0))),IF($AN2="",TRUE,$R2=INDEX(CaseTypeCol!$B:$B,MATCH($AN2,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V2" t="s">
         <v>12</v>
       </c>
-      <c r="U2" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T2,DataCollection!$A:$A,0))</f>
+      <c r="W2" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V2,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W2" s="14">
+      <c r="Y2" s="14">
         <v>36526</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>357</v>
       </c>
-      <c r="Y2" s="6" t="str">
-        <f>IF($X2="","",INDEX(CaseTypeCol!$G:$G,MATCH($X2,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA2" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB2" s="6" t="str">
+        <f>IF($Z2="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z2,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z2" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB2" s="6" t="str">
-        <f>IF($AA2="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA2,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE2" s="6" t="str">
-        <f>IF($AD2="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD2,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC2" ca="1">IF($Z2="",TRUE,IF($I2="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I2)&amp;"|"&amp;$Z2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AD2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD2" ca="1">IF($Z2="",TRUE,IF($I2="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I2)&amp;"|"&amp;$Z2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AE2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE2" ca="1">IF($Z2="",TRUE,IF($M2="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M2)&amp;"|"&amp;$Z2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF2" ca="1">IF($Z2="",TRUE,IF($M2="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M2)&amp;"|"&amp;$Z2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI2" s="6" t="str">
+        <f>IF($AG2="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG2,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ2" ca="1">IF($AG2="",TRUE,IF($I2="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I2)&amp;"|"&amp;$AG2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK2" ca="1">IF($AG2="",TRUE,IF($I2="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I2)&amp;"|"&amp;$AG2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL2" ca="1">IF($AG2="",TRUE,IF($M2="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M2)&amp;"|"&amp;$AG2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM2" ca="1">IF($AG2="",TRUE,IF($M2="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M2)&amp;"|"&amp;$AG2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP2" s="6" t="str">
+        <f>IF($AN2="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN2,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ2" ca="1">IF($AN2="",TRUE,IF($I2="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I2)&amp;"|"&amp;$AN2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR2" ca="1">IF($AN2="",TRUE,IF($I2="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I2)&amp;"|"&amp;$AN2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS2" ca="1">IF($AN2="",TRUE,IF($M2="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M2)&amp;"|"&amp;$AN2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT2" ca="1">IF($AN2="",TRUE,IF($M2="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M2)&amp;"|"&amp;$AN2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="C3" t="s">
         <v>660</v>
@@ -6885,106 +7475,150 @@
         <f>INDEX(User!$C:$C,MATCH($C3,User!$A:$A,0))</f>
         <v>app_admin1_1</v>
       </c>
-      <c r="E3" s="6" t="str">
+      <c r="E3" t="s">
+        <v>914</v>
+      </c>
+      <c r="F3" s="19" t="b">
+        <f t="shared" ref="F3:F33" si="0">IF($E3="CREATE",$H3,IF($E3="CASES_CREATE",OR($H3,AND($J3,$K3,$N3,$O3,$AD3,AF3,$AK3,$AM3,$AR3,$AT3)),"TBD"))</f>
+        <v>1</v>
+      </c>
+      <c r="G3" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C3,User!$A:$A,0))</f>
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
       </c>
-      <c r="F3" t="s">
-        <v>918</v>
-      </c>
-      <c r="G3" s="6" t="b">
+      <c r="H3" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C3,User!$A:$A,0))</f>
         <v>1</v>
       </c>
-      <c r="H3" s="6">
-        <f>IF(ISNA(MATCH($E3&amp;"|"&amp;$T3,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E3&amp;"|"&amp;$T3,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I3" s="6">
+        <f>IF(ISNA(MATCH($G3&amp;"|"&amp;$V3,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G3&amp;"|"&amp;$V3,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v>2</v>
       </c>
-      <c r="I3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I3" ca="1">IF($H3="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H3),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H3)&amp;"|"&amp;$P3,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
       <c r="J3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J3" ca="1">IF($H3="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H3),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H3)&amp;"|"&amp;$P3,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="K3" s="6" t="str">
-        <f>IF(ISNA(MATCH($C3&amp;"|"&amp;$T3,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C3&amp;"|"&amp;$T3,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="J3" ca="1">IF($I3="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I3)&amp;"|"&amp;$R3,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="K3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K3" ca="1">IF($I3="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I3),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I3)&amp;"|"&amp;$R3,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="L3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L3" ca="1">IF($I3="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I3),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I3)&amp;"|"&amp;$R3,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M3" s="6" t="str">
+        <f>IF(ISNA(MATCH($C3&amp;"|"&amp;$V3,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C3&amp;"|"&amp;$V3,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L3" ca="1">IF($K3="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K3),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K3)&amp;"|"&amp;$P3,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M3" ca="1">IF($K3="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K3),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K3)&amp;"|"&amp;$P3,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="6" t="b">
-        <f t="shared" ref="N3:N29" ca="1" si="0">IF($F3="CREATE",OR($G3,AND($I3,$L3)),"TBD")</f>
-        <v>1</v>
-      </c>
-      <c r="O3" t="s">
-        <v>860</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="N3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N3" ca="1">IF($M3="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M3)&amp;"|"&amp;$R3,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O3" ca="1">IF($M3="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M3),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M3)&amp;"|"&amp;$R3,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P3" ca="1">IF($M3="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M3),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M3)&amp;"|"&amp;$R3,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>857</v>
+      </c>
+      <c r="R3" t="s">
         <v>334</v>
       </c>
-      <c r="Q3" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P3,CaseType!$A:$A,0))</f>
+      <c r="S3" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R3,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R3" s="6" t="b">
-        <f>AND(IF($X3="",TRUE,$P3=INDEX(CaseTypeCol!$B:$B,MATCH($X3,CaseTypeCol!$A:$A,0))),IF($AA3="",TRUE,$P3=INDEX(CaseTypeCol!$B:$B,MATCH($AA3,CaseTypeCol!$A:$A,0))),IF($AD3="",TRUE,$P3=INDEX(CaseTypeCol!$B:$B,MATCH($AD3,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T3" t="s">
+      <c r="T3" s="6" t="b">
+        <f>AND(IF($Z3="",TRUE,$R3=INDEX(CaseTypeCol!$B:$B,MATCH($Z3,CaseTypeCol!$A:$A,0))),IF($AG3="",TRUE,$R3=INDEX(CaseTypeCol!$B:$B,MATCH($AG3,CaseTypeCol!$A:$A,0))),IF($AN3="",TRUE,$R3=INDEX(CaseTypeCol!$B:$B,MATCH($AN3,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V3" t="s">
         <v>12</v>
       </c>
-      <c r="U3" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T3,DataCollection!$A:$A,0))</f>
+      <c r="W3" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V3,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W3" s="14">
+      <c r="Y3" s="14">
         <v>36526</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Z3" t="s">
         <v>357</v>
       </c>
-      <c r="Y3" s="6" t="str">
-        <f>IF($X3="","",INDEX(CaseTypeCol!$G:$G,MATCH($X3,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA3" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB3" s="6" t="str">
+        <f>IF($Z3="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z3,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z3" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB3" s="6" t="str">
-        <f>IF($AA3="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA3,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE3" s="6" t="str">
-        <f>IF($AD3="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD3,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC3" ca="1">IF($Z3="",TRUE,IF($I3="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I3)&amp;"|"&amp;$Z3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AD3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD3" ca="1">IF($Z3="",TRUE,IF($I3="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I3)&amp;"|"&amp;$Z3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AE3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE3" ca="1">IF($Z3="",TRUE,IF($M3="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M3)&amp;"|"&amp;$Z3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF3" ca="1">IF($Z3="",TRUE,IF($M3="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M3)&amp;"|"&amp;$Z3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI3" s="6" t="str">
+        <f>IF($AG3="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG3,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ3" ca="1">IF($AG3="",TRUE,IF($I3="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I3)&amp;"|"&amp;$AG3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK3" ca="1">IF($AG3="",TRUE,IF($I3="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I3)&amp;"|"&amp;$AG3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL3" ca="1">IF($AG3="",TRUE,IF($M3="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M3)&amp;"|"&amp;$AG3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM3" ca="1">IF($AG3="",TRUE,IF($M3="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M3)&amp;"|"&amp;$AG3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP3" s="6" t="str">
+        <f>IF($AN3="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN3,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ3" ca="1">IF($AN3="",TRUE,IF($I3="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I3)&amp;"|"&amp;$AN3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR3" ca="1">IF($AN3="",TRUE,IF($I3="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I3)&amp;"|"&amp;$AN3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS3" ca="1">IF($AN3="",TRUE,IF($M3="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M3)&amp;"|"&amp;$AN3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT3" ca="1">IF($AN3="",TRUE,IF($M3="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M3)&amp;"|"&amp;$AN3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="C4" t="s">
         <v>662</v>
@@ -6993,106 +7627,150 @@
         <f>INDEX(User!$C:$C,MATCH($C4,User!$A:$A,0))</f>
         <v>metadata_admin1_1</v>
       </c>
-      <c r="E4" s="6" t="str">
+      <c r="E4" t="s">
+        <v>914</v>
+      </c>
+      <c r="F4" s="19" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C4,User!$A:$A,0))</f>
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
       </c>
-      <c r="F4" t="s">
-        <v>918</v>
-      </c>
-      <c r="G4" s="6" t="b">
+      <c r="H4" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C4,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H4" s="6">
-        <f>IF(ISNA(MATCH($E4&amp;"|"&amp;$T4,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E4&amp;"|"&amp;$T4,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I4" s="6">
+        <f>IF(ISNA(MATCH($G4&amp;"|"&amp;$V4,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G4&amp;"|"&amp;$V4,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v>2</v>
       </c>
-      <c r="I4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I4" ca="1">IF($H4="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H4),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H4)&amp;"|"&amp;$P4,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
       <c r="J4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J4" ca="1">IF($H4="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H4),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H4)&amp;"|"&amp;$P4,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="K4" s="6" t="str">
-        <f>IF(ISNA(MATCH($C4&amp;"|"&amp;$T4,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C4&amp;"|"&amp;$T4,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="J4" ca="1">IF($I4="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I4)&amp;"|"&amp;$R4,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="K4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K4" ca="1">IF($I4="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I4),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I4)&amp;"|"&amp;$R4,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="L4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L4" ca="1">IF($I4="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I4),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I4)&amp;"|"&amp;$R4,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M4" s="6" t="str">
+        <f>IF(ISNA(MATCH($C4&amp;"|"&amp;$V4,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C4&amp;"|"&amp;$V4,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L4" ca="1">IF($K4="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K4),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K4)&amp;"|"&amp;$P4,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M4" ca="1">IF($K4="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K4),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K4)&amp;"|"&amp;$P4,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N4" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>890</v>
-      </c>
-      <c r="P4" t="s">
+      <c r="N4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N4" ca="1">IF($M4="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M4)&amp;"|"&amp;$R4,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O4" ca="1">IF($M4="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M4),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M4)&amp;"|"&amp;$R4,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P4" ca="1">IF($M4="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M4),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M4)&amp;"|"&amp;$R4,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>887</v>
+      </c>
+      <c r="R4" t="s">
         <v>334</v>
       </c>
-      <c r="Q4" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P4,CaseType!$A:$A,0))</f>
+      <c r="S4" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R4,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R4" s="6" t="b">
-        <f>AND(IF($X4="",TRUE,$P4=INDEX(CaseTypeCol!$B:$B,MATCH($X4,CaseTypeCol!$A:$A,0))),IF($AA4="",TRUE,$P4=INDEX(CaseTypeCol!$B:$B,MATCH($AA4,CaseTypeCol!$A:$A,0))),IF($AD4="",TRUE,$P4=INDEX(CaseTypeCol!$B:$B,MATCH($AD4,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T4" t="s">
+      <c r="T4" s="6" t="b">
+        <f>AND(IF($Z4="",TRUE,$R4=INDEX(CaseTypeCol!$B:$B,MATCH($Z4,CaseTypeCol!$A:$A,0))),IF($AG4="",TRUE,$R4=INDEX(CaseTypeCol!$B:$B,MATCH($AG4,CaseTypeCol!$A:$A,0))),IF($AN4="",TRUE,$R4=INDEX(CaseTypeCol!$B:$B,MATCH($AN4,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V4" t="s">
         <v>12</v>
       </c>
-      <c r="U4" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T4,DataCollection!$A:$A,0))</f>
+      <c r="W4" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V4,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W4" s="14">
+      <c r="Y4" s="14">
         <v>36526</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Z4" t="s">
         <v>357</v>
       </c>
-      <c r="Y4" s="6" t="str">
-        <f>IF($X4="","",INDEX(CaseTypeCol!$G:$G,MATCH($X4,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA4" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB4" s="6" t="str">
+        <f>IF($Z4="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z4,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z4" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB4" s="6" t="str">
-        <f>IF($AA4="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA4,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE4" s="6" t="str">
-        <f>IF($AD4="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD4,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC4" ca="1">IF($Z4="",TRUE,IF($I4="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I4)&amp;"|"&amp;$Z4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AD4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD4" ca="1">IF($Z4="",TRUE,IF($I4="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I4)&amp;"|"&amp;$Z4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AE4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE4" ca="1">IF($Z4="",TRUE,IF($M4="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M4)&amp;"|"&amp;$Z4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF4" ca="1">IF($Z4="",TRUE,IF($M4="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M4)&amp;"|"&amp;$Z4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="6" t="str">
+        <f>IF($AG4="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG4,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ4" ca="1">IF($AG4="",TRUE,IF($I4="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I4)&amp;"|"&amp;$AG4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK4" ca="1">IF($AG4="",TRUE,IF($I4="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I4)&amp;"|"&amp;$AG4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL4" ca="1">IF($AG4="",TRUE,IF($M4="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M4)&amp;"|"&amp;$AG4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM4" ca="1">IF($AG4="",TRUE,IF($M4="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M4)&amp;"|"&amp;$AG4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP4" s="6" t="str">
+        <f>IF($AN4="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN4,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ4" ca="1">IF($AN4="",TRUE,IF($I4="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I4)&amp;"|"&amp;$AN4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR4" ca="1">IF($AN4="",TRUE,IF($I4="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I4)&amp;"|"&amp;$AN4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS4" ca="1">IF($AN4="",TRUE,IF($M4="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M4)&amp;"|"&amp;$AN4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT4" ca="1">IF($AN4="",TRUE,IF($M4="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M4)&amp;"|"&amp;$AN4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>865</v>
+        <v>965</v>
       </c>
       <c r="C5" t="s">
         <v>85</v>
@@ -7101,2705 +7779,4415 @@
         <f>INDEX(User!$C:$C,MATCH($C5,User!$A:$A,0))</f>
         <v>org_admin1_1</v>
       </c>
-      <c r="E5" s="6" t="str">
+      <c r="E5" t="s">
+        <v>914</v>
+      </c>
+      <c r="F5" s="19" t="b">
+        <f t="shared" ref="F5:F6" si="1">IF($E5="CREATE",$H5,IF($E5="CASES_CREATE",OR($H5,AND($J5,$K5,$N5,$O5,$AD5,AF5,$AK5,$AM5,$AR5,$AT5)),"TBD"))</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C5,User!$A:$A,0))</f>
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
       </c>
-      <c r="F5" t="s">
-        <v>918</v>
-      </c>
-      <c r="G5" s="6" t="b">
+      <c r="H5" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C5,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H5" s="6">
-        <f>IF(ISNA(MATCH($E5&amp;"|"&amp;$T5,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E5&amp;"|"&amp;$T5,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I5" s="6">
+        <f>IF(ISNA(MATCH($G5&amp;"|"&amp;$V5,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G5&amp;"|"&amp;$V5,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v>2</v>
       </c>
-      <c r="I5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I5" ca="1">IF($H5="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H5),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H5)&amp;"|"&amp;$P5,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
       <c r="J5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J5" ca="1">IF($H5="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H5),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H5)&amp;"|"&amp;$P5,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="K5" s="6" t="str">
-        <f>IF(ISNA(MATCH($C5&amp;"|"&amp;$T5,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C5&amp;"|"&amp;$T5,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="J5" ca="1">IF($I5="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I5)&amp;"|"&amp;$R5,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="K5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K5" ca="1">IF($I5="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I5),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I5)&amp;"|"&amp;$R5,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="L5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L5" ca="1">IF($I5="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I5),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I5)&amp;"|"&amp;$R5,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M5" s="6" t="str">
+        <f>IF(ISNA(MATCH($C5&amp;"|"&amp;$V5,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C5&amp;"|"&amp;$V5,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L5" ca="1">IF($K5="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K5),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K5)&amp;"|"&amp;$P5,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M5" ca="1">IF($K5="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K5),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K5)&amp;"|"&amp;$P5,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N5" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>891</v>
-      </c>
-      <c r="P5" t="s">
+      <c r="N5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N5" ca="1">IF($M5="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M5)&amp;"|"&amp;$R5,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O5" ca="1">IF($M5="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M5),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M5)&amp;"|"&amp;$R5,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P5" ca="1">IF($M5="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M5),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M5)&amp;"|"&amp;$R5,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>969</v>
+      </c>
+      <c r="R5" t="s">
         <v>334</v>
       </c>
-      <c r="Q5" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P5,CaseType!$A:$A,0))</f>
+      <c r="S5" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R5,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R5" s="6" t="b">
-        <f>AND(IF($X5="",TRUE,$P5=INDEX(CaseTypeCol!$B:$B,MATCH($X5,CaseTypeCol!$A:$A,0))),IF($AA5="",TRUE,$P5=INDEX(CaseTypeCol!$B:$B,MATCH($AA5,CaseTypeCol!$A:$A,0))),IF($AD5="",TRUE,$P5=INDEX(CaseTypeCol!$B:$B,MATCH($AD5,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T5" t="s">
+      <c r="T5" s="6" t="b">
+        <f>AND(IF($Z5="",TRUE,$R5=INDEX(CaseTypeCol!$B:$B,MATCH($Z5,CaseTypeCol!$A:$A,0))),IF($AG5="",TRUE,$R5=INDEX(CaseTypeCol!$B:$B,MATCH($AG5,CaseTypeCol!$A:$A,0))),IF($AN5="",TRUE,$R5=INDEX(CaseTypeCol!$B:$B,MATCH($AN5,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V5" t="s">
         <v>12</v>
       </c>
-      <c r="U5" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T5,DataCollection!$A:$A,0))</f>
+      <c r="W5" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V5,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W5" s="14">
+      <c r="Y5" s="14">
         <v>36526</v>
       </c>
-      <c r="X5" t="s">
+      <c r="Z5" t="s">
         <v>357</v>
       </c>
-      <c r="Y5" s="6" t="str">
-        <f>IF($X5="","",INDEX(CaseTypeCol!$G:$G,MATCH($X5,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA5" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB5" s="6" t="str">
+        <f>IF($Z5="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z5,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z5" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB5" s="6" t="str">
-        <f>IF($AA5="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA5,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE5" s="6" t="str">
-        <f>IF($AD5="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD5,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC5" ca="1">IF($Z5="",TRUE,IF($I5="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I5)&amp;"|"&amp;$Z5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AD5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD5" ca="1">IF($Z5="",TRUE,IF($I5="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I5)&amp;"|"&amp;$Z5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AE5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE5" ca="1">IF($Z5="",TRUE,IF($M5="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M5)&amp;"|"&amp;$Z5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF5" ca="1">IF($Z5="",TRUE,IF($M5="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M5)&amp;"|"&amp;$Z5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI5" s="6" t="str">
+        <f>IF($AG5="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG5,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ5" ca="1">IF($AG5="",TRUE,IF($I5="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I5)&amp;"|"&amp;$AG5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK5" ca="1">IF($AG5="",TRUE,IF($I5="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I5)&amp;"|"&amp;$AG5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL5" ca="1">IF($AG5="",TRUE,IF($M5="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M5)&amp;"|"&amp;$AG5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM5" ca="1">IF($AG5="",TRUE,IF($M5="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M5)&amp;"|"&amp;$AG5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP5" s="6" t="str">
+        <f>IF($AN5="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN5,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ5" ca="1">IF($AN5="",TRUE,IF($I5="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I5)&amp;"|"&amp;$AN5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR5" ca="1">IF($AN5="",TRUE,IF($I5="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I5)&amp;"|"&amp;$AN5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS5" ca="1">IF($AN5="",TRUE,IF($M5="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M5)&amp;"|"&amp;$AN5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT5" ca="1">IF($AN5="",TRUE,IF($M5="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M5)&amp;"|"&amp;$AN5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>866</v>
+        <v>966</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="D6" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C6,User!$A:$A,0))</f>
-        <v>org_admin2_1</v>
-      </c>
-      <c r="E6" s="6" t="str">
+        <v>org_user1_1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>914</v>
+      </c>
+      <c r="F6" s="19" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C6,User!$A:$A,0))</f>
-        <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3</v>
-      </c>
-      <c r="F6" t="s">
-        <v>918</v>
-      </c>
-      <c r="G6" s="6" t="b">
+        <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
+      </c>
+      <c r="H6" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C6,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H6" s="6" t="str">
-        <f>IF(ISNA(MATCH($E6&amp;"|"&amp;$T6,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E6&amp;"|"&amp;$T6,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I6" s="6">
+        <f>IF(ISNA(MATCH($G6&amp;"|"&amp;$V6,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G6&amp;"|"&amp;$V6,OrganizationAccessCasePolicy!$V:$V,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="J6" ca="1">IF($I6="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I6)&amp;"|"&amp;$R6,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="K6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K6" ca="1">IF($I6="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I6),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I6)&amp;"|"&amp;$R6,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="L6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L6" ca="1">IF($I6="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I6),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I6)&amp;"|"&amp;$R6,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M6" s="6">
+        <f>IF(ISNA(MATCH($C6&amp;"|"&amp;$V6,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C6&amp;"|"&amp;$V6,UserAccessCasePolicy!$W:$W,0))</f>
+        <v>2</v>
+      </c>
+      <c r="N6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N6" ca="1">IF($M6="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M6)&amp;"|"&amp;$R6,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="O6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O6" ca="1">IF($M6="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M6),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M6)&amp;"|"&amp;$R6,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="P6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P6" ca="1">IF($M6="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M6),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M6)&amp;"|"&amp;$R6,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>970</v>
+      </c>
+      <c r="R6" t="s">
+        <v>334</v>
+      </c>
+      <c r="S6" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R6,CaseType!$A:$A,0))</f>
+        <v>case_type1</v>
+      </c>
+      <c r="T6" s="6" t="b">
+        <f>AND(IF($Z6="",TRUE,$R6=INDEX(CaseTypeCol!$B:$B,MATCH($Z6,CaseTypeCol!$A:$A,0))),IF($AG6="",TRUE,$R6=INDEX(CaseTypeCol!$B:$B,MATCH($AG6,CaseTypeCol!$A:$A,0))),IF($AN6="",TRUE,$R6=INDEX(CaseTypeCol!$B:$B,MATCH($AN6,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V6" t="s">
+        <v>12</v>
+      </c>
+      <c r="W6" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V6,DataCollection!$A:$A,0))</f>
+        <v>data_collection1</v>
+      </c>
+      <c r="Y6" s="14">
+        <v>36526</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>357</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB6" s="6" t="str">
+        <f>IF($Z6="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z6,CaseTypeCol!$A:$A,0)))</f>
+        <v>case_type1_dim1_1_text</v>
+      </c>
+      <c r="AC6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC6" ca="1">IF($Z6="",TRUE,IF($I6="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I6)&amp;"|"&amp;$Z6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AD6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD6" ca="1">IF($Z6="",TRUE,IF($I6="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I6)&amp;"|"&amp;$Z6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AE6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE6" ca="1">IF($Z6="",TRUE,IF($M6="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M6)&amp;"|"&amp;$Z6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AF6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF6" ca="1">IF($Z6="",TRUE,IF($M6="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M6)&amp;"|"&amp;$Z6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AI6" s="6" t="str">
+        <f>IF($AG6="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG6,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="I6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I6" ca="1">IF($H6="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H6),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H6)&amp;"|"&amp;$P6,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J6" ca="1">IF($H6="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H6),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H6)&amp;"|"&amp;$P6,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="6" t="str">
-        <f>IF(ISNA(MATCH($C6&amp;"|"&amp;$T6,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C6&amp;"|"&amp;$T6,UserAccessCasePolicy!$W:$W,0))</f>
+      <c r="AJ6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ6" ca="1">IF($AG6="",TRUE,IF($I6="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I6)&amp;"|"&amp;$AG6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK6" ca="1">IF($AG6="",TRUE,IF($I6="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I6)&amp;"|"&amp;$AG6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL6" ca="1">IF($AG6="",TRUE,IF($M6="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M6)&amp;"|"&amp;$AG6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM6" ca="1">IF($AG6="",TRUE,IF($M6="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M6)&amp;"|"&amp;$AG6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP6" s="6" t="str">
+        <f>IF($AN6="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN6,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="L6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L6" ca="1">IF($K6="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K6),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K6)&amp;"|"&amp;$P6,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M6" ca="1">IF($K6="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K6),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K6)&amp;"|"&amp;$P6,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>892</v>
-      </c>
-      <c r="P6" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q6" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P6,CaseType!$A:$A,0))</f>
-        <v>case_type1</v>
-      </c>
-      <c r="R6" s="6" t="b">
-        <f>AND(IF($X6="",TRUE,$P6=INDEX(CaseTypeCol!$B:$B,MATCH($X6,CaseTypeCol!$A:$A,0))),IF($AA6="",TRUE,$P6=INDEX(CaseTypeCol!$B:$B,MATCH($AA6,CaseTypeCol!$A:$A,0))),IF($AD6="",TRUE,$P6=INDEX(CaseTypeCol!$B:$B,MATCH($AD6,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T6" t="s">
-        <v>12</v>
-      </c>
-      <c r="U6" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T6,DataCollection!$A:$A,0))</f>
-        <v>data_collection1</v>
-      </c>
-      <c r="W6" s="14">
-        <v>36526</v>
-      </c>
-      <c r="X6" t="s">
-        <v>357</v>
-      </c>
-      <c r="Y6" s="6" t="str">
-        <f>IF($X6="","",INDEX(CaseTypeCol!$G:$G,MATCH($X6,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim1_1_text</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB6" s="6" t="str">
-        <f>IF($AA6="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA6,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE6" s="6" t="str">
-        <f>IF($AD6="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD6,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AQ6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ6" ca="1">IF($AN6="",TRUE,IF($I6="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I6)&amp;"|"&amp;$AN6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR6" ca="1">IF($AN6="",TRUE,IF($I6="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I6)&amp;"|"&amp;$AN6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS6" ca="1">IF($AN6="",TRUE,IF($M6="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M6)&amp;"|"&amp;$AN6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT6" ca="1">IF($AN6="",TRUE,IF($M6="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M6)&amp;"|"&amp;$AN6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>867</v>
+        <v>967</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>658</v>
       </c>
       <c r="D7" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C7,User!$A:$A,0))</f>
-        <v>org_admin3_1</v>
-      </c>
-      <c r="E7" s="6" t="str">
+        <v>root1_1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>964</v>
+      </c>
+      <c r="F7" s="19" t="b">
+        <f ca="1">IF($E7="CREATE",$H7,IF($E7="CASES_CREATE",OR($H7,AND($J7,$K7,$N7,$O7,$AD7,AF7,$AK7,$AM7,$AR7,$AT7)),"TBD"))</f>
+        <v>1</v>
+      </c>
+      <c r="G7" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C7,User!$A:$A,0))</f>
-        <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037</v>
-      </c>
-      <c r="F7" t="s">
-        <v>918</v>
-      </c>
-      <c r="G7" s="6" t="b">
+        <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
+      </c>
+      <c r="H7" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C7,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="6" t="str">
-        <f>IF(ISNA(MATCH($E7&amp;"|"&amp;$T7,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E7&amp;"|"&amp;$T7,OrganizationAccessCasePolicy!$V:$V,0))</f>
+        <v>1</v>
+      </c>
+      <c r="I7" s="6">
+        <f>IF(ISNA(MATCH($G7&amp;"|"&amp;$V7,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G7&amp;"|"&amp;$V7,OrganizationAccessCasePolicy!$V:$V,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="J7" ca="1">IF($I7="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I7)&amp;"|"&amp;$R7,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="K7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K7" ca="1">IF($I7="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I7),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I7)&amp;"|"&amp;$R7,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="L7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L7" ca="1">IF($I7="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I7),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I7)&amp;"|"&amp;$R7,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M7" s="6" t="str">
+        <f>IF(ISNA(MATCH($C7&amp;"|"&amp;$V7,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C7&amp;"|"&amp;$V7,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="I7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I7" ca="1">IF($H7="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H7),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H7)&amp;"|"&amp;$P7,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J7" ca="1">IF($H7="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H7),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H7)&amp;"|"&amp;$P7,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="6" t="str">
-        <f>IF(ISNA(MATCH($C7&amp;"|"&amp;$T7,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C7&amp;"|"&amp;$T7,UserAccessCasePolicy!$W:$W,0))</f>
+      <c r="N7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N7" ca="1">IF($M7="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M7)&amp;"|"&amp;$R7,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O7" ca="1">IF($M7="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M7),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M7)&amp;"|"&amp;$R7,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P7" ca="1">IF($M7="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M7),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M7)&amp;"|"&amp;$R7,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>971</v>
+      </c>
+      <c r="R7" t="s">
+        <v>334</v>
+      </c>
+      <c r="S7" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R7,CaseType!$A:$A,0))</f>
+        <v>case_type1</v>
+      </c>
+      <c r="T7" s="6" t="b">
+        <f>AND(IF($Z7="",TRUE,$R7=INDEX(CaseTypeCol!$B:$B,MATCH($Z7,CaseTypeCol!$A:$A,0))),IF($AG7="",TRUE,$R7=INDEX(CaseTypeCol!$B:$B,MATCH($AG7,CaseTypeCol!$A:$A,0))),IF($AN7="",TRUE,$R7=INDEX(CaseTypeCol!$B:$B,MATCH($AN7,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V7" t="s">
+        <v>12</v>
+      </c>
+      <c r="W7" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V7,DataCollection!$A:$A,0))</f>
+        <v>data_collection1</v>
+      </c>
+      <c r="Y7" s="14">
+        <v>36526</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>357</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB7" s="6" t="str">
+        <f>IF($Z7="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z7,CaseTypeCol!$A:$A,0)))</f>
+        <v>case_type1_dim1_1_text</v>
+      </c>
+      <c r="AC7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC7" ca="1">IF($Z7="",TRUE,IF($I7="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I7)&amp;"|"&amp;$Z7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AD7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD7" ca="1">IF($Z7="",TRUE,IF($I7="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I7)&amp;"|"&amp;$Z7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AE7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE7" ca="1">IF($Z7="",TRUE,IF($M7="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M7)&amp;"|"&amp;$Z7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF7" ca="1">IF($Z7="",TRUE,IF($M7="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M7)&amp;"|"&amp;$Z7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="6" t="str">
+        <f>IF($AG7="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG7,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="L7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L7" ca="1">IF($K7="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K7),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K7)&amp;"|"&amp;$P7,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M7" ca="1">IF($K7="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K7),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K7)&amp;"|"&amp;$P7,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>893</v>
-      </c>
-      <c r="P7" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q7" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P7,CaseType!$A:$A,0))</f>
-        <v>case_type1</v>
-      </c>
-      <c r="R7" s="6" t="b">
-        <f>AND(IF($X7="",TRUE,$P7=INDEX(CaseTypeCol!$B:$B,MATCH($X7,CaseTypeCol!$A:$A,0))),IF($AA7="",TRUE,$P7=INDEX(CaseTypeCol!$B:$B,MATCH($AA7,CaseTypeCol!$A:$A,0))),IF($AD7="",TRUE,$P7=INDEX(CaseTypeCol!$B:$B,MATCH($AD7,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T7" t="s">
-        <v>12</v>
-      </c>
-      <c r="U7" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T7,DataCollection!$A:$A,0))</f>
-        <v>data_collection1</v>
-      </c>
-      <c r="W7" s="14">
-        <v>36526</v>
-      </c>
-      <c r="X7" t="s">
-        <v>357</v>
-      </c>
-      <c r="Y7" s="6" t="str">
-        <f>IF($X7="","",INDEX(CaseTypeCol!$G:$G,MATCH($X7,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim1_1_text</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB7" s="6" t="str">
-        <f>IF($AA7="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA7,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE7" s="6" t="str">
-        <f>IF($AD7="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD7,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AJ7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ7" ca="1">IF($AG7="",TRUE,IF($I7="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I7)&amp;"|"&amp;$AG7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK7" ca="1">IF($AG7="",TRUE,IF($I7="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I7)&amp;"|"&amp;$AG7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL7" ca="1">IF($AG7="",TRUE,IF($M7="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M7)&amp;"|"&amp;$AG7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM7" ca="1">IF($AG7="",TRUE,IF($M7="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M7)&amp;"|"&amp;$AG7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP7" s="6" t="str">
+        <f>IF($AN7="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN7,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ7" ca="1">IF($AN7="",TRUE,IF($I7="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I7)&amp;"|"&amp;$AN7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR7" ca="1">IF($AN7="",TRUE,IF($I7="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I7)&amp;"|"&amp;$AN7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS7" ca="1">IF($AN7="",TRUE,IF($M7="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M7)&amp;"|"&amp;$AN7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT7" ca="1">IF($AN7="",TRUE,IF($M7="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M7)&amp;"|"&amp;$AN7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>868</v>
+        <v>968</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>660</v>
       </c>
       <c r="D8" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C8,User!$A:$A,0))</f>
-        <v>org_admin4_1</v>
-      </c>
-      <c r="E8" s="6" t="str">
+        <v>app_admin1_1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>964</v>
+      </c>
+      <c r="F8" s="19" t="b">
+        <f t="shared" ref="F8" ca="1" si="2">IF($E8="CREATE",$H8,IF($E8="CASES_CREATE",OR($H8,AND($J8,$K8,$N8,$O8,$AD8,AF8,$AK8,$AM8,$AR8,$AT8)),"TBD"))</f>
+        <v>1</v>
+      </c>
+      <c r="G8" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C8,User!$A:$A,0))</f>
-        <v>0195d18c-1c92-d419-4c71-a570f428499b</v>
-      </c>
-      <c r="F8" t="s">
-        <v>918</v>
-      </c>
-      <c r="G8" s="6" t="b">
+        <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
+      </c>
+      <c r="H8" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C8,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="6" t="str">
-        <f>IF(ISNA(MATCH($E8&amp;"|"&amp;$T8,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E8&amp;"|"&amp;$T8,OrganizationAccessCasePolicy!$V:$V,0))</f>
+        <v>1</v>
+      </c>
+      <c r="I8" s="6">
+        <f>IF(ISNA(MATCH($G8&amp;"|"&amp;$V8,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G8&amp;"|"&amp;$V8,OrganizationAccessCasePolicy!$V:$V,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="J8" ca="1">IF($I8="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I8)&amp;"|"&amp;$R8,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="K8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K8" ca="1">IF($I8="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I8),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I8)&amp;"|"&amp;$R8,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="L8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L8" ca="1">IF($I8="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I8),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I8)&amp;"|"&amp;$R8,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M8" s="6" t="str">
+        <f>IF(ISNA(MATCH($C8&amp;"|"&amp;$V8,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C8&amp;"|"&amp;$V8,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="I8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I8" ca="1">IF($H8="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H8),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H8)&amp;"|"&amp;$P8,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J8" ca="1">IF($H8="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H8),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H8)&amp;"|"&amp;$P8,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="6" t="str">
-        <f>IF(ISNA(MATCH($C8&amp;"|"&amp;$T8,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C8&amp;"|"&amp;$T8,UserAccessCasePolicy!$W:$W,0))</f>
+      <c r="N8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N8" ca="1">IF($M8="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M8)&amp;"|"&amp;$R8,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O8" ca="1">IF($M8="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M8),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M8)&amp;"|"&amp;$R8,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P8" ca="1">IF($M8="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M8),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M8)&amp;"|"&amp;$R8,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>972</v>
+      </c>
+      <c r="R8" t="s">
+        <v>334</v>
+      </c>
+      <c r="S8" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R8,CaseType!$A:$A,0))</f>
+        <v>case_type1</v>
+      </c>
+      <c r="T8" s="6" t="b">
+        <f>AND(IF($Z8="",TRUE,$R8=INDEX(CaseTypeCol!$B:$B,MATCH($Z8,CaseTypeCol!$A:$A,0))),IF($AG8="",TRUE,$R8=INDEX(CaseTypeCol!$B:$B,MATCH($AG8,CaseTypeCol!$A:$A,0))),IF($AN8="",TRUE,$R8=INDEX(CaseTypeCol!$B:$B,MATCH($AN8,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V8" t="s">
+        <v>12</v>
+      </c>
+      <c r="W8" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V8,DataCollection!$A:$A,0))</f>
+        <v>data_collection1</v>
+      </c>
+      <c r="Y8" s="14">
+        <v>36526</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>357</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB8" s="6" t="str">
+        <f>IF($Z8="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z8,CaseTypeCol!$A:$A,0)))</f>
+        <v>case_type1_dim1_1_text</v>
+      </c>
+      <c r="AC8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC8" ca="1">IF($Z8="",TRUE,IF($I8="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I8)&amp;"|"&amp;$Z8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AD8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD8" ca="1">IF($Z8="",TRUE,IF($I8="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I8)&amp;"|"&amp;$Z8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AE8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE8" ca="1">IF($Z8="",TRUE,IF($M8="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M8)&amp;"|"&amp;$Z8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF8" ca="1">IF($Z8="",TRUE,IF($M8="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M8)&amp;"|"&amp;$Z8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI8" s="6" t="str">
+        <f>IF($AG8="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG8,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="L8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L8" ca="1">IF($K8="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K8),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K8)&amp;"|"&amp;$P8,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M8" ca="1">IF($K8="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K8),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K8)&amp;"|"&amp;$P8,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N8" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>894</v>
-      </c>
-      <c r="P8" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q8" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P8,CaseType!$A:$A,0))</f>
-        <v>case_type1</v>
-      </c>
-      <c r="R8" s="6" t="b">
-        <f>AND(IF($X8="",TRUE,$P8=INDEX(CaseTypeCol!$B:$B,MATCH($X8,CaseTypeCol!$A:$A,0))),IF($AA8="",TRUE,$P8=INDEX(CaseTypeCol!$B:$B,MATCH($AA8,CaseTypeCol!$A:$A,0))),IF($AD8="",TRUE,$P8=INDEX(CaseTypeCol!$B:$B,MATCH($AD8,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T8" t="s">
-        <v>12</v>
-      </c>
-      <c r="U8" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T8,DataCollection!$A:$A,0))</f>
-        <v>data_collection1</v>
-      </c>
-      <c r="W8" s="14">
-        <v>36526</v>
-      </c>
-      <c r="X8" t="s">
-        <v>357</v>
-      </c>
-      <c r="Y8" s="6" t="str">
-        <f>IF($X8="","",INDEX(CaseTypeCol!$G:$G,MATCH($X8,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim1_1_text</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB8" s="6" t="str">
-        <f>IF($AA8="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA8,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE8" s="6" t="str">
-        <f>IF($AD8="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD8,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AJ8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ8" ca="1">IF($AG8="",TRUE,IF($I8="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I8)&amp;"|"&amp;$AG8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK8" ca="1">IF($AG8="",TRUE,IF($I8="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I8)&amp;"|"&amp;$AG8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL8" ca="1">IF($AG8="",TRUE,IF($M8="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M8)&amp;"|"&amp;$AG8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM8" ca="1">IF($AG8="",TRUE,IF($M8="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M8)&amp;"|"&amp;$AG8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP8" s="6" t="str">
+        <f>IF($AN8="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN8,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ8" ca="1">IF($AN8="",TRUE,IF($I8="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I8)&amp;"|"&amp;$AN8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR8" ca="1">IF($AN8="",TRUE,IF($I8="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I8)&amp;"|"&amp;$AN8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS8" ca="1">IF($AN8="",TRUE,IF($M8="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M8)&amp;"|"&amp;$AN8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT8" ca="1">IF($AN8="",TRUE,IF($M8="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M8)&amp;"|"&amp;$AN8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D9" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C9,User!$A:$A,0))</f>
-        <v>org_admin5_1</v>
-      </c>
-      <c r="E9" s="6" t="str">
+        <v>org_admin1_1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>964</v>
+      </c>
+      <c r="F9" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C9,User!$A:$A,0))</f>
-        <v>0195d18c-1c93-02a2-6920-7e4dbfb73ce0</v>
-      </c>
-      <c r="F9" t="s">
-        <v>918</v>
-      </c>
-      <c r="G9" s="6" t="b">
+        <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
+      </c>
+      <c r="H9" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C9,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H9" s="6" t="str">
-        <f>IF(ISNA(MATCH($E9&amp;"|"&amp;$T9,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E9&amp;"|"&amp;$T9,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I9" s="6">
+        <f>IF(ISNA(MATCH($G9&amp;"|"&amp;$V9,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G9&amp;"|"&amp;$V9,OrganizationAccessCasePolicy!$V:$V,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="J9" ca="1">IF($I9="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I9)&amp;"|"&amp;$R9,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="K9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K9" ca="1">IF($I9="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I9),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I9)&amp;"|"&amp;$R9,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="L9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L9" ca="1">IF($I9="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I9),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I9)&amp;"|"&amp;$R9,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M9" s="6" t="str">
+        <f>IF(ISNA(MATCH($C9&amp;"|"&amp;$V9,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C9&amp;"|"&amp;$V9,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="I9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I9" ca="1">IF($H9="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H9),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H9)&amp;"|"&amp;$P9,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J9" ca="1">IF($H9="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H9),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H9)&amp;"|"&amp;$P9,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="6" t="str">
-        <f>IF(ISNA(MATCH($C9&amp;"|"&amp;$T9,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C9&amp;"|"&amp;$T9,UserAccessCasePolicy!$W:$W,0))</f>
+      <c r="N9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N9" ca="1">IF($M9="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M9)&amp;"|"&amp;$R9,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O9" ca="1">IF($M9="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M9),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M9)&amp;"|"&amp;$R9,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P9" ca="1">IF($M9="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M9),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M9)&amp;"|"&amp;$R9,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>888</v>
+      </c>
+      <c r="R9" t="s">
+        <v>334</v>
+      </c>
+      <c r="S9" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R9,CaseType!$A:$A,0))</f>
+        <v>case_type1</v>
+      </c>
+      <c r="T9" s="6" t="b">
+        <f>AND(IF($Z9="",TRUE,$R9=INDEX(CaseTypeCol!$B:$B,MATCH($Z9,CaseTypeCol!$A:$A,0))),IF($AG9="",TRUE,$R9=INDEX(CaseTypeCol!$B:$B,MATCH($AG9,CaseTypeCol!$A:$A,0))),IF($AN9="",TRUE,$R9=INDEX(CaseTypeCol!$B:$B,MATCH($AN9,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V9" t="s">
+        <v>12</v>
+      </c>
+      <c r="W9" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V9,DataCollection!$A:$A,0))</f>
+        <v>data_collection1</v>
+      </c>
+      <c r="Y9" s="14">
+        <v>36526</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>357</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB9" s="6" t="str">
+        <f>IF($Z9="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z9,CaseTypeCol!$A:$A,0)))</f>
+        <v>case_type1_dim1_1_text</v>
+      </c>
+      <c r="AC9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC9" ca="1">IF($Z9="",TRUE,IF($I9="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I9)&amp;"|"&amp;$Z9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AD9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD9" ca="1">IF($Z9="",TRUE,IF($I9="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I9)&amp;"|"&amp;$Z9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AE9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE9" ca="1">IF($Z9="",TRUE,IF($M9="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M9)&amp;"|"&amp;$Z9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF9" ca="1">IF($Z9="",TRUE,IF($M9="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M9)&amp;"|"&amp;$Z9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI9" s="6" t="str">
+        <f>IF($AG9="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG9,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="L9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L9" ca="1">IF($K9="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K9),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K9)&amp;"|"&amp;$P9,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M9" ca="1">IF($K9="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K9),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K9)&amp;"|"&amp;$P9,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>895</v>
-      </c>
-      <c r="P9" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q9" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P9,CaseType!$A:$A,0))</f>
-        <v>case_type1</v>
-      </c>
-      <c r="R9" s="6" t="b">
-        <f>AND(IF($X9="",TRUE,$P9=INDEX(CaseTypeCol!$B:$B,MATCH($X9,CaseTypeCol!$A:$A,0))),IF($AA9="",TRUE,$P9=INDEX(CaseTypeCol!$B:$B,MATCH($AA9,CaseTypeCol!$A:$A,0))),IF($AD9="",TRUE,$P9=INDEX(CaseTypeCol!$B:$B,MATCH($AD9,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T9" t="s">
-        <v>12</v>
-      </c>
-      <c r="U9" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T9,DataCollection!$A:$A,0))</f>
-        <v>data_collection1</v>
-      </c>
-      <c r="W9" s="14">
-        <v>36526</v>
-      </c>
-      <c r="X9" t="s">
-        <v>357</v>
-      </c>
-      <c r="Y9" s="6" t="str">
-        <f>IF($X9="","",INDEX(CaseTypeCol!$G:$G,MATCH($X9,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim1_1_text</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB9" s="6" t="str">
-        <f>IF($AA9="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA9,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE9" s="6" t="str">
-        <f>IF($AD9="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD9,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AJ9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ9" ca="1">IF($AG9="",TRUE,IF($I9="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I9)&amp;"|"&amp;$AG9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK9" ca="1">IF($AG9="",TRUE,IF($I9="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I9)&amp;"|"&amp;$AG9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL9" ca="1">IF($AG9="",TRUE,IF($M9="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M9)&amp;"|"&amp;$AG9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM9" ca="1">IF($AG9="",TRUE,IF($M9="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M9)&amp;"|"&amp;$AG9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP9" s="6" t="str">
+        <f>IF($AN9="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN9,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ9" ca="1">IF($AN9="",TRUE,IF($I9="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I9)&amp;"|"&amp;$AN9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR9" ca="1">IF($AN9="",TRUE,IF($I9="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I9)&amp;"|"&amp;$AN9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS9" ca="1">IF($AN9="",TRUE,IF($M9="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M9)&amp;"|"&amp;$AN9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT9" ca="1">IF($AN9="",TRUE,IF($M9="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M9)&amp;"|"&amp;$AN9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="D10" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C10,User!$A:$A,0))</f>
-        <v>org_user1_1</v>
-      </c>
-      <c r="E10" s="6" t="str">
+        <v>org_admin2_1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>964</v>
+      </c>
+      <c r="F10" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C10,User!$A:$A,0))</f>
-        <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
-      </c>
-      <c r="F10" t="s">
-        <v>918</v>
-      </c>
-      <c r="G10" s="6" t="b">
+        <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3</v>
+      </c>
+      <c r="H10" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C10,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H10" s="6">
-        <f>IF(ISNA(MATCH($E10&amp;"|"&amp;$T10,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E10&amp;"|"&amp;$T10,OrganizationAccessCasePolicy!$V:$V,0))</f>
-        <v>2</v>
-      </c>
-      <c r="I10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I10" ca="1">IF($H10="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H10),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H10)&amp;"|"&amp;$P10,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
+      <c r="I10" s="6" t="str">
+        <f>IF(ISNA(MATCH($G10&amp;"|"&amp;$V10,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G10&amp;"|"&amp;$V10,OrganizationAccessCasePolicy!$V:$V,0))</f>
+        <v/>
       </c>
       <c r="J10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J10" ca="1">IF($H10="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H10),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H10)&amp;"|"&amp;$P10,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="K10" s="6">
-        <f>IF(ISNA(MATCH($C10&amp;"|"&amp;$T10,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C10&amp;"|"&amp;$T10,UserAccessCasePolicy!$W:$W,0))</f>
-        <v>2</v>
+        <f t="array" aca="1" ref="J10" ca="1">IF($I10="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I10)&amp;"|"&amp;$R10,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K10" ca="1">IF($I10="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I10),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I10)&amp;"|"&amp;$R10,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
       </c>
       <c r="L10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L10" ca="1">IF($K10="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K10),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K10)&amp;"|"&amp;$P10,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="M10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M10" ca="1">IF($K10="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K10),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K10)&amp;"|"&amp;$P10,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="N10" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O10" t="s">
-        <v>896</v>
-      </c>
-      <c r="P10" t="s">
+        <f t="array" aca="1" ref="L10" ca="1">IF($I10="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I10),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I10)&amp;"|"&amp;$R10,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="6" t="str">
+        <f>IF(ISNA(MATCH($C10&amp;"|"&amp;$V10,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C10&amp;"|"&amp;$V10,UserAccessCasePolicy!$W:$W,0))</f>
+        <v/>
+      </c>
+      <c r="N10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N10" ca="1">IF($M10="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M10)&amp;"|"&amp;$R10,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O10" ca="1">IF($M10="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M10),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M10)&amp;"|"&amp;$R10,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P10" ca="1">IF($M10="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M10),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M10)&amp;"|"&amp;$R10,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>889</v>
+      </c>
+      <c r="R10" t="s">
         <v>334</v>
       </c>
-      <c r="Q10" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P10,CaseType!$A:$A,0))</f>
+      <c r="S10" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R10,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R10" s="6" t="b">
-        <f>AND(IF($X10="",TRUE,$P10=INDEX(CaseTypeCol!$B:$B,MATCH($X10,CaseTypeCol!$A:$A,0))),IF($AA10="",TRUE,$P10=INDEX(CaseTypeCol!$B:$B,MATCH($AA10,CaseTypeCol!$A:$A,0))),IF($AD10="",TRUE,$P10=INDEX(CaseTypeCol!$B:$B,MATCH($AD10,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T10" t="s">
+      <c r="T10" s="6" t="b">
+        <f>AND(IF($Z10="",TRUE,$R10=INDEX(CaseTypeCol!$B:$B,MATCH($Z10,CaseTypeCol!$A:$A,0))),IF($AG10="",TRUE,$R10=INDEX(CaseTypeCol!$B:$B,MATCH($AG10,CaseTypeCol!$A:$A,0))),IF($AN10="",TRUE,$R10=INDEX(CaseTypeCol!$B:$B,MATCH($AN10,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V10" t="s">
         <v>12</v>
       </c>
-      <c r="U10" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T10,DataCollection!$A:$A,0))</f>
+      <c r="W10" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V10,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W10" s="14">
+      <c r="Y10" s="14">
         <v>36526</v>
       </c>
-      <c r="X10" t="s">
+      <c r="Z10" t="s">
         <v>357</v>
       </c>
-      <c r="Y10" s="6" t="str">
-        <f>IF($X10="","",INDEX(CaseTypeCol!$G:$G,MATCH($X10,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA10" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB10" s="6" t="str">
+        <f>IF($Z10="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z10,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z10" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB10" s="6" t="str">
-        <f>IF($AA10="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA10,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE10" s="6" t="str">
-        <f>IF($AD10="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD10,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC10" ca="1">IF($Z10="",TRUE,IF($I10="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I10)&amp;"|"&amp;$Z10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD10" ca="1">IF($Z10="",TRUE,IF($I10="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I10)&amp;"|"&amp;$Z10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE10" ca="1">IF($Z10="",TRUE,IF($M10="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M10)&amp;"|"&amp;$Z10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF10" ca="1">IF($Z10="",TRUE,IF($M10="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M10)&amp;"|"&amp;$Z10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI10" s="6" t="str">
+        <f>IF($AG10="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG10,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ10" ca="1">IF($AG10="",TRUE,IF($I10="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I10)&amp;"|"&amp;$AG10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK10" ca="1">IF($AG10="",TRUE,IF($I10="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I10)&amp;"|"&amp;$AG10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL10" ca="1">IF($AG10="",TRUE,IF($M10="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M10)&amp;"|"&amp;$AG10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM10" ca="1">IF($AG10="",TRUE,IF($M10="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M10)&amp;"|"&amp;$AG10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP10" s="6" t="str">
+        <f>IF($AN10="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN10,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ10" ca="1">IF($AN10="",TRUE,IF($I10="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I10)&amp;"|"&amp;$AN10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR10" ca="1">IF($AN10="",TRUE,IF($I10="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I10)&amp;"|"&amp;$AN10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS10" ca="1">IF($AN10="",TRUE,IF($M10="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M10)&amp;"|"&amp;$AN10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT10" ca="1">IF($AN10="",TRUE,IF($M10="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M10)&amp;"|"&amp;$AN10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="D11" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C11,User!$A:$A,0))</f>
-        <v>org_user1_2</v>
-      </c>
-      <c r="E11" s="6" t="str">
+        <v>org_admin3_1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>964</v>
+      </c>
+      <c r="F11" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C11,User!$A:$A,0))</f>
-        <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
-      </c>
-      <c r="F11" t="s">
-        <v>918</v>
-      </c>
-      <c r="G11" s="6" t="b">
+        <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037</v>
+      </c>
+      <c r="H11" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C11,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H11" s="6">
-        <f>IF(ISNA(MATCH($E11&amp;"|"&amp;$T11,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E11&amp;"|"&amp;$T11,OrganizationAccessCasePolicy!$V:$V,0))</f>
-        <v>2</v>
-      </c>
-      <c r="I11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I11" ca="1">IF($H11="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H11),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H11)&amp;"|"&amp;$P11,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
+      <c r="I11" s="6" t="str">
+        <f>IF(ISNA(MATCH($G11&amp;"|"&amp;$V11,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G11&amp;"|"&amp;$V11,OrganizationAccessCasePolicy!$V:$V,0))</f>
+        <v/>
       </c>
       <c r="J11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J11" ca="1">IF($H11="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H11),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H11)&amp;"|"&amp;$P11,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="K11" s="6" t="str">
-        <f>IF(ISNA(MATCH($C11&amp;"|"&amp;$T11,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C11&amp;"|"&amp;$T11,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="J11" ca="1">IF($I11="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I11)&amp;"|"&amp;$R11,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K11" ca="1">IF($I11="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I11),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I11)&amp;"|"&amp;$R11,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L11" ca="1">IF($I11="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I11),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I11)&amp;"|"&amp;$R11,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="6" t="str">
+        <f>IF(ISNA(MATCH($C11&amp;"|"&amp;$V11,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C11&amp;"|"&amp;$V11,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L11" ca="1">IF($K11="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K11),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K11)&amp;"|"&amp;$P11,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M11" ca="1">IF($K11="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K11),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K11)&amp;"|"&amp;$P11,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>897</v>
-      </c>
-      <c r="P11" t="s">
+      <c r="N11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N11" ca="1">IF($M11="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M11)&amp;"|"&amp;$R11,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O11" ca="1">IF($M11="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M11),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M11)&amp;"|"&amp;$R11,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P11" ca="1">IF($M11="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M11),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M11)&amp;"|"&amp;$R11,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>890</v>
+      </c>
+      <c r="R11" t="s">
         <v>334</v>
       </c>
-      <c r="Q11" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P11,CaseType!$A:$A,0))</f>
+      <c r="S11" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R11,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R11" s="6" t="b">
-        <f>AND(IF($X11="",TRUE,$P11=INDEX(CaseTypeCol!$B:$B,MATCH($X11,CaseTypeCol!$A:$A,0))),IF($AA11="",TRUE,$P11=INDEX(CaseTypeCol!$B:$B,MATCH($AA11,CaseTypeCol!$A:$A,0))),IF($AD11="",TRUE,$P11=INDEX(CaseTypeCol!$B:$B,MATCH($AD11,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T11" t="s">
+      <c r="T11" s="6" t="b">
+        <f>AND(IF($Z11="",TRUE,$R11=INDEX(CaseTypeCol!$B:$B,MATCH($Z11,CaseTypeCol!$A:$A,0))),IF($AG11="",TRUE,$R11=INDEX(CaseTypeCol!$B:$B,MATCH($AG11,CaseTypeCol!$A:$A,0))),IF($AN11="",TRUE,$R11=INDEX(CaseTypeCol!$B:$B,MATCH($AN11,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V11" t="s">
         <v>12</v>
       </c>
-      <c r="U11" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T11,DataCollection!$A:$A,0))</f>
+      <c r="W11" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V11,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W11" s="14">
+      <c r="Y11" s="14">
         <v>36526</v>
       </c>
-      <c r="X11" t="s">
+      <c r="Z11" t="s">
         <v>357</v>
       </c>
-      <c r="Y11" s="6" t="str">
-        <f>IF($X11="","",INDEX(CaseTypeCol!$G:$G,MATCH($X11,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA11" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB11" s="6" t="str">
+        <f>IF($Z11="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z11,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z11" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB11" s="6" t="str">
-        <f>IF($AA11="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA11,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE11" s="6" t="str">
-        <f>IF($AD11="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD11,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC11" ca="1">IF($Z11="",TRUE,IF($I11="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I11)&amp;"|"&amp;$Z11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD11" ca="1">IF($Z11="",TRUE,IF($I11="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I11)&amp;"|"&amp;$Z11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE11" ca="1">IF($Z11="",TRUE,IF($M11="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M11)&amp;"|"&amp;$Z11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF11" ca="1">IF($Z11="",TRUE,IF($M11="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M11)&amp;"|"&amp;$Z11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI11" s="6" t="str">
+        <f>IF($AG11="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG11,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ11" ca="1">IF($AG11="",TRUE,IF($I11="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I11)&amp;"|"&amp;$AG11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK11" ca="1">IF($AG11="",TRUE,IF($I11="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I11)&amp;"|"&amp;$AG11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL11" ca="1">IF($AG11="",TRUE,IF($M11="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M11)&amp;"|"&amp;$AG11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM11" ca="1">IF($AG11="",TRUE,IF($M11="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M11)&amp;"|"&amp;$AG11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP11" s="6" t="str">
+        <f>IF($AN11="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN11,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ11" ca="1">IF($AN11="",TRUE,IF($I11="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I11)&amp;"|"&amp;$AN11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR11" ca="1">IF($AN11="",TRUE,IF($I11="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I11)&amp;"|"&amp;$AN11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS11" ca="1">IF($AN11="",TRUE,IF($M11="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M11)&amp;"|"&amp;$AN11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT11" ca="1">IF($AN11="",TRUE,IF($M11="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M11)&amp;"|"&amp;$AN11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="D12" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C12,User!$A:$A,0))</f>
-        <v>org_user1_3</v>
-      </c>
-      <c r="E12" s="6" t="str">
+        <v>org_admin4_1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>964</v>
+      </c>
+      <c r="F12" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C12,User!$A:$A,0))</f>
-        <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
-      </c>
-      <c r="F12" t="s">
-        <v>918</v>
-      </c>
-      <c r="G12" s="6" t="b">
+        <v>0195d18c-1c92-d419-4c71-a570f428499b</v>
+      </c>
+      <c r="H12" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C12,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H12" s="6">
-        <f>IF(ISNA(MATCH($E12&amp;"|"&amp;$T12,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E12&amp;"|"&amp;$T12,OrganizationAccessCasePolicy!$V:$V,0))</f>
-        <v>2</v>
-      </c>
-      <c r="I12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I12" ca="1">IF($H12="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H12),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H12)&amp;"|"&amp;$P12,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
+      <c r="I12" s="6" t="str">
+        <f>IF(ISNA(MATCH($G12&amp;"|"&amp;$V12,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G12&amp;"|"&amp;$V12,OrganizationAccessCasePolicy!$V:$V,0))</f>
+        <v/>
       </c>
       <c r="J12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J12" ca="1">IF($H12="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H12),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H12)&amp;"|"&amp;$P12,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="K12" s="6" t="str">
-        <f>IF(ISNA(MATCH($C12&amp;"|"&amp;$T12,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C12&amp;"|"&amp;$T12,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="J12" ca="1">IF($I12="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I12)&amp;"|"&amp;$R12,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K12" ca="1">IF($I12="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I12),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I12)&amp;"|"&amp;$R12,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L12" ca="1">IF($I12="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I12),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I12)&amp;"|"&amp;$R12,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="6" t="str">
+        <f>IF(ISNA(MATCH($C12&amp;"|"&amp;$V12,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C12&amp;"|"&amp;$V12,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L12" ca="1">IF($K12="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K12),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K12)&amp;"|"&amp;$P12,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M12" ca="1">IF($K12="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K12),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K12)&amp;"|"&amp;$P12,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N12" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>898</v>
-      </c>
-      <c r="P12" t="s">
+      <c r="N12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N12" ca="1">IF($M12="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M12)&amp;"|"&amp;$R12,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O12" ca="1">IF($M12="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M12),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M12)&amp;"|"&amp;$R12,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P12" ca="1">IF($M12="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M12),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M12)&amp;"|"&amp;$R12,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>891</v>
+      </c>
+      <c r="R12" t="s">
         <v>334</v>
       </c>
-      <c r="Q12" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P12,CaseType!$A:$A,0))</f>
+      <c r="S12" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R12,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R12" s="6" t="b">
-        <f>AND(IF($X12="",TRUE,$P12=INDEX(CaseTypeCol!$B:$B,MATCH($X12,CaseTypeCol!$A:$A,0))),IF($AA12="",TRUE,$P12=INDEX(CaseTypeCol!$B:$B,MATCH($AA12,CaseTypeCol!$A:$A,0))),IF($AD12="",TRUE,$P12=INDEX(CaseTypeCol!$B:$B,MATCH($AD12,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T12" t="s">
+      <c r="T12" s="6" t="b">
+        <f>AND(IF($Z12="",TRUE,$R12=INDEX(CaseTypeCol!$B:$B,MATCH($Z12,CaseTypeCol!$A:$A,0))),IF($AG12="",TRUE,$R12=INDEX(CaseTypeCol!$B:$B,MATCH($AG12,CaseTypeCol!$A:$A,0))),IF($AN12="",TRUE,$R12=INDEX(CaseTypeCol!$B:$B,MATCH($AN12,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V12" t="s">
         <v>12</v>
       </c>
-      <c r="U12" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T12,DataCollection!$A:$A,0))</f>
+      <c r="W12" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V12,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W12" s="14">
+      <c r="Y12" s="14">
         <v>36526</v>
       </c>
-      <c r="X12" t="s">
+      <c r="Z12" t="s">
         <v>357</v>
       </c>
-      <c r="Y12" s="6" t="str">
-        <f>IF($X12="","",INDEX(CaseTypeCol!$G:$G,MATCH($X12,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA12" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB12" s="6" t="str">
+        <f>IF($Z12="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z12,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z12" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB12" s="6" t="str">
-        <f>IF($AA12="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA12,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE12" s="6" t="str">
-        <f>IF($AD12="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD12,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC12" ca="1">IF($Z12="",TRUE,IF($I12="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I12)&amp;"|"&amp;$Z12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD12" ca="1">IF($Z12="",TRUE,IF($I12="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I12)&amp;"|"&amp;$Z12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE12" ca="1">IF($Z12="",TRUE,IF($M12="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M12)&amp;"|"&amp;$Z12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF12" ca="1">IF($Z12="",TRUE,IF($M12="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M12)&amp;"|"&amp;$Z12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI12" s="6" t="str">
+        <f>IF($AG12="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG12,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ12" ca="1">IF($AG12="",TRUE,IF($I12="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I12)&amp;"|"&amp;$AG12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK12" ca="1">IF($AG12="",TRUE,IF($I12="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I12)&amp;"|"&amp;$AG12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL12" ca="1">IF($AG12="",TRUE,IF($M12="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M12)&amp;"|"&amp;$AG12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM12" ca="1">IF($AG12="",TRUE,IF($M12="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M12)&amp;"|"&amp;$AG12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP12" s="6" t="str">
+        <f>IF($AN12="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN12,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ12" ca="1">IF($AN12="",TRUE,IF($I12="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I12)&amp;"|"&amp;$AN12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR12" ca="1">IF($AN12="",TRUE,IF($I12="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I12)&amp;"|"&amp;$AN12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS12" ca="1">IF($AN12="",TRUE,IF($M12="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M12)&amp;"|"&amp;$AN12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT12" ca="1">IF($AN12="",TRUE,IF($M12="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M12)&amp;"|"&amp;$AN12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="D13" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C13,User!$A:$A,0))</f>
-        <v>org_user1_4</v>
-      </c>
-      <c r="E13" s="6" t="str">
+        <v>org_admin5_1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>964</v>
+      </c>
+      <c r="F13" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C13,User!$A:$A,0))</f>
-        <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
-      </c>
-      <c r="F13" t="s">
-        <v>918</v>
-      </c>
-      <c r="G13" s="6" t="b">
+        <v>0195d18c-1c93-02a2-6920-7e4dbfb73ce0</v>
+      </c>
+      <c r="H13" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C13,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H13" s="6">
-        <f>IF(ISNA(MATCH($E13&amp;"|"&amp;$T13,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E13&amp;"|"&amp;$T13,OrganizationAccessCasePolicy!$V:$V,0))</f>
-        <v>2</v>
-      </c>
-      <c r="I13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I13" ca="1">IF($H13="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H13),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H13)&amp;"|"&amp;$P13,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
+      <c r="I13" s="6" t="str">
+        <f>IF(ISNA(MATCH($G13&amp;"|"&amp;$V13,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G13&amp;"|"&amp;$V13,OrganizationAccessCasePolicy!$V:$V,0))</f>
+        <v/>
       </c>
       <c r="J13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J13" ca="1">IF($H13="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H13),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H13)&amp;"|"&amp;$P13,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="K13" s="6" t="str">
-        <f>IF(ISNA(MATCH($C13&amp;"|"&amp;$T13,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C13&amp;"|"&amp;$T13,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="J13" ca="1">IF($I13="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I13)&amp;"|"&amp;$R13,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K13" ca="1">IF($I13="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I13),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I13)&amp;"|"&amp;$R13,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L13" ca="1">IF($I13="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I13),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I13)&amp;"|"&amp;$R13,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="6" t="str">
+        <f>IF(ISNA(MATCH($C13&amp;"|"&amp;$V13,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C13&amp;"|"&amp;$V13,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L13" ca="1">IF($K13="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K13),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K13)&amp;"|"&amp;$P13,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M13" ca="1">IF($K13="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K13),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K13)&amp;"|"&amp;$P13,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>899</v>
-      </c>
-      <c r="P13" t="s">
+      <c r="N13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N13" ca="1">IF($M13="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M13)&amp;"|"&amp;$R13,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O13" ca="1">IF($M13="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M13),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M13)&amp;"|"&amp;$R13,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P13" ca="1">IF($M13="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M13),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M13)&amp;"|"&amp;$R13,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>892</v>
+      </c>
+      <c r="R13" t="s">
         <v>334</v>
       </c>
-      <c r="Q13" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P13,CaseType!$A:$A,0))</f>
+      <c r="S13" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R13,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R13" s="6" t="b">
-        <f>AND(IF($X13="",TRUE,$P13=INDEX(CaseTypeCol!$B:$B,MATCH($X13,CaseTypeCol!$A:$A,0))),IF($AA13="",TRUE,$P13=INDEX(CaseTypeCol!$B:$B,MATCH($AA13,CaseTypeCol!$A:$A,0))),IF($AD13="",TRUE,$P13=INDEX(CaseTypeCol!$B:$B,MATCH($AD13,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T13" t="s">
+      <c r="T13" s="6" t="b">
+        <f>AND(IF($Z13="",TRUE,$R13=INDEX(CaseTypeCol!$B:$B,MATCH($Z13,CaseTypeCol!$A:$A,0))),IF($AG13="",TRUE,$R13=INDEX(CaseTypeCol!$B:$B,MATCH($AG13,CaseTypeCol!$A:$A,0))),IF($AN13="",TRUE,$R13=INDEX(CaseTypeCol!$B:$B,MATCH($AN13,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V13" t="s">
         <v>12</v>
       </c>
-      <c r="U13" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T13,DataCollection!$A:$A,0))</f>
+      <c r="W13" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V13,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W13" s="14">
+      <c r="Y13" s="14">
         <v>36526</v>
       </c>
-      <c r="X13" t="s">
+      <c r="Z13" t="s">
         <v>357</v>
       </c>
-      <c r="Y13" s="6" t="str">
-        <f>IF($X13="","",INDEX(CaseTypeCol!$G:$G,MATCH($X13,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA13" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB13" s="6" t="str">
+        <f>IF($Z13="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z13,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z13" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB13" s="6" t="str">
-        <f>IF($AA13="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA13,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE13" s="6" t="str">
-        <f>IF($AD13="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD13,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC13" ca="1">IF($Z13="",TRUE,IF($I13="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I13)&amp;"|"&amp;$Z13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD13" ca="1">IF($Z13="",TRUE,IF($I13="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I13)&amp;"|"&amp;$Z13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE13" ca="1">IF($Z13="",TRUE,IF($M13="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M13)&amp;"|"&amp;$Z13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF13" ca="1">IF($Z13="",TRUE,IF($M13="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M13)&amp;"|"&amp;$Z13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI13" s="6" t="str">
+        <f>IF($AG13="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG13,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ13" ca="1">IF($AG13="",TRUE,IF($I13="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I13)&amp;"|"&amp;$AG13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK13" ca="1">IF($AG13="",TRUE,IF($I13="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I13)&amp;"|"&amp;$AG13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL13" ca="1">IF($AG13="",TRUE,IF($M13="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M13)&amp;"|"&amp;$AG13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM13" ca="1">IF($AG13="",TRUE,IF($M13="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M13)&amp;"|"&amp;$AG13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP13" s="6" t="str">
+        <f>IF($AN13="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN13,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ13" ca="1">IF($AN13="",TRUE,IF($I13="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I13)&amp;"|"&amp;$AN13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR13" ca="1">IF($AN13="",TRUE,IF($I13="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I13)&amp;"|"&amp;$AN13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS13" ca="1">IF($AN13="",TRUE,IF($M13="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M13)&amp;"|"&amp;$AN13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT13" ca="1">IF($AN13="",TRUE,IF($M13="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M13)&amp;"|"&amp;$AN13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D14" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C14,User!$A:$A,0))</f>
-        <v>org_user2_1</v>
-      </c>
-      <c r="E14" s="6" t="str">
+        <v>org_user1_1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>964</v>
+      </c>
+      <c r="F14" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G14" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C14,User!$A:$A,0))</f>
-        <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3</v>
-      </c>
-      <c r="F14" t="s">
-        <v>918</v>
-      </c>
-      <c r="G14" s="6" t="b">
+        <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
+      </c>
+      <c r="H14" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C14,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H14" s="6" t="str">
-        <f>IF(ISNA(MATCH($E14&amp;"|"&amp;$T14,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E14&amp;"|"&amp;$T14,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I14" s="6">
+        <f>IF(ISNA(MATCH($G14&amp;"|"&amp;$V14,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G14&amp;"|"&amp;$V14,OrganizationAccessCasePolicy!$V:$V,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="J14" ca="1">IF($I14="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I14)&amp;"|"&amp;$R14,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="K14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K14" ca="1">IF($I14="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I14),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I14)&amp;"|"&amp;$R14,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="L14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L14" ca="1">IF($I14="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I14),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I14)&amp;"|"&amp;$R14,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M14" s="6">
+        <f>IF(ISNA(MATCH($C14&amp;"|"&amp;$V14,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C14&amp;"|"&amp;$V14,UserAccessCasePolicy!$W:$W,0))</f>
+        <v>2</v>
+      </c>
+      <c r="N14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N14" ca="1">IF($M14="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M14)&amp;"|"&amp;$R14,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="O14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O14" ca="1">IF($M14="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M14),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M14)&amp;"|"&amp;$R14,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="P14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P14" ca="1">IF($M14="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M14),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M14)&amp;"|"&amp;$R14,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>893</v>
+      </c>
+      <c r="R14" t="s">
+        <v>334</v>
+      </c>
+      <c r="S14" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R14,CaseType!$A:$A,0))</f>
+        <v>case_type1</v>
+      </c>
+      <c r="T14" s="6" t="b">
+        <f>AND(IF($Z14="",TRUE,$R14=INDEX(CaseTypeCol!$B:$B,MATCH($Z14,CaseTypeCol!$A:$A,0))),IF($AG14="",TRUE,$R14=INDEX(CaseTypeCol!$B:$B,MATCH($AG14,CaseTypeCol!$A:$A,0))),IF($AN14="",TRUE,$R14=INDEX(CaseTypeCol!$B:$B,MATCH($AN14,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V14" t="s">
+        <v>12</v>
+      </c>
+      <c r="W14" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V14,DataCollection!$A:$A,0))</f>
+        <v>data_collection1</v>
+      </c>
+      <c r="Y14" s="14">
+        <v>36526</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>357</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB14" s="6" t="str">
+        <f>IF($Z14="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z14,CaseTypeCol!$A:$A,0)))</f>
+        <v>case_type1_dim1_1_text</v>
+      </c>
+      <c r="AC14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC14" ca="1">IF($Z14="",TRUE,IF($I14="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I14)&amp;"|"&amp;$Z14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AD14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD14" ca="1">IF($Z14="",TRUE,IF($I14="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I14)&amp;"|"&amp;$Z14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AE14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE14" ca="1">IF($Z14="",TRUE,IF($M14="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M14)&amp;"|"&amp;$Z14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AF14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF14" ca="1">IF($Z14="",TRUE,IF($M14="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M14)&amp;"|"&amp;$Z14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AI14" s="6" t="str">
+        <f>IF($AG14="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG14,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="I14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I14" ca="1">IF($H14="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H14),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H14)&amp;"|"&amp;$P14,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J14" ca="1">IF($H14="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H14),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H14)&amp;"|"&amp;$P14,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="6" t="str">
-        <f>IF(ISNA(MATCH($C14&amp;"|"&amp;$T14,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C14&amp;"|"&amp;$T14,UserAccessCasePolicy!$W:$W,0))</f>
+      <c r="AJ14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ14" ca="1">IF($AG14="",TRUE,IF($I14="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I14)&amp;"|"&amp;$AG14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK14" ca="1">IF($AG14="",TRUE,IF($I14="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I14)&amp;"|"&amp;$AG14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL14" ca="1">IF($AG14="",TRUE,IF($M14="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M14)&amp;"|"&amp;$AG14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM14" ca="1">IF($AG14="",TRUE,IF($M14="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M14)&amp;"|"&amp;$AG14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP14" s="6" t="str">
+        <f>IF($AN14="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN14,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="L14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L14" ca="1">IF($K14="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K14),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K14)&amp;"|"&amp;$P14,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M14" ca="1">IF($K14="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K14),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K14)&amp;"|"&amp;$P14,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N14" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>900</v>
-      </c>
-      <c r="P14" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q14" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P14,CaseType!$A:$A,0))</f>
-        <v>case_type1</v>
-      </c>
-      <c r="R14" s="6" t="b">
-        <f>AND(IF($X14="",TRUE,$P14=INDEX(CaseTypeCol!$B:$B,MATCH($X14,CaseTypeCol!$A:$A,0))),IF($AA14="",TRUE,$P14=INDEX(CaseTypeCol!$B:$B,MATCH($AA14,CaseTypeCol!$A:$A,0))),IF($AD14="",TRUE,$P14=INDEX(CaseTypeCol!$B:$B,MATCH($AD14,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T14" t="s">
-        <v>12</v>
-      </c>
-      <c r="U14" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T14,DataCollection!$A:$A,0))</f>
-        <v>data_collection1</v>
-      </c>
-      <c r="W14" s="14">
-        <v>36526</v>
-      </c>
-      <c r="X14" t="s">
-        <v>357</v>
-      </c>
-      <c r="Y14" s="6" t="str">
-        <f>IF($X14="","",INDEX(CaseTypeCol!$G:$G,MATCH($X14,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim1_1_text</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB14" s="6" t="str">
-        <f>IF($AA14="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA14,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE14" s="6" t="str">
-        <f>IF($AD14="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD14,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AQ14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ14" ca="1">IF($AN14="",TRUE,IF($I14="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I14)&amp;"|"&amp;$AN14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR14" ca="1">IF($AN14="",TRUE,IF($I14="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I14)&amp;"|"&amp;$AN14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS14" ca="1">IF($AN14="",TRUE,IF($M14="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M14)&amp;"|"&amp;$AN14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT14" ca="1">IF($AN14="",TRUE,IF($M14="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M14)&amp;"|"&amp;$AN14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D15" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C15,User!$A:$A,0))</f>
-        <v>org_user2_2</v>
-      </c>
-      <c r="E15" s="6" t="str">
+        <v>org_user1_2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>964</v>
+      </c>
+      <c r="F15" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C15,User!$A:$A,0))</f>
-        <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3</v>
-      </c>
-      <c r="F15" t="s">
-        <v>918</v>
-      </c>
-      <c r="G15" s="6" t="b">
+        <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
+      </c>
+      <c r="H15" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C15,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H15" s="6" t="str">
-        <f>IF(ISNA(MATCH($E15&amp;"|"&amp;$T15,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E15&amp;"|"&amp;$T15,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I15" s="6">
+        <f>IF(ISNA(MATCH($G15&amp;"|"&amp;$V15,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G15&amp;"|"&amp;$V15,OrganizationAccessCasePolicy!$V:$V,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="J15" ca="1">IF($I15="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I15)&amp;"|"&amp;$R15,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="K15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K15" ca="1">IF($I15="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I15),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I15)&amp;"|"&amp;$R15,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="L15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L15" ca="1">IF($I15="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I15),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I15)&amp;"|"&amp;$R15,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M15" s="6" t="str">
+        <f>IF(ISNA(MATCH($C15&amp;"|"&amp;$V15,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C15&amp;"|"&amp;$V15,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="I15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I15" ca="1">IF($H15="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H15),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H15)&amp;"|"&amp;$P15,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J15" ca="1">IF($H15="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H15),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H15)&amp;"|"&amp;$P15,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="6" t="str">
-        <f>IF(ISNA(MATCH($C15&amp;"|"&amp;$T15,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C15&amp;"|"&amp;$T15,UserAccessCasePolicy!$W:$W,0))</f>
+      <c r="N15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N15" ca="1">IF($M15="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M15)&amp;"|"&amp;$R15,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O15" ca="1">IF($M15="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M15),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M15)&amp;"|"&amp;$R15,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P15" ca="1">IF($M15="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M15),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M15)&amp;"|"&amp;$R15,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>894</v>
+      </c>
+      <c r="R15" t="s">
+        <v>334</v>
+      </c>
+      <c r="S15" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R15,CaseType!$A:$A,0))</f>
+        <v>case_type1</v>
+      </c>
+      <c r="T15" s="6" t="b">
+        <f>AND(IF($Z15="",TRUE,$R15=INDEX(CaseTypeCol!$B:$B,MATCH($Z15,CaseTypeCol!$A:$A,0))),IF($AG15="",TRUE,$R15=INDEX(CaseTypeCol!$B:$B,MATCH($AG15,CaseTypeCol!$A:$A,0))),IF($AN15="",TRUE,$R15=INDEX(CaseTypeCol!$B:$B,MATCH($AN15,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V15" t="s">
+        <v>12</v>
+      </c>
+      <c r="W15" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V15,DataCollection!$A:$A,0))</f>
+        <v>data_collection1</v>
+      </c>
+      <c r="Y15" s="14">
+        <v>36526</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>357</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB15" s="6" t="str">
+        <f>IF($Z15="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z15,CaseTypeCol!$A:$A,0)))</f>
+        <v>case_type1_dim1_1_text</v>
+      </c>
+      <c r="AC15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC15" ca="1">IF($Z15="",TRUE,IF($I15="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I15)&amp;"|"&amp;$Z15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AD15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD15" ca="1">IF($Z15="",TRUE,IF($I15="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I15)&amp;"|"&amp;$Z15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AE15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE15" ca="1">IF($Z15="",TRUE,IF($M15="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M15)&amp;"|"&amp;$Z15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF15" ca="1">IF($Z15="",TRUE,IF($M15="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M15)&amp;"|"&amp;$Z15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI15" s="6" t="str">
+        <f>IF($AG15="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG15,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="L15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L15" ca="1">IF($K15="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K15),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K15)&amp;"|"&amp;$P15,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M15" ca="1">IF($K15="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K15),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K15)&amp;"|"&amp;$P15,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N15" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>901</v>
-      </c>
-      <c r="P15" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q15" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P15,CaseType!$A:$A,0))</f>
-        <v>case_type1</v>
-      </c>
-      <c r="R15" s="6" t="b">
-        <f>AND(IF($X15="",TRUE,$P15=INDEX(CaseTypeCol!$B:$B,MATCH($X15,CaseTypeCol!$A:$A,0))),IF($AA15="",TRUE,$P15=INDEX(CaseTypeCol!$B:$B,MATCH($AA15,CaseTypeCol!$A:$A,0))),IF($AD15="",TRUE,$P15=INDEX(CaseTypeCol!$B:$B,MATCH($AD15,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T15" t="s">
-        <v>12</v>
-      </c>
-      <c r="U15" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T15,DataCollection!$A:$A,0))</f>
-        <v>data_collection1</v>
-      </c>
-      <c r="W15" s="14">
-        <v>36526</v>
-      </c>
-      <c r="X15" t="s">
-        <v>357</v>
-      </c>
-      <c r="Y15" s="6" t="str">
-        <f>IF($X15="","",INDEX(CaseTypeCol!$G:$G,MATCH($X15,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim1_1_text</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB15" s="6" t="str">
-        <f>IF($AA15="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA15,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE15" s="6" t="str">
-        <f>IF($AD15="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD15,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AJ15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ15" ca="1">IF($AG15="",TRUE,IF($I15="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I15)&amp;"|"&amp;$AG15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK15" ca="1">IF($AG15="",TRUE,IF($I15="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I15)&amp;"|"&amp;$AG15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL15" ca="1">IF($AG15="",TRUE,IF($M15="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M15)&amp;"|"&amp;$AG15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM15" ca="1">IF($AG15="",TRUE,IF($M15="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M15)&amp;"|"&amp;$AG15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP15" s="6" t="str">
+        <f>IF($AN15="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN15,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ15" ca="1">IF($AN15="",TRUE,IF($I15="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I15)&amp;"|"&amp;$AN15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR15" ca="1">IF($AN15="",TRUE,IF($I15="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I15)&amp;"|"&amp;$AN15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS15" ca="1">IF($AN15="",TRUE,IF($M15="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M15)&amp;"|"&amp;$AN15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT15" ca="1">IF($AN15="",TRUE,IF($M15="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M15)&amp;"|"&amp;$AN15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D16" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C16,User!$A:$A,0))</f>
-        <v>org_user2_3</v>
-      </c>
-      <c r="E16" s="6" t="str">
+        <v>org_user1_3</v>
+      </c>
+      <c r="E16" t="s">
+        <v>964</v>
+      </c>
+      <c r="F16" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C16,User!$A:$A,0))</f>
-        <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3</v>
-      </c>
-      <c r="F16" t="s">
-        <v>918</v>
-      </c>
-      <c r="G16" s="6" t="b">
+        <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
+      </c>
+      <c r="H16" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C16,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H16" s="6" t="str">
-        <f>IF(ISNA(MATCH($E16&amp;"|"&amp;$T16,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E16&amp;"|"&amp;$T16,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I16" s="6">
+        <f>IF(ISNA(MATCH($G16&amp;"|"&amp;$V16,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G16&amp;"|"&amp;$V16,OrganizationAccessCasePolicy!$V:$V,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="J16" ca="1">IF($I16="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I16)&amp;"|"&amp;$R16,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="K16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K16" ca="1">IF($I16="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I16),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I16)&amp;"|"&amp;$R16,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="L16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L16" ca="1">IF($I16="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I16),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I16)&amp;"|"&amp;$R16,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M16" s="6" t="str">
+        <f>IF(ISNA(MATCH($C16&amp;"|"&amp;$V16,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C16&amp;"|"&amp;$V16,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="I16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I16" ca="1">IF($H16="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H16),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H16)&amp;"|"&amp;$P16,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J16" ca="1">IF($H16="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H16),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H16)&amp;"|"&amp;$P16,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="6" t="str">
-        <f>IF(ISNA(MATCH($C16&amp;"|"&amp;$T16,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C16&amp;"|"&amp;$T16,UserAccessCasePolicy!$W:$W,0))</f>
+      <c r="N16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N16" ca="1">IF($M16="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M16)&amp;"|"&amp;$R16,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O16" ca="1">IF($M16="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M16),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M16)&amp;"|"&amp;$R16,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P16" ca="1">IF($M16="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M16),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M16)&amp;"|"&amp;$R16,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>895</v>
+      </c>
+      <c r="R16" t="s">
+        <v>334</v>
+      </c>
+      <c r="S16" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R16,CaseType!$A:$A,0))</f>
+        <v>case_type1</v>
+      </c>
+      <c r="T16" s="6" t="b">
+        <f>AND(IF($Z16="",TRUE,$R16=INDEX(CaseTypeCol!$B:$B,MATCH($Z16,CaseTypeCol!$A:$A,0))),IF($AG16="",TRUE,$R16=INDEX(CaseTypeCol!$B:$B,MATCH($AG16,CaseTypeCol!$A:$A,0))),IF($AN16="",TRUE,$R16=INDEX(CaseTypeCol!$B:$B,MATCH($AN16,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V16" t="s">
+        <v>12</v>
+      </c>
+      <c r="W16" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V16,DataCollection!$A:$A,0))</f>
+        <v>data_collection1</v>
+      </c>
+      <c r="Y16" s="14">
+        <v>36526</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>357</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB16" s="6" t="str">
+        <f>IF($Z16="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z16,CaseTypeCol!$A:$A,0)))</f>
+        <v>case_type1_dim1_1_text</v>
+      </c>
+      <c r="AC16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC16" ca="1">IF($Z16="",TRUE,IF($I16="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I16)&amp;"|"&amp;$Z16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AD16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD16" ca="1">IF($Z16="",TRUE,IF($I16="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I16)&amp;"|"&amp;$Z16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AE16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE16" ca="1">IF($Z16="",TRUE,IF($M16="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M16)&amp;"|"&amp;$Z16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF16" ca="1">IF($Z16="",TRUE,IF($M16="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M16)&amp;"|"&amp;$Z16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI16" s="6" t="str">
+        <f>IF($AG16="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG16,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="L16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L16" ca="1">IF($K16="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K16),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K16)&amp;"|"&amp;$P16,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M16" ca="1">IF($K16="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K16),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K16)&amp;"|"&amp;$P16,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>902</v>
-      </c>
-      <c r="P16" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q16" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P16,CaseType!$A:$A,0))</f>
-        <v>case_type1</v>
-      </c>
-      <c r="R16" s="6" t="b">
-        <f>AND(IF($X16="",TRUE,$P16=INDEX(CaseTypeCol!$B:$B,MATCH($X16,CaseTypeCol!$A:$A,0))),IF($AA16="",TRUE,$P16=INDEX(CaseTypeCol!$B:$B,MATCH($AA16,CaseTypeCol!$A:$A,0))),IF($AD16="",TRUE,$P16=INDEX(CaseTypeCol!$B:$B,MATCH($AD16,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T16" t="s">
-        <v>12</v>
-      </c>
-      <c r="U16" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T16,DataCollection!$A:$A,0))</f>
-        <v>data_collection1</v>
-      </c>
-      <c r="W16" s="14">
-        <v>36526</v>
-      </c>
-      <c r="X16" t="s">
-        <v>357</v>
-      </c>
-      <c r="Y16" s="6" t="str">
-        <f>IF($X16="","",INDEX(CaseTypeCol!$G:$G,MATCH($X16,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim1_1_text</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB16" s="6" t="str">
-        <f>IF($AA16="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA16,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE16" s="6" t="str">
-        <f>IF($AD16="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD16,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AJ16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ16" ca="1">IF($AG16="",TRUE,IF($I16="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I16)&amp;"|"&amp;$AG16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK16" ca="1">IF($AG16="",TRUE,IF($I16="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I16)&amp;"|"&amp;$AG16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL16" ca="1">IF($AG16="",TRUE,IF($M16="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M16)&amp;"|"&amp;$AG16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM16" ca="1">IF($AG16="",TRUE,IF($M16="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M16)&amp;"|"&amp;$AG16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP16" s="6" t="str">
+        <f>IF($AN16="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN16,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ16" ca="1">IF($AN16="",TRUE,IF($I16="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I16)&amp;"|"&amp;$AN16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR16" ca="1">IF($AN16="",TRUE,IF($I16="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I16)&amp;"|"&amp;$AN16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS16" ca="1">IF($AN16="",TRUE,IF($M16="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M16)&amp;"|"&amp;$AN16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT16" ca="1">IF($AN16="",TRUE,IF($M16="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M16)&amp;"|"&amp;$AN16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>877</v>
+        <v>870</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D17" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C17,User!$A:$A,0))</f>
-        <v>org_user2_4</v>
-      </c>
-      <c r="E17" s="6" t="str">
+        <v>org_user1_4</v>
+      </c>
+      <c r="E17" t="s">
+        <v>964</v>
+      </c>
+      <c r="F17" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C17,User!$A:$A,0))</f>
-        <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3</v>
-      </c>
-      <c r="F17" t="s">
-        <v>918</v>
-      </c>
-      <c r="G17" s="6" t="b">
+        <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
+      </c>
+      <c r="H17" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C17,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H17" s="6" t="str">
-        <f>IF(ISNA(MATCH($E17&amp;"|"&amp;$T17,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E17&amp;"|"&amp;$T17,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I17" s="6">
+        <f>IF(ISNA(MATCH($G17&amp;"|"&amp;$V17,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G17&amp;"|"&amp;$V17,OrganizationAccessCasePolicy!$V:$V,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="J17" ca="1">IF($I17="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I17)&amp;"|"&amp;$R17,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="K17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K17" ca="1">IF($I17="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I17),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I17)&amp;"|"&amp;$R17,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="L17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L17" ca="1">IF($I17="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I17),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I17)&amp;"|"&amp;$R17,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M17" s="6" t="str">
+        <f>IF(ISNA(MATCH($C17&amp;"|"&amp;$V17,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C17&amp;"|"&amp;$V17,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="I17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I17" ca="1">IF($H17="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H17),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H17)&amp;"|"&amp;$P17,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J17" ca="1">IF($H17="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H17),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H17)&amp;"|"&amp;$P17,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="6" t="str">
-        <f>IF(ISNA(MATCH($C17&amp;"|"&amp;$T17,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C17&amp;"|"&amp;$T17,UserAccessCasePolicy!$W:$W,0))</f>
+      <c r="N17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N17" ca="1">IF($M17="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M17)&amp;"|"&amp;$R17,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O17" ca="1">IF($M17="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M17),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M17)&amp;"|"&amp;$R17,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P17" ca="1">IF($M17="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M17),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M17)&amp;"|"&amp;$R17,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>896</v>
+      </c>
+      <c r="R17" t="s">
+        <v>334</v>
+      </c>
+      <c r="S17" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R17,CaseType!$A:$A,0))</f>
+        <v>case_type1</v>
+      </c>
+      <c r="T17" s="6" t="b">
+        <f>AND(IF($Z17="",TRUE,$R17=INDEX(CaseTypeCol!$B:$B,MATCH($Z17,CaseTypeCol!$A:$A,0))),IF($AG17="",TRUE,$R17=INDEX(CaseTypeCol!$B:$B,MATCH($AG17,CaseTypeCol!$A:$A,0))),IF($AN17="",TRUE,$R17=INDEX(CaseTypeCol!$B:$B,MATCH($AN17,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V17" t="s">
+        <v>12</v>
+      </c>
+      <c r="W17" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V17,DataCollection!$A:$A,0))</f>
+        <v>data_collection1</v>
+      </c>
+      <c r="Y17" s="14">
+        <v>36526</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>357</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB17" s="6" t="str">
+        <f>IF($Z17="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z17,CaseTypeCol!$A:$A,0)))</f>
+        <v>case_type1_dim1_1_text</v>
+      </c>
+      <c r="AC17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC17" ca="1">IF($Z17="",TRUE,IF($I17="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I17)&amp;"|"&amp;$Z17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AD17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD17" ca="1">IF($Z17="",TRUE,IF($I17="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I17)&amp;"|"&amp;$Z17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AE17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE17" ca="1">IF($Z17="",TRUE,IF($M17="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M17)&amp;"|"&amp;$Z17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF17" ca="1">IF($Z17="",TRUE,IF($M17="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M17)&amp;"|"&amp;$Z17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI17" s="6" t="str">
+        <f>IF($AG17="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG17,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="L17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L17" ca="1">IF($K17="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K17),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K17)&amp;"|"&amp;$P17,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M17" ca="1">IF($K17="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K17),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K17)&amp;"|"&amp;$P17,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N17" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>903</v>
-      </c>
-      <c r="P17" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q17" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P17,CaseType!$A:$A,0))</f>
-        <v>case_type1</v>
-      </c>
-      <c r="R17" s="6" t="b">
-        <f>AND(IF($X17="",TRUE,$P17=INDEX(CaseTypeCol!$B:$B,MATCH($X17,CaseTypeCol!$A:$A,0))),IF($AA17="",TRUE,$P17=INDEX(CaseTypeCol!$B:$B,MATCH($AA17,CaseTypeCol!$A:$A,0))),IF($AD17="",TRUE,$P17=INDEX(CaseTypeCol!$B:$B,MATCH($AD17,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T17" t="s">
-        <v>12</v>
-      </c>
-      <c r="U17" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T17,DataCollection!$A:$A,0))</f>
-        <v>data_collection1</v>
-      </c>
-      <c r="W17" s="14">
-        <v>36526</v>
-      </c>
-      <c r="X17" t="s">
-        <v>357</v>
-      </c>
-      <c r="Y17" s="6" t="str">
-        <f>IF($X17="","",INDEX(CaseTypeCol!$G:$G,MATCH($X17,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim1_1_text</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB17" s="6" t="str">
-        <f>IF($AA17="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA17,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE17" s="6" t="str">
-        <f>IF($AD17="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD17,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AJ17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ17" ca="1">IF($AG17="",TRUE,IF($I17="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I17)&amp;"|"&amp;$AG17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK17" ca="1">IF($AG17="",TRUE,IF($I17="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I17)&amp;"|"&amp;$AG17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL17" ca="1">IF($AG17="",TRUE,IF($M17="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M17)&amp;"|"&amp;$AG17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM17" ca="1">IF($AG17="",TRUE,IF($M17="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M17)&amp;"|"&amp;$AG17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP17" s="6" t="str">
+        <f>IF($AN17="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN17,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ17" ca="1">IF($AN17="",TRUE,IF($I17="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I17)&amp;"|"&amp;$AN17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR17" ca="1">IF($AN17="",TRUE,IF($I17="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I17)&amp;"|"&amp;$AN17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS17" ca="1">IF($AN17="",TRUE,IF($M17="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M17)&amp;"|"&amp;$AN17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT17" ca="1">IF($AN17="",TRUE,IF($M17="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M17)&amp;"|"&amp;$AN17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>878</v>
+        <v>871</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D18" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C18,User!$A:$A,0))</f>
-        <v>org_user3_1</v>
-      </c>
-      <c r="E18" s="6" t="str">
+        <v>org_user2_1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>964</v>
+      </c>
+      <c r="F18" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C18,User!$A:$A,0))</f>
-        <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037</v>
-      </c>
-      <c r="F18" t="s">
-        <v>918</v>
-      </c>
-      <c r="G18" s="6" t="b">
+        <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3</v>
+      </c>
+      <c r="H18" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C18,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H18" s="6" t="str">
-        <f>IF(ISNA(MATCH($E18&amp;"|"&amp;$T18,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E18&amp;"|"&amp;$T18,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I18" s="6" t="str">
+        <f>IF(ISNA(MATCH($G18&amp;"|"&amp;$V18,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G18&amp;"|"&amp;$V18,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="I18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I18" ca="1">IF($H18="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H18),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H18)&amp;"|"&amp;$P18,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
       <c r="J18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J18" ca="1">IF($H18="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H18),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H18)&amp;"|"&amp;$P18,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="6" t="str">
-        <f>IF(ISNA(MATCH($C18&amp;"|"&amp;$T18,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C18&amp;"|"&amp;$T18,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="J18" ca="1">IF($I18="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I18)&amp;"|"&amp;$R18,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K18" ca="1">IF($I18="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I18),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I18)&amp;"|"&amp;$R18,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L18" ca="1">IF($I18="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I18),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I18)&amp;"|"&amp;$R18,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="6" t="str">
+        <f>IF(ISNA(MATCH($C18&amp;"|"&amp;$V18,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C18&amp;"|"&amp;$V18,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L18" ca="1">IF($K18="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K18),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K18)&amp;"|"&amp;$P18,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M18" ca="1">IF($K18="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K18),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K18)&amp;"|"&amp;$P18,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N18" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
-        <v>904</v>
-      </c>
-      <c r="P18" t="s">
+      <c r="N18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N18" ca="1">IF($M18="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M18)&amp;"|"&amp;$R18,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O18" ca="1">IF($M18="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M18),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M18)&amp;"|"&amp;$R18,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P18" ca="1">IF($M18="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M18),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M18)&amp;"|"&amp;$R18,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>897</v>
+      </c>
+      <c r="R18" t="s">
         <v>334</v>
       </c>
-      <c r="Q18" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P18,CaseType!$A:$A,0))</f>
+      <c r="S18" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R18,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R18" s="6" t="b">
-        <f>AND(IF($X18="",TRUE,$P18=INDEX(CaseTypeCol!$B:$B,MATCH($X18,CaseTypeCol!$A:$A,0))),IF($AA18="",TRUE,$P18=INDEX(CaseTypeCol!$B:$B,MATCH($AA18,CaseTypeCol!$A:$A,0))),IF($AD18="",TRUE,$P18=INDEX(CaseTypeCol!$B:$B,MATCH($AD18,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T18" t="s">
+      <c r="T18" s="6" t="b">
+        <f>AND(IF($Z18="",TRUE,$R18=INDEX(CaseTypeCol!$B:$B,MATCH($Z18,CaseTypeCol!$A:$A,0))),IF($AG18="",TRUE,$R18=INDEX(CaseTypeCol!$B:$B,MATCH($AG18,CaseTypeCol!$A:$A,0))),IF($AN18="",TRUE,$R18=INDEX(CaseTypeCol!$B:$B,MATCH($AN18,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V18" t="s">
         <v>12</v>
       </c>
-      <c r="U18" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T18,DataCollection!$A:$A,0))</f>
+      <c r="W18" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V18,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W18" s="14">
+      <c r="Y18" s="14">
         <v>36526</v>
       </c>
-      <c r="X18" t="s">
+      <c r="Z18" t="s">
         <v>357</v>
       </c>
-      <c r="Y18" s="6" t="str">
-        <f>IF($X18="","",INDEX(CaseTypeCol!$G:$G,MATCH($X18,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA18" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB18" s="6" t="str">
+        <f>IF($Z18="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z18,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z18" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB18" s="6" t="str">
-        <f>IF($AA18="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA18,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE18" s="6" t="str">
-        <f>IF($AD18="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD18,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC18" ca="1">IF($Z18="",TRUE,IF($I18="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I18)&amp;"|"&amp;$Z18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD18" ca="1">IF($Z18="",TRUE,IF($I18="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I18)&amp;"|"&amp;$Z18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE18" ca="1">IF($Z18="",TRUE,IF($M18="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M18)&amp;"|"&amp;$Z18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF18" ca="1">IF($Z18="",TRUE,IF($M18="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M18)&amp;"|"&amp;$Z18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI18" s="6" t="str">
+        <f>IF($AG18="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG18,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ18" ca="1">IF($AG18="",TRUE,IF($I18="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I18)&amp;"|"&amp;$AG18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK18" ca="1">IF($AG18="",TRUE,IF($I18="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I18)&amp;"|"&amp;$AG18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL18" ca="1">IF($AG18="",TRUE,IF($M18="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M18)&amp;"|"&amp;$AG18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM18" ca="1">IF($AG18="",TRUE,IF($M18="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M18)&amp;"|"&amp;$AG18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP18" s="6" t="str">
+        <f>IF($AN18="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN18,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ18" ca="1">IF($AN18="",TRUE,IF($I18="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I18)&amp;"|"&amp;$AN18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR18" ca="1">IF($AN18="",TRUE,IF($I18="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I18)&amp;"|"&amp;$AN18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS18" ca="1">IF($AN18="",TRUE,IF($M18="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M18)&amp;"|"&amp;$AN18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT18" ca="1">IF($AN18="",TRUE,IF($M18="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M18)&amp;"|"&amp;$AN18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D19" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C19,User!$A:$A,0))</f>
-        <v>org_user3_2</v>
-      </c>
-      <c r="E19" s="6" t="str">
+        <v>org_user2_2</v>
+      </c>
+      <c r="E19" t="s">
+        <v>964</v>
+      </c>
+      <c r="F19" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C19,User!$A:$A,0))</f>
-        <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037</v>
-      </c>
-      <c r="F19" t="s">
-        <v>918</v>
-      </c>
-      <c r="G19" s="6" t="b">
+        <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3</v>
+      </c>
+      <c r="H19" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C19,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H19" s="6" t="str">
-        <f>IF(ISNA(MATCH($E19&amp;"|"&amp;$T19,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E19&amp;"|"&amp;$T19,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I19" s="6" t="str">
+        <f>IF(ISNA(MATCH($G19&amp;"|"&amp;$V19,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G19&amp;"|"&amp;$V19,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="I19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I19" ca="1">IF($H19="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H19),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H19)&amp;"|"&amp;$P19,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
       <c r="J19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J19" ca="1">IF($H19="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H19),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H19)&amp;"|"&amp;$P19,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="6" t="str">
-        <f>IF(ISNA(MATCH($C19&amp;"|"&amp;$T19,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C19&amp;"|"&amp;$T19,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="J19" ca="1">IF($I19="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I19)&amp;"|"&amp;$R19,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K19" ca="1">IF($I19="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I19),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I19)&amp;"|"&amp;$R19,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L19" ca="1">IF($I19="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I19),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I19)&amp;"|"&amp;$R19,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="6" t="str">
+        <f>IF(ISNA(MATCH($C19&amp;"|"&amp;$V19,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C19&amp;"|"&amp;$V19,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L19" ca="1">IF($K19="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K19),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K19)&amp;"|"&amp;$P19,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M19" ca="1">IF($K19="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K19),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K19)&amp;"|"&amp;$P19,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N19" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>905</v>
-      </c>
-      <c r="P19" t="s">
+      <c r="N19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N19" ca="1">IF($M19="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M19)&amp;"|"&amp;$R19,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O19" ca="1">IF($M19="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M19),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M19)&amp;"|"&amp;$R19,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P19" ca="1">IF($M19="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M19),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M19)&amp;"|"&amp;$R19,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>898</v>
+      </c>
+      <c r="R19" t="s">
         <v>334</v>
       </c>
-      <c r="Q19" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P19,CaseType!$A:$A,0))</f>
+      <c r="S19" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R19,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R19" s="6" t="b">
-        <f>AND(IF($X19="",TRUE,$P19=INDEX(CaseTypeCol!$B:$B,MATCH($X19,CaseTypeCol!$A:$A,0))),IF($AA19="",TRUE,$P19=INDEX(CaseTypeCol!$B:$B,MATCH($AA19,CaseTypeCol!$A:$A,0))),IF($AD19="",TRUE,$P19=INDEX(CaseTypeCol!$B:$B,MATCH($AD19,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T19" t="s">
+      <c r="T19" s="6" t="b">
+        <f>AND(IF($Z19="",TRUE,$R19=INDEX(CaseTypeCol!$B:$B,MATCH($Z19,CaseTypeCol!$A:$A,0))),IF($AG19="",TRUE,$R19=INDEX(CaseTypeCol!$B:$B,MATCH($AG19,CaseTypeCol!$A:$A,0))),IF($AN19="",TRUE,$R19=INDEX(CaseTypeCol!$B:$B,MATCH($AN19,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V19" t="s">
         <v>12</v>
       </c>
-      <c r="U19" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T19,DataCollection!$A:$A,0))</f>
+      <c r="W19" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V19,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W19" s="14">
+      <c r="Y19" s="14">
         <v>36526</v>
       </c>
-      <c r="X19" t="s">
+      <c r="Z19" t="s">
         <v>357</v>
       </c>
-      <c r="Y19" s="6" t="str">
-        <f>IF($X19="","",INDEX(CaseTypeCol!$G:$G,MATCH($X19,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA19" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB19" s="6" t="str">
+        <f>IF($Z19="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z19,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z19" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB19" s="6" t="str">
-        <f>IF($AA19="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA19,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE19" s="6" t="str">
-        <f>IF($AD19="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD19,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC19" ca="1">IF($Z19="",TRUE,IF($I19="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I19)&amp;"|"&amp;$Z19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD19" ca="1">IF($Z19="",TRUE,IF($I19="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I19)&amp;"|"&amp;$Z19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE19" ca="1">IF($Z19="",TRUE,IF($M19="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M19)&amp;"|"&amp;$Z19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF19" ca="1">IF($Z19="",TRUE,IF($M19="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M19)&amp;"|"&amp;$Z19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI19" s="6" t="str">
+        <f>IF($AG19="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG19,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ19" ca="1">IF($AG19="",TRUE,IF($I19="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I19)&amp;"|"&amp;$AG19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK19" ca="1">IF($AG19="",TRUE,IF($I19="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I19)&amp;"|"&amp;$AG19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL19" ca="1">IF($AG19="",TRUE,IF($M19="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M19)&amp;"|"&amp;$AG19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM19" ca="1">IF($AG19="",TRUE,IF($M19="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M19)&amp;"|"&amp;$AG19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP19" s="6" t="str">
+        <f>IF($AN19="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN19,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ19" ca="1">IF($AN19="",TRUE,IF($I19="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I19)&amp;"|"&amp;$AN19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR19" ca="1">IF($AN19="",TRUE,IF($I19="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I19)&amp;"|"&amp;$AN19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS19" ca="1">IF($AN19="",TRUE,IF($M19="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M19)&amp;"|"&amp;$AN19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT19" ca="1">IF($AN19="",TRUE,IF($M19="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M19)&amp;"|"&amp;$AN19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D20" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C20,User!$A:$A,0))</f>
-        <v>org_user3_3</v>
-      </c>
-      <c r="E20" s="6" t="str">
+        <v>org_user2_3</v>
+      </c>
+      <c r="E20" t="s">
+        <v>964</v>
+      </c>
+      <c r="F20" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C20,User!$A:$A,0))</f>
-        <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037</v>
-      </c>
-      <c r="F20" t="s">
-        <v>918</v>
-      </c>
-      <c r="G20" s="6" t="b">
+        <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3</v>
+      </c>
+      <c r="H20" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C20,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H20" s="6" t="str">
-        <f>IF(ISNA(MATCH($E20&amp;"|"&amp;$T20,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E20&amp;"|"&amp;$T20,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I20" s="6" t="str">
+        <f>IF(ISNA(MATCH($G20&amp;"|"&amp;$V20,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G20&amp;"|"&amp;$V20,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="I20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I20" ca="1">IF($H20="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H20),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H20)&amp;"|"&amp;$P20,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
       <c r="J20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J20" ca="1">IF($H20="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H20),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H20)&amp;"|"&amp;$P20,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K20" s="6" t="str">
-        <f>IF(ISNA(MATCH($C20&amp;"|"&amp;$T20,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C20&amp;"|"&amp;$T20,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="J20" ca="1">IF($I20="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I20)&amp;"|"&amp;$R20,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K20" ca="1">IF($I20="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I20),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I20)&amp;"|"&amp;$R20,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L20" ca="1">IF($I20="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I20),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I20)&amp;"|"&amp;$R20,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="6" t="str">
+        <f>IF(ISNA(MATCH($C20&amp;"|"&amp;$V20,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C20&amp;"|"&amp;$V20,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L20" ca="1">IF($K20="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K20),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K20)&amp;"|"&amp;$P20,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M20" ca="1">IF($K20="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K20),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K20)&amp;"|"&amp;$P20,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N20" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
-        <v>906</v>
-      </c>
-      <c r="P20" t="s">
+      <c r="N20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N20" ca="1">IF($M20="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M20)&amp;"|"&amp;$R20,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O20" ca="1">IF($M20="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M20),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M20)&amp;"|"&amp;$R20,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P20" ca="1">IF($M20="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M20),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M20)&amp;"|"&amp;$R20,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>899</v>
+      </c>
+      <c r="R20" t="s">
         <v>334</v>
       </c>
-      <c r="Q20" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P20,CaseType!$A:$A,0))</f>
+      <c r="S20" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R20,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R20" s="6" t="b">
-        <f>AND(IF($X20="",TRUE,$P20=INDEX(CaseTypeCol!$B:$B,MATCH($X20,CaseTypeCol!$A:$A,0))),IF($AA20="",TRUE,$P20=INDEX(CaseTypeCol!$B:$B,MATCH($AA20,CaseTypeCol!$A:$A,0))),IF($AD20="",TRUE,$P20=INDEX(CaseTypeCol!$B:$B,MATCH($AD20,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T20" t="s">
+      <c r="T20" s="6" t="b">
+        <f>AND(IF($Z20="",TRUE,$R20=INDEX(CaseTypeCol!$B:$B,MATCH($Z20,CaseTypeCol!$A:$A,0))),IF($AG20="",TRUE,$R20=INDEX(CaseTypeCol!$B:$B,MATCH($AG20,CaseTypeCol!$A:$A,0))),IF($AN20="",TRUE,$R20=INDEX(CaseTypeCol!$B:$B,MATCH($AN20,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V20" t="s">
         <v>12</v>
       </c>
-      <c r="U20" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T20,DataCollection!$A:$A,0))</f>
+      <c r="W20" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V20,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W20" s="14">
+      <c r="Y20" s="14">
         <v>36526</v>
       </c>
-      <c r="X20" t="s">
+      <c r="Z20" t="s">
         <v>357</v>
       </c>
-      <c r="Y20" s="6" t="str">
-        <f>IF($X20="","",INDEX(CaseTypeCol!$G:$G,MATCH($X20,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA20" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB20" s="6" t="str">
+        <f>IF($Z20="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z20,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z20" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB20" s="6" t="str">
-        <f>IF($AA20="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA20,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE20" s="6" t="str">
-        <f>IF($AD20="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD20,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC20" ca="1">IF($Z20="",TRUE,IF($I20="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I20)&amp;"|"&amp;$Z20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD20" ca="1">IF($Z20="",TRUE,IF($I20="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I20)&amp;"|"&amp;$Z20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE20" ca="1">IF($Z20="",TRUE,IF($M20="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M20)&amp;"|"&amp;$Z20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF20" ca="1">IF($Z20="",TRUE,IF($M20="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M20)&amp;"|"&amp;$Z20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI20" s="6" t="str">
+        <f>IF($AG20="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG20,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ20" ca="1">IF($AG20="",TRUE,IF($I20="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I20)&amp;"|"&amp;$AG20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK20" ca="1">IF($AG20="",TRUE,IF($I20="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I20)&amp;"|"&amp;$AG20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL20" ca="1">IF($AG20="",TRUE,IF($M20="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M20)&amp;"|"&amp;$AG20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM20" ca="1">IF($AG20="",TRUE,IF($M20="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M20)&amp;"|"&amp;$AG20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP20" s="6" t="str">
+        <f>IF($AN20="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN20,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ20" ca="1">IF($AN20="",TRUE,IF($I20="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I20)&amp;"|"&amp;$AN20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR20" ca="1">IF($AN20="",TRUE,IF($I20="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I20)&amp;"|"&amp;$AN20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS20" ca="1">IF($AN20="",TRUE,IF($M20="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M20)&amp;"|"&amp;$AN20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT20" ca="1">IF($AN20="",TRUE,IF($M20="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M20)&amp;"|"&amp;$AN20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D21" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C21,User!$A:$A,0))</f>
-        <v>org_user3_4</v>
-      </c>
-      <c r="E21" s="6" t="str">
+        <v>org_user2_4</v>
+      </c>
+      <c r="E21" t="s">
+        <v>964</v>
+      </c>
+      <c r="F21" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C21,User!$A:$A,0))</f>
-        <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037</v>
-      </c>
-      <c r="F21" t="s">
-        <v>918</v>
-      </c>
-      <c r="G21" s="6" t="b">
+        <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3</v>
+      </c>
+      <c r="H21" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C21,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H21" s="6" t="str">
-        <f>IF(ISNA(MATCH($E21&amp;"|"&amp;$T21,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E21&amp;"|"&amp;$T21,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I21" s="6" t="str">
+        <f>IF(ISNA(MATCH($G21&amp;"|"&amp;$V21,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G21&amp;"|"&amp;$V21,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="I21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I21" ca="1">IF($H21="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H21),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H21)&amp;"|"&amp;$P21,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
       <c r="J21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J21" ca="1">IF($H21="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H21),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H21)&amp;"|"&amp;$P21,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="6" t="str">
-        <f>IF(ISNA(MATCH($C21&amp;"|"&amp;$T21,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C21&amp;"|"&amp;$T21,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="J21" ca="1">IF($I21="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I21)&amp;"|"&amp;$R21,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K21" ca="1">IF($I21="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I21),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I21)&amp;"|"&amp;$R21,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L21" ca="1">IF($I21="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I21),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I21)&amp;"|"&amp;$R21,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="6" t="str">
+        <f>IF(ISNA(MATCH($C21&amp;"|"&amp;$V21,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C21&amp;"|"&amp;$V21,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L21" ca="1">IF($K21="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K21),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K21)&amp;"|"&amp;$P21,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M21" ca="1">IF($K21="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K21),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K21)&amp;"|"&amp;$P21,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N21" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
-        <v>907</v>
-      </c>
-      <c r="P21" t="s">
+      <c r="N21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N21" ca="1">IF($M21="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M21)&amp;"|"&amp;$R21,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O21" ca="1">IF($M21="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M21),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M21)&amp;"|"&amp;$R21,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P21" ca="1">IF($M21="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M21),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M21)&amp;"|"&amp;$R21,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>900</v>
+      </c>
+      <c r="R21" t="s">
         <v>334</v>
       </c>
-      <c r="Q21" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P21,CaseType!$A:$A,0))</f>
+      <c r="S21" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R21,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R21" s="6" t="b">
-        <f>AND(IF($X21="",TRUE,$P21=INDEX(CaseTypeCol!$B:$B,MATCH($X21,CaseTypeCol!$A:$A,0))),IF($AA21="",TRUE,$P21=INDEX(CaseTypeCol!$B:$B,MATCH($AA21,CaseTypeCol!$A:$A,0))),IF($AD21="",TRUE,$P21=INDEX(CaseTypeCol!$B:$B,MATCH($AD21,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T21" t="s">
+      <c r="T21" s="6" t="b">
+        <f>AND(IF($Z21="",TRUE,$R21=INDEX(CaseTypeCol!$B:$B,MATCH($Z21,CaseTypeCol!$A:$A,0))),IF($AG21="",TRUE,$R21=INDEX(CaseTypeCol!$B:$B,MATCH($AG21,CaseTypeCol!$A:$A,0))),IF($AN21="",TRUE,$R21=INDEX(CaseTypeCol!$B:$B,MATCH($AN21,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V21" t="s">
         <v>12</v>
       </c>
-      <c r="U21" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T21,DataCollection!$A:$A,0))</f>
+      <c r="W21" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V21,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W21" s="14">
+      <c r="Y21" s="14">
         <v>36526</v>
       </c>
-      <c r="X21" t="s">
+      <c r="Z21" t="s">
         <v>357</v>
       </c>
-      <c r="Y21" s="6" t="str">
-        <f>IF($X21="","",INDEX(CaseTypeCol!$G:$G,MATCH($X21,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA21" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB21" s="6" t="str">
+        <f>IF($Z21="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z21,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z21" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB21" s="6" t="str">
-        <f>IF($AA21="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA21,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE21" s="6" t="str">
-        <f>IF($AD21="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD21,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC21" ca="1">IF($Z21="",TRUE,IF($I21="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I21)&amp;"|"&amp;$Z21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD21" ca="1">IF($Z21="",TRUE,IF($I21="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I21)&amp;"|"&amp;$Z21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE21" ca="1">IF($Z21="",TRUE,IF($M21="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M21)&amp;"|"&amp;$Z21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF21" ca="1">IF($Z21="",TRUE,IF($M21="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M21)&amp;"|"&amp;$Z21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI21" s="6" t="str">
+        <f>IF($AG21="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG21,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ21" ca="1">IF($AG21="",TRUE,IF($I21="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I21)&amp;"|"&amp;$AG21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK21" ca="1">IF($AG21="",TRUE,IF($I21="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I21)&amp;"|"&amp;$AG21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL21" ca="1">IF($AG21="",TRUE,IF($M21="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M21)&amp;"|"&amp;$AG21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM21" ca="1">IF($AG21="",TRUE,IF($M21="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M21)&amp;"|"&amp;$AG21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP21" s="6" t="str">
+        <f>IF($AN21="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN21,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ21" ca="1">IF($AN21="",TRUE,IF($I21="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I21)&amp;"|"&amp;$AN21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR21" ca="1">IF($AN21="",TRUE,IF($I21="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I21)&amp;"|"&amp;$AN21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS21" ca="1">IF($AN21="",TRUE,IF($M21="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M21)&amp;"|"&amp;$AN21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT21" ca="1">IF($AN21="",TRUE,IF($M21="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M21)&amp;"|"&amp;$AN21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D22" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C22,User!$A:$A,0))</f>
-        <v>org_user4_1</v>
-      </c>
-      <c r="E22" s="6" t="str">
+        <v>org_user3_1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>964</v>
+      </c>
+      <c r="F22" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C22,User!$A:$A,0))</f>
-        <v>0195d18c-1c92-d419-4c71-a570f428499b</v>
-      </c>
-      <c r="F22" t="s">
-        <v>918</v>
-      </c>
-      <c r="G22" s="6" t="b">
+        <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037</v>
+      </c>
+      <c r="H22" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C22,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H22" s="6" t="str">
-        <f>IF(ISNA(MATCH($E22&amp;"|"&amp;$T22,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E22&amp;"|"&amp;$T22,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I22" s="6" t="str">
+        <f>IF(ISNA(MATCH($G22&amp;"|"&amp;$V22,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G22&amp;"|"&amp;$V22,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="I22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I22" ca="1">IF($H22="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H22),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H22)&amp;"|"&amp;$P22,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
       <c r="J22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J22" ca="1">IF($H22="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H22),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H22)&amp;"|"&amp;$P22,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="6" t="str">
-        <f>IF(ISNA(MATCH($C22&amp;"|"&amp;$T22,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C22&amp;"|"&amp;$T22,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="J22" ca="1">IF($I22="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I22)&amp;"|"&amp;$R22,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K22" ca="1">IF($I22="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I22),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I22)&amp;"|"&amp;$R22,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L22" ca="1">IF($I22="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I22),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I22)&amp;"|"&amp;$R22,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="6" t="str">
+        <f>IF(ISNA(MATCH($C22&amp;"|"&amp;$V22,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C22&amp;"|"&amp;$V22,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L22" ca="1">IF($K22="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K22),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K22)&amp;"|"&amp;$P22,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M22" ca="1">IF($K22="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K22),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K22)&amp;"|"&amp;$P22,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N22" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
-        <v>908</v>
-      </c>
-      <c r="P22" t="s">
+      <c r="N22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N22" ca="1">IF($M22="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M22)&amp;"|"&amp;$R22,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O22" ca="1">IF($M22="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M22),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M22)&amp;"|"&amp;$R22,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P22" ca="1">IF($M22="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M22),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M22)&amp;"|"&amp;$R22,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>901</v>
+      </c>
+      <c r="R22" t="s">
         <v>334</v>
       </c>
-      <c r="Q22" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P22,CaseType!$A:$A,0))</f>
+      <c r="S22" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R22,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R22" s="6" t="b">
-        <f>AND(IF($X22="",TRUE,$P22=INDEX(CaseTypeCol!$B:$B,MATCH($X22,CaseTypeCol!$A:$A,0))),IF($AA22="",TRUE,$P22=INDEX(CaseTypeCol!$B:$B,MATCH($AA22,CaseTypeCol!$A:$A,0))),IF($AD22="",TRUE,$P22=INDEX(CaseTypeCol!$B:$B,MATCH($AD22,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T22" t="s">
+      <c r="T22" s="6" t="b">
+        <f>AND(IF($Z22="",TRUE,$R22=INDEX(CaseTypeCol!$B:$B,MATCH($Z22,CaseTypeCol!$A:$A,0))),IF($AG22="",TRUE,$R22=INDEX(CaseTypeCol!$B:$B,MATCH($AG22,CaseTypeCol!$A:$A,0))),IF($AN22="",TRUE,$R22=INDEX(CaseTypeCol!$B:$B,MATCH($AN22,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V22" t="s">
         <v>12</v>
       </c>
-      <c r="U22" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T22,DataCollection!$A:$A,0))</f>
+      <c r="W22" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V22,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W22" s="14">
+      <c r="Y22" s="14">
         <v>36526</v>
       </c>
-      <c r="X22" t="s">
+      <c r="Z22" t="s">
         <v>357</v>
       </c>
-      <c r="Y22" s="6" t="str">
-        <f>IF($X22="","",INDEX(CaseTypeCol!$G:$G,MATCH($X22,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA22" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB22" s="6" t="str">
+        <f>IF($Z22="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z22,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z22" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB22" s="6" t="str">
-        <f>IF($AA22="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA22,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC22" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE22" s="6" t="str">
-        <f>IF($AD22="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD22,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC22" ca="1">IF($Z22="",TRUE,IF($I22="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I22)&amp;"|"&amp;$Z22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD22" ca="1">IF($Z22="",TRUE,IF($I22="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I22)&amp;"|"&amp;$Z22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE22" ca="1">IF($Z22="",TRUE,IF($M22="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M22)&amp;"|"&amp;$Z22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF22" ca="1">IF($Z22="",TRUE,IF($M22="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M22)&amp;"|"&amp;$Z22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI22" s="6" t="str">
+        <f>IF($AG22="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG22,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ22" ca="1">IF($AG22="",TRUE,IF($I22="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I22)&amp;"|"&amp;$AG22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK22" ca="1">IF($AG22="",TRUE,IF($I22="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I22)&amp;"|"&amp;$AG22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL22" ca="1">IF($AG22="",TRUE,IF($M22="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M22)&amp;"|"&amp;$AG22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM22" ca="1">IF($AG22="",TRUE,IF($M22="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M22)&amp;"|"&amp;$AG22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP22" s="6" t="str">
+        <f>IF($AN22="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN22,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ22" ca="1">IF($AN22="",TRUE,IF($I22="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I22)&amp;"|"&amp;$AN22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR22" ca="1">IF($AN22="",TRUE,IF($I22="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I22)&amp;"|"&amp;$AN22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS22" ca="1">IF($AN22="",TRUE,IF($M22="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M22)&amp;"|"&amp;$AN22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT22" ca="1">IF($AN22="",TRUE,IF($M22="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M22)&amp;"|"&amp;$AN22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="D23" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C23,User!$A:$A,0))</f>
-        <v>org_user4_2</v>
-      </c>
-      <c r="E23" s="6" t="str">
+        <v>org_user3_2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>964</v>
+      </c>
+      <c r="F23" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C23,User!$A:$A,0))</f>
-        <v>0195d18c-1c92-d419-4c71-a570f428499b</v>
-      </c>
-      <c r="F23" t="s">
-        <v>918</v>
-      </c>
-      <c r="G23" s="6" t="b">
+        <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037</v>
+      </c>
+      <c r="H23" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C23,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H23" s="6" t="str">
-        <f>IF(ISNA(MATCH($E23&amp;"|"&amp;$T23,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E23&amp;"|"&amp;$T23,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I23" s="6" t="str">
+        <f>IF(ISNA(MATCH($G23&amp;"|"&amp;$V23,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G23&amp;"|"&amp;$V23,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="I23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I23" ca="1">IF($H23="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H23),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H23)&amp;"|"&amp;$P23,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
       <c r="J23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J23" ca="1">IF($H23="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H23),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H23)&amp;"|"&amp;$P23,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K23" s="6" t="str">
-        <f>IF(ISNA(MATCH($C23&amp;"|"&amp;$T23,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C23&amp;"|"&amp;$T23,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="J23" ca="1">IF($I23="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I23)&amp;"|"&amp;$R23,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K23" ca="1">IF($I23="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I23),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I23)&amp;"|"&amp;$R23,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L23" ca="1">IF($I23="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I23),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I23)&amp;"|"&amp;$R23,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="6" t="str">
+        <f>IF(ISNA(MATCH($C23&amp;"|"&amp;$V23,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C23&amp;"|"&amp;$V23,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L23" ca="1">IF($K23="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K23),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K23)&amp;"|"&amp;$P23,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M23" ca="1">IF($K23="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K23),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K23)&amp;"|"&amp;$P23,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N23" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O23" t="s">
-        <v>909</v>
-      </c>
-      <c r="P23" t="s">
+      <c r="N23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N23" ca="1">IF($M23="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M23)&amp;"|"&amp;$R23,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O23" ca="1">IF($M23="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M23),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M23)&amp;"|"&amp;$R23,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P23" ca="1">IF($M23="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M23),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M23)&amp;"|"&amp;$R23,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>902</v>
+      </c>
+      <c r="R23" t="s">
         <v>334</v>
       </c>
-      <c r="Q23" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P23,CaseType!$A:$A,0))</f>
+      <c r="S23" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R23,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R23" s="6" t="b">
-        <f>AND(IF($X23="",TRUE,$P23=INDEX(CaseTypeCol!$B:$B,MATCH($X23,CaseTypeCol!$A:$A,0))),IF($AA23="",TRUE,$P23=INDEX(CaseTypeCol!$B:$B,MATCH($AA23,CaseTypeCol!$A:$A,0))),IF($AD23="",TRUE,$P23=INDEX(CaseTypeCol!$B:$B,MATCH($AD23,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T23" t="s">
+      <c r="T23" s="6" t="b">
+        <f>AND(IF($Z23="",TRUE,$R23=INDEX(CaseTypeCol!$B:$B,MATCH($Z23,CaseTypeCol!$A:$A,0))),IF($AG23="",TRUE,$R23=INDEX(CaseTypeCol!$B:$B,MATCH($AG23,CaseTypeCol!$A:$A,0))),IF($AN23="",TRUE,$R23=INDEX(CaseTypeCol!$B:$B,MATCH($AN23,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V23" t="s">
         <v>12</v>
       </c>
-      <c r="U23" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T23,DataCollection!$A:$A,0))</f>
+      <c r="W23" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V23,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W23" s="14">
+      <c r="Y23" s="14">
         <v>36526</v>
       </c>
-      <c r="X23" t="s">
+      <c r="Z23" t="s">
         <v>357</v>
       </c>
-      <c r="Y23" s="6" t="str">
-        <f>IF($X23="","",INDEX(CaseTypeCol!$G:$G,MATCH($X23,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA23" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB23" s="6" t="str">
+        <f>IF($Z23="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z23,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z23" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA23" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB23" s="6" t="str">
-        <f>IF($AA23="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA23,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC23" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE23" s="6" t="str">
-        <f>IF($AD23="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD23,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC23" ca="1">IF($Z23="",TRUE,IF($I23="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I23)&amp;"|"&amp;$Z23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD23" ca="1">IF($Z23="",TRUE,IF($I23="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I23)&amp;"|"&amp;$Z23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE23" ca="1">IF($Z23="",TRUE,IF($M23="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M23)&amp;"|"&amp;$Z23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF23" ca="1">IF($Z23="",TRUE,IF($M23="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M23)&amp;"|"&amp;$Z23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI23" s="6" t="str">
+        <f>IF($AG23="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG23,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ23" ca="1">IF($AG23="",TRUE,IF($I23="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I23)&amp;"|"&amp;$AG23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK23" ca="1">IF($AG23="",TRUE,IF($I23="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I23)&amp;"|"&amp;$AG23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL23" ca="1">IF($AG23="",TRUE,IF($M23="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M23)&amp;"|"&amp;$AG23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM23" ca="1">IF($AG23="",TRUE,IF($M23="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M23)&amp;"|"&amp;$AG23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP23" s="6" t="str">
+        <f>IF($AN23="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN23,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ23" ca="1">IF($AN23="",TRUE,IF($I23="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I23)&amp;"|"&amp;$AN23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR23" ca="1">IF($AN23="",TRUE,IF($I23="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I23)&amp;"|"&amp;$AN23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS23" ca="1">IF($AN23="",TRUE,IF($M23="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M23)&amp;"|"&amp;$AN23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT23" ca="1">IF($AN23="",TRUE,IF($M23="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M23)&amp;"|"&amp;$AN23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D24" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C24,User!$A:$A,0))</f>
-        <v>org_user4_3</v>
-      </c>
-      <c r="E24" s="6" t="str">
+        <v>org_user3_3</v>
+      </c>
+      <c r="E24" t="s">
+        <v>964</v>
+      </c>
+      <c r="F24" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C24,User!$A:$A,0))</f>
-        <v>0195d18c-1c92-d419-4c71-a570f428499b</v>
-      </c>
-      <c r="F24" t="s">
-        <v>918</v>
-      </c>
-      <c r="G24" s="6" t="b">
+        <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037</v>
+      </c>
+      <c r="H24" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C24,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H24" s="6" t="str">
-        <f>IF(ISNA(MATCH($E24&amp;"|"&amp;$T24,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E24&amp;"|"&amp;$T24,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I24" s="6" t="str">
+        <f>IF(ISNA(MATCH($G24&amp;"|"&amp;$V24,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G24&amp;"|"&amp;$V24,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="I24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I24" ca="1">IF($H24="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H24),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H24)&amp;"|"&amp;$P24,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
       <c r="J24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J24" ca="1">IF($H24="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H24),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H24)&amp;"|"&amp;$P24,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="6" t="str">
-        <f>IF(ISNA(MATCH($C24&amp;"|"&amp;$T24,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C24&amp;"|"&amp;$T24,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="J24" ca="1">IF($I24="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I24)&amp;"|"&amp;$R24,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K24" ca="1">IF($I24="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I24),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I24)&amp;"|"&amp;$R24,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L24" ca="1">IF($I24="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I24),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I24)&amp;"|"&amp;$R24,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="6" t="str">
+        <f>IF(ISNA(MATCH($C24&amp;"|"&amp;$V24,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C24&amp;"|"&amp;$V24,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L24" ca="1">IF($K24="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K24),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K24)&amp;"|"&amp;$P24,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M24" ca="1">IF($K24="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K24),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K24)&amp;"|"&amp;$P24,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N24" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O24" t="s">
-        <v>910</v>
-      </c>
-      <c r="P24" t="s">
+      <c r="N24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N24" ca="1">IF($M24="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M24)&amp;"|"&amp;$R24,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O24" ca="1">IF($M24="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M24),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M24)&amp;"|"&amp;$R24,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P24" ca="1">IF($M24="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M24),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M24)&amp;"|"&amp;$R24,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>903</v>
+      </c>
+      <c r="R24" t="s">
         <v>334</v>
       </c>
-      <c r="Q24" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P24,CaseType!$A:$A,0))</f>
+      <c r="S24" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R24,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R24" s="6" t="b">
-        <f>AND(IF($X24="",TRUE,$P24=INDEX(CaseTypeCol!$B:$B,MATCH($X24,CaseTypeCol!$A:$A,0))),IF($AA24="",TRUE,$P24=INDEX(CaseTypeCol!$B:$B,MATCH($AA24,CaseTypeCol!$A:$A,0))),IF($AD24="",TRUE,$P24=INDEX(CaseTypeCol!$B:$B,MATCH($AD24,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T24" t="s">
+      <c r="T24" s="6" t="b">
+        <f>AND(IF($Z24="",TRUE,$R24=INDEX(CaseTypeCol!$B:$B,MATCH($Z24,CaseTypeCol!$A:$A,0))),IF($AG24="",TRUE,$R24=INDEX(CaseTypeCol!$B:$B,MATCH($AG24,CaseTypeCol!$A:$A,0))),IF($AN24="",TRUE,$R24=INDEX(CaseTypeCol!$B:$B,MATCH($AN24,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V24" t="s">
         <v>12</v>
       </c>
-      <c r="U24" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T24,DataCollection!$A:$A,0))</f>
+      <c r="W24" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V24,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W24" s="14">
+      <c r="Y24" s="14">
         <v>36526</v>
       </c>
-      <c r="X24" t="s">
+      <c r="Z24" t="s">
         <v>357</v>
       </c>
-      <c r="Y24" s="6" t="str">
-        <f>IF($X24="","",INDEX(CaseTypeCol!$G:$G,MATCH($X24,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA24" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB24" s="6" t="str">
+        <f>IF($Z24="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z24,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z24" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB24" s="6" t="str">
-        <f>IF($AA24="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA24,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC24" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE24" s="6" t="str">
-        <f>IF($AD24="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD24,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC24" ca="1">IF($Z24="",TRUE,IF($I24="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I24)&amp;"|"&amp;$Z24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD24" ca="1">IF($Z24="",TRUE,IF($I24="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I24)&amp;"|"&amp;$Z24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE24" ca="1">IF($Z24="",TRUE,IF($M24="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M24)&amp;"|"&amp;$Z24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF24" ca="1">IF($Z24="",TRUE,IF($M24="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M24)&amp;"|"&amp;$Z24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI24" s="6" t="str">
+        <f>IF($AG24="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG24,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ24" ca="1">IF($AG24="",TRUE,IF($I24="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I24)&amp;"|"&amp;$AG24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK24" ca="1">IF($AG24="",TRUE,IF($I24="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I24)&amp;"|"&amp;$AG24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL24" ca="1">IF($AG24="",TRUE,IF($M24="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M24)&amp;"|"&amp;$AG24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM24" ca="1">IF($AG24="",TRUE,IF($M24="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M24)&amp;"|"&amp;$AG24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP24" s="6" t="str">
+        <f>IF($AN24="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN24,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ24" ca="1">IF($AN24="",TRUE,IF($I24="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I24)&amp;"|"&amp;$AN24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR24" ca="1">IF($AN24="",TRUE,IF($I24="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I24)&amp;"|"&amp;$AN24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS24" ca="1">IF($AN24="",TRUE,IF($M24="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M24)&amp;"|"&amp;$AN24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT24" ca="1">IF($AN24="",TRUE,IF($M24="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M24)&amp;"|"&amp;$AN24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D25" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C25,User!$A:$A,0))</f>
-        <v>org_user4_4</v>
-      </c>
-      <c r="E25" s="6" t="str">
+        <v>org_user3_4</v>
+      </c>
+      <c r="E25" t="s">
+        <v>964</v>
+      </c>
+      <c r="F25" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C25,User!$A:$A,0))</f>
-        <v>0195d18c-1c92-d419-4c71-a570f428499b</v>
-      </c>
-      <c r="F25" t="s">
-        <v>918</v>
-      </c>
-      <c r="G25" s="6" t="b">
+        <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037</v>
+      </c>
+      <c r="H25" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C25,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H25" s="6" t="str">
-        <f>IF(ISNA(MATCH($E25&amp;"|"&amp;$T25,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E25&amp;"|"&amp;$T25,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I25" s="6" t="str">
+        <f>IF(ISNA(MATCH($G25&amp;"|"&amp;$V25,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G25&amp;"|"&amp;$V25,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="I25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I25" ca="1">IF($H25="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H25),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H25)&amp;"|"&amp;$P25,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
       <c r="J25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J25" ca="1">IF($H25="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H25),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H25)&amp;"|"&amp;$P25,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="6" t="str">
-        <f>IF(ISNA(MATCH($C25&amp;"|"&amp;$T25,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C25&amp;"|"&amp;$T25,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="J25" ca="1">IF($I25="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I25)&amp;"|"&amp;$R25,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K25" ca="1">IF($I25="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I25),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I25)&amp;"|"&amp;$R25,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L25" ca="1">IF($I25="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I25),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I25)&amp;"|"&amp;$R25,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="6" t="str">
+        <f>IF(ISNA(MATCH($C25&amp;"|"&amp;$V25,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C25&amp;"|"&amp;$V25,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L25" ca="1">IF($K25="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K25),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K25)&amp;"|"&amp;$P25,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M25" ca="1">IF($K25="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K25),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K25)&amp;"|"&amp;$P25,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N25" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O25" t="s">
-        <v>911</v>
-      </c>
-      <c r="P25" t="s">
+      <c r="N25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N25" ca="1">IF($M25="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M25)&amp;"|"&amp;$R25,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O25" ca="1">IF($M25="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M25),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M25)&amp;"|"&amp;$R25,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P25" ca="1">IF($M25="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M25),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M25)&amp;"|"&amp;$R25,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>904</v>
+      </c>
+      <c r="R25" t="s">
         <v>334</v>
       </c>
-      <c r="Q25" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P25,CaseType!$A:$A,0))</f>
+      <c r="S25" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R25,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R25" s="6" t="b">
-        <f>AND(IF($X25="",TRUE,$P25=INDEX(CaseTypeCol!$B:$B,MATCH($X25,CaseTypeCol!$A:$A,0))),IF($AA25="",TRUE,$P25=INDEX(CaseTypeCol!$B:$B,MATCH($AA25,CaseTypeCol!$A:$A,0))),IF($AD25="",TRUE,$P25=INDEX(CaseTypeCol!$B:$B,MATCH($AD25,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T25" t="s">
+      <c r="T25" s="6" t="b">
+        <f>AND(IF($Z25="",TRUE,$R25=INDEX(CaseTypeCol!$B:$B,MATCH($Z25,CaseTypeCol!$A:$A,0))),IF($AG25="",TRUE,$R25=INDEX(CaseTypeCol!$B:$B,MATCH($AG25,CaseTypeCol!$A:$A,0))),IF($AN25="",TRUE,$R25=INDEX(CaseTypeCol!$B:$B,MATCH($AN25,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V25" t="s">
         <v>12</v>
       </c>
-      <c r="U25" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T25,DataCollection!$A:$A,0))</f>
+      <c r="W25" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V25,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W25" s="14">
+      <c r="Y25" s="14">
         <v>36526</v>
       </c>
-      <c r="X25" t="s">
+      <c r="Z25" t="s">
         <v>357</v>
       </c>
-      <c r="Y25" s="6" t="str">
-        <f>IF($X25="","",INDEX(CaseTypeCol!$G:$G,MATCH($X25,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA25" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB25" s="6" t="str">
+        <f>IF($Z25="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z25,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z25" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB25" s="6" t="str">
-        <f>IF($AA25="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA25,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC25" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD25" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE25" s="6" t="str">
-        <f>IF($AD25="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD25,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC25" ca="1">IF($Z25="",TRUE,IF($I25="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I25)&amp;"|"&amp;$Z25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD25" ca="1">IF($Z25="",TRUE,IF($I25="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I25)&amp;"|"&amp;$Z25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE25" ca="1">IF($Z25="",TRUE,IF($M25="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M25)&amp;"|"&amp;$Z25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF25" ca="1">IF($Z25="",TRUE,IF($M25="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M25)&amp;"|"&amp;$Z25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI25" s="6" t="str">
+        <f>IF($AG25="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG25,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ25" ca="1">IF($AG25="",TRUE,IF($I25="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I25)&amp;"|"&amp;$AG25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK25" ca="1">IF($AG25="",TRUE,IF($I25="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I25)&amp;"|"&amp;$AG25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL25" ca="1">IF($AG25="",TRUE,IF($M25="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M25)&amp;"|"&amp;$AG25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM25" ca="1">IF($AG25="",TRUE,IF($M25="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M25)&amp;"|"&amp;$AG25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP25" s="6" t="str">
+        <f>IF($AN25="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN25,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ25" ca="1">IF($AN25="",TRUE,IF($I25="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I25)&amp;"|"&amp;$AN25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR25" ca="1">IF($AN25="",TRUE,IF($I25="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I25)&amp;"|"&amp;$AN25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS25" ca="1">IF($AN25="",TRUE,IF($M25="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M25)&amp;"|"&amp;$AN25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT25" ca="1">IF($AN25="",TRUE,IF($M25="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M25)&amp;"|"&amp;$AN25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D26" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C26,User!$A:$A,0))</f>
-        <v>org_user5_1</v>
-      </c>
-      <c r="E26" s="6" t="str">
+        <v>org_user4_1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>964</v>
+      </c>
+      <c r="F26" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C26,User!$A:$A,0))</f>
-        <v>0195d18c-1c93-02a2-6920-7e4dbfb73ce0</v>
-      </c>
-      <c r="F26" t="s">
-        <v>918</v>
-      </c>
-      <c r="G26" s="6" t="b">
+        <v>0195d18c-1c92-d419-4c71-a570f428499b</v>
+      </c>
+      <c r="H26" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C26,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H26" s="6" t="str">
-        <f>IF(ISNA(MATCH($E26&amp;"|"&amp;$T26,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E26&amp;"|"&amp;$T26,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I26" s="6" t="str">
+        <f>IF(ISNA(MATCH($G26&amp;"|"&amp;$V26,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G26&amp;"|"&amp;$V26,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="I26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I26" ca="1">IF($H26="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H26),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H26)&amp;"|"&amp;$P26,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
       <c r="J26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J26" ca="1">IF($H26="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H26),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H26)&amp;"|"&amp;$P26,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="6" t="str">
-        <f>IF(ISNA(MATCH($C26&amp;"|"&amp;$T26,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C26&amp;"|"&amp;$T26,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="J26" ca="1">IF($I26="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I26)&amp;"|"&amp;$R26,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K26" ca="1">IF($I26="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I26),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I26)&amp;"|"&amp;$R26,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L26" ca="1">IF($I26="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I26),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I26)&amp;"|"&amp;$R26,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="6" t="str">
+        <f>IF(ISNA(MATCH($C26&amp;"|"&amp;$V26,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C26&amp;"|"&amp;$V26,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L26" ca="1">IF($K26="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K26),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K26)&amp;"|"&amp;$P26,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M26" ca="1">IF($K26="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K26),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K26)&amp;"|"&amp;$P26,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N26" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O26" t="s">
-        <v>912</v>
-      </c>
-      <c r="P26" t="s">
+      <c r="N26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N26" ca="1">IF($M26="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M26)&amp;"|"&amp;$R26,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O26" ca="1">IF($M26="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M26),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M26)&amp;"|"&amp;$R26,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P26" ca="1">IF($M26="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M26),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M26)&amp;"|"&amp;$R26,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>905</v>
+      </c>
+      <c r="R26" t="s">
         <v>334</v>
       </c>
-      <c r="Q26" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P26,CaseType!$A:$A,0))</f>
+      <c r="S26" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R26,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R26" s="6" t="b">
-        <f>AND(IF($X26="",TRUE,$P26=INDEX(CaseTypeCol!$B:$B,MATCH($X26,CaseTypeCol!$A:$A,0))),IF($AA26="",TRUE,$P26=INDEX(CaseTypeCol!$B:$B,MATCH($AA26,CaseTypeCol!$A:$A,0))),IF($AD26="",TRUE,$P26=INDEX(CaseTypeCol!$B:$B,MATCH($AD26,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T26" t="s">
+      <c r="T26" s="6" t="b">
+        <f>AND(IF($Z26="",TRUE,$R26=INDEX(CaseTypeCol!$B:$B,MATCH($Z26,CaseTypeCol!$A:$A,0))),IF($AG26="",TRUE,$R26=INDEX(CaseTypeCol!$B:$B,MATCH($AG26,CaseTypeCol!$A:$A,0))),IF($AN26="",TRUE,$R26=INDEX(CaseTypeCol!$B:$B,MATCH($AN26,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V26" t="s">
         <v>12</v>
       </c>
-      <c r="U26" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T26,DataCollection!$A:$A,0))</f>
+      <c r="W26" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V26,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W26" s="14">
+      <c r="Y26" s="14">
         <v>36526</v>
       </c>
-      <c r="X26" t="s">
+      <c r="Z26" t="s">
         <v>357</v>
       </c>
-      <c r="Y26" s="6" t="str">
-        <f>IF($X26="","",INDEX(CaseTypeCol!$G:$G,MATCH($X26,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA26" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB26" s="6" t="str">
+        <f>IF($Z26="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z26,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z26" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA26" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB26" s="6" t="str">
-        <f>IF($AA26="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA26,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC26" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD26" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE26" s="6" t="str">
-        <f>IF($AD26="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD26,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC26" ca="1">IF($Z26="",TRUE,IF($I26="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I26)&amp;"|"&amp;$Z26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD26" ca="1">IF($Z26="",TRUE,IF($I26="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I26)&amp;"|"&amp;$Z26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE26" ca="1">IF($Z26="",TRUE,IF($M26="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M26)&amp;"|"&amp;$Z26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF26" ca="1">IF($Z26="",TRUE,IF($M26="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M26)&amp;"|"&amp;$Z26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI26" s="6" t="str">
+        <f>IF($AG26="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG26,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ26" ca="1">IF($AG26="",TRUE,IF($I26="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I26)&amp;"|"&amp;$AG26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK26" ca="1">IF($AG26="",TRUE,IF($I26="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I26)&amp;"|"&amp;$AG26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL26" ca="1">IF($AG26="",TRUE,IF($M26="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M26)&amp;"|"&amp;$AG26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM26" ca="1">IF($AG26="",TRUE,IF($M26="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M26)&amp;"|"&amp;$AG26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP26" s="6" t="str">
+        <f>IF($AN26="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN26,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ26" ca="1">IF($AN26="",TRUE,IF($I26="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I26)&amp;"|"&amp;$AN26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR26" ca="1">IF($AN26="",TRUE,IF($I26="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I26)&amp;"|"&amp;$AN26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS26" ca="1">IF($AN26="",TRUE,IF($M26="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M26)&amp;"|"&amp;$AN26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT26" ca="1">IF($AN26="",TRUE,IF($M26="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M26)&amp;"|"&amp;$AN26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>887</v>
+        <v>880</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="D27" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C27,User!$A:$A,0))</f>
-        <v>org_user5_2</v>
-      </c>
-      <c r="E27" s="6" t="str">
+        <v>org_user4_2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>964</v>
+      </c>
+      <c r="F27" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C27,User!$A:$A,0))</f>
-        <v>0195d18c-1c93-02a2-6920-7e4dbfb73ce0</v>
-      </c>
-      <c r="F27" t="s">
-        <v>918</v>
-      </c>
-      <c r="G27" s="6" t="b">
+        <v>0195d18c-1c92-d419-4c71-a570f428499b</v>
+      </c>
+      <c r="H27" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C27,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H27" s="6" t="str">
-        <f>IF(ISNA(MATCH($E27&amp;"|"&amp;$T27,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E27&amp;"|"&amp;$T27,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I27" s="6" t="str">
+        <f>IF(ISNA(MATCH($G27&amp;"|"&amp;$V27,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G27&amp;"|"&amp;$V27,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="I27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I27" ca="1">IF($H27="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H27),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H27)&amp;"|"&amp;$P27,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
       <c r="J27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J27" ca="1">IF($H27="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H27),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H27)&amp;"|"&amp;$P27,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K27" s="6" t="str">
-        <f>IF(ISNA(MATCH($C27&amp;"|"&amp;$T27,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C27&amp;"|"&amp;$T27,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="J27" ca="1">IF($I27="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I27)&amp;"|"&amp;$R27,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K27" ca="1">IF($I27="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I27),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I27)&amp;"|"&amp;$R27,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L27" ca="1">IF($I27="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I27),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I27)&amp;"|"&amp;$R27,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="6" t="str">
+        <f>IF(ISNA(MATCH($C27&amp;"|"&amp;$V27,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C27&amp;"|"&amp;$V27,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L27" ca="1">IF($K27="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K27),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K27)&amp;"|"&amp;$P27,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M27" ca="1">IF($K27="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K27),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K27)&amp;"|"&amp;$P27,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N27" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O27" t="s">
-        <v>913</v>
-      </c>
-      <c r="P27" t="s">
+      <c r="N27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N27" ca="1">IF($M27="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M27)&amp;"|"&amp;$R27,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O27" ca="1">IF($M27="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M27),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M27)&amp;"|"&amp;$R27,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P27" ca="1">IF($M27="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M27),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M27)&amp;"|"&amp;$R27,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>906</v>
+      </c>
+      <c r="R27" t="s">
         <v>334</v>
       </c>
-      <c r="Q27" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P27,CaseType!$A:$A,0))</f>
+      <c r="S27" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R27,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R27" s="6" t="b">
-        <f>AND(IF($X27="",TRUE,$P27=INDEX(CaseTypeCol!$B:$B,MATCH($X27,CaseTypeCol!$A:$A,0))),IF($AA27="",TRUE,$P27=INDEX(CaseTypeCol!$B:$B,MATCH($AA27,CaseTypeCol!$A:$A,0))),IF($AD27="",TRUE,$P27=INDEX(CaseTypeCol!$B:$B,MATCH($AD27,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T27" t="s">
+      <c r="T27" s="6" t="b">
+        <f>AND(IF($Z27="",TRUE,$R27=INDEX(CaseTypeCol!$B:$B,MATCH($Z27,CaseTypeCol!$A:$A,0))),IF($AG27="",TRUE,$R27=INDEX(CaseTypeCol!$B:$B,MATCH($AG27,CaseTypeCol!$A:$A,0))),IF($AN27="",TRUE,$R27=INDEX(CaseTypeCol!$B:$B,MATCH($AN27,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V27" t="s">
         <v>12</v>
       </c>
-      <c r="U27" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T27,DataCollection!$A:$A,0))</f>
+      <c r="W27" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V27,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W27" s="14">
+      <c r="Y27" s="14">
         <v>36526</v>
       </c>
-      <c r="X27" t="s">
+      <c r="Z27" t="s">
         <v>357</v>
       </c>
-      <c r="Y27" s="6" t="str">
-        <f>IF($X27="","",INDEX(CaseTypeCol!$G:$G,MATCH($X27,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA27" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB27" s="6" t="str">
+        <f>IF($Z27="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z27,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z27" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA27" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB27" s="6" t="str">
-        <f>IF($AA27="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA27,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC27" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD27" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE27" s="6" t="str">
-        <f>IF($AD27="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD27,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC27" ca="1">IF($Z27="",TRUE,IF($I27="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I27)&amp;"|"&amp;$Z27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD27" ca="1">IF($Z27="",TRUE,IF($I27="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I27)&amp;"|"&amp;$Z27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE27" ca="1">IF($Z27="",TRUE,IF($M27="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M27)&amp;"|"&amp;$Z27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF27" ca="1">IF($Z27="",TRUE,IF($M27="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M27)&amp;"|"&amp;$Z27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI27" s="6" t="str">
+        <f>IF($AG27="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG27,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ27" ca="1">IF($AG27="",TRUE,IF($I27="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I27)&amp;"|"&amp;$AG27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK27" ca="1">IF($AG27="",TRUE,IF($I27="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I27)&amp;"|"&amp;$AG27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL27" ca="1">IF($AG27="",TRUE,IF($M27="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M27)&amp;"|"&amp;$AG27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM27" ca="1">IF($AG27="",TRUE,IF($M27="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M27)&amp;"|"&amp;$AG27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP27" s="6" t="str">
+        <f>IF($AN27="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN27,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ27" ca="1">IF($AN27="",TRUE,IF($I27="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I27)&amp;"|"&amp;$AN27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR27" ca="1">IF($AN27="",TRUE,IF($I27="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I27)&amp;"|"&amp;$AN27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS27" ca="1">IF($AN27="",TRUE,IF($M27="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M27)&amp;"|"&amp;$AN27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT27" ca="1">IF($AN27="",TRUE,IF($M27="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M27)&amp;"|"&amp;$AN27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="D28" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C28,User!$A:$A,0))</f>
-        <v>org_user5_3</v>
-      </c>
-      <c r="E28" s="6" t="str">
+        <v>org_user4_3</v>
+      </c>
+      <c r="E28" t="s">
+        <v>964</v>
+      </c>
+      <c r="F28" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="6" t="str">
         <f>INDEX(User!$F:$F,MATCH($C28,User!$A:$A,0))</f>
-        <v>0195d18c-1c93-02a2-6920-7e4dbfb73ce0</v>
-      </c>
-      <c r="F28" t="s">
-        <v>918</v>
-      </c>
-      <c r="G28" s="6" t="b">
+        <v>0195d18c-1c92-d419-4c71-a570f428499b</v>
+      </c>
+      <c r="H28" s="6" t="b">
         <f>INDEX(User!$L:$L,MATCH($C28,User!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="H28" s="6" t="str">
-        <f>IF(ISNA(MATCH($E28&amp;"|"&amp;$T28,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E28&amp;"|"&amp;$T28,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I28" s="6" t="str">
+        <f>IF(ISNA(MATCH($G28&amp;"|"&amp;$V28,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G28&amp;"|"&amp;$V28,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="I28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I28" ca="1">IF($H28="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H28),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H28)&amp;"|"&amp;$P28,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
       <c r="J28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J28" ca="1">IF($H28="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H28),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H28)&amp;"|"&amp;$P28,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="6" t="str">
-        <f>IF(ISNA(MATCH($C28&amp;"|"&amp;$T28,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C28&amp;"|"&amp;$T28,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="J28" ca="1">IF($I28="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I28)&amp;"|"&amp;$R28,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K28" ca="1">IF($I28="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I28),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I28)&amp;"|"&amp;$R28,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L28" ca="1">IF($I28="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I28),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I28)&amp;"|"&amp;$R28,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="6" t="str">
+        <f>IF(ISNA(MATCH($C28&amp;"|"&amp;$V28,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C28&amp;"|"&amp;$V28,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L28" ca="1">IF($K28="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K28),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K28)&amp;"|"&amp;$P28,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M28" ca="1">IF($K28="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K28),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K28)&amp;"|"&amp;$P28,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N28" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O28" t="s">
-        <v>914</v>
-      </c>
-      <c r="P28" t="s">
+      <c r="N28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N28" ca="1">IF($M28="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M28)&amp;"|"&amp;$R28,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O28" ca="1">IF($M28="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M28),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M28)&amp;"|"&amp;$R28,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P28" ca="1">IF($M28="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M28),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M28)&amp;"|"&amp;$R28,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>907</v>
+      </c>
+      <c r="R28" t="s">
         <v>334</v>
       </c>
-      <c r="Q28" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P28,CaseType!$A:$A,0))</f>
+      <c r="S28" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R28,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R28" s="6" t="b">
-        <f>AND(IF($X28="",TRUE,$P28=INDEX(CaseTypeCol!$B:$B,MATCH($X28,CaseTypeCol!$A:$A,0))),IF($AA28="",TRUE,$P28=INDEX(CaseTypeCol!$B:$B,MATCH($AA28,CaseTypeCol!$A:$A,0))),IF($AD28="",TRUE,$P28=INDEX(CaseTypeCol!$B:$B,MATCH($AD28,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T28" t="s">
+      <c r="T28" s="6" t="b">
+        <f>AND(IF($Z28="",TRUE,$R28=INDEX(CaseTypeCol!$B:$B,MATCH($Z28,CaseTypeCol!$A:$A,0))),IF($AG28="",TRUE,$R28=INDEX(CaseTypeCol!$B:$B,MATCH($AG28,CaseTypeCol!$A:$A,0))),IF($AN28="",TRUE,$R28=INDEX(CaseTypeCol!$B:$B,MATCH($AN28,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V28" t="s">
         <v>12</v>
       </c>
-      <c r="U28" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T28,DataCollection!$A:$A,0))</f>
+      <c r="W28" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V28,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W28" s="14">
+      <c r="Y28" s="14">
         <v>36526</v>
       </c>
-      <c r="X28" t="s">
+      <c r="Z28" t="s">
         <v>357</v>
       </c>
-      <c r="Y28" s="6" t="str">
-        <f>IF($X28="","",INDEX(CaseTypeCol!$G:$G,MATCH($X28,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA28" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB28" s="6" t="str">
+        <f>IF($Z28="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z28,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z28" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA28" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB28" s="6" t="str">
-        <f>IF($AA28="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA28,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC28" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE28" s="6" t="str">
-        <f>IF($AD28="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD28,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="AC28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC28" ca="1">IF($Z28="",TRUE,IF($I28="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I28)&amp;"|"&amp;$Z28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD28" ca="1">IF($Z28="",TRUE,IF($I28="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I28)&amp;"|"&amp;$Z28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE28" ca="1">IF($Z28="",TRUE,IF($M28="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M28)&amp;"|"&amp;$Z28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF28" ca="1">IF($Z28="",TRUE,IF($M28="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M28)&amp;"|"&amp;$Z28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI28" s="6" t="str">
+        <f>IF($AG28="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG28,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ28" ca="1">IF($AG28="",TRUE,IF($I28="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I28)&amp;"|"&amp;$AG28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK28" ca="1">IF($AG28="",TRUE,IF($I28="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I28)&amp;"|"&amp;$AG28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL28" ca="1">IF($AG28="",TRUE,IF($M28="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M28)&amp;"|"&amp;$AG28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM28" ca="1">IF($AG28="",TRUE,IF($M28="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M28)&amp;"|"&amp;$AG28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP28" s="6" t="str">
+        <f>IF($AN28="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN28,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ28" ca="1">IF($AN28="",TRUE,IF($I28="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I28)&amp;"|"&amp;$AN28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR28" ca="1">IF($AN28="",TRUE,IF($I28="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I28)&amp;"|"&amp;$AN28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS28" ca="1">IF($AN28="",TRUE,IF($M28="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M28)&amp;"|"&amp;$AN28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT28" ca="1">IF($AN28="",TRUE,IF($M28="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M28)&amp;"|"&amp;$AN28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="C29" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D29" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C29,User!$A:$A,0))</f>
+        <v>org_user4_4</v>
+      </c>
+      <c r="E29" t="s">
+        <v>964</v>
+      </c>
+      <c r="F29" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($C29,User!$A:$A,0))</f>
+        <v>0195d18c-1c92-d419-4c71-a570f428499b</v>
+      </c>
+      <c r="H29" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($C29,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="6" t="str">
+        <f>IF(ISNA(MATCH($G29&amp;"|"&amp;$V29,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G29&amp;"|"&amp;$V29,OrganizationAccessCasePolicy!$V:$V,0))</f>
+        <v/>
+      </c>
+      <c r="J29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="J29" ca="1">IF($I29="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I29)&amp;"|"&amp;$R29,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K29" ca="1">IF($I29="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I29),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I29)&amp;"|"&amp;$R29,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L29" ca="1">IF($I29="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I29),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I29)&amp;"|"&amp;$R29,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="6" t="str">
+        <f>IF(ISNA(MATCH($C29&amp;"|"&amp;$V29,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C29&amp;"|"&amp;$V29,UserAccessCasePolicy!$W:$W,0))</f>
+        <v/>
+      </c>
+      <c r="N29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N29" ca="1">IF($M29="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M29)&amp;"|"&amp;$R29,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O29" ca="1">IF($M29="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M29),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M29)&amp;"|"&amp;$R29,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P29" ca="1">IF($M29="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M29),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M29)&amp;"|"&amp;$R29,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>908</v>
+      </c>
+      <c r="R29" t="s">
+        <v>334</v>
+      </c>
+      <c r="S29" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R29,CaseType!$A:$A,0))</f>
+        <v>case_type1</v>
+      </c>
+      <c r="T29" s="6" t="b">
+        <f>AND(IF($Z29="",TRUE,$R29=INDEX(CaseTypeCol!$B:$B,MATCH($Z29,CaseTypeCol!$A:$A,0))),IF($AG29="",TRUE,$R29=INDEX(CaseTypeCol!$B:$B,MATCH($AG29,CaseTypeCol!$A:$A,0))),IF($AN29="",TRUE,$R29=INDEX(CaseTypeCol!$B:$B,MATCH($AN29,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V29" t="s">
+        <v>12</v>
+      </c>
+      <c r="W29" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V29,DataCollection!$A:$A,0))</f>
+        <v>data_collection1</v>
+      </c>
+      <c r="Y29" s="14">
+        <v>36526</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>357</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB29" s="6" t="str">
+        <f>IF($Z29="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z29,CaseTypeCol!$A:$A,0)))</f>
+        <v>case_type1_dim1_1_text</v>
+      </c>
+      <c r="AC29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC29" ca="1">IF($Z29="",TRUE,IF($I29="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I29)&amp;"|"&amp;$Z29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD29" ca="1">IF($Z29="",TRUE,IF($I29="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I29)&amp;"|"&amp;$Z29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE29" ca="1">IF($Z29="",TRUE,IF($M29="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M29)&amp;"|"&amp;$Z29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF29" ca="1">IF($Z29="",TRUE,IF($M29="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M29)&amp;"|"&amp;$Z29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI29" s="6" t="str">
+        <f>IF($AG29="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG29,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ29" ca="1">IF($AG29="",TRUE,IF($I29="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I29)&amp;"|"&amp;$AG29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK29" ca="1">IF($AG29="",TRUE,IF($I29="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I29)&amp;"|"&amp;$AG29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL29" ca="1">IF($AG29="",TRUE,IF($M29="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M29)&amp;"|"&amp;$AG29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM29" ca="1">IF($AG29="",TRUE,IF($M29="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M29)&amp;"|"&amp;$AG29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP29" s="6" t="str">
+        <f>IF($AN29="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN29,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ29" ca="1">IF($AN29="",TRUE,IF($I29="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I29)&amp;"|"&amp;$AN29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR29" ca="1">IF($AN29="",TRUE,IF($I29="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I29)&amp;"|"&amp;$AN29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS29" ca="1">IF($AN29="",TRUE,IF($M29="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M29)&amp;"|"&amp;$AN29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT29" ca="1">IF($AN29="",TRUE,IF($M29="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M29)&amp;"|"&amp;$AN29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:46" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>883</v>
+      </c>
+      <c r="C30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($C30,User!$A:$A,0))</f>
+        <v>org_user5_1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>964</v>
+      </c>
+      <c r="F30" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($C30,User!$A:$A,0))</f>
+        <v>0195d18c-1c93-02a2-6920-7e4dbfb73ce0</v>
+      </c>
+      <c r="H30" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($C30,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="6" t="str">
+        <f>IF(ISNA(MATCH($G30&amp;"|"&amp;$V30,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G30&amp;"|"&amp;$V30,OrganizationAccessCasePolicy!$V:$V,0))</f>
+        <v/>
+      </c>
+      <c r="J30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="J30" ca="1">IF($I30="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I30)&amp;"|"&amp;$R30,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K30" ca="1">IF($I30="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I30),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I30)&amp;"|"&amp;$R30,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L30" ca="1">IF($I30="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I30),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I30)&amp;"|"&amp;$R30,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="6" t="str">
+        <f>IF(ISNA(MATCH($C30&amp;"|"&amp;$V30,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C30&amp;"|"&amp;$V30,UserAccessCasePolicy!$W:$W,0))</f>
+        <v/>
+      </c>
+      <c r="N30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N30" ca="1">IF($M30="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M30)&amp;"|"&amp;$R30,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O30" ca="1">IF($M30="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M30),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M30)&amp;"|"&amp;$R30,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P30" ca="1">IF($M30="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M30),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M30)&amp;"|"&amp;$R30,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>909</v>
+      </c>
+      <c r="R30" t="s">
+        <v>334</v>
+      </c>
+      <c r="S30" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R30,CaseType!$A:$A,0))</f>
+        <v>case_type1</v>
+      </c>
+      <c r="T30" s="6" t="b">
+        <f>AND(IF($Z30="",TRUE,$R30=INDEX(CaseTypeCol!$B:$B,MATCH($Z30,CaseTypeCol!$A:$A,0))),IF($AG30="",TRUE,$R30=INDEX(CaseTypeCol!$B:$B,MATCH($AG30,CaseTypeCol!$A:$A,0))),IF($AN30="",TRUE,$R30=INDEX(CaseTypeCol!$B:$B,MATCH($AN30,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V30" t="s">
+        <v>12</v>
+      </c>
+      <c r="W30" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V30,DataCollection!$A:$A,0))</f>
+        <v>data_collection1</v>
+      </c>
+      <c r="Y30" s="14">
+        <v>36526</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>357</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB30" s="6" t="str">
+        <f>IF($Z30="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z30,CaseTypeCol!$A:$A,0)))</f>
+        <v>case_type1_dim1_1_text</v>
+      </c>
+      <c r="AC30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC30" ca="1">IF($Z30="",TRUE,IF($I30="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I30)&amp;"|"&amp;$Z30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD30" ca="1">IF($Z30="",TRUE,IF($I30="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I30)&amp;"|"&amp;$Z30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE30" ca="1">IF($Z30="",TRUE,IF($M30="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M30)&amp;"|"&amp;$Z30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF30" ca="1">IF($Z30="",TRUE,IF($M30="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M30)&amp;"|"&amp;$Z30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI30" s="6" t="str">
+        <f>IF($AG30="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG30,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ30" ca="1">IF($AG30="",TRUE,IF($I30="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I30)&amp;"|"&amp;$AG30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK30" ca="1">IF($AG30="",TRUE,IF($I30="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I30)&amp;"|"&amp;$AG30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL30" ca="1">IF($AG30="",TRUE,IF($M30="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M30)&amp;"|"&amp;$AG30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM30" ca="1">IF($AG30="",TRUE,IF($M30="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M30)&amp;"|"&amp;$AG30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP30" s="6" t="str">
+        <f>IF($AN30="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN30,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ30" ca="1">IF($AN30="",TRUE,IF($I30="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I30)&amp;"|"&amp;$AN30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR30" ca="1">IF($AN30="",TRUE,IF($I30="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I30)&amp;"|"&amp;$AN30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS30" ca="1">IF($AN30="",TRUE,IF($M30="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M30)&amp;"|"&amp;$AN30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT30" ca="1">IF($AN30="",TRUE,IF($M30="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M30)&amp;"|"&amp;$AN30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:46" x14ac:dyDescent="0.4">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>884</v>
+      </c>
+      <c r="C31" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($C31,User!$A:$A,0))</f>
+        <v>org_user5_2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>964</v>
+      </c>
+      <c r="F31" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($C31,User!$A:$A,0))</f>
+        <v>0195d18c-1c93-02a2-6920-7e4dbfb73ce0</v>
+      </c>
+      <c r="H31" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($C31,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="6" t="str">
+        <f>IF(ISNA(MATCH($G31&amp;"|"&amp;$V31,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G31&amp;"|"&amp;$V31,OrganizationAccessCasePolicy!$V:$V,0))</f>
+        <v/>
+      </c>
+      <c r="J31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="J31" ca="1">IF($I31="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I31)&amp;"|"&amp;$R31,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K31" ca="1">IF($I31="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I31),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I31)&amp;"|"&amp;$R31,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L31" ca="1">IF($I31="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I31),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I31)&amp;"|"&amp;$R31,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="6" t="str">
+        <f>IF(ISNA(MATCH($C31&amp;"|"&amp;$V31,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C31&amp;"|"&amp;$V31,UserAccessCasePolicy!$W:$W,0))</f>
+        <v/>
+      </c>
+      <c r="N31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N31" ca="1">IF($M31="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M31)&amp;"|"&amp;$R31,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O31" ca="1">IF($M31="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M31),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M31)&amp;"|"&amp;$R31,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P31" ca="1">IF($M31="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M31),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M31)&amp;"|"&amp;$R31,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>910</v>
+      </c>
+      <c r="R31" t="s">
+        <v>334</v>
+      </c>
+      <c r="S31" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R31,CaseType!$A:$A,0))</f>
+        <v>case_type1</v>
+      </c>
+      <c r="T31" s="6" t="b">
+        <f>AND(IF($Z31="",TRUE,$R31=INDEX(CaseTypeCol!$B:$B,MATCH($Z31,CaseTypeCol!$A:$A,0))),IF($AG31="",TRUE,$R31=INDEX(CaseTypeCol!$B:$B,MATCH($AG31,CaseTypeCol!$A:$A,0))),IF($AN31="",TRUE,$R31=INDEX(CaseTypeCol!$B:$B,MATCH($AN31,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V31" t="s">
+        <v>12</v>
+      </c>
+      <c r="W31" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V31,DataCollection!$A:$A,0))</f>
+        <v>data_collection1</v>
+      </c>
+      <c r="Y31" s="14">
+        <v>36526</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>357</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB31" s="6" t="str">
+        <f>IF($Z31="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z31,CaseTypeCol!$A:$A,0)))</f>
+        <v>case_type1_dim1_1_text</v>
+      </c>
+      <c r="AC31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC31" ca="1">IF($Z31="",TRUE,IF($I31="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I31)&amp;"|"&amp;$Z31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD31" ca="1">IF($Z31="",TRUE,IF($I31="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I31)&amp;"|"&amp;$Z31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE31" ca="1">IF($Z31="",TRUE,IF($M31="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M31)&amp;"|"&amp;$Z31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF31" ca="1">IF($Z31="",TRUE,IF($M31="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M31)&amp;"|"&amp;$Z31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI31" s="6" t="str">
+        <f>IF($AG31="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG31,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ31" ca="1">IF($AG31="",TRUE,IF($I31="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I31)&amp;"|"&amp;$AG31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK31" ca="1">IF($AG31="",TRUE,IF($I31="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I31)&amp;"|"&amp;$AG31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL31" ca="1">IF($AG31="",TRUE,IF($M31="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M31)&amp;"|"&amp;$AG31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM31" ca="1">IF($AG31="",TRUE,IF($M31="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M31)&amp;"|"&amp;$AG31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP31" s="6" t="str">
+        <f>IF($AN31="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN31,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ31" ca="1">IF($AN31="",TRUE,IF($I31="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I31)&amp;"|"&amp;$AN31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR31" ca="1">IF($AN31="",TRUE,IF($I31="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I31)&amp;"|"&amp;$AN31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS31" ca="1">IF($AN31="",TRUE,IF($M31="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M31)&amp;"|"&amp;$AN31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT31" ca="1">IF($AN31="",TRUE,IF($M31="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M31)&amp;"|"&amp;$AN31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:46" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>885</v>
+      </c>
+      <c r="C32" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($C32,User!$A:$A,0))</f>
+        <v>org_user5_3</v>
+      </c>
+      <c r="E32" t="s">
+        <v>964</v>
+      </c>
+      <c r="F32" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($C32,User!$A:$A,0))</f>
+        <v>0195d18c-1c93-02a2-6920-7e4dbfb73ce0</v>
+      </c>
+      <c r="H32" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($C32,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="6" t="str">
+        <f>IF(ISNA(MATCH($G32&amp;"|"&amp;$V32,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G32&amp;"|"&amp;$V32,OrganizationAccessCasePolicy!$V:$V,0))</f>
+        <v/>
+      </c>
+      <c r="J32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="J32" ca="1">IF($I32="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I32)&amp;"|"&amp;$R32,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K32" ca="1">IF($I32="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I32),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I32)&amp;"|"&amp;$R32,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L32" ca="1">IF($I32="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I32),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I32)&amp;"|"&amp;$R32,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="6" t="str">
+        <f>IF(ISNA(MATCH($C32&amp;"|"&amp;$V32,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C32&amp;"|"&amp;$V32,UserAccessCasePolicy!$W:$W,0))</f>
+        <v/>
+      </c>
+      <c r="N32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N32" ca="1">IF($M32="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M32)&amp;"|"&amp;$R32,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O32" ca="1">IF($M32="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M32),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M32)&amp;"|"&amp;$R32,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P32" ca="1">IF($M32="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M32),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M32)&amp;"|"&amp;$R32,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>911</v>
+      </c>
+      <c r="R32" t="s">
+        <v>334</v>
+      </c>
+      <c r="S32" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R32,CaseType!$A:$A,0))</f>
+        <v>case_type1</v>
+      </c>
+      <c r="T32" s="6" t="b">
+        <f>AND(IF($Z32="",TRUE,$R32=INDEX(CaseTypeCol!$B:$B,MATCH($Z32,CaseTypeCol!$A:$A,0))),IF($AG32="",TRUE,$R32=INDEX(CaseTypeCol!$B:$B,MATCH($AG32,CaseTypeCol!$A:$A,0))),IF($AN32="",TRUE,$R32=INDEX(CaseTypeCol!$B:$B,MATCH($AN32,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V32" t="s">
+        <v>12</v>
+      </c>
+      <c r="W32" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V32,DataCollection!$A:$A,0))</f>
+        <v>data_collection1</v>
+      </c>
+      <c r="Y32" s="14">
+        <v>36526</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>357</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB32" s="6" t="str">
+        <f>IF($Z32="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z32,CaseTypeCol!$A:$A,0)))</f>
+        <v>case_type1_dim1_1_text</v>
+      </c>
+      <c r="AC32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC32" ca="1">IF($Z32="",TRUE,IF($I32="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I32)&amp;"|"&amp;$Z32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD32" ca="1">IF($Z32="",TRUE,IF($I32="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I32)&amp;"|"&amp;$Z32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE32" ca="1">IF($Z32="",TRUE,IF($M32="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M32)&amp;"|"&amp;$Z32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF32" ca="1">IF($Z32="",TRUE,IF($M32="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M32)&amp;"|"&amp;$Z32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI32" s="6" t="str">
+        <f>IF($AG32="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG32,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ32" ca="1">IF($AG32="",TRUE,IF($I32="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I32)&amp;"|"&amp;$AG32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK32" ca="1">IF($AG32="",TRUE,IF($I32="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I32)&amp;"|"&amp;$AG32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL32" ca="1">IF($AG32="",TRUE,IF($M32="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M32)&amp;"|"&amp;$AG32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM32" ca="1">IF($AG32="",TRUE,IF($M32="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M32)&amp;"|"&amp;$AG32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP32" s="6" t="str">
+        <f>IF($AN32="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN32,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ32" ca="1">IF($AN32="",TRUE,IF($I32="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I32)&amp;"|"&amp;$AN32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR32" ca="1">IF($AN32="",TRUE,IF($I32="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I32)&amp;"|"&amp;$AN32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS32" ca="1">IF($AN32="",TRUE,IF($M32="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M32)&amp;"|"&amp;$AN32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT32" ca="1">IF($AN32="",TRUE,IF($M32="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M32)&amp;"|"&amp;$AN32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:46" x14ac:dyDescent="0.4">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>886</v>
+      </c>
+      <c r="C33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($C33,User!$A:$A,0))</f>
         <v>org_user5_4</v>
       </c>
-      <c r="E29" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C29,User!$A:$A,0))</f>
+      <c r="E33" t="s">
+        <v>964</v>
+      </c>
+      <c r="F33" s="19" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($C33,User!$A:$A,0))</f>
         <v>0195d18c-1c93-02a2-6920-7e4dbfb73ce0</v>
       </c>
-      <c r="F29" t="s">
-        <v>918</v>
-      </c>
-      <c r="G29" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C29,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="6" t="str">
-        <f>IF(ISNA(MATCH($E29&amp;"|"&amp;$T29,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($E29&amp;"|"&amp;$T29,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="H33" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($C33,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="6" t="str">
+        <f>IF(ISNA(MATCH($G33&amp;"|"&amp;$V33,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G33&amp;"|"&amp;$V33,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="I29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="I29" ca="1">IF($H29="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$H29),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H29)&amp;"|"&amp;$P29,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J29" ca="1">IF($H29="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$H29),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$H29)&amp;"|"&amp;$P29,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="K29" s="6" t="str">
-        <f>IF(ISNA(MATCH($C29&amp;"|"&amp;$T29,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C29&amp;"|"&amp;$T29,UserAccessCasePolicy!$W:$W,0))</f>
+      <c r="J33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="J33" ca="1">IF($I33="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I33)&amp;"|"&amp;$R33,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="K33" ca="1">IF($I33="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I33),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I33)&amp;"|"&amp;$R33,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="L33" ca="1">IF($I33="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I33),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I33)&amp;"|"&amp;$R33,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="6" t="str">
+        <f>IF(ISNA(MATCH($C33&amp;"|"&amp;$V33,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C33&amp;"|"&amp;$V33,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="L29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L29" ca="1">IF($K29="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$K29),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K29)&amp;"|"&amp;$P29,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="M29" ca="1">IF($K29="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$K29),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$K29)&amp;"|"&amp;$P29,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="N29" s="6" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O29" t="s">
-        <v>915</v>
-      </c>
-      <c r="P29" t="s">
+      <c r="N33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="N33" ca="1">IF($M33="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M33)&amp;"|"&amp;$R33,CaseTypeSetMember!$H:$H,0))))</f>
+        <v>0</v>
+      </c>
+      <c r="O33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="O33" ca="1">IF($M33="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M33),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M33)&amp;"|"&amp;$R33,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="P33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="P33" ca="1">IF($M33="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M33),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M33)&amp;"|"&amp;$R33,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>912</v>
+      </c>
+      <c r="R33" t="s">
         <v>334</v>
       </c>
-      <c r="Q29" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($P29,CaseType!$A:$A,0))</f>
+      <c r="S33" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($R33,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="R29" s="6" t="b">
-        <f>AND(IF($X29="",TRUE,$P29=INDEX(CaseTypeCol!$B:$B,MATCH($X29,CaseTypeCol!$A:$A,0))),IF($AA29="",TRUE,$P29=INDEX(CaseTypeCol!$B:$B,MATCH($AA29,CaseTypeCol!$A:$A,0))),IF($AD29="",TRUE,$P29=INDEX(CaseTypeCol!$B:$B,MATCH($AD29,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="T29" t="s">
+      <c r="T33" s="6" t="b">
+        <f>AND(IF($Z33="",TRUE,$R33=INDEX(CaseTypeCol!$B:$B,MATCH($Z33,CaseTypeCol!$A:$A,0))),IF($AG33="",TRUE,$R33=INDEX(CaseTypeCol!$B:$B,MATCH($AG33,CaseTypeCol!$A:$A,0))),IF($AN33="",TRUE,$R33=INDEX(CaseTypeCol!$B:$B,MATCH($AN33,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="V33" t="s">
         <v>12</v>
       </c>
-      <c r="U29" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($T29,DataCollection!$A:$A,0))</f>
+      <c r="W33" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($V33,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="W29" s="14">
+      <c r="Y33" s="14">
         <v>36526</v>
       </c>
-      <c r="X29" t="s">
+      <c r="Z33" t="s">
         <v>357</v>
       </c>
-      <c r="Y29" s="6" t="str">
-        <f>IF($X29="","",INDEX(CaseTypeCol!$G:$G,MATCH($X29,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AA33" t="s">
+        <v>917</v>
+      </c>
+      <c r="AB33" s="6" t="str">
+        <f>IF($Z33="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z33,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="Z29" t="s">
-        <v>921</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB29" s="6" t="str">
-        <f>IF($AA29="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA29,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim2_1_text</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>922</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE29" s="6" t="str">
-        <f>IF($AD29="","",INDEX(CaseTypeCol!$G:$G,MATCH($AD29,CaseTypeCol!$A:$A,0)))</f>
-        <v>case_type1_dim3_1_text</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>923</v>
+      <c r="AC33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AC33" ca="1">IF($Z33="",TRUE,IF($I33="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I33)&amp;"|"&amp;$Z33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AD33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AD33" ca="1">IF($Z33="",TRUE,IF($I33="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I33)&amp;"|"&amp;$Z33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AE33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AE33" ca="1">IF($Z33="",TRUE,IF($M33="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M33)&amp;"|"&amp;$Z33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AF33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AF33" ca="1">IF($Z33="",TRUE,IF($M33="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M33)&amp;"|"&amp;$Z33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AI33" s="6" t="str">
+        <f>IF($AG33="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG33,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AJ33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AJ33" ca="1">IF($AG33="",TRUE,IF($I33="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I33)&amp;"|"&amp;$AG33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AK33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AK33" ca="1">IF($AG33="",TRUE,IF($I33="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I33)&amp;"|"&amp;$AG33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AL33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AL33" ca="1">IF($AG33="",TRUE,IF($M33="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M33)&amp;"|"&amp;$AG33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AM33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AM33" ca="1">IF($AG33="",TRUE,IF($M33="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M33)&amp;"|"&amp;$AG33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AP33" s="6" t="str">
+        <f>IF($AN33="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN33,CaseTypeCol!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="AQ33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AQ33" ca="1">IF($AN33="",TRUE,IF($I33="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I33)&amp;"|"&amp;$AN33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AR33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AR33" ca="1">IF($AN33="",TRUE,IF($I33="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I33)&amp;"|"&amp;$AN33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AS33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AS33" ca="1">IF($AN33="",TRUE,IF($M33="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M33)&amp;"|"&amp;$AN33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AT33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AT33" ca="1">IF($AN33="",TRUE,IF($M33="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M33)&amp;"|"&amp;$AN33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AU33" xr:uid="{8E0C7C33-6768-4AAE-A57E-F80585DED472}"/>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="R2:R29">
+  <conditionalFormatting sqref="T2:T33">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>R2=FALSE</formula>
+      <formula>T2=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F0F389-1562-4A7F-BB5E-AAA96B2F3DDB}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:V11"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
@@ -9891,7 +12279,7 @@
         <v>818</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.4">
@@ -9931,9 +12319,12 @@
         <f>IF($J2="","",INDEX(CaseTypeColSet!$B:$B,MATCH($J2,CaseTypeColSet!$A:$A,0)))</f>
         <v>case_type_col_set1_1_1</v>
       </c>
+      <c r="L2" t="s">
+        <v>108</v>
+      </c>
       <c r="M2" s="4" t="str">
         <f>IF($L2="","",INDEX(CaseTypeColSet!$B:$B,MATCH($L2,CaseTypeColSet!$A:$A,0)))</f>
-        <v/>
+        <v>case_type_col_set1_1_1</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -9967,7 +12358,7 @@
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653|0195d18c-1ca2-a23d-1f64-00271f63199c</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:22" hidden="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -10004,9 +12395,12 @@
         <f>IF($J3="","",INDEX(CaseTypeColSet!$B:$B,MATCH($J3,CaseTypeColSet!$A:$A,0)))</f>
         <v>case_type_col_set2_1_1</v>
       </c>
+      <c r="L3" t="s">
+        <v>112</v>
+      </c>
       <c r="M3" s="4" t="str">
         <f>IF($L3="","",INDEX(CaseTypeColSet!$B:$B,MATCH($L3,CaseTypeColSet!$A:$A,0)))</f>
-        <v/>
+        <v>case_type_col_set2_1_1</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -10040,7 +12434,7 @@
         <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3|0195d18c-1ca2-2a29-96a5-37c6bf87f586</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:22" hidden="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>139</v>
       </c>
@@ -10077,9 +12471,12 @@
         <f>IF($J4="","",INDEX(CaseTypeColSet!$B:$B,MATCH($J4,CaseTypeColSet!$A:$A,0)))</f>
         <v>case_type_col_set3_1_1</v>
       </c>
+      <c r="L4" t="s">
+        <v>116</v>
+      </c>
       <c r="M4" s="4" t="str">
         <f>IF($L4="","",INDEX(CaseTypeColSet!$B:$B,MATCH($L4,CaseTypeColSet!$A:$A,0)))</f>
-        <v/>
+        <v>case_type_col_set3_1_1</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -10113,7 +12510,7 @@
         <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037|0195d18c-1ca2-3a4f-1878-fbe3282c9c76</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:22" hidden="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>151</v>
       </c>
@@ -10150,9 +12547,12 @@
         <f>IF($J5="","",INDEX(CaseTypeColSet!$B:$B,MATCH($J5,CaseTypeColSet!$A:$A,0)))</f>
         <v>case_type_col_set4_1_1</v>
       </c>
+      <c r="L5" t="s">
+        <v>120</v>
+      </c>
       <c r="M5" s="4" t="str">
         <f>IF($L5="","",INDEX(CaseTypeColSet!$B:$B,MATCH($L5,CaseTypeColSet!$A:$A,0)))</f>
-        <v/>
+        <v>case_type_col_set4_1_1</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -10186,7 +12586,7 @@
         <v>0195d18c-1c92-d419-4c71-a570f428499b|0195d18c-1ca2-e55a-608d-a42fc6f948e1</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:22" hidden="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>163</v>
       </c>
@@ -10223,9 +12623,12 @@
         <f>IF($J6="","",INDEX(CaseTypeColSet!$B:$B,MATCH($J6,CaseTypeColSet!$A:$A,0)))</f>
         <v>case_type_col_set5_1_1</v>
       </c>
+      <c r="L6" t="s">
+        <v>124</v>
+      </c>
       <c r="M6" s="4" t="str">
         <f>IF($L6="","",INDEX(CaseTypeColSet!$B:$B,MATCH($L6,CaseTypeColSet!$A:$A,0)))</f>
-        <v/>
+        <v>case_type_col_set5_1_1</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -10332,7 +12735,7 @@
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653|0195d18c-1ca3-f309-f6f1-e4807afe3802</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:22" hidden="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>177</v>
       </c>
@@ -10405,7 +12808,7 @@
         <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3|0195d18c-1ca3-db40-a2a8-6dc905d6c1e9</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:22" hidden="1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>189</v>
       </c>
@@ -10478,7 +12881,7 @@
         <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037|0195d18c-1ca3-da0a-44bb-877b3a1eb73e</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:22" hidden="1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>201</v>
       </c>
@@ -10551,7 +12954,7 @@
         <v>0195d18c-1c92-d419-4c71-a570f428499b|0195d18c-1ca3-4d34-d0e9-8f024ad8651a</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:22" hidden="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>213</v>
       </c>
@@ -10625,13 +13028,20 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U11" xr:uid="{A6F0F389-1562-4A7F-BB5E-AAA96B2F3DDB}"/>
+  <autoFilter ref="A1:U11" xr:uid="{A6F0F389-1562-4A7F-BB5E-AAA96B2F3DDB}">
+    <filterColumn colId="18">
+      <filters>
+        <filter val="org1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{413B6EDF-4214-4325-A1BD-732A42D052EA}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:W11"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
@@ -10726,7 +13136,7 @@
         <v>819</v>
       </c>
       <c r="W1" s="15" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.4">
@@ -10810,7 +13220,7 @@
         <v>0195d18c-1c98-7e0b-0c91-8cafbdb2c852|0195d18c-1ca2-a23d-1f64-00271f63199c</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -10891,7 +13301,7 @@
         <v>0195d18c-1c9a-1178-0519-9124131763a6|0195d18c-1ca2-2a29-96a5-37c6bf87f586</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>139</v>
       </c>
@@ -10972,7 +13382,7 @@
         <v>0195d18c-1c9c-0d8f-435a-5ca8b45939b8|0195d18c-1ca2-3a4f-1878-fbe3282c9c76</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>151</v>
       </c>
@@ -11053,7 +13463,7 @@
         <v>0195d18c-1c9e-1c4a-1311-4f22f0d59f61|0195d18c-1ca2-e55a-608d-a42fc6f948e1</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>163</v>
       </c>
@@ -11215,7 +13625,7 @@
         <v>0195d18c-1c98-7e0b-0c91-8cafbdb2c852|0195d18c-1ca3-f309-f6f1-e4807afe3802</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>177</v>
       </c>
@@ -11296,7 +13706,7 @@
         <v>0195d18c-1c9a-1178-0519-9124131763a6|0195d18c-1ca3-db40-a2a8-6dc905d6c1e9</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>189</v>
       </c>
@@ -11377,7 +13787,7 @@
         <v>0195d18c-1c9c-0d8f-435a-5ca8b45939b8|0195d18c-1ca3-da0a-44bb-877b3a1eb73e</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>201</v>
       </c>
@@ -11458,7 +13868,7 @@
         <v>0195d18c-1c9e-1c4a-1311-4f22f0d59f61|0195d18c-1ca3-4d34-d0e9-8f024ad8651a</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>213</v>
       </c>
@@ -11540,12 +13950,176 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V11" xr:uid="{413B6EDF-4214-4325-A1BD-732A42D052EA}"/>
+  <autoFilter ref="A1:V11" xr:uid="{413B6EDF-4214-4325-A1BD-732A42D052EA}">
+    <filterColumn colId="21">
+      <filters>
+        <filter val="org_user1_1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="36.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.23046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.3046875" style="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>689</v>
+      </c>
+      <c r="C2" s="6" t="str">
+        <f>"dc"&amp;RIGHT($B2,LEN($B2)-15)</f>
+        <v>dc1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>690</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <f t="shared" ref="C3:C12" si="0">"dc"&amp;RIGHT($B3,LEN($B3)-15)</f>
+        <v>dc2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>691</v>
+      </c>
+      <c r="C4" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>dc3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" t="s">
+        <v>692</v>
+      </c>
+      <c r="C5" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>dc4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" t="s">
+        <v>693</v>
+      </c>
+      <c r="C6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>dc5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>694</v>
+      </c>
+      <c r="C7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>dc6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>695</v>
+      </c>
+      <c r="C8" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>dc7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>696</v>
+      </c>
+      <c r="C9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>dc8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>697</v>
+      </c>
+      <c r="C10" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>dc9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" t="s">
+        <v>698</v>
+      </c>
+      <c r="C11" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>dc10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" t="s">
+        <v>699</v>
+      </c>
+      <c r="C12" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>dc11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46B1A0CE-352C-4E69-8986-540397C3CD9D}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -11682,7 +14256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21E03A8B-A0A1-46B6-957F-B8B3E001E975}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -11804,165 +14378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="36.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.23046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.3046875" style="6" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>689</v>
-      </c>
-      <c r="C2" s="6" t="str">
-        <f>"dc"&amp;RIGHT($B2,LEN($B2)-15)</f>
-        <v>dc1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>690</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <f t="shared" ref="C3:C12" si="0">"dc"&amp;RIGHT($B3,LEN($B3)-15)</f>
-        <v>dc2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" t="s">
-        <v>691</v>
-      </c>
-      <c r="C4" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>dc3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" t="s">
-        <v>692</v>
-      </c>
-      <c r="C5" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>dc4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6" t="s">
-        <v>693</v>
-      </c>
-      <c r="C6" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>dc5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>694</v>
-      </c>
-      <c r="C7" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>dc6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>695</v>
-      </c>
-      <c r="C8" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>dc7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" t="s">
-        <v>696</v>
-      </c>
-      <c r="C9" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>dc8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" t="s">
-        <v>697</v>
-      </c>
-      <c r="C10" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>dc9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11" t="s">
-        <v>698</v>
-      </c>
-      <c r="C11" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>dc10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" t="s">
-        <v>699</v>
-      </c>
-      <c r="C12" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>dc11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -12242,7 +14658,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M56"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -14780,7 +17196,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L56"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -17151,7 +19567,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -17948,7 +20364,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:L42"/>
@@ -19697,19 +22113,19 @@
         <v>816</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="L1" s="17" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
@@ -22407,19 +24823,168 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BFE9DBA-4D09-4E45-A394-72AC78245E1D}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="34.765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B2" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B3" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B4" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>348</v>
+      </c>
+      <c r="B5" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>352</v>
+      </c>
+      <c r="B6" t="s">
+        <v>952</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFBF5204-3F7C-438F-A194-7543BC84CF2A}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="35.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.07421875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B2" t="s">
+        <v>954</v>
+      </c>
+      <c r="C2" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B3" t="s">
+        <v>955</v>
+      </c>
+      <c r="C3" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B4" t="s">
+        <v>956</v>
+      </c>
+      <c r="C4" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>349</v>
+      </c>
+      <c r="B5" t="s">
+        <v>957</v>
+      </c>
+      <c r="C5" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>353</v>
+      </c>
+      <c r="B6" t="s">
+        <v>958</v>
+      </c>
+      <c r="C6" t="s">
+        <v>961</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="35.53515625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="10.07421875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34.765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.3046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.07421875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.765625" style="13" customWidth="1"/>
+    <col min="6" max="6" width="6.921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.3046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.3046875" style="13" customWidth="1"/>
+    <col min="9" max="9" width="15.07421875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -22432,17 +24997,23 @@
       <c r="D1" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="12" t="s">
+        <v>959</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="12" t="s">
+        <v>960</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>334</v>
       </c>
@@ -22452,11 +25023,19 @@
       <c r="D2" t="s">
         <v>336</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E2" s="13" t="str">
+        <f>INDEX(Disease!$B:$B,MATCH($D2,Disease!$A:$A,0))</f>
+        <v>disease1</v>
+      </c>
+      <c r="G2" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H2" s="13" t="str">
+        <f>INDEX(EtiologicalAgent!$B:$B,MATCH($G2,EtiologicalAgent!$A:$A,0))</f>
+        <v>etiological_agent1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>338</v>
       </c>
@@ -22466,11 +25045,19 @@
       <c r="D3" t="s">
         <v>340</v>
       </c>
-      <c r="F3" t="s">
+      <c r="E3" s="13" t="str">
+        <f>INDEX(Disease!$B:$B,MATCH($D3,Disease!$A:$A,0))</f>
+        <v>disease2</v>
+      </c>
+      <c r="G3" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H3" s="13" t="str">
+        <f>INDEX(EtiologicalAgent!$B:$B,MATCH($G3,EtiologicalAgent!$A:$A,0))</f>
+        <v>etiological_agent2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>342</v>
       </c>
@@ -22480,11 +25067,19 @@
       <c r="D4" t="s">
         <v>344</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E4" s="13" t="str">
+        <f>INDEX(Disease!$B:$B,MATCH($D4,Disease!$A:$A,0))</f>
+        <v>disease3</v>
+      </c>
+      <c r="G4" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H4" s="13" t="str">
+        <f>INDEX(EtiologicalAgent!$B:$B,MATCH($G4,EtiologicalAgent!$A:$A,0))</f>
+        <v>etiological_agent3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>346</v>
       </c>
@@ -22494,11 +25089,19 @@
       <c r="D5" t="s">
         <v>348</v>
       </c>
-      <c r="F5" t="s">
+      <c r="E5" s="13" t="str">
+        <f>INDEX(Disease!$B:$B,MATCH($D5,Disease!$A:$A,0))</f>
+        <v>disease4</v>
+      </c>
+      <c r="G5" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H5" s="13" t="str">
+        <f>INDEX(EtiologicalAgent!$B:$B,MATCH($G5,EtiologicalAgent!$A:$A,0))</f>
+        <v>etiological_agent4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>350</v>
       </c>
@@ -22508,368 +25111,16 @@
       <c r="D6" t="s">
         <v>352</v>
       </c>
-      <c r="F6" t="s">
+      <c r="E6" s="13" t="str">
+        <f>INDEX(Disease!$B:$B,MATCH($D6,Disease!$A:$A,0))</f>
+        <v>disease5</v>
+      </c>
+      <c r="G6" t="s">
         <v>353</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="34.23046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.07421875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.53515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.84375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>302</v>
-      </c>
-      <c r="B2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="35.84375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.07421875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.07421875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.23046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.61328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.53515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>840</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E2" s="6" t="str">
-        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D2,CaseTypeSetCategory!$A:$A,0))</f>
-        <v>case_type_set_category1</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B3" t="s">
-        <v>303</v>
-      </c>
-      <c r="D3" t="s">
-        <v>302</v>
-      </c>
-      <c r="E3" s="6" t="str">
-        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D3,CaseTypeSetCategory!$A:$A,0))</f>
-        <v>case_type_set_category1</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" t="s">
-        <v>304</v>
-      </c>
-      <c r="D4" t="s">
-        <v>302</v>
-      </c>
-      <c r="E4" s="6" t="str">
-        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D4,CaseTypeSetCategory!$A:$A,0))</f>
-        <v>case_type_set_category1</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B5" t="s">
-        <v>305</v>
-      </c>
-      <c r="D5" t="s">
-        <v>302</v>
-      </c>
-      <c r="E5" s="6" t="str">
-        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D5,CaseTypeSetCategory!$A:$A,0))</f>
-        <v>case_type_set_category1</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B6" t="s">
-        <v>306</v>
-      </c>
-      <c r="D6" t="s">
-        <v>302</v>
-      </c>
-      <c r="E6" s="6" t="str">
-        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D6,CaseTypeSetCategory!$A:$A,0))</f>
-        <v>case_type_set_category1</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>307</v>
-      </c>
-      <c r="B7" t="s">
-        <v>308</v>
-      </c>
-      <c r="D7" t="s">
-        <v>302</v>
-      </c>
-      <c r="E7" s="6" t="str">
-        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D7,CaseTypeSetCategory!$A:$A,0))</f>
-        <v>case_type_set_category1</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>309</v>
-      </c>
-      <c r="B8" t="s">
-        <v>310</v>
-      </c>
-      <c r="D8" t="s">
-        <v>302</v>
-      </c>
-      <c r="E8" s="6" t="str">
-        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D8,CaseTypeSetCategory!$A:$A,0))</f>
-        <v>case_type_set_category1</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>311</v>
-      </c>
-      <c r="B9" t="s">
-        <v>312</v>
-      </c>
-      <c r="D9" t="s">
-        <v>302</v>
-      </c>
-      <c r="E9" s="6" t="str">
-        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D9,CaseTypeSetCategory!$A:$A,0))</f>
-        <v>case_type_set_category1</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>313</v>
-      </c>
-      <c r="B10" t="s">
-        <v>314</v>
-      </c>
-      <c r="D10" t="s">
-        <v>302</v>
-      </c>
-      <c r="E10" s="6" t="str">
-        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D10,CaseTypeSetCategory!$A:$A,0))</f>
-        <v>case_type_set_category1</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>315</v>
-      </c>
-      <c r="B11" t="s">
-        <v>316</v>
-      </c>
-      <c r="D11" t="s">
-        <v>302</v>
-      </c>
-      <c r="E11" s="6" t="str">
-        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D11,CaseTypeSetCategory!$A:$A,0))</f>
-        <v>case_type_set_category1</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>317</v>
-      </c>
-      <c r="B12" t="s">
-        <v>318</v>
-      </c>
-      <c r="D12" t="s">
-        <v>302</v>
-      </c>
-      <c r="E12" s="6" t="str">
-        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D12,CaseTypeSetCategory!$A:$A,0))</f>
-        <v>case_type_set_category1</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>319</v>
-      </c>
-      <c r="B13" t="s">
-        <v>320</v>
-      </c>
-      <c r="D13" t="s">
-        <v>302</v>
-      </c>
-      <c r="E13" s="6" t="str">
-        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D13,CaseTypeSetCategory!$A:$A,0))</f>
-        <v>case_type_set_category1</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>321</v>
-      </c>
-      <c r="B14" t="s">
-        <v>322</v>
-      </c>
-      <c r="D14" t="s">
-        <v>302</v>
-      </c>
-      <c r="E14" s="6" t="str">
-        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D14,CaseTypeSetCategory!$A:$A,0))</f>
-        <v>case_type_set_category1</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>323</v>
-      </c>
-      <c r="B15" t="s">
-        <v>324</v>
-      </c>
-      <c r="D15" t="s">
-        <v>302</v>
-      </c>
-      <c r="E15" s="6" t="str">
-        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D15,CaseTypeSetCategory!$A:$A,0))</f>
-        <v>case_type_set_category1</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>325</v>
-      </c>
-      <c r="B16" t="s">
-        <v>326</v>
-      </c>
-      <c r="D16" t="s">
-        <v>302</v>
-      </c>
-      <c r="E16" s="6" t="str">
-        <f>INDEX(CaseTypeSetCategory!$B:$B,MATCH($D16,CaseTypeSetCategory!$A:$A,0))</f>
-        <v>case_type_set_category1</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
+      <c r="H6" s="13" t="str">
+        <f>INDEX(EtiologicalAgent!$B:$B,MATCH($G6,EtiologicalAgent!$A:$A,0))</f>
+        <v>etiological_agent5</v>
       </c>
     </row>
   </sheetData>

--- a/test/casedb/integration/case_access/test_case_access.xlsx
+++ b/test/casedb/integration/case_access/test_case_access.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivo_v\Documents\gen-epix-api\test\casedb\integration\case_access\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sander/development/gen-epix-api/test/casedb/integration/case_access/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DE2C17-DA4F-4801-9D69-A2C766C910BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF1578C-803F-A14B-9897-41798CB5CF6C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="20057" tabRatio="913" firstSheet="2" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="62540" yWindow="-9440" windowWidth="33120" windowHeight="20060" tabRatio="913" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Organization" sheetId="17" r:id="rId1"/>
@@ -48,33 +48,19 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">OrganizationAccessCasePolicy!$A$1:$U$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">UserAccessCasePolicy!$A$1:$V$11</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -2080,9 +2066,6 @@
     <t>0195d18c-1c93-bcbb-eea8-94332d77b172</t>
   </si>
   <si>
-    <t>metadata_admin1_1@org1.org</t>
-  </si>
-  <si>
     <t>org_admin1_1@org1.org</t>
   </si>
   <si>
@@ -2452,9 +2435,6 @@
     <t>["APP_ADMIN"]</t>
   </si>
   <si>
-    <t>["METADATA_ADMIN"]</t>
-  </si>
-  <si>
     <t>["ORG_ADMIN"]</t>
   </si>
   <si>
@@ -2872,9 +2852,6 @@
     <t>dm.roles.is_app_admin</t>
   </si>
   <si>
-    <t>dm.roles.is_metadata_admin</t>
-  </si>
-  <si>
     <t>dm.roles.is_org_user</t>
   </si>
   <si>
@@ -3011,6 +2988,15 @@
   </si>
   <si>
     <t>user.name</t>
+  </si>
+  <si>
+    <t>dm.roles.is_refdata_admin</t>
+  </si>
+  <si>
+    <t>refdata_admin1_1@org1.org</t>
+  </si>
+  <si>
+    <t>["REFDATA_ADMIN"]</t>
   </si>
 </sst>
 </file>
@@ -3020,7 +3006,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3047,6 +3033,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3142,10 +3136,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3192,8 +3187,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -3503,16 +3500,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.84375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.23046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3520,68 +3517,68 @@
         <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C2" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>87</v>
       </c>
       <c r="B3" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C3" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>90</v>
       </c>
       <c r="B4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C4" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C5" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>96</v>
       </c>
       <c r="B6" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C6" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
   </sheetData>
@@ -3592,16 +3589,16 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="34.23046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.07421875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.53515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3618,7 +3615,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>302</v>
       </c>
@@ -3640,18 +3637,18 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.84375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.07421875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.07421875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.23046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.61328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.53515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3665,7 +3662,7 @@
         <v>298</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>299</v>
@@ -3674,7 +3671,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>107</v>
       </c>
@@ -3692,7 +3689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>111</v>
       </c>
@@ -3710,7 +3707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>115</v>
       </c>
@@ -3728,7 +3725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>119</v>
       </c>
@@ -3746,7 +3743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>123</v>
       </c>
@@ -3764,7 +3761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>307</v>
       </c>
@@ -3782,7 +3779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>309</v>
       </c>
@@ -3800,7 +3797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>311</v>
       </c>
@@ -3818,7 +3815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>313</v>
       </c>
@@ -3836,7 +3833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>315</v>
       </c>
@@ -3854,7 +3851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>317</v>
       </c>
@@ -3872,7 +3869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>319</v>
       </c>
@@ -3890,7 +3887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>321</v>
       </c>
@@ -3908,7 +3905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>323</v>
       </c>
@@ -3926,7 +3923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>325</v>
       </c>
@@ -3953,19 +3950,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.53515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.61328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.53515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.07421875" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.15234375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.23046875" style="6"/>
+    <col min="1" max="2" width="35.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.1640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3973,7 +3969,7 @@
         <v>99</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>100</v>
@@ -3982,16 +3978,16 @@
         <v>531</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>532</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>603</v>
       </c>
@@ -4014,7 +4010,7 @@
         <v>0195d18c-1cb8-5af5-9939-74dc8b5d3b5b|0195d18c-1ca6-fd99-9d76-fcfa0c0cf400</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>604</v>
       </c>
@@ -4034,7 +4030,7 @@
       </c>
       <c r="H3"/>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>605</v>
       </c>
@@ -4054,7 +4050,7 @@
       </c>
       <c r="H4"/>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>606</v>
       </c>
@@ -4074,7 +4070,7 @@
       </c>
       <c r="H5"/>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>607</v>
       </c>
@@ -4094,7 +4090,7 @@
       </c>
       <c r="H6"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>608</v>
       </c>
@@ -4117,7 +4113,7 @@
         <v>0195d18c-1cbb-d7b8-d852-987a801e0ad5|0195d18c-1ca6-fd99-9d76-fcfa0c0cf400</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>609</v>
       </c>
@@ -4137,7 +4133,7 @@
       </c>
       <c r="H8"/>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>610</v>
       </c>
@@ -4157,7 +4153,7 @@
       </c>
       <c r="H9"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>611</v>
       </c>
@@ -4180,7 +4176,7 @@
         <v>0195d18c-1cbb-5047-ab67-71cb2cb84047|0195d18c-1ca6-fd99-9d76-fcfa0c0cf400</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>612</v>
       </c>
@@ -4203,7 +4199,7 @@
         <v>0195d18c-1cbc-41fb-3ad7-2eed31140bd6|0195d18c-1ca6-fd99-9d76-fcfa0c0cf400</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>613</v>
       </c>
@@ -4223,7 +4219,7 @@
       </c>
       <c r="H12"/>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>614</v>
       </c>
@@ -4243,7 +4239,7 @@
       </c>
       <c r="H13"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>615</v>
       </c>
@@ -4266,7 +4262,7 @@
         <v>0195d18c-1cbc-cf9a-b28d-bd77d3b30365|0195d18c-1ca6-fd99-9d76-fcfa0c0cf400</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>616</v>
       </c>
@@ -4286,7 +4282,7 @@
       </c>
       <c r="H15"/>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>617</v>
       </c>
@@ -4306,7 +4302,7 @@
       </c>
       <c r="H16"/>
     </row>
-    <row r="17" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>618</v>
       </c>
@@ -4325,7 +4321,7 @@
         <v>case_type4</v>
       </c>
     </row>
-    <row r="18" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>619</v>
       </c>
@@ -4344,7 +4340,7 @@
         <v>case_type2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>620</v>
       </c>
@@ -4363,7 +4359,7 @@
         <v>case_type5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>621</v>
       </c>
@@ -4382,7 +4378,7 @@
         <v>case_type2</v>
       </c>
     </row>
-    <row r="21" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>622</v>
       </c>
@@ -4401,7 +4397,7 @@
         <v>case_type3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>623</v>
       </c>
@@ -4420,7 +4416,7 @@
         <v>case_type4</v>
       </c>
     </row>
-    <row r="23" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>624</v>
       </c>
@@ -4439,7 +4435,7 @@
         <v>case_type3</v>
       </c>
     </row>
-    <row r="24" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>625</v>
       </c>
@@ -4458,7 +4454,7 @@
         <v>case_type5</v>
       </c>
     </row>
-    <row r="25" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>626</v>
       </c>
@@ -4477,7 +4473,7 @@
         <v>case_type5</v>
       </c>
     </row>
-    <row r="26" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>627</v>
       </c>
@@ -4511,31 +4507,31 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:T46"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.61328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.15234375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.3828125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.23046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.53515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.07421875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.4609375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.84375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.53515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.23046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.61328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.07421875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="31.3046875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.15234375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.53515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4597,7 +4593,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>357</v>
       </c>
@@ -4614,7 +4610,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>360</v>
       </c>
@@ -4631,7 +4627,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>363</v>
       </c>
@@ -4648,7 +4644,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>366</v>
       </c>
@@ -4665,7 +4661,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>369</v>
       </c>
@@ -4682,7 +4678,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>372</v>
       </c>
@@ -4699,7 +4695,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>375</v>
       </c>
@@ -4716,7 +4712,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>378</v>
       </c>
@@ -4733,7 +4729,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>381</v>
       </c>
@@ -4750,7 +4746,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>383</v>
       </c>
@@ -4767,7 +4763,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>386</v>
       </c>
@@ -4784,7 +4780,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>389</v>
       </c>
@@ -4801,7 +4797,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>392</v>
       </c>
@@ -4818,7 +4814,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>395</v>
       </c>
@@ -4835,7 +4831,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>398</v>
       </c>
@@ -4852,7 +4848,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>401</v>
       </c>
@@ -4869,7 +4865,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>404</v>
       </c>
@@ -4886,7 +4882,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>407</v>
       </c>
@@ -4903,7 +4899,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>409</v>
       </c>
@@ -4920,7 +4916,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>412</v>
       </c>
@@ -4937,7 +4933,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>415</v>
       </c>
@@ -4954,7 +4950,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>418</v>
       </c>
@@ -4971,7 +4967,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>421</v>
       </c>
@@ -4988,7 +4984,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>424</v>
       </c>
@@ -5005,7 +5001,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>427</v>
       </c>
@@ -5022,7 +5018,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>430</v>
       </c>
@@ -5039,7 +5035,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>433</v>
       </c>
@@ -5056,7 +5052,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>435</v>
       </c>
@@ -5073,7 +5069,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>438</v>
       </c>
@@ -5090,7 +5086,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>441</v>
       </c>
@@ -5107,7 +5103,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>444</v>
       </c>
@@ -5124,7 +5120,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>447</v>
       </c>
@@ -5141,7 +5137,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>450</v>
       </c>
@@ -5158,7 +5154,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>453</v>
       </c>
@@ -5175,7 +5171,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>456</v>
       </c>
@@ -5192,7 +5188,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>459</v>
       </c>
@@ -5209,7 +5205,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>461</v>
       </c>
@@ -5226,7 +5222,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>464</v>
       </c>
@@ -5243,7 +5239,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>467</v>
       </c>
@@ -5260,7 +5256,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>470</v>
       </c>
@@ -5277,7 +5273,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>473</v>
       </c>
@@ -5294,7 +5290,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>476</v>
       </c>
@@ -5311,7 +5307,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>479</v>
       </c>
@@ -5328,7 +5324,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>482</v>
       </c>
@@ -5345,7 +5341,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>485</v>
       </c>
@@ -5370,13 +5366,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C46"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="21.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="21.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5387,7 +5383,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>108</v>
       </c>
@@ -5398,7 +5394,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>359</v>
       </c>
@@ -5409,7 +5405,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>362</v>
       </c>
@@ -5420,7 +5416,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>365</v>
       </c>
@@ -5431,7 +5427,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>368</v>
       </c>
@@ -5442,7 +5438,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>371</v>
       </c>
@@ -5453,7 +5449,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>374</v>
       </c>
@@ -5464,7 +5460,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>377</v>
       </c>
@@ -5475,7 +5471,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>380</v>
       </c>
@@ -5486,7 +5482,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>112</v>
       </c>
@@ -5497,7 +5493,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>385</v>
       </c>
@@ -5508,7 +5504,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>388</v>
       </c>
@@ -5519,7 +5515,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>391</v>
       </c>
@@ -5530,7 +5526,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>394</v>
       </c>
@@ -5541,7 +5537,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>397</v>
       </c>
@@ -5552,7 +5548,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>400</v>
       </c>
@@ -5563,7 +5559,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>403</v>
       </c>
@@ -5574,7 +5570,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>406</v>
       </c>
@@ -5585,7 +5581,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>116</v>
       </c>
@@ -5596,7 +5592,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>411</v>
       </c>
@@ -5607,7 +5603,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>414</v>
       </c>
@@ -5618,7 +5614,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>417</v>
       </c>
@@ -5629,7 +5625,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>420</v>
       </c>
@@ -5640,7 +5636,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>423</v>
       </c>
@@ -5651,7 +5647,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>426</v>
       </c>
@@ -5662,7 +5658,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>429</v>
       </c>
@@ -5673,7 +5669,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>432</v>
       </c>
@@ -5684,7 +5680,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>120</v>
       </c>
@@ -5695,7 +5691,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>437</v>
       </c>
@@ -5706,7 +5702,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>440</v>
       </c>
@@ -5717,7 +5713,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>443</v>
       </c>
@@ -5728,7 +5724,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>446</v>
       </c>
@@ -5739,7 +5735,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>449</v>
       </c>
@@ -5750,7 +5746,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>452</v>
       </c>
@@ -5761,7 +5757,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>455</v>
       </c>
@@ -5772,7 +5768,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>458</v>
       </c>
@@ -5783,7 +5779,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>124</v>
       </c>
@@ -5794,7 +5790,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>463</v>
       </c>
@@ -5805,7 +5801,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>466</v>
       </c>
@@ -5816,7 +5812,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>469</v>
       </c>
@@ -5827,7 +5823,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>472</v>
       </c>
@@ -5838,7 +5834,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>475</v>
       </c>
@@ -5849,7 +5845,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>478</v>
       </c>
@@ -5860,7 +5856,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>481</v>
       </c>
@@ -5871,7 +5867,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>484</v>
       </c>
@@ -5890,19 +5886,19 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:H46"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.07421875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.61328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.61328125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="12.53515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.23046875" style="6"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.6640625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.1640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5910,7 +5906,7 @@
         <v>101</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>102</v>
@@ -5919,16 +5915,16 @@
         <v>354</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>355</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>356</v>
       </c>
@@ -5951,7 +5947,7 @@
         <v>0195d18c-1cc1-44c2-1d6e-874dad333458|0195d18c-1caa-1722-0366-f73bd3f09ee8</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>358</v>
       </c>
@@ -5974,7 +5970,7 @@
         <v>0195d18c-1cc1-c475-eba4-c3df5aea8858|0195d18c-1cab-86f3-5faf-507bfa221cf6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>361</v>
       </c>
@@ -5997,7 +5993,7 @@
         <v>0195d18c-1cc2-37d1-f6c3-0e7c8d6b1f07|0195d18c-1cab-b4e5-a81b-6acdcc710af2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>364</v>
       </c>
@@ -6020,7 +6016,7 @@
         <v>0195d18c-1cc2-7cf5-8b5c-03f41714d8b8|0195d18c-1cab-3208-7ccc-820a8c522208</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>367</v>
       </c>
@@ -6043,7 +6039,7 @@
         <v>0195d18c-1cc2-50aa-7113-6b261eaeec7a|0195d18c-1cab-767e-81b1-986e918827fb</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>370</v>
       </c>
@@ -6066,7 +6062,7 @@
         <v>0195d18c-1cc3-0cbc-2362-c1cfe3fdec5a|0195d18c-1cab-22f7-dda1-cc74cee303ca</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>373</v>
       </c>
@@ -6089,7 +6085,7 @@
         <v>0195d18c-1cc3-e9c0-5858-8bf9d9d8c36f|0195d18c-1cac-4ed2-2296-a46fa423ce99</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>376</v>
       </c>
@@ -6112,7 +6108,7 @@
         <v>0195d18c-1cc4-9f18-3767-29d288f47190|0195d18c-1cac-9221-a9c7-72e70e09dea9</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>379</v>
       </c>
@@ -6135,7 +6131,7 @@
         <v>0195d18c-1cc5-2ea3-8102-7b410f3146c8|0195d18c-1cac-4d0a-db2e-5a54065df180</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>382</v>
       </c>
@@ -6158,7 +6154,7 @@
         <v>0195d18c-1cc6-a324-3f72-222014292515|0195d18c-1cad-37c6-0826-9671f313fb2b</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>384</v>
       </c>
@@ -6181,7 +6177,7 @@
         <v>0195d18c-1cc7-243f-f4e7-3dbdfe691c71|0195d18c-1cad-5b48-8a72-25050cbf379e</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>387</v>
       </c>
@@ -6204,7 +6200,7 @@
         <v>0195d18c-1cc7-60b4-b4e6-8ff7fabb2b09|0195d18c-1cad-e18e-a87d-8af6760d00e1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>390</v>
       </c>
@@ -6227,7 +6223,7 @@
         <v>0195d18c-1cc8-bcf2-c56f-04928f2e3635|0195d18c-1cad-9467-449f-6341c820b944</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>393</v>
       </c>
@@ -6250,7 +6246,7 @@
         <v>0195d18c-1cc8-18f5-27a5-fd3874e6b78b|0195d18c-1cae-fcea-56fe-4577ada0491d</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>396</v>
       </c>
@@ -6273,7 +6269,7 @@
         <v>0195d18c-1cc8-5a76-0a72-16117b0a5a5e|0195d18c-1cae-cdba-00d9-e8405172259e</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>399</v>
       </c>
@@ -6296,7 +6292,7 @@
         <v>0195d18c-1cc9-7181-fd5b-078012e228f2|0195d18c-1cae-faa7-ac0d-22cce7d230ec</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>402</v>
       </c>
@@ -6319,7 +6315,7 @@
         <v>0195d18c-1cc9-c61f-4e7e-a00189d3cc75|0195d18c-1cae-45ab-ca21-9cee527b9482</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>405</v>
       </c>
@@ -6342,7 +6338,7 @@
         <v>0195d18c-1cca-878e-2110-0116e848541b|0195d18c-1caf-d364-c3b5-e73ba434270e</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>408</v>
       </c>
@@ -6365,7 +6361,7 @@
         <v>0195d18c-1cca-26c0-66df-979380a43b16|0195d18c-1caf-b3af-f64e-bd18810c4521</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>410</v>
       </c>
@@ -6388,7 +6384,7 @@
         <v>0195d18c-1ccb-f06f-162f-a5dc745a5198|0195d18c-1caf-84ca-1737-a8f8788cd464</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>413</v>
       </c>
@@ -6411,7 +6407,7 @@
         <v>0195d18c-1ccb-b068-d845-d61fb54721f1|0195d18c-1cb0-7655-a8bb-f656b1b8b72c</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>416</v>
       </c>
@@ -6434,7 +6430,7 @@
         <v>0195d18c-1ccc-f754-4a4f-89cdc532a3be|0195d18c-1cb0-4c24-e2e8-b92cfc74f7cc</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>419</v>
       </c>
@@ -6457,7 +6453,7 @@
         <v>0195d18c-1ccc-3f10-cc4e-636793b1e9dd|0195d18c-1cb0-8d34-e3f0-ab091b80ab8f</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>422</v>
       </c>
@@ -6480,7 +6476,7 @@
         <v>0195d18c-1ccd-3f53-ad72-f2d3c667b246|0195d18c-1cb0-db51-ed28-2a4481c5f1ac</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>425</v>
       </c>
@@ -6503,7 +6499,7 @@
         <v>0195d18c-1ccd-d664-179c-a1a90c3c886c|0195d18c-1cb1-b5d5-ee26-96c6a9678489</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>428</v>
       </c>
@@ -6526,7 +6522,7 @@
         <v>0195d18c-1ccd-12ae-b807-5b71d1b4e1f1|0195d18c-1cb1-f7bb-aa5b-6f2c6f5d3696</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>431</v>
       </c>
@@ -6549,7 +6545,7 @@
         <v>0195d18c-1cce-3516-017e-cf05c78d4433|0195d18c-1cb1-2097-fae7-ffcb7e109be5</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>434</v>
       </c>
@@ -6572,7 +6568,7 @@
         <v>0195d18c-1cce-585d-e95b-79f3fbfdd12b|0195d18c-1cb2-95e6-139d-1dbe7ffdd3d0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>436</v>
       </c>
@@ -6595,7 +6591,7 @@
         <v>0195d18c-1ccf-c9fa-4e69-800cfa6c5e86|0195d18c-1cb2-995c-625d-dfa62a674ff8</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>439</v>
       </c>
@@ -6618,7 +6614,7 @@
         <v>0195d18c-1ccf-d319-afba-0f13f0d06256|0195d18c-1cb2-7a1f-c2f8-ce2096e4cbbc</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>442</v>
       </c>
@@ -6641,7 +6637,7 @@
         <v>0195d18c-1cd0-951a-878d-5fe5fcd0015a|0195d18c-1cb3-b49c-ddc2-f5174414bfdc</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>445</v>
       </c>
@@ -6664,7 +6660,7 @@
         <v>0195d18c-1cd0-0128-08ed-42804fabb534|0195d18c-1cb3-9495-0b74-a14fa0378944</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>448</v>
       </c>
@@ -6687,7 +6683,7 @@
         <v>0195d18c-1cd1-9702-2218-87932d7bfde7|0195d18c-1cb3-7165-f2c8-1549624bce57</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>451</v>
       </c>
@@ -6710,7 +6706,7 @@
         <v>0195d18c-1cd1-a4b4-2764-66bf69a9f28c|0195d18c-1cb4-62ef-acc3-d4754efbcff5</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>454</v>
       </c>
@@ -6733,7 +6729,7 @@
         <v>0195d18c-1cd2-3359-f0c5-d09dfe10cbd9|0195d18c-1cb4-4080-ce72-0ae401b350e2</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>457</v>
       </c>
@@ -6756,7 +6752,7 @@
         <v>0195d18c-1cd2-c028-2759-dfa197e2e6c0|0195d18c-1cb4-7eca-c0f5-e64333747c9b</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>460</v>
       </c>
@@ -6779,7 +6775,7 @@
         <v>0195d18c-1cd3-02c7-4a0d-80f544cc425a|0195d18c-1cb5-c3e7-b945-7d438ce70962</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>462</v>
       </c>
@@ -6802,7 +6798,7 @@
         <v>0195d18c-1cd3-acd1-2f6c-f9db7a3cd290|0195d18c-1cb5-8fdb-b13a-19f20c06817d</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>465</v>
       </c>
@@ -6825,7 +6821,7 @@
         <v>0195d18c-1cd4-44f9-ea4c-4ab401e03f8f|0195d18c-1cb5-5dbb-4903-872ca139254e</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>468</v>
       </c>
@@ -6848,7 +6844,7 @@
         <v>0195d18c-1cd4-a35d-3e85-41eb9f24a911|0195d18c-1cb6-9ffa-e835-0b70cc4b0ae9</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>471</v>
       </c>
@@ -6871,7 +6867,7 @@
         <v>0195d18c-1cd5-e8f4-76f8-56e13a8aec12|0195d18c-1cb6-a2b9-4827-77425c5ab615</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>474</v>
       </c>
@@ -6894,7 +6890,7 @@
         <v>0195d18c-1cd6-da43-ec75-25feee641928|0195d18c-1cb6-04b0-5474-a6411b693a97</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>477</v>
       </c>
@@ -6917,7 +6913,7 @@
         <v>0195d18c-1cd6-2f81-aefd-93fce854296f|0195d18c-1cb7-05e5-fd6b-6914a124e649</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>480</v>
       </c>
@@ -6940,7 +6936,7 @@
         <v>0195d18c-1cd7-22bb-71ce-9110669bbfef|0195d18c-1cb7-44c6-2f56-594e12327604</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>483</v>
       </c>
@@ -6971,17 +6967,17 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.3046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.07421875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.69140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.07421875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -6989,19 +6985,19 @@
         <v>82</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>83</v>
       </c>
@@ -7023,7 +7019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -7045,7 +7041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>89</v>
       </c>
@@ -7067,7 +7063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -7089,7 +7085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>95</v>
       </c>
@@ -7119,202 +7115,202 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E0C7C33-6768-4AAE-A57E-F80585DED472}">
   <dimension ref="A1:AT33"/>
-  <sheetFormatPr defaultColWidth="5.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="5.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.15234375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.765625" style="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.53515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.61328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37.23046875" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="62.84375" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="41.69140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="62.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="41.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="45" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="30.4609375" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="56.15234375" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="34.921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="38.23046875" style="6" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="36.15234375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="33.53515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.3828125" style="6" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="28.765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.69140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="34.53515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="38.3828125" style="6" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.921875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.4609375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="34.765625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="32.53515625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="35.3828125" style="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="66.15234375" style="6" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="66.765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="59.3828125" style="6" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="60.07421875" style="6" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="29.61328125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="32.53515625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="35.3828125" style="6" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="66.15234375" style="6" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="66.765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="59.3828125" style="6" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="60.07421875" style="6" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="29.61328125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="32.53515625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="35.3828125" style="6" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="66.15234375" style="6" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="66.765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="59.3828125" style="6" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="60.07421875" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="56.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="38.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="36.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="33.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="28.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="34.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="38.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="34.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="35.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="66.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="66.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="59.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="60" style="6" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="35.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="66.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="66.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="59.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="60" style="6" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="35.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="66.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="66.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="59.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="60" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>839</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>842</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>970</v>
+      </c>
+      <c r="E1" t="s">
+        <v>840</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>850</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>917</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>921</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>918</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>926</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>851</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>920</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>927</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>854</v>
+      </c>
+      <c r="Q1" t="s">
         <v>841</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="R1" t="s">
+        <v>843</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>916</v>
+      </c>
+      <c r="U1" t="s">
         <v>844</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>973</v>
-      </c>
-      <c r="E1" t="s">
-        <v>842</v>
-      </c>
-      <c r="F1" s="19" t="s">
-        <v>852</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>919</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>923</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>920</v>
-      </c>
-      <c r="J1" s="6" t="s">
+      <c r="V1" t="s">
+        <v>845</v>
+      </c>
+      <c r="W1" s="6" t="s">
         <v>929</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>853</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>854</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>922</v>
-      </c>
-      <c r="N1" s="6" t="s">
+      <c r="X1" t="s">
+        <v>846</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>847</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>848</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>849</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>928</v>
+      </c>
+      <c r="AC1" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="AD1" s="6" t="s">
+        <v>933</v>
+      </c>
+      <c r="AE1" s="6" t="s">
+        <v>938</v>
+      </c>
+      <c r="AF1" s="6" t="s">
+        <v>939</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>913</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>959</v>
+      </c>
+      <c r="AI1" s="6" t="s">
         <v>930</v>
       </c>
-      <c r="O1" s="6" t="s">
-        <v>855</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>856</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>843</v>
-      </c>
-      <c r="R1" t="s">
-        <v>845</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>913</v>
-      </c>
-      <c r="T1" s="6" t="s">
-        <v>918</v>
-      </c>
-      <c r="U1" t="s">
-        <v>846</v>
-      </c>
-      <c r="V1" t="s">
-        <v>847</v>
-      </c>
-      <c r="W1" s="6" t="s">
-        <v>932</v>
-      </c>
-      <c r="X1" t="s">
-        <v>848</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>849</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>850</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>851</v>
-      </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="AK1" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="AL1" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="AM1" s="6" t="s">
+        <v>941</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>914</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>960</v>
+      </c>
+      <c r="AP1" s="6" t="s">
         <v>931</v>
       </c>
-      <c r="AC1" s="6" t="s">
-        <v>935</v>
-      </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>936</v>
       </c>
-      <c r="AE1" s="6" t="s">
-        <v>941</v>
-      </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
+        <v>937</v>
+      </c>
+      <c r="AS1" s="6" t="s">
         <v>942</v>
       </c>
-      <c r="AG1" t="s">
-        <v>915</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>962</v>
-      </c>
-      <c r="AI1" s="6" t="s">
-        <v>933</v>
-      </c>
-      <c r="AJ1" s="6" t="s">
-        <v>937</v>
-      </c>
-      <c r="AK1" s="6" t="s">
-        <v>938</v>
-      </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="AM1" s="6" t="s">
-        <v>944</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>916</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>963</v>
-      </c>
-      <c r="AP1" s="6" t="s">
-        <v>934</v>
-      </c>
-      <c r="AQ1" s="6" t="s">
-        <v>939</v>
-      </c>
-      <c r="AR1" s="6" t="s">
-        <v>940</v>
-      </c>
-      <c r="AS1" s="6" t="s">
-        <v>945</v>
-      </c>
-      <c r="AT1" s="6" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="C2" t="s">
         <v>658</v>
@@ -7324,7 +7320,7 @@
         <v>root1_1</v>
       </c>
       <c r="E2" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="F2" s="19" t="b">
         <f>IF($E2="CREATE",$H2,IF($E2="CASES_CREATE",OR($H2,AND($J2,$K2,$N2,$O2,$AD2,AF2,$AK2,$AM2,$AR2,$AT2)),"TBD"))</f>
@@ -7371,7 +7367,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="R2" t="s">
         <v>334</v>
@@ -7398,7 +7394,7 @@
         <v>357</v>
       </c>
       <c r="AA2" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB2" s="6" t="str">
         <f>IF($Z2="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z2,CaseTypeCol!$A:$A,0)))</f>
@@ -7461,12 +7457,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C3" t="s">
         <v>660</v>
@@ -7476,7 +7472,7 @@
         <v>app_admin1_1</v>
       </c>
       <c r="E3" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="F3" s="19" t="b">
         <f t="shared" ref="F3:F33" si="0">IF($E3="CREATE",$H3,IF($E3="CASES_CREATE",OR($H3,AND($J3,$K3,$N3,$O3,$AD3,AF3,$AK3,$AM3,$AR3,$AT3)),"TBD"))</f>
@@ -7523,7 +7519,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="R3" t="s">
         <v>334</v>
@@ -7550,7 +7546,7 @@
         <v>357</v>
       </c>
       <c r="AA3" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB3" s="6" t="str">
         <f>IF($Z3="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z3,CaseTypeCol!$A:$A,0)))</f>
@@ -7613,22 +7609,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C4" t="s">
         <v>662</v>
       </c>
       <c r="D4" s="6" t="str">
         <f>INDEX(User!$C:$C,MATCH($C4,User!$A:$A,0))</f>
-        <v>metadata_admin1_1</v>
+        <v>refdata_admin1_1</v>
       </c>
       <c r="E4" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="F4" s="19" t="b">
         <f t="shared" si="0"/>
@@ -7675,7 +7671,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="R4" t="s">
         <v>334</v>
@@ -7702,7 +7698,7 @@
         <v>357</v>
       </c>
       <c r="AA4" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB4" s="6" t="str">
         <f>IF($Z4="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z4,CaseTypeCol!$A:$A,0)))</f>
@@ -7765,12 +7761,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="C5" t="s">
         <v>85</v>
@@ -7780,7 +7776,7 @@
         <v>org_admin1_1</v>
       </c>
       <c r="E5" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="F5" s="19" t="b">
         <f t="shared" ref="F5:F6" si="1">IF($E5="CREATE",$H5,IF($E5="CASES_CREATE",OR($H5,AND($J5,$K5,$N5,$O5,$AD5,AF5,$AK5,$AM5,$AR5,$AT5)),"TBD"))</f>
@@ -7827,7 +7823,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="R5" t="s">
         <v>334</v>
@@ -7854,7 +7850,7 @@
         <v>357</v>
       </c>
       <c r="AA5" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB5" s="6" t="str">
         <f>IF($Z5="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z5,CaseTypeCol!$A:$A,0)))</f>
@@ -7917,12 +7913,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
@@ -7932,7 +7928,7 @@
         <v>org_user1_1</v>
       </c>
       <c r="E6" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="F6" s="19" t="b">
         <f t="shared" si="1"/>
@@ -7979,7 +7975,7 @@
         <v>1</v>
       </c>
       <c r="Q6" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="R6" t="s">
         <v>334</v>
@@ -8006,7 +8002,7 @@
         <v>357</v>
       </c>
       <c r="AA6" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB6" s="6" t="str">
         <f>IF($Z6="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z6,CaseTypeCol!$A:$A,0)))</f>
@@ -8069,12 +8065,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="C7" t="s">
         <v>658</v>
@@ -8084,7 +8080,7 @@
         <v>root1_1</v>
       </c>
       <c r="E7" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F7" s="19" t="b">
         <f ca="1">IF($E7="CREATE",$H7,IF($E7="CASES_CREATE",OR($H7,AND($J7,$K7,$N7,$O7,$AD7,AF7,$AK7,$AM7,$AR7,$AT7)),"TBD"))</f>
@@ -8131,7 +8127,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="R7" t="s">
         <v>334</v>
@@ -8158,7 +8154,7 @@
         <v>357</v>
       </c>
       <c r="AA7" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB7" s="6" t="str">
         <f>IF($Z7="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z7,CaseTypeCol!$A:$A,0)))</f>
@@ -8221,12 +8217,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="C8" t="s">
         <v>660</v>
@@ -8236,7 +8232,7 @@
         <v>app_admin1_1</v>
       </c>
       <c r="E8" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F8" s="19" t="b">
         <f t="shared" ref="F8" ca="1" si="2">IF($E8="CREATE",$H8,IF($E8="CASES_CREATE",OR($H8,AND($J8,$K8,$N8,$O8,$AD8,AF8,$AK8,$AM8,$AR8,$AT8)),"TBD"))</f>
@@ -8283,7 +8279,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="R8" t="s">
         <v>334</v>
@@ -8310,7 +8306,7 @@
         <v>357</v>
       </c>
       <c r="AA8" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB8" s="6" t="str">
         <f>IF($Z8="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z8,CaseTypeCol!$A:$A,0)))</f>
@@ -8373,12 +8369,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="C9" t="s">
         <v>85</v>
@@ -8388,7 +8384,7 @@
         <v>org_admin1_1</v>
       </c>
       <c r="E9" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F9" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -8435,7 +8431,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="R9" t="s">
         <v>334</v>
@@ -8462,7 +8458,7 @@
         <v>357</v>
       </c>
       <c r="AA9" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB9" s="6" t="str">
         <f>IF($Z9="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z9,CaseTypeCol!$A:$A,0)))</f>
@@ -8525,12 +8521,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C10" t="s">
         <v>88</v>
@@ -8540,7 +8536,7 @@
         <v>org_admin2_1</v>
       </c>
       <c r="E10" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F10" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -8587,7 +8583,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="R10" t="s">
         <v>334</v>
@@ -8614,7 +8610,7 @@
         <v>357</v>
       </c>
       <c r="AA10" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB10" s="6" t="str">
         <f>IF($Z10="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z10,CaseTypeCol!$A:$A,0)))</f>
@@ -8677,12 +8673,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C11" t="s">
         <v>91</v>
@@ -8692,7 +8688,7 @@
         <v>org_admin3_1</v>
       </c>
       <c r="E11" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F11" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -8739,7 +8735,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="R11" t="s">
         <v>334</v>
@@ -8766,7 +8762,7 @@
         <v>357</v>
       </c>
       <c r="AA11" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB11" s="6" t="str">
         <f>IF($Z11="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z11,CaseTypeCol!$A:$A,0)))</f>
@@ -8829,12 +8825,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C12" t="s">
         <v>94</v>
@@ -8844,7 +8840,7 @@
         <v>org_admin4_1</v>
       </c>
       <c r="E12" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F12" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -8891,7 +8887,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="R12" t="s">
         <v>334</v>
@@ -8918,7 +8914,7 @@
         <v>357</v>
       </c>
       <c r="AA12" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB12" s="6" t="str">
         <f>IF($Z12="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z12,CaseTypeCol!$A:$A,0)))</f>
@@ -8981,12 +8977,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C13" t="s">
         <v>97</v>
@@ -8996,7 +8992,7 @@
         <v>org_admin5_1</v>
       </c>
       <c r="E13" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F13" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -9043,7 +9039,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="R13" t="s">
         <v>334</v>
@@ -9070,7 +9066,7 @@
         <v>357</v>
       </c>
       <c r="AA13" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB13" s="6" t="str">
         <f>IF($Z13="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z13,CaseTypeCol!$A:$A,0)))</f>
@@ -9133,12 +9129,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
@@ -9148,7 +9144,7 @@
         <v>org_user1_1</v>
       </c>
       <c r="E14" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F14" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -9195,7 +9191,7 @@
         <v>1</v>
       </c>
       <c r="Q14" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="R14" t="s">
         <v>334</v>
@@ -9222,7 +9218,7 @@
         <v>357</v>
       </c>
       <c r="AA14" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB14" s="6" t="str">
         <f>IF($Z14="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z14,CaseTypeCol!$A:$A,0)))</f>
@@ -9285,12 +9281,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
@@ -9300,7 +9296,7 @@
         <v>org_user1_2</v>
       </c>
       <c r="E15" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F15" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -9347,7 +9343,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="R15" t="s">
         <v>334</v>
@@ -9374,7 +9370,7 @@
         <v>357</v>
       </c>
       <c r="AA15" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB15" s="6" t="str">
         <f>IF($Z15="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z15,CaseTypeCol!$A:$A,0)))</f>
@@ -9437,12 +9433,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="C16" t="s">
         <v>16</v>
@@ -9452,7 +9448,7 @@
         <v>org_user1_3</v>
       </c>
       <c r="E16" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F16" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -9499,7 +9495,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="R16" t="s">
         <v>334</v>
@@ -9526,7 +9522,7 @@
         <v>357</v>
       </c>
       <c r="AA16" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB16" s="6" t="str">
         <f>IF($Z16="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z16,CaseTypeCol!$A:$A,0)))</f>
@@ -9589,12 +9585,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
@@ -9604,7 +9600,7 @@
         <v>org_user1_4</v>
       </c>
       <c r="E17" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F17" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -9651,7 +9647,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="R17" t="s">
         <v>334</v>
@@ -9678,7 +9674,7 @@
         <v>357</v>
       </c>
       <c r="AA17" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB17" s="6" t="str">
         <f>IF($Z17="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z17,CaseTypeCol!$A:$A,0)))</f>
@@ -9741,12 +9737,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C18" t="s">
         <v>25</v>
@@ -9756,7 +9752,7 @@
         <v>org_user2_1</v>
       </c>
       <c r="E18" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F18" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -9803,7 +9799,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="R18" t="s">
         <v>334</v>
@@ -9830,7 +9826,7 @@
         <v>357</v>
       </c>
       <c r="AA18" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB18" s="6" t="str">
         <f>IF($Z18="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z18,CaseTypeCol!$A:$A,0)))</f>
@@ -9893,12 +9889,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C19" t="s">
         <v>28</v>
@@ -9908,7 +9904,7 @@
         <v>org_user2_2</v>
       </c>
       <c r="E19" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F19" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -9955,7 +9951,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="R19" t="s">
         <v>334</v>
@@ -9982,7 +9978,7 @@
         <v>357</v>
       </c>
       <c r="AA19" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB19" s="6" t="str">
         <f>IF($Z19="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z19,CaseTypeCol!$A:$A,0)))</f>
@@ -10045,12 +10041,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C20" t="s">
         <v>30</v>
@@ -10060,7 +10056,7 @@
         <v>org_user2_3</v>
       </c>
       <c r="E20" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F20" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -10107,7 +10103,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="R20" t="s">
         <v>334</v>
@@ -10134,7 +10130,7 @@
         <v>357</v>
       </c>
       <c r="AA20" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB20" s="6" t="str">
         <f>IF($Z20="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z20,CaseTypeCol!$A:$A,0)))</f>
@@ -10197,12 +10193,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C21" t="s">
         <v>32</v>
@@ -10212,7 +10208,7 @@
         <v>org_user2_4</v>
       </c>
       <c r="E21" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F21" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -10259,7 +10255,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="R21" t="s">
         <v>334</v>
@@ -10286,7 +10282,7 @@
         <v>357</v>
       </c>
       <c r="AA21" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB21" s="6" t="str">
         <f>IF($Z21="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z21,CaseTypeCol!$A:$A,0)))</f>
@@ -10349,12 +10345,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C22" t="s">
         <v>39</v>
@@ -10364,7 +10360,7 @@
         <v>org_user3_1</v>
       </c>
       <c r="E22" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F22" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -10411,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="R22" t="s">
         <v>334</v>
@@ -10438,7 +10434,7 @@
         <v>357</v>
       </c>
       <c r="AA22" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB22" s="6" t="str">
         <f>IF($Z22="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z22,CaseTypeCol!$A:$A,0)))</f>
@@ -10501,12 +10497,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C23" t="s">
         <v>42</v>
@@ -10516,7 +10512,7 @@
         <v>org_user3_2</v>
       </c>
       <c r="E23" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F23" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -10563,7 +10559,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="R23" t="s">
         <v>334</v>
@@ -10590,7 +10586,7 @@
         <v>357</v>
       </c>
       <c r="AA23" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB23" s="6" t="str">
         <f>IF($Z23="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z23,CaseTypeCol!$A:$A,0)))</f>
@@ -10653,12 +10649,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C24" t="s">
         <v>44</v>
@@ -10668,7 +10664,7 @@
         <v>org_user3_3</v>
       </c>
       <c r="E24" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F24" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -10715,7 +10711,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="R24" t="s">
         <v>334</v>
@@ -10742,7 +10738,7 @@
         <v>357</v>
       </c>
       <c r="AA24" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB24" s="6" t="str">
         <f>IF($Z24="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z24,CaseTypeCol!$A:$A,0)))</f>
@@ -10805,12 +10801,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -10820,7 +10816,7 @@
         <v>org_user3_4</v>
       </c>
       <c r="E25" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F25" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -10867,7 +10863,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="R25" t="s">
         <v>334</v>
@@ -10894,7 +10890,7 @@
         <v>357</v>
       </c>
       <c r="AA25" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB25" s="6" t="str">
         <f>IF($Z25="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z25,CaseTypeCol!$A:$A,0)))</f>
@@ -10957,12 +10953,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C26" t="s">
         <v>53</v>
@@ -10972,7 +10968,7 @@
         <v>org_user4_1</v>
       </c>
       <c r="E26" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F26" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -11019,7 +11015,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="R26" t="s">
         <v>334</v>
@@ -11046,7 +11042,7 @@
         <v>357</v>
       </c>
       <c r="AA26" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB26" s="6" t="str">
         <f>IF($Z26="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z26,CaseTypeCol!$A:$A,0)))</f>
@@ -11109,12 +11105,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C27" t="s">
         <v>56</v>
@@ -11124,7 +11120,7 @@
         <v>org_user4_2</v>
       </c>
       <c r="E27" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F27" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -11171,7 +11167,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="R27" t="s">
         <v>334</v>
@@ -11198,7 +11194,7 @@
         <v>357</v>
       </c>
       <c r="AA27" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB27" s="6" t="str">
         <f>IF($Z27="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z27,CaseTypeCol!$A:$A,0)))</f>
@@ -11261,12 +11257,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C28" t="s">
         <v>58</v>
@@ -11276,7 +11272,7 @@
         <v>org_user4_3</v>
       </c>
       <c r="E28" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F28" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -11323,7 +11319,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="R28" t="s">
         <v>334</v>
@@ -11350,7 +11346,7 @@
         <v>357</v>
       </c>
       <c r="AA28" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB28" s="6" t="str">
         <f>IF($Z28="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z28,CaseTypeCol!$A:$A,0)))</f>
@@ -11413,12 +11409,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C29" t="s">
         <v>60</v>
@@ -11428,7 +11424,7 @@
         <v>org_user4_4</v>
       </c>
       <c r="E29" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F29" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -11475,7 +11471,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="R29" t="s">
         <v>334</v>
@@ -11502,7 +11498,7 @@
         <v>357</v>
       </c>
       <c r="AA29" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB29" s="6" t="str">
         <f>IF($Z29="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z29,CaseTypeCol!$A:$A,0)))</f>
@@ -11565,12 +11561,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C30" t="s">
         <v>67</v>
@@ -11580,7 +11576,7 @@
         <v>org_user5_1</v>
       </c>
       <c r="E30" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F30" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -11627,7 +11623,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="R30" t="s">
         <v>334</v>
@@ -11654,7 +11650,7 @@
         <v>357</v>
       </c>
       <c r="AA30" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB30" s="6" t="str">
         <f>IF($Z30="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z30,CaseTypeCol!$A:$A,0)))</f>
@@ -11717,12 +11713,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C31" t="s">
         <v>70</v>
@@ -11732,7 +11728,7 @@
         <v>org_user5_2</v>
       </c>
       <c r="E31" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F31" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -11779,7 +11775,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="R31" t="s">
         <v>334</v>
@@ -11806,7 +11802,7 @@
         <v>357</v>
       </c>
       <c r="AA31" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB31" s="6" t="str">
         <f>IF($Z31="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z31,CaseTypeCol!$A:$A,0)))</f>
@@ -11869,12 +11865,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="C32" t="s">
         <v>72</v>
@@ -11884,7 +11880,7 @@
         <v>org_user5_3</v>
       </c>
       <c r="E32" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F32" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -11931,7 +11927,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="R32" t="s">
         <v>334</v>
@@ -11958,7 +11954,7 @@
         <v>357</v>
       </c>
       <c r="AA32" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB32" s="6" t="str">
         <f>IF($Z32="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z32,CaseTypeCol!$A:$A,0)))</f>
@@ -12021,12 +12017,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C33" t="s">
         <v>74</v>
@@ -12036,7 +12032,7 @@
         <v>org_user5_4</v>
       </c>
       <c r="E33" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F33" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
@@ -12083,7 +12079,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="R33" t="s">
         <v>334</v>
@@ -12110,7 +12106,7 @@
         <v>357</v>
       </c>
       <c r="AA33" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AB33" s="6" t="str">
         <f>IF($Z33="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z33,CaseTypeCol!$A:$A,0)))</f>
@@ -12189,32 +12185,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F0F389-1562-4A7F-BB5E-AAA96B2F3DDB}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:V11"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.07421875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.23046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.07421875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.07421875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.23046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.07421875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.07421875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="35.84375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.3046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.84375" customWidth="1"/>
-    <col min="13" max="13" width="30.765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.3046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.69140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.84375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.4609375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.83203125" customWidth="1"/>
+    <col min="13" max="13" width="30.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="36" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.3046875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="33.4609375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="26.53515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.4609375" customWidth="1"/>
+    <col min="19" max="19" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="33.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="26.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -12222,19 +12218,19 @@
         <v>2</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>4</v>
@@ -12243,16 +12239,16 @@
         <v>5</v>
       </c>
       <c r="J1" s="7" t="s">
+        <v>810</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>812</v>
       </c>
-      <c r="K1" s="8" t="s">
-        <v>814</v>
-      </c>
       <c r="L1" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="M1" s="8" t="s">
         <v>813</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>815</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>6</v>
@@ -12270,19 +12266,19 @@
         <v>82</v>
       </c>
       <c r="S1" s="8" t="s">
+        <v>814</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="U1" s="8" t="s">
         <v>816</v>
       </c>
-      <c r="T1" s="4" t="s">
-        <v>817</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>818</v>
-      </c>
       <c r="V1" s="8" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.4">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>105</v>
       </c>
@@ -12358,7 +12354,7 @@
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653|0195d18c-1ca2-a23d-1f64-00271f63199c</v>
       </c>
     </row>
-    <row r="3" spans="1:22" hidden="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -12434,7 +12430,7 @@
         <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3|0195d18c-1ca2-2a29-96a5-37c6bf87f586</v>
       </c>
     </row>
-    <row r="4" spans="1:22" hidden="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>139</v>
       </c>
@@ -12510,7 +12506,7 @@
         <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037|0195d18c-1ca2-3a4f-1878-fbe3282c9c76</v>
       </c>
     </row>
-    <row r="5" spans="1:22" hidden="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>151</v>
       </c>
@@ -12586,7 +12582,7 @@
         <v>0195d18c-1c92-d419-4c71-a570f428499b|0195d18c-1ca2-e55a-608d-a42fc6f948e1</v>
       </c>
     </row>
-    <row r="6" spans="1:22" hidden="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>163</v>
       </c>
@@ -12662,7 +12658,7 @@
         <v>0195d18c-1c93-02a2-6920-7e4dbfb73ce0|0195d18c-1ca2-b728-a2a1-d2a4cf7b8eb8</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>165</v>
       </c>
@@ -12735,7 +12731,7 @@
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653|0195d18c-1ca3-f309-f6f1-e4807afe3802</v>
       </c>
     </row>
-    <row r="8" spans="1:22" hidden="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>177</v>
       </c>
@@ -12808,7 +12804,7 @@
         <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3|0195d18c-1ca3-db40-a2a8-6dc905d6c1e9</v>
       </c>
     </row>
-    <row r="9" spans="1:22" hidden="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>189</v>
       </c>
@@ -12881,7 +12877,7 @@
         <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037|0195d18c-1ca3-da0a-44bb-877b3a1eb73e</v>
       </c>
     </row>
-    <row r="10" spans="1:22" hidden="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>201</v>
       </c>
@@ -12954,7 +12950,7 @@
         <v>0195d18c-1c92-d419-4c71-a570f428499b|0195d18c-1ca3-4d34-d0e9-8f024ad8651a</v>
       </c>
     </row>
-    <row r="11" spans="1:22" hidden="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>213</v>
       </c>
@@ -13043,32 +13039,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{413B6EDF-4214-4325-A1BD-732A42D052EA}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:W11"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.07421875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.23046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.07421875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.07421875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.23046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.07421875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.84375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.3046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.84375" customWidth="1"/>
-    <col min="12" max="12" width="30.765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.3046875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.69140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.84375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.4609375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="36.3046875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.23046875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="42.765625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="26.53515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.83203125" customWidth="1"/>
+    <col min="12" max="12" width="30.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="42.83203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26.5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="36" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="20.3046875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -13076,13 +13072,13 @@
         <v>2</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>3</v>
@@ -13094,16 +13090,16 @@
         <v>5</v>
       </c>
       <c r="I1" s="7" t="s">
+        <v>810</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>812</v>
       </c>
-      <c r="J1" s="8" t="s">
-        <v>814</v>
-      </c>
       <c r="K1" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>813</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>815</v>
       </c>
       <c r="M1" s="7" t="s">
         <v>6</v>
@@ -13118,28 +13114,28 @@
         <v>9</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="S1" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="V1" s="8" t="s">
         <v>817</v>
       </c>
-      <c r="T1" s="8" t="s">
-        <v>818</v>
-      </c>
-      <c r="U1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V1" s="8" t="s">
-        <v>819</v>
-      </c>
       <c r="W1" s="15" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.4">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>105</v>
       </c>
@@ -13220,7 +13216,7 @@
         <v>0195d18c-1c98-7e0b-0c91-8cafbdb2c852|0195d18c-1ca2-a23d-1f64-00271f63199c</v>
       </c>
     </row>
-    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -13301,7 +13297,7 @@
         <v>0195d18c-1c9a-1178-0519-9124131763a6|0195d18c-1ca2-2a29-96a5-37c6bf87f586</v>
       </c>
     </row>
-    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>139</v>
       </c>
@@ -13382,7 +13378,7 @@
         <v>0195d18c-1c9c-0d8f-435a-5ca8b45939b8|0195d18c-1ca2-3a4f-1878-fbe3282c9c76</v>
       </c>
     </row>
-    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>151</v>
       </c>
@@ -13463,7 +13459,7 @@
         <v>0195d18c-1c9e-1c4a-1311-4f22f0d59f61|0195d18c-1ca2-e55a-608d-a42fc6f948e1</v>
       </c>
     </row>
-    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>163</v>
       </c>
@@ -13544,7 +13540,7 @@
         <v>0195d18c-1ca0-e0db-7a87-6237ad6380c8|0195d18c-1ca2-b728-a2a1-d2a4cf7b8eb8</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>165</v>
       </c>
@@ -13625,7 +13621,7 @@
         <v>0195d18c-1c98-7e0b-0c91-8cafbdb2c852|0195d18c-1ca3-f309-f6f1-e4807afe3802</v>
       </c>
     </row>
-    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>177</v>
       </c>
@@ -13706,7 +13702,7 @@
         <v>0195d18c-1c9a-1178-0519-9124131763a6|0195d18c-1ca3-db40-a2a8-6dc905d6c1e9</v>
       </c>
     </row>
-    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>189</v>
       </c>
@@ -13787,7 +13783,7 @@
         <v>0195d18c-1c9c-0d8f-435a-5ca8b45939b8|0195d18c-1ca3-da0a-44bb-877b3a1eb73e</v>
       </c>
     </row>
-    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>201</v>
       </c>
@@ -13868,7 +13864,7 @@
         <v>0195d18c-1c9e-1c4a-1311-4f22f0d59f61|0195d18c-1ca3-4d34-d0e9-8f024ad8651a</v>
       </c>
     </row>
-    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>213</v>
       </c>
@@ -13964,14 +13960,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.23046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.3046875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13982,132 +13978,132 @@
         <v>297</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C2" s="6" t="str">
         <f>"dc"&amp;RIGHT($B2,LEN($B2)-15)</f>
         <v>dc1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C3" s="6" t="str">
         <f t="shared" ref="C3:C12" si="0">"dc"&amp;RIGHT($B3,LEN($B3)-15)</f>
         <v>dc2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C4" s="6" t="str">
         <f t="shared" si="0"/>
         <v>dc3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C5" s="6" t="str">
         <f t="shared" si="0"/>
         <v>dc4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>68</v>
       </c>
       <c r="B6" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C6" s="6" t="str">
         <f t="shared" si="0"/>
         <v>dc5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C7" s="6" t="str">
         <f t="shared" si="0"/>
         <v>dc6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C8" s="6" t="str">
         <f t="shared" si="0"/>
         <v>dc7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C9" s="6" t="str">
         <f t="shared" si="0"/>
         <v>dc8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C10" s="6" t="str">
         <f t="shared" si="0"/>
         <v>dc9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>76</v>
       </c>
       <c r="B11" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C11" s="6" t="str">
         <f t="shared" si="0"/>
         <v>dc10</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C12" s="6" t="str">
         <f t="shared" si="0"/>
@@ -14122,26 +14118,26 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46B1A0CE-352C-4E69-8986-540397C3CD9D}">
   <dimension ref="A1:P2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="35.4609375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.69140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.69140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.07421875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.07421875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.84375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.07421875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.4609375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.3046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="36" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.69140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35.4609375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14149,13 +14145,13 @@
         <v>2</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D1" t="s">
         <v>99</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -14173,27 +14169,27 @@
         <v>7</v>
       </c>
       <c r="K1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>820</v>
       </c>
-      <c r="M1" s="6" t="s">
-        <v>822</v>
-      </c>
       <c r="N1" s="3" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="O1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="P1" s="8" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>819</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>821</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
@@ -14259,25 +14255,25 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21E03A8B-A0A1-46B6-957F-B8B3E001E975}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.23046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.69140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.07421875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.07421875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.84375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.07421875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.4609375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.3046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="36" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.53515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14285,13 +14281,13 @@
         <v>2</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D1" t="s">
         <v>99</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -14309,21 +14305,21 @@
         <v>7</v>
       </c>
       <c r="K1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="M1" t="s">
         <v>82</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
@@ -14381,39 +14377,39 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.07421875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.23046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.07421875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.23046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>710</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>711</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -14433,9 +14429,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -14455,9 +14451,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -14477,9 +14473,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
@@ -14499,9 +14495,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B6" t="s">
         <v>40</v>
@@ -14521,9 +14517,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B7" t="s">
         <v>40</v>
@@ -14543,9 +14539,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B8" t="s">
         <v>54</v>
@@ -14565,9 +14561,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B9" t="s">
         <v>54</v>
@@ -14587,9 +14583,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B10" t="s">
         <v>68</v>
@@ -14609,9 +14605,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B11" t="s">
         <v>68</v>
@@ -14631,9 +14627,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B12" t="s">
         <v>20</v>
@@ -14661,21 +14657,21 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M56"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.53515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.53515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.07421875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.4609375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.07421875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.53515625" customWidth="1"/>
-    <col min="9" max="9" width="35.84375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.5" customWidth="1"/>
+    <col min="9" max="9" width="35.83203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14686,25 +14682,25 @@
         <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>101</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>3</v>
@@ -14716,7 +14712,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>105</v>
       </c>
@@ -14761,7 +14757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>109</v>
       </c>
@@ -14806,7 +14802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>113</v>
       </c>
@@ -14851,7 +14847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>117</v>
       </c>
@@ -14896,7 +14892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>121</v>
       </c>
@@ -14941,7 +14937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>125</v>
       </c>
@@ -14986,7 +14982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>127</v>
       </c>
@@ -15031,7 +15027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>129</v>
       </c>
@@ -15076,7 +15072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>131</v>
       </c>
@@ -15121,7 +15117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>133</v>
       </c>
@@ -15166,7 +15162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>135</v>
       </c>
@@ -15211,7 +15207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>137</v>
       </c>
@@ -15256,7 +15252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>139</v>
       </c>
@@ -15301,7 +15297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>141</v>
       </c>
@@ -15346,7 +15342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>143</v>
       </c>
@@ -15391,7 +15387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>145</v>
       </c>
@@ -15436,7 +15432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>147</v>
       </c>
@@ -15481,7 +15477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>149</v>
       </c>
@@ -15526,7 +15522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>151</v>
       </c>
@@ -15571,7 +15567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>153</v>
       </c>
@@ -15616,7 +15612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>155</v>
       </c>
@@ -15661,7 +15657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>157</v>
       </c>
@@ -15706,7 +15702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>159</v>
       </c>
@@ -15751,7 +15747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>161</v>
       </c>
@@ -15796,7 +15792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>163</v>
       </c>
@@ -15841,7 +15837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>165</v>
       </c>
@@ -15886,7 +15882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>167</v>
       </c>
@@ -15931,7 +15927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>169</v>
       </c>
@@ -15976,7 +15972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>171</v>
       </c>
@@ -16021,7 +16017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>173</v>
       </c>
@@ -16066,7 +16062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>175</v>
       </c>
@@ -16111,7 +16107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>177</v>
       </c>
@@ -16156,7 +16152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>179</v>
       </c>
@@ -16201,7 +16197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>181</v>
       </c>
@@ -16246,7 +16242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>183</v>
       </c>
@@ -16291,12 +16287,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B37" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C37" t="s">
         <v>84</v>
@@ -16336,12 +16332,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B38" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C38" t="s">
         <v>84</v>
@@ -16381,12 +16377,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B39" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C39" t="s">
         <v>84</v>
@@ -16426,12 +16422,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B40" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C40" t="s">
         <v>84</v>
@@ -16471,12 +16467,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B41" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C41" t="s">
         <v>84</v>
@@ -16516,7 +16512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>185</v>
       </c>
@@ -16561,7 +16557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>187</v>
       </c>
@@ -16606,7 +16602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>189</v>
       </c>
@@ -16651,7 +16647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>191</v>
       </c>
@@ -16696,7 +16692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>193</v>
       </c>
@@ -16741,7 +16737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>195</v>
       </c>
@@ -16786,7 +16782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>197</v>
       </c>
@@ -16831,7 +16827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>199</v>
       </c>
@@ -16876,7 +16872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>201</v>
       </c>
@@ -16921,7 +16917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>203</v>
       </c>
@@ -16966,7 +16962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>205</v>
       </c>
@@ -17011,7 +17007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>207</v>
       </c>
@@ -17056,7 +17052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>209</v>
       </c>
@@ -17101,7 +17097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>211</v>
       </c>
@@ -17146,7 +17142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>213</v>
       </c>
@@ -17199,22 +17195,22 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L56"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.23046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.07421875" customWidth="1"/>
-    <col min="3" max="3" width="17.69140625" customWidth="1"/>
-    <col min="4" max="4" width="36.07421875" customWidth="1"/>
-    <col min="5" max="5" width="26.23046875" customWidth="1"/>
-    <col min="6" max="6" width="36.07421875" customWidth="1"/>
-    <col min="7" max="7" width="26.84375" customWidth="1"/>
-    <col min="8" max="8" width="4.765625" customWidth="1"/>
-    <col min="9" max="9" width="23.53515625" customWidth="1"/>
-    <col min="10" max="10" width="8.23046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="5.4609375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="5" max="5" width="26.1640625" customWidth="1"/>
+    <col min="6" max="6" width="36" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+    <col min="8" max="8" width="4.83203125" customWidth="1"/>
+    <col min="9" max="9" width="23.5" customWidth="1"/>
+    <col min="10" max="10" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -17222,25 +17218,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>99</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>101</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>3</v>
@@ -17252,7 +17248,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>215</v>
       </c>
@@ -17294,7 +17290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>216</v>
       </c>
@@ -17336,7 +17332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>217</v>
       </c>
@@ -17378,7 +17374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>218</v>
       </c>
@@ -17420,7 +17416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>219</v>
       </c>
@@ -17462,7 +17458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>220</v>
       </c>
@@ -17504,7 +17500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>221</v>
       </c>
@@ -17546,7 +17542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>222</v>
       </c>
@@ -17588,7 +17584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>223</v>
       </c>
@@ -17630,7 +17626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>224</v>
       </c>
@@ -17672,7 +17668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>225</v>
       </c>
@@ -17714,7 +17710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>226</v>
       </c>
@@ -17756,7 +17752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>227</v>
       </c>
@@ -17798,7 +17794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>228</v>
       </c>
@@ -17840,7 +17836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>229</v>
       </c>
@@ -17882,7 +17878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>230</v>
       </c>
@@ -17924,7 +17920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>231</v>
       </c>
@@ -17966,7 +17962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>232</v>
       </c>
@@ -18008,7 +18004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>233</v>
       </c>
@@ -18050,7 +18046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>234</v>
       </c>
@@ -18092,7 +18088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>235</v>
       </c>
@@ -18134,7 +18130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>236</v>
       </c>
@@ -18176,7 +18172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>237</v>
       </c>
@@ -18218,7 +18214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>238</v>
       </c>
@@ -18260,7 +18256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>239</v>
       </c>
@@ -18302,7 +18298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>240</v>
       </c>
@@ -18344,7 +18340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>241</v>
       </c>
@@ -18386,7 +18382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>242</v>
       </c>
@@ -18428,7 +18424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>243</v>
       </c>
@@ -18470,7 +18466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>244</v>
       </c>
@@ -18512,7 +18508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>245</v>
       </c>
@@ -18554,7 +18550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>246</v>
       </c>
@@ -18596,7 +18592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>247</v>
       </c>
@@ -18638,7 +18634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>248</v>
       </c>
@@ -18680,7 +18676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>249</v>
       </c>
@@ -18722,9 +18718,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B37" t="s">
         <v>11</v>
@@ -18764,9 +18760,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
@@ -18806,9 +18802,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
@@ -18848,9 +18844,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B40" t="s">
         <v>11</v>
@@ -18890,9 +18886,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
@@ -18932,7 +18928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>250</v>
       </c>
@@ -18974,7 +18970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>251</v>
       </c>
@@ -19016,7 +19012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>252</v>
       </c>
@@ -19058,7 +19054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>253</v>
       </c>
@@ -19100,7 +19096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>254</v>
       </c>
@@ -19142,7 +19138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>255</v>
       </c>
@@ -19184,7 +19180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>256</v>
       </c>
@@ -19226,7 +19222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>257</v>
       </c>
@@ -19268,7 +19264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>258</v>
       </c>
@@ -19310,7 +19306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>259</v>
       </c>
@@ -19352,7 +19348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>260</v>
       </c>
@@ -19394,7 +19390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>261</v>
       </c>
@@ -19436,7 +19432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>262</v>
       </c>
@@ -19478,7 +19474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>263</v>
       </c>
@@ -19520,7 +19516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>264</v>
       </c>
@@ -19570,23 +19566,23 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M18"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.23046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.4609375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.84375" customWidth="1"/>
-    <col min="4" max="4" width="15.07421875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.53515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.4609375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.3046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.4609375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.07421875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -19597,13 +19593,13 @@
         <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
@@ -19627,7 +19623,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>265</v>
       </c>
@@ -19670,7 +19666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>267</v>
       </c>
@@ -19713,7 +19709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>269</v>
       </c>
@@ -19756,7 +19752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>271</v>
       </c>
@@ -19799,7 +19795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>273</v>
       </c>
@@ -19842,7 +19838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>275</v>
       </c>
@@ -19885,12 +19881,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B8" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C8" t="s">
         <v>84</v>
@@ -19928,7 +19924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>277</v>
       </c>
@@ -19971,7 +19967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>279</v>
       </c>
@@ -20014,7 +20010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>281</v>
       </c>
@@ -20057,7 +20053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>283</v>
       </c>
@@ -20100,7 +20096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>285</v>
       </c>
@@ -20143,7 +20139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>287</v>
       </c>
@@ -20186,7 +20182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>289</v>
       </c>
@@ -20229,7 +20225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>291</v>
       </c>
@@ -20272,7 +20268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>293</v>
       </c>
@@ -20315,7 +20311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>295</v>
       </c>
@@ -20368,22 +20364,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:L42"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.84375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.3046875" customWidth="1"/>
-    <col min="4" max="4" width="36.53515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.4609375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.4609375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.07421875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20391,13 +20387,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -20421,7 +20417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -20461,7 +20457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -20501,7 +20497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -20541,7 +20537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -20581,7 +20577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -20621,7 +20617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -20661,7 +20657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -20701,7 +20697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -20741,7 +20737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -20781,7 +20777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -20821,7 +20817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -20861,7 +20857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -20901,7 +20897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -20941,7 +20937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -20981,7 +20977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -21021,7 +21017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -21061,7 +21057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -21101,7 +21097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -21141,7 +21137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -21181,7 +21177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>45</v>
       </c>
@@ -21221,7 +21217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -21261,7 +21257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -21301,7 +21297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -21341,7 +21337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>51</v>
       </c>
@@ -21381,7 +21377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>52</v>
       </c>
@@ -21421,7 +21417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -21461,7 +21457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>57</v>
       </c>
@@ -21501,7 +21497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>59</v>
       </c>
@@ -21541,7 +21537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -21581,7 +21577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -21621,7 +21617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>64</v>
       </c>
@@ -21661,7 +21657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>65</v>
       </c>
@@ -21701,7 +21697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>66</v>
       </c>
@@ -21741,7 +21737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -21781,7 +21777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>71</v>
       </c>
@@ -21821,7 +21817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>73</v>
       </c>
@@ -21861,7 +21857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>75</v>
       </c>
@@ -21901,7 +21897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>77</v>
       </c>
@@ -21941,7 +21937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>78</v>
       </c>
@@ -21981,7 +21977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>79</v>
       </c>
@@ -22021,7 +22017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -22076,21 +22072,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:L29"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.07421875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="36" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.3046875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.4609375" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.4609375" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.23046875" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -22110,25 +22106,25 @@
         <v>82</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>924</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>971</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>925</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>926</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>927</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>928</v>
-      </c>
       <c r="L1" s="17" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>658</v>
       </c>
@@ -22143,7 +22139,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="F2" t="s">
         <v>84</v>
@@ -22173,7 +22169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>660</v>
       </c>
@@ -22188,7 +22184,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="F3" t="s">
         <v>84</v>
@@ -22218,22 +22214,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>662</v>
       </c>
-      <c r="B4" t="s">
-        <v>663</v>
+      <c r="B4" s="20" t="s">
+        <v>972</v>
       </c>
       <c r="C4" t="str">
         <f t="shared" si="0"/>
-        <v>metadata_admin1_1</v>
+        <v>refdata_admin1_1</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>787</v>
+        <v>973</v>
       </c>
       <c r="F4" t="s">
         <v>84</v>
@@ -22252,7 +22248,7 @@
       </c>
       <c r="J4" s="18" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="18" t="b">
         <f t="shared" si="4"/>
@@ -22263,12 +22259,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>85</v>
       </c>
       <c r="B5" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C5" t="str">
         <f t="shared" si="0"/>
@@ -22278,7 +22274,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="F5" t="s">
         <v>84</v>
@@ -22308,12 +22304,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>88</v>
       </c>
       <c r="B6" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
@@ -22323,7 +22319,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="F6" t="s">
         <v>87</v>
@@ -22353,12 +22349,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>91</v>
       </c>
       <c r="B7" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="0"/>
@@ -22368,7 +22364,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="F7" t="s">
         <v>90</v>
@@ -22398,12 +22394,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>94</v>
       </c>
       <c r="B8" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="0"/>
@@ -22413,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="F8" t="s">
         <v>93</v>
@@ -22443,12 +22439,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>97</v>
       </c>
       <c r="B9" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="0"/>
@@ -22458,7 +22454,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="F9" t="s">
         <v>96</v>
@@ -22488,12 +22484,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="0"/>
@@ -22503,7 +22499,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F10" t="s">
         <v>84</v>
@@ -22533,12 +22529,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="0"/>
@@ -22548,7 +22544,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F11" t="s">
         <v>84</v>
@@ -22578,12 +22574,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C12" t="str">
         <f t="shared" si="0"/>
@@ -22593,7 +22589,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F12" t="s">
         <v>84</v>
@@ -22623,12 +22619,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C13" t="str">
         <f t="shared" si="0"/>
@@ -22638,7 +22634,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F13" t="s">
         <v>84</v>
@@ -22668,12 +22664,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C14" t="str">
         <f t="shared" si="0"/>
@@ -22683,7 +22679,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F14" t="s">
         <v>87</v>
@@ -22713,12 +22709,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C15" t="str">
         <f t="shared" si="0"/>
@@ -22728,7 +22724,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F15" t="s">
         <v>87</v>
@@ -22758,12 +22754,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="0"/>
@@ -22773,7 +22769,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F16" t="s">
         <v>87</v>
@@ -22803,12 +22799,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="0"/>
@@ -22818,7 +22814,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F17" t="s">
         <v>87</v>
@@ -22848,12 +22844,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>
@@ -22863,7 +22859,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F18" t="s">
         <v>90</v>
@@ -22893,12 +22889,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="0"/>
@@ -22908,7 +22904,7 @@
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F19" t="s">
         <v>90</v>
@@ -22938,12 +22934,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="0"/>
@@ -22953,7 +22949,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F20" t="s">
         <v>90</v>
@@ -22983,12 +22979,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="0"/>
@@ -22998,7 +22994,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F21" t="s">
         <v>90</v>
@@ -23028,12 +23024,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" si="0"/>
@@ -23043,7 +23039,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F22" t="s">
         <v>93</v>
@@ -23073,12 +23069,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>56</v>
       </c>
       <c r="B23" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
@@ -23088,7 +23084,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F23" t="s">
         <v>93</v>
@@ -23118,12 +23114,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>58</v>
       </c>
       <c r="B24" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -23133,7 +23129,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F24" t="s">
         <v>93</v>
@@ -23163,12 +23159,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -23178,7 +23174,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F25" t="s">
         <v>93</v>
@@ -23208,12 +23204,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -23223,7 +23219,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F26" t="s">
         <v>96</v>
@@ -23253,12 +23249,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -23268,7 +23264,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F27" t="s">
         <v>96</v>
@@ -23298,12 +23294,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>72</v>
       </c>
       <c r="B28" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -23313,7 +23309,7 @@
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F28" t="s">
         <v>96</v>
@@ -23343,12 +23339,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -23358,7 +23354,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F29" t="s">
         <v>96</v>
@@ -23389,6 +23385,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B4" r:id="rId1" xr:uid="{6720259D-8B8B-404B-BBFC-255A858BC201}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23396,21 +23395,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.07421875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.07421875" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.23046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.07421875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.23046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.53515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" style="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="36" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.4609375" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -23418,33 +23417,33 @@
         <v>656</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>722</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>723</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>657</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>82</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B2" t="s">
         <v>661</v>
@@ -23454,13 +23453,13 @@
         <v>app_admin1_1</v>
       </c>
       <c r="D2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E2" s="2">
         <v>45743.390918726589</v>
       </c>
       <c r="F2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="G2" t="s">
         <v>658</v>
@@ -23477,25 +23476,25 @@
         <v>org1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>727</v>
-      </c>
-      <c r="B3" t="s">
-        <v>663</v>
+        <v>726</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>972</v>
       </c>
       <c r="C3" s="6" t="str">
         <f t="shared" ref="C3:C28" si="0">LEFT($B3,LEN($B3)-9)</f>
-        <v>metadata_admin1_1</v>
+        <v>refdata_admin1_1</v>
       </c>
       <c r="D3" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E3" s="2">
         <v>45743.390918741461</v>
       </c>
       <c r="F3" t="s">
-        <v>787</v>
+        <v>973</v>
       </c>
       <c r="G3" t="s">
         <v>660</v>
@@ -23512,25 +23511,25 @@
         <v>org1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C4" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_admin1_1</v>
       </c>
       <c r="D4" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E4" s="2">
         <v>45743.390918746562</v>
       </c>
       <c r="F4" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="G4" t="s">
         <v>660</v>
@@ -23547,25 +23546,25 @@
         <v>org1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C5" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_admin2_1</v>
       </c>
       <c r="D5" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E5" s="2">
         <v>45743.390918763551</v>
       </c>
       <c r="F5" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="G5" t="s">
         <v>660</v>
@@ -23582,25 +23581,25 @@
         <v>org2</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B6" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C6" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_admin3_1</v>
       </c>
       <c r="D6" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E6" s="2">
         <v>45743.390918772537</v>
       </c>
       <c r="F6" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="G6" t="s">
         <v>660</v>
@@ -23617,25 +23616,25 @@
         <v>org3</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C7" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_admin4_1</v>
       </c>
       <c r="D7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E7" s="2">
         <v>45743.390918781181</v>
       </c>
       <c r="F7" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="G7" t="s">
         <v>660</v>
@@ -23652,25 +23651,25 @@
         <v>org4</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B8" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C8" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_admin5_1</v>
       </c>
       <c r="D8" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E8" s="2">
         <v>45743.3909187889</v>
       </c>
       <c r="F8" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="G8" t="s">
         <v>660</v>
@@ -23687,25 +23686,25 @@
         <v>org5</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B9" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C9" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user1_1</v>
       </c>
       <c r="D9" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E9" s="2">
         <v>45743.390918796598</v>
       </c>
       <c r="F9" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G9" t="s">
         <v>660</v>
@@ -23722,25 +23721,25 @@
         <v>org1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B10" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C10" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user1_2</v>
       </c>
       <c r="D10" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E10" s="2">
         <v>45743.390918801953</v>
       </c>
       <c r="F10" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G10" t="s">
         <v>660</v>
@@ -23757,25 +23756,25 @@
         <v>org1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B11" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C11" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user1_3</v>
       </c>
       <c r="D11" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E11" s="2">
         <v>45743.390918807163</v>
       </c>
       <c r="F11" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G11" t="s">
         <v>660</v>
@@ -23792,25 +23791,25 @@
         <v>org1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B12" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C12" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user1_4</v>
       </c>
       <c r="D12" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E12" s="2">
         <v>45743.3909188123</v>
       </c>
       <c r="F12" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G12" t="s">
         <v>660</v>
@@ -23827,25 +23826,25 @@
         <v>org1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B13" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C13" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user2_1</v>
       </c>
       <c r="D13" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E13" s="2">
         <v>45743.390918817633</v>
       </c>
       <c r="F13" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G13" t="s">
         <v>660</v>
@@ -23862,25 +23861,25 @@
         <v>org2</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B14" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C14" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user2_2</v>
       </c>
       <c r="D14" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E14" s="2">
         <v>45743.390918822908</v>
       </c>
       <c r="F14" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G14" t="s">
         <v>660</v>
@@ -23897,25 +23896,25 @@
         <v>org2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B15" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C15" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user2_3</v>
       </c>
       <c r="D15" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E15" s="2">
         <v>45743.390918828743</v>
       </c>
       <c r="F15" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G15" t="s">
         <v>660</v>
@@ -23932,25 +23931,25 @@
         <v>org2</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B16" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C16" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user2_4</v>
       </c>
       <c r="D16" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E16" s="2">
         <v>45743.390918834302</v>
       </c>
       <c r="F16" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G16" t="s">
         <v>660</v>
@@ -23967,25 +23966,25 @@
         <v>org2</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B17" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C17" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user3_1</v>
       </c>
       <c r="D17" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E17" s="2">
         <v>45743.390918839839</v>
       </c>
       <c r="F17" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G17" t="s">
         <v>660</v>
@@ -24002,25 +24001,25 @@
         <v>org3</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B18" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C18" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user3_2</v>
       </c>
       <c r="D18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E18" s="2">
         <v>45743.390918845187</v>
       </c>
       <c r="F18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G18" t="s">
         <v>660</v>
@@ -24037,25 +24036,25 @@
         <v>org3</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B19" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C19" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user3_3</v>
       </c>
       <c r="D19" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E19" s="2">
         <v>45743.390918851088</v>
       </c>
       <c r="F19" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G19" t="s">
         <v>660</v>
@@ -24072,25 +24071,25 @@
         <v>org3</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B20" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C20" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user3_4</v>
       </c>
       <c r="D20" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E20" s="2">
         <v>45743.39091885696</v>
       </c>
       <c r="F20" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G20" t="s">
         <v>660</v>
@@ -24107,25 +24106,25 @@
         <v>org3</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B21" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C21" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user4_1</v>
       </c>
       <c r="D21" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E21" s="2">
         <v>45743.390918862962</v>
       </c>
       <c r="F21" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G21" t="s">
         <v>660</v>
@@ -24142,25 +24141,25 @@
         <v>org4</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B22" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C22" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user4_2</v>
       </c>
       <c r="D22" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E22" s="2">
         <v>45743.390918868739</v>
       </c>
       <c r="F22" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G22" t="s">
         <v>660</v>
@@ -24177,25 +24176,25 @@
         <v>org4</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B23" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C23" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user4_3</v>
       </c>
       <c r="D23" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E23" s="2">
         <v>45743.390918874728</v>
       </c>
       <c r="F23" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G23" t="s">
         <v>660</v>
@@ -24212,25 +24211,25 @@
         <v>org4</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B24" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C24" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user4_4</v>
       </c>
       <c r="D24" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E24" s="2">
         <v>45743.390918881109</v>
       </c>
       <c r="F24" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G24" t="s">
         <v>660</v>
@@ -24247,25 +24246,25 @@
         <v>org4</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B25" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C25" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user5_1</v>
       </c>
       <c r="D25" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E25" s="2">
         <v>45743.390918887373</v>
       </c>
       <c r="F25" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G25" t="s">
         <v>660</v>
@@ -24282,25 +24281,25 @@
         <v>org5</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B26" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C26" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user5_2</v>
       </c>
       <c r="D26" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E26" s="2">
         <v>45743.39091889358</v>
       </c>
       <c r="F26" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G26" t="s">
         <v>660</v>
@@ -24317,25 +24316,25 @@
         <v>org5</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B27" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C27" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user5_3</v>
       </c>
       <c r="D27" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E27" s="2">
         <v>45743.390918900091</v>
       </c>
       <c r="F27" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G27" t="s">
         <v>660</v>
@@ -24352,25 +24351,25 @@
         <v>org5</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B28" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C28" s="6" t="str">
         <f t="shared" si="0"/>
         <v>org_user5_4</v>
       </c>
       <c r="D28" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E28" s="2">
         <v>45743.390918906553</v>
       </c>
       <c r="F28" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G28" t="s">
         <v>660</v>
@@ -24388,6 +24387,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{C6CE08DD-189A-544E-9566-622F7BE1E7EA}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -24395,19 +24397,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.07421875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.4609375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.3046875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -24433,15 +24434,15 @@
         <v>547</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>639</v>
       </c>
       <c r="B2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D2" t="s">
         <v>653</v>
@@ -24454,15 +24455,15 @@
         <v>550</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>643</v>
       </c>
       <c r="B3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="D3" t="s">
         <v>654</v>
@@ -24475,15 +24476,15 @@
         <v>550</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>647</v>
       </c>
       <c r="B4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D4" t="s">
         <v>655</v>
@@ -24504,27 +24505,27 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:P10"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.23046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.69140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.23046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.53515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.23046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.23046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.84375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.23046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.3046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.23046875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.53515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.69140625" style="13" customWidth="1"/>
-    <col min="16" max="16" width="5.765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" style="13" customWidth="1"/>
+    <col min="16" max="16" width="5.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -24574,7 +24575,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>548</v>
       </c>
@@ -24582,7 +24583,7 @@
         <v>639</v>
       </c>
       <c r="E2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -24591,7 +24592,7 @@
         <v>640</v>
       </c>
       <c r="H2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O2" s="13" t="str">
         <f>"col"&amp;$E2&amp;"("&amp;$H2&amp;")"</f>
@@ -24601,7 +24602,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>551</v>
       </c>
@@ -24609,7 +24610,7 @@
         <v>639</v>
       </c>
       <c r="E3" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -24618,7 +24619,7 @@
         <v>641</v>
       </c>
       <c r="H3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O3" s="13" t="str">
         <f t="shared" ref="O3:O10" si="0">"col"&amp;$E3&amp;"("&amp;$H3&amp;")"</f>
@@ -24628,7 +24629,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>553</v>
       </c>
@@ -24636,7 +24637,7 @@
         <v>639</v>
       </c>
       <c r="E4" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -24645,7 +24646,7 @@
         <v>642</v>
       </c>
       <c r="H4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O4" s="13" t="str">
         <f t="shared" si="0"/>
@@ -24655,7 +24656,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>555</v>
       </c>
@@ -24663,7 +24664,7 @@
         <v>643</v>
       </c>
       <c r="E5" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -24672,7 +24673,7 @@
         <v>644</v>
       </c>
       <c r="H5" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O5" s="13" t="str">
         <f t="shared" si="0"/>
@@ -24682,7 +24683,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>557</v>
       </c>
@@ -24690,7 +24691,7 @@
         <v>643</v>
       </c>
       <c r="E6" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -24699,7 +24700,7 @@
         <v>645</v>
       </c>
       <c r="H6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O6" s="13" t="str">
         <f t="shared" si="0"/>
@@ -24709,7 +24710,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>559</v>
       </c>
@@ -24717,7 +24718,7 @@
         <v>643</v>
       </c>
       <c r="E7" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -24726,7 +24727,7 @@
         <v>646</v>
       </c>
       <c r="H7" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O7" s="13" t="str">
         <f t="shared" si="0"/>
@@ -24736,7 +24737,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>561</v>
       </c>
@@ -24744,7 +24745,7 @@
         <v>647</v>
       </c>
       <c r="E8" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -24753,7 +24754,7 @@
         <v>648</v>
       </c>
       <c r="H8" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O8" s="13" t="str">
         <f t="shared" si="0"/>
@@ -24763,7 +24764,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>563</v>
       </c>
@@ -24771,7 +24772,7 @@
         <v>647</v>
       </c>
       <c r="E9" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -24780,7 +24781,7 @@
         <v>649</v>
       </c>
       <c r="H9" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O9" s="13" t="str">
         <f t="shared" si="0"/>
@@ -24790,7 +24791,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>565</v>
       </c>
@@ -24798,7 +24799,7 @@
         <v>647</v>
       </c>
       <c r="E10" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="F10">
         <v>3</v>
@@ -24807,7 +24808,7 @@
         <v>650</v>
       </c>
       <c r="H10" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O10" s="13" t="str">
         <f t="shared" si="0"/>
@@ -24825,12 +24826,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BFE9DBA-4D09-4E45-A394-72AC78245E1D}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="34.765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -24838,47 +24839,47 @@
         <v>98</v>
       </c>
       <c r="C1" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>336</v>
       </c>
       <c r="B2" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>340</v>
       </c>
       <c r="B3" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>344</v>
       </c>
       <c r="B4" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>348</v>
       </c>
       <c r="B5" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>352</v>
       </c>
       <c r="B6" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
     </row>
   </sheetData>
@@ -24890,14 +24891,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFBF5204-3F7C-438F-A194-7543BC84CF2A}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.07421875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -24905,62 +24906,62 @@
         <v>98</v>
       </c>
       <c r="C1" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>337</v>
       </c>
       <c r="B2" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="C2" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>341</v>
       </c>
       <c r="B3" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="C3" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>345</v>
       </c>
       <c r="B4" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="C4" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>349</v>
       </c>
       <c r="B5" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="C5" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>353</v>
       </c>
       <c r="B6" t="s">
+        <v>955</v>
+      </c>
+      <c r="C6" t="s">
         <v>958</v>
-      </c>
-      <c r="C6" t="s">
-        <v>961</v>
       </c>
     </row>
   </sheetData>
@@ -24972,19 +24973,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.07421875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.765625" style="13" customWidth="1"/>
-    <col min="6" max="6" width="6.921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.3046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.3046875" style="13" customWidth="1"/>
-    <col min="9" max="9" width="15.07421875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.83203125" style="13" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.33203125" style="13" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -24998,7 +24999,7 @@
         <v>330</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>331</v>
@@ -25007,13 +25008,13 @@
         <v>332</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>334</v>
       </c>
@@ -25035,7 +25036,7 @@
         <v>etiological_agent1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>338</v>
       </c>
@@ -25057,7 +25058,7 @@
         <v>etiological_agent2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>342</v>
       </c>
@@ -25079,7 +25080,7 @@
         <v>etiological_agent3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>346</v>
       </c>
@@ -25101,7 +25102,7 @@
         <v>etiological_agent4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>350</v>
       </c>

--- a/test/casedb/integration/case_access/test_case_access.xlsx
+++ b/test/casedb/integration/case_access/test_case_access.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivo_v\Documents\gen-epix-api\test\casedb\integration\case_access\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC56F4C-8C83-4C95-AF98-992B989F9472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB63340-ABA8-4F02-AA39-53A97332F0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="913" firstSheet="2" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="913" firstSheet="2" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Organization" sheetId="17" r:id="rId1"/>
@@ -36,7 +36,7 @@
     <sheet name="OrganizationShareCasePolicy" sheetId="22" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">CaseCrudCommand!$A$1:$AT$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">CaseCrudCommand!$A$1:$AU$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">CaseTypeSetMember!$A$1:$G$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">OrganizationAccessCasePolicy!$A$1:$U$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">UserAccessCasePolicy!$A$1:$V$11</definedName>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1686" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="725">
   <si>
     <t>id</t>
   </si>
@@ -2253,6 +2253,9 @@
   </si>
   <si>
     <t>CREATE_CASES</t>
+  </si>
+  <si>
+    <t>dm.is_active</t>
   </si>
 </sst>
 </file>
@@ -6370,5067 +6373,5167 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E0C7C33-6768-4AAE-A57E-F80585DED472}">
-  <dimension ref="A1:AT33"/>
+  <dimension ref="A1:AU33"/>
   <sheetFormatPr defaultColWidth="5.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.77734375" style="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="62.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="41.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="45" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="30.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="56.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="38.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="28.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="38.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="34.77734375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="32.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="35.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="66.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="66.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="59.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="60" style="6" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="32.44140625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="35.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="66.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="66.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="59.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="60" style="6" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="32.44140625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="35.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="66.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="66.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="59.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="60" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="3" max="3" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" style="19" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="37.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="62.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="41.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="45" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="56.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="35" style="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="38.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="28.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="38.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="35.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="66.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="66.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="59.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="60" style="6" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="35.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="66.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="66.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="59.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="60" style="6" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="35.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="66.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="66.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="59.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="60" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>589</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>724</v>
       </c>
       <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
         <v>592</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>719</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>590</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="G1" s="19" t="s">
         <v>600</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>667</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>671</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>668</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>676</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>601</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>602</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>670</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>677</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>603</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>604</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>591</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>593</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>661</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>666</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>594</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>595</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>679</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>596</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>597</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>598</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>599</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>678</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>682</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>683</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>688</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>689</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>663</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>709</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>680</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>684</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>685</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>690</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>691</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>664</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>710</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>681</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
         <v>686</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AS1" s="6" t="s">
         <v>687</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>692</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AU1" s="6" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>608</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>443</v>
       </c>
-      <c r="D2" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C2,User!$A:$A,0))</f>
+      <c r="E2" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D2,User!$A:$A,0))</f>
         <v>root1_1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>662</v>
       </c>
-      <c r="F2" s="19" t="b">
-        <f t="shared" ref="F2:F33" si="0">IF($E2="CREATE",$H2,IF($E2="CREATE_CASES",OR($H2,AND($J2,$K2,$N2,$O2,$AD2,AF2,$AK2,$AM2,$AR2,$AT2)),"TBD"))</f>
-        <v>1</v>
-      </c>
-      <c r="G2" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C2,User!$A:$A,0))</f>
+      <c r="G2" s="19" t="b">
+        <f t="shared" ref="G2:G33" si="0">IF($F2="CREATE",$I2,IF($F2="CREATE_CASES",OR($I2,AND($K2,$L2,$O2,$P2,$AE2,AG2,$AL2,$AN2,$AS2,$AU2)),"TBD"))</f>
+        <v>1</v>
+      </c>
+      <c r="H2" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D2,User!$A:$A,0))</f>
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
       </c>
-      <c r="H2" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C2,User!$A:$A,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I2" s="6">
-        <f>IF(ISNA(MATCH($G2&amp;"|"&amp;$V2,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G2&amp;"|"&amp;$V2,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I2" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D2,User!$A:$A,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J2" s="6">
+        <f>IF(ISNA(MATCH($H2&amp;"|"&amp;$W2,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H2&amp;"|"&amp;$W2,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J2" ca="1">IF($I2="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I2)&amp;"|"&amp;$R2,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>1</v>
-      </c>
       <c r="K2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K2" ca="1">IF($I2="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I2),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I2)&amp;"|"&amp;$R2,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K2" ca="1">IF($J2="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J2)&amp;"|"&amp;$S2,CaseTypeSetMember!$H:$H,0))))</f>
         <v>1</v>
       </c>
       <c r="L2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L2" ca="1">IF($I2="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I2),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I2)&amp;"|"&amp;$R2,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="M2" s="6" t="str">
-        <f>IF(ISNA(MATCH($C2&amp;"|"&amp;$V2,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C2&amp;"|"&amp;$V2,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L2" ca="1">IF($J2="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J2),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J2)&amp;"|"&amp;$S2,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M2" ca="1">IF($J2="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J2),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J2)&amp;"|"&amp;$S2,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="N2" s="6" t="str">
+        <f>IF(ISNA(MATCH($D2&amp;"|"&amp;$W2,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D2&amp;"|"&amp;$W2,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N2" ca="1">IF($M2="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M2)&amp;"|"&amp;$R2,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O2" ca="1">IF($M2="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M2),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M2)&amp;"|"&amp;$R2,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O2" ca="1">IF($N2="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N2)&amp;"|"&amp;$S2,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P2" ca="1">IF($M2="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M2),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M2)&amp;"|"&amp;$R2,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q2" t="s">
+        <f t="array" aca="1" ref="P2" ca="1">IF($N2="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N2),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N2)&amp;"|"&amp;$S2,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q2" ca="1">IF($N2="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N2),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N2)&amp;"|"&amp;$S2,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R2" t="s">
         <v>607</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>119</v>
       </c>
-      <c r="S2" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R2,CaseType!$A:$A,0))</f>
+      <c r="T2" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S2,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T2" s="6" t="b">
-        <f>AND(IF($Z2="",TRUE,$R2=INDEX(CaseTypeCol!$B:$B,MATCH($Z2,CaseTypeCol!$A:$A,0))),IF($AG2="",TRUE,$R2=INDEX(CaseTypeCol!$B:$B,MATCH($AG2,CaseTypeCol!$A:$A,0))),IF($AN2="",TRUE,$R2=INDEX(CaseTypeCol!$B:$B,MATCH($AN2,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="U2" s="6" t="b">
+        <f>AND(IF($AA2="",TRUE,$S2=INDEX(CaseTypeCol!$B:$B,MATCH($AA2,CaseTypeCol!$A:$A,0))),IF($AH2="",TRUE,$S2=INDEX(CaseTypeCol!$B:$B,MATCH($AH2,CaseTypeCol!$A:$A,0))),IF($AO2="",TRUE,$S2=INDEX(CaseTypeCol!$B:$B,MATCH($AO2,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
         <v>11</v>
       </c>
-      <c r="W2" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V2,DataCollection!$A:$A,0))</f>
+      <c r="X2" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W2,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y2" s="14">
+      <c r="Z2" s="14">
         <v>36526</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>142</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>665</v>
       </c>
-      <c r="AB2" s="6" t="str">
-        <f>IF($Z2="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z2,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC2" s="6" t="str">
+        <f>IF($AA2="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA2,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC2" ca="1">IF($Z2="",TRUE,IF($I2="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I2)&amp;"|"&amp;$Z2,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AD2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD2" ca="1">IF($Z2="",TRUE,IF($I2="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I2)&amp;"|"&amp;$Z2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD2" ca="1">IF($AA2="",TRUE,IF($J2="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J2)&amp;"|"&amp;$AA2,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AE2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE2" ca="1">IF($Z2="",TRUE,IF($M2="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M2)&amp;"|"&amp;$Z2,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
+        <f t="array" aca="1" ref="AE2" ca="1">IF($AA2="",TRUE,IF($J2="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J2)&amp;"|"&amp;$AA2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
       </c>
       <c r="AF2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF2" ca="1">IF($Z2="",TRUE,IF($M2="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M2)&amp;"|"&amp;$Z2,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI2" s="6" t="str">
-        <f>IF($AG2="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG2,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF2" ca="1">IF($AA2="",TRUE,IF($N2="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N2)&amp;"|"&amp;$AA2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG2" ca="1">IF($AA2="",TRUE,IF($N2="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N2)&amp;"|"&amp;$AA2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="6" t="str">
+        <f>IF($AH2="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH2,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ2" ca="1">IF($AG2="",TRUE,IF($I2="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I2)&amp;"|"&amp;$AG2,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK2" ca="1">IF($AG2="",TRUE,IF($I2="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I2)&amp;"|"&amp;$AG2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK2" ca="1">IF($AH2="",TRUE,IF($J2="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J2)&amp;"|"&amp;$AH2,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL2" ca="1">IF($AG2="",TRUE,IF($M2="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M2)&amp;"|"&amp;$AG2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL2" ca="1">IF($AH2="",TRUE,IF($J2="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J2)&amp;"|"&amp;$AH2,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM2" ca="1">IF($AG2="",TRUE,IF($M2="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M2)&amp;"|"&amp;$AG2,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP2" s="6" t="str">
-        <f>IF($AN2="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN2,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM2" ca="1">IF($AH2="",TRUE,IF($N2="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N2)&amp;"|"&amp;$AH2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN2" ca="1">IF($AH2="",TRUE,IF($N2="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N2)&amp;"|"&amp;$AH2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ2" s="6" t="str">
+        <f>IF($AO2="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO2,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ2" ca="1">IF($AN2="",TRUE,IF($I2="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I2)&amp;"|"&amp;$AN2,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR2" ca="1">IF($AN2="",TRUE,IF($I2="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I2)&amp;"|"&amp;$AN2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR2" ca="1">IF($AO2="",TRUE,IF($J2="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J2)&amp;"|"&amp;$AO2,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS2" ca="1">IF($AN2="",TRUE,IF($M2="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M2)&amp;"|"&amp;$AN2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS2" ca="1">IF($AO2="",TRUE,IF($J2="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J2)&amp;"|"&amp;$AO2,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT2" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT2" ca="1">IF($AN2="",TRUE,IF($M2="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M2)&amp;"|"&amp;$AN2,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT2" ca="1">IF($AO2="",TRUE,IF($N2="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N2)&amp;"|"&amp;$AO2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU2" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU2" ca="1">IF($AO2="",TRUE,IF($N2="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N2)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N2)&amp;"|"&amp;$AO2,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
         <v>606</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>445</v>
       </c>
-      <c r="D3" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C3,User!$A:$A,0))</f>
+      <c r="E3" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D3,User!$A:$A,0))</f>
         <v>app_admin1_1</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>662</v>
       </c>
-      <c r="F3" s="19" t="b">
+      <c r="G3" s="19" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G3" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C3,User!$A:$A,0))</f>
+      <c r="H3" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D3,User!$A:$A,0))</f>
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
       </c>
-      <c r="H3" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C3,User!$A:$A,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I3" s="6">
-        <f>IF(ISNA(MATCH($G3&amp;"|"&amp;$V3,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G3&amp;"|"&amp;$V3,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I3" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D3,User!$A:$A,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J3" s="6">
+        <f>IF(ISNA(MATCH($H3&amp;"|"&amp;$W3,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H3&amp;"|"&amp;$W3,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v>2</v>
       </c>
-      <c r="J3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J3" ca="1">IF($I3="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I3)&amp;"|"&amp;$R3,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>1</v>
-      </c>
       <c r="K3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K3" ca="1">IF($I3="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I3),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I3)&amp;"|"&amp;$R3,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K3" ca="1">IF($J3="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J3)&amp;"|"&amp;$S3,CaseTypeSetMember!$H:$H,0))))</f>
         <v>1</v>
       </c>
       <c r="L3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L3" ca="1">IF($I3="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I3),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I3)&amp;"|"&amp;$R3,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="M3" s="6" t="str">
-        <f>IF(ISNA(MATCH($C3&amp;"|"&amp;$V3,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C3&amp;"|"&amp;$V3,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L3" ca="1">IF($J3="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J3),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J3)&amp;"|"&amp;$S3,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M3" ca="1">IF($J3="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J3),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J3)&amp;"|"&amp;$S3,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="N3" s="6" t="str">
+        <f>IF(ISNA(MATCH($D3&amp;"|"&amp;$W3,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D3&amp;"|"&amp;$W3,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N3" ca="1">IF($M3="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M3)&amp;"|"&amp;$R3,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O3" ca="1">IF($M3="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M3),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M3)&amp;"|"&amp;$R3,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O3" ca="1">IF($N3="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N3)&amp;"|"&amp;$S3,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P3" ca="1">IF($M3="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M3),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M3)&amp;"|"&amp;$R3,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q3" t="s">
+        <f t="array" aca="1" ref="P3" ca="1">IF($N3="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N3),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N3)&amp;"|"&amp;$S3,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q3" ca="1">IF($N3="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N3),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N3)&amp;"|"&amp;$S3,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R3" t="s">
         <v>605</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>119</v>
       </c>
-      <c r="S3" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R3,CaseType!$A:$A,0))</f>
+      <c r="T3" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S3,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T3" s="6" t="b">
-        <f>AND(IF($Z3="",TRUE,$R3=INDEX(CaseTypeCol!$B:$B,MATCH($Z3,CaseTypeCol!$A:$A,0))),IF($AG3="",TRUE,$R3=INDEX(CaseTypeCol!$B:$B,MATCH($AG3,CaseTypeCol!$A:$A,0))),IF($AN3="",TRUE,$R3=INDEX(CaseTypeCol!$B:$B,MATCH($AN3,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V3" t="s">
+      <c r="U3" s="6" t="b">
+        <f>AND(IF($AA3="",TRUE,$S3=INDEX(CaseTypeCol!$B:$B,MATCH($AA3,CaseTypeCol!$A:$A,0))),IF($AH3="",TRUE,$S3=INDEX(CaseTypeCol!$B:$B,MATCH($AH3,CaseTypeCol!$A:$A,0))),IF($AO3="",TRUE,$S3=INDEX(CaseTypeCol!$B:$B,MATCH($AO3,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W3" t="s">
         <v>11</v>
       </c>
-      <c r="W3" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V3,DataCollection!$A:$A,0))</f>
+      <c r="X3" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W3,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y3" s="14">
+      <c r="Z3" s="14">
         <v>36526</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AA3" t="s">
         <v>142</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>665</v>
       </c>
-      <c r="AB3" s="6" t="str">
-        <f>IF($Z3="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z3,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC3" s="6" t="str">
+        <f>IF($AA3="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA3,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC3" ca="1">IF($Z3="",TRUE,IF($I3="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I3)&amp;"|"&amp;$Z3,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AD3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD3" ca="1">IF($Z3="",TRUE,IF($I3="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I3)&amp;"|"&amp;$Z3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD3" ca="1">IF($AA3="",TRUE,IF($J3="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J3)&amp;"|"&amp;$AA3,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AE3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE3" ca="1">IF($Z3="",TRUE,IF($M3="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M3)&amp;"|"&amp;$Z3,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
+        <f t="array" aca="1" ref="AE3" ca="1">IF($AA3="",TRUE,IF($J3="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J3)&amp;"|"&amp;$AA3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
       </c>
       <c r="AF3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF3" ca="1">IF($Z3="",TRUE,IF($M3="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M3)&amp;"|"&amp;$Z3,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI3" s="6" t="str">
-        <f>IF($AG3="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG3,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF3" ca="1">IF($AA3="",TRUE,IF($N3="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N3)&amp;"|"&amp;$AA3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG3" ca="1">IF($AA3="",TRUE,IF($N3="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N3)&amp;"|"&amp;$AA3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="6" t="str">
+        <f>IF($AH3="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH3,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ3" ca="1">IF($AG3="",TRUE,IF($I3="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I3)&amp;"|"&amp;$AG3,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK3" ca="1">IF($AG3="",TRUE,IF($I3="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I3)&amp;"|"&amp;$AG3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK3" ca="1">IF($AH3="",TRUE,IF($J3="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J3)&amp;"|"&amp;$AH3,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL3" ca="1">IF($AG3="",TRUE,IF($M3="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M3)&amp;"|"&amp;$AG3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL3" ca="1">IF($AH3="",TRUE,IF($J3="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J3)&amp;"|"&amp;$AH3,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM3" ca="1">IF($AG3="",TRUE,IF($M3="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M3)&amp;"|"&amp;$AG3,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP3" s="6" t="str">
-        <f>IF($AN3="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN3,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM3" ca="1">IF($AH3="",TRUE,IF($N3="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N3)&amp;"|"&amp;$AH3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN3" ca="1">IF($AH3="",TRUE,IF($N3="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N3)&amp;"|"&amp;$AH3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ3" s="6" t="str">
+        <f>IF($AO3="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO3,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ3" ca="1">IF($AN3="",TRUE,IF($I3="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I3)&amp;"|"&amp;$AN3,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR3" ca="1">IF($AN3="",TRUE,IF($I3="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I3)&amp;"|"&amp;$AN3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR3" ca="1">IF($AO3="",TRUE,IF($J3="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J3)&amp;"|"&amp;$AO3,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS3" ca="1">IF($AN3="",TRUE,IF($M3="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M3)&amp;"|"&amp;$AN3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS3" ca="1">IF($AO3="",TRUE,IF($J3="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J3)&amp;"|"&amp;$AO3,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT3" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT3" ca="1">IF($AN3="",TRUE,IF($M3="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M3)&amp;"|"&amp;$AN3,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT3" ca="1">IF($AO3="",TRUE,IF($N3="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N3)&amp;"|"&amp;$AO3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU3" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU3" ca="1">IF($AO3="",TRUE,IF($N3="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N3)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N3)&amp;"|"&amp;$AO3,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
         <v>609</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>447</v>
       </c>
-      <c r="D4" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C4,User!$A:$A,0))</f>
+      <c r="E4" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D4,User!$A:$A,0))</f>
         <v>refdata_admin1_1</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>662</v>
       </c>
-      <c r="F4" s="19" t="b">
+      <c r="G4" s="19" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G4" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C4,User!$A:$A,0))</f>
+      <c r="H4" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D4,User!$A:$A,0))</f>
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
       </c>
-      <c r="H4" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C4,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="6">
-        <f>IF(ISNA(MATCH($G4&amp;"|"&amp;$V4,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G4&amp;"|"&amp;$V4,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I4" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D4,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <f>IF(ISNA(MATCH($H4&amp;"|"&amp;$W4,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H4&amp;"|"&amp;$W4,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v>2</v>
       </c>
-      <c r="J4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J4" ca="1">IF($I4="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I4)&amp;"|"&amp;$R4,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>1</v>
-      </c>
       <c r="K4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K4" ca="1">IF($I4="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I4),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I4)&amp;"|"&amp;$R4,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K4" ca="1">IF($J4="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J4)&amp;"|"&amp;$S4,CaseTypeSetMember!$H:$H,0))))</f>
         <v>1</v>
       </c>
       <c r="L4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L4" ca="1">IF($I4="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I4),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I4)&amp;"|"&amp;$R4,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="M4" s="6" t="str">
-        <f>IF(ISNA(MATCH($C4&amp;"|"&amp;$V4,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C4&amp;"|"&amp;$V4,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L4" ca="1">IF($J4="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J4),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J4)&amp;"|"&amp;$S4,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M4" ca="1">IF($J4="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J4),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J4)&amp;"|"&amp;$S4,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="N4" s="6" t="str">
+        <f>IF(ISNA(MATCH($D4&amp;"|"&amp;$W4,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D4&amp;"|"&amp;$W4,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N4" ca="1">IF($M4="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M4)&amp;"|"&amp;$R4,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O4" ca="1">IF($M4="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M4),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M4)&amp;"|"&amp;$R4,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O4" ca="1">IF($N4="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N4)&amp;"|"&amp;$S4,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P4" ca="1">IF($M4="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M4),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M4)&amp;"|"&amp;$R4,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q4" t="s">
+        <f t="array" aca="1" ref="P4" ca="1">IF($N4="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N4),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N4)&amp;"|"&amp;$S4,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q4" ca="1">IF($N4="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N4),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N4)&amp;"|"&amp;$S4,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R4" t="s">
         <v>635</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>119</v>
       </c>
-      <c r="S4" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R4,CaseType!$A:$A,0))</f>
+      <c r="T4" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S4,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T4" s="6" t="b">
-        <f>AND(IF($Z4="",TRUE,$R4=INDEX(CaseTypeCol!$B:$B,MATCH($Z4,CaseTypeCol!$A:$A,0))),IF($AG4="",TRUE,$R4=INDEX(CaseTypeCol!$B:$B,MATCH($AG4,CaseTypeCol!$A:$A,0))),IF($AN4="",TRUE,$R4=INDEX(CaseTypeCol!$B:$B,MATCH($AN4,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V4" t="s">
+      <c r="U4" s="6" t="b">
+        <f>AND(IF($AA4="",TRUE,$S4=INDEX(CaseTypeCol!$B:$B,MATCH($AA4,CaseTypeCol!$A:$A,0))),IF($AH4="",TRUE,$S4=INDEX(CaseTypeCol!$B:$B,MATCH($AH4,CaseTypeCol!$A:$A,0))),IF($AO4="",TRUE,$S4=INDEX(CaseTypeCol!$B:$B,MATCH($AO4,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W4" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V4,DataCollection!$A:$A,0))</f>
+      <c r="X4" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W4,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y4" s="14">
+      <c r="Z4" s="14">
         <v>36526</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>142</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>665</v>
       </c>
-      <c r="AB4" s="6" t="str">
-        <f>IF($Z4="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z4,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC4" s="6" t="str">
+        <f>IF($AA4="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA4,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC4" ca="1">IF($Z4="",TRUE,IF($I4="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I4)&amp;"|"&amp;$Z4,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AD4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD4" ca="1">IF($Z4="",TRUE,IF($I4="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I4)&amp;"|"&amp;$Z4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD4" ca="1">IF($AA4="",TRUE,IF($J4="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J4)&amp;"|"&amp;$AA4,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AE4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE4" ca="1">IF($Z4="",TRUE,IF($M4="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M4)&amp;"|"&amp;$Z4,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
+        <f t="array" aca="1" ref="AE4" ca="1">IF($AA4="",TRUE,IF($J4="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J4)&amp;"|"&amp;$AA4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
       </c>
       <c r="AF4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF4" ca="1">IF($Z4="",TRUE,IF($M4="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M4)&amp;"|"&amp;$Z4,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI4" s="6" t="str">
-        <f>IF($AG4="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG4,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF4" ca="1">IF($AA4="",TRUE,IF($N4="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N4)&amp;"|"&amp;$AA4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG4" ca="1">IF($AA4="",TRUE,IF($N4="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N4)&amp;"|"&amp;$AA4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="6" t="str">
+        <f>IF($AH4="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH4,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ4" ca="1">IF($AG4="",TRUE,IF($I4="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I4)&amp;"|"&amp;$AG4,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK4" ca="1">IF($AG4="",TRUE,IF($I4="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I4)&amp;"|"&amp;$AG4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK4" ca="1">IF($AH4="",TRUE,IF($J4="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J4)&amp;"|"&amp;$AH4,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL4" ca="1">IF($AG4="",TRUE,IF($M4="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M4)&amp;"|"&amp;$AG4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL4" ca="1">IF($AH4="",TRUE,IF($J4="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J4)&amp;"|"&amp;$AH4,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM4" ca="1">IF($AG4="",TRUE,IF($M4="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M4)&amp;"|"&amp;$AG4,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP4" s="6" t="str">
-        <f>IF($AN4="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN4,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM4" ca="1">IF($AH4="",TRUE,IF($N4="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N4)&amp;"|"&amp;$AH4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN4" ca="1">IF($AH4="",TRUE,IF($N4="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N4)&amp;"|"&amp;$AH4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ4" s="6" t="str">
+        <f>IF($AO4="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO4,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ4" ca="1">IF($AN4="",TRUE,IF($I4="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I4)&amp;"|"&amp;$AN4,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR4" ca="1">IF($AN4="",TRUE,IF($I4="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I4)&amp;"|"&amp;$AN4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR4" ca="1">IF($AO4="",TRUE,IF($J4="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J4)&amp;"|"&amp;$AO4,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS4" ca="1">IF($AN4="",TRUE,IF($M4="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M4)&amp;"|"&amp;$AN4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS4" ca="1">IF($AO4="",TRUE,IF($J4="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J4)&amp;"|"&amp;$AO4,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT4" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT4" ca="1">IF($AN4="",TRUE,IF($M4="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M4)&amp;"|"&amp;$AN4,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT4" ca="1">IF($AO4="",TRUE,IF($N4="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N4)&amp;"|"&amp;$AO4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU4" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU4" ca="1">IF($AO4="",TRUE,IF($N4="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N4)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N4)&amp;"|"&amp;$AO4,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
         <v>711</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C5,User!$A:$A,0))</f>
+      <c r="E5" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D5,User!$A:$A,0))</f>
         <v>org_admin1_1</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>662</v>
       </c>
-      <c r="F5" s="19" t="b">
+      <c r="G5" s="19" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G5" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C5,User!$A:$A,0))</f>
+      <c r="H5" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D5,User!$A:$A,0))</f>
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
       </c>
-      <c r="H5" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C5,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="6">
-        <f>IF(ISNA(MATCH($G5&amp;"|"&amp;$V5,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G5&amp;"|"&amp;$V5,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I5" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D5,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="6">
+        <f>IF(ISNA(MATCH($H5&amp;"|"&amp;$W5,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H5&amp;"|"&amp;$W5,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v>2</v>
       </c>
-      <c r="J5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J5" ca="1">IF($I5="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I5)&amp;"|"&amp;$R5,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>1</v>
-      </c>
       <c r="K5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K5" ca="1">IF($I5="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I5),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I5)&amp;"|"&amp;$R5,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K5" ca="1">IF($J5="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J5)&amp;"|"&amp;$S5,CaseTypeSetMember!$H:$H,0))))</f>
         <v>1</v>
       </c>
       <c r="L5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L5" ca="1">IF($I5="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I5),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I5)&amp;"|"&amp;$R5,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="M5" s="6" t="str">
-        <f>IF(ISNA(MATCH($C5&amp;"|"&amp;$V5,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C5&amp;"|"&amp;$V5,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L5" ca="1">IF($J5="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J5),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J5)&amp;"|"&amp;$S5,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M5" ca="1">IF($J5="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J5),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J5)&amp;"|"&amp;$S5,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="N5" s="6" t="str">
+        <f>IF(ISNA(MATCH($D5&amp;"|"&amp;$W5,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D5&amp;"|"&amp;$W5,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N5" ca="1">IF($M5="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M5)&amp;"|"&amp;$R5,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O5" ca="1">IF($M5="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M5),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M5)&amp;"|"&amp;$R5,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O5" ca="1">IF($N5="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N5)&amp;"|"&amp;$S5,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P5" ca="1">IF($M5="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M5),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M5)&amp;"|"&amp;$R5,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q5" t="s">
+        <f t="array" aca="1" ref="P5" ca="1">IF($N5="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N5),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N5)&amp;"|"&amp;$S5,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q5" ca="1">IF($N5="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N5),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N5)&amp;"|"&amp;$S5,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R5" t="s">
         <v>715</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>119</v>
       </c>
-      <c r="S5" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R5,CaseType!$A:$A,0))</f>
+      <c r="T5" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S5,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T5" s="6" t="b">
-        <f>AND(IF($Z5="",TRUE,$R5=INDEX(CaseTypeCol!$B:$B,MATCH($Z5,CaseTypeCol!$A:$A,0))),IF($AG5="",TRUE,$R5=INDEX(CaseTypeCol!$B:$B,MATCH($AG5,CaseTypeCol!$A:$A,0))),IF($AN5="",TRUE,$R5=INDEX(CaseTypeCol!$B:$B,MATCH($AN5,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V5" t="s">
+      <c r="U5" s="6" t="b">
+        <f>AND(IF($AA5="",TRUE,$S5=INDEX(CaseTypeCol!$B:$B,MATCH($AA5,CaseTypeCol!$A:$A,0))),IF($AH5="",TRUE,$S5=INDEX(CaseTypeCol!$B:$B,MATCH($AH5,CaseTypeCol!$A:$A,0))),IF($AO5="",TRUE,$S5=INDEX(CaseTypeCol!$B:$B,MATCH($AO5,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W5" t="s">
         <v>11</v>
       </c>
-      <c r="W5" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V5,DataCollection!$A:$A,0))</f>
+      <c r="X5" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W5,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y5" s="14">
+      <c r="Z5" s="14">
         <v>36526</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AA5" t="s">
         <v>142</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AB5" t="s">
         <v>665</v>
       </c>
-      <c r="AB5" s="6" t="str">
-        <f>IF($Z5="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z5,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC5" s="6" t="str">
+        <f>IF($AA5="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA5,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC5" ca="1">IF($Z5="",TRUE,IF($I5="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I5)&amp;"|"&amp;$Z5,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AD5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD5" ca="1">IF($Z5="",TRUE,IF($I5="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I5)&amp;"|"&amp;$Z5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD5" ca="1">IF($AA5="",TRUE,IF($J5="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J5)&amp;"|"&amp;$AA5,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AE5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE5" ca="1">IF($Z5="",TRUE,IF($M5="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M5)&amp;"|"&amp;$Z5,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
+        <f t="array" aca="1" ref="AE5" ca="1">IF($AA5="",TRUE,IF($J5="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J5)&amp;"|"&amp;$AA5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
       </c>
       <c r="AF5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF5" ca="1">IF($Z5="",TRUE,IF($M5="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M5)&amp;"|"&amp;$Z5,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI5" s="6" t="str">
-        <f>IF($AG5="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG5,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF5" ca="1">IF($AA5="",TRUE,IF($N5="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N5)&amp;"|"&amp;$AA5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG5" ca="1">IF($AA5="",TRUE,IF($N5="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N5)&amp;"|"&amp;$AA5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="6" t="str">
+        <f>IF($AH5="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH5,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ5" ca="1">IF($AG5="",TRUE,IF($I5="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I5)&amp;"|"&amp;$AG5,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK5" ca="1">IF($AG5="",TRUE,IF($I5="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I5)&amp;"|"&amp;$AG5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK5" ca="1">IF($AH5="",TRUE,IF($J5="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J5)&amp;"|"&amp;$AH5,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL5" ca="1">IF($AG5="",TRUE,IF($M5="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M5)&amp;"|"&amp;$AG5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL5" ca="1">IF($AH5="",TRUE,IF($J5="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J5)&amp;"|"&amp;$AH5,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM5" ca="1">IF($AG5="",TRUE,IF($M5="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M5)&amp;"|"&amp;$AG5,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP5" s="6" t="str">
-        <f>IF($AN5="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN5,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM5" ca="1">IF($AH5="",TRUE,IF($N5="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N5)&amp;"|"&amp;$AH5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN5" ca="1">IF($AH5="",TRUE,IF($N5="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N5)&amp;"|"&amp;$AH5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ5" s="6" t="str">
+        <f>IF($AO5="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO5,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ5" ca="1">IF($AN5="",TRUE,IF($I5="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I5)&amp;"|"&amp;$AN5,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR5" ca="1">IF($AN5="",TRUE,IF($I5="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I5)&amp;"|"&amp;$AN5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR5" ca="1">IF($AO5="",TRUE,IF($J5="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J5)&amp;"|"&amp;$AO5,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS5" ca="1">IF($AN5="",TRUE,IF($M5="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M5)&amp;"|"&amp;$AN5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS5" ca="1">IF($AO5="",TRUE,IF($J5="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J5)&amp;"|"&amp;$AO5,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT5" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT5" ca="1">IF($AN5="",TRUE,IF($M5="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M5)&amp;"|"&amp;$AN5,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT5" ca="1">IF($AO5="",TRUE,IF($N5="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N5)&amp;"|"&amp;$AO5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU5" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU5" ca="1">IF($AO5="",TRUE,IF($N5="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N5)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N5)&amp;"|"&amp;$AO5,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="b">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
         <v>712</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C6,User!$A:$A,0))</f>
+      <c r="E6" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D6,User!$A:$A,0))</f>
         <v>org_user1_1</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>662</v>
       </c>
-      <c r="F6" s="19" t="b">
+      <c r="G6" s="19" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C6,User!$A:$A,0))</f>
+      <c r="H6" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D6,User!$A:$A,0))</f>
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
       </c>
-      <c r="H6" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C6,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="6">
-        <f>IF(ISNA(MATCH($G6&amp;"|"&amp;$V6,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G6&amp;"|"&amp;$V6,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I6" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D6,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="6">
+        <f>IF(ISNA(MATCH($H6&amp;"|"&amp;$W6,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H6&amp;"|"&amp;$W6,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v>2</v>
       </c>
-      <c r="J6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J6" ca="1">IF($I6="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I6)&amp;"|"&amp;$R6,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>1</v>
-      </c>
       <c r="K6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K6" ca="1">IF($I6="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I6),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I6)&amp;"|"&amp;$R6,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K6" ca="1">IF($J6="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J6)&amp;"|"&amp;$S6,CaseTypeSetMember!$H:$H,0))))</f>
         <v>1</v>
       </c>
       <c r="L6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L6" ca="1">IF($I6="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I6),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I6)&amp;"|"&amp;$R6,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="M6" s="6">
-        <f>IF(ISNA(MATCH($C6&amp;"|"&amp;$V6,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C6&amp;"|"&amp;$V6,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L6" ca="1">IF($J6="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J6),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J6)&amp;"|"&amp;$S6,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M6" ca="1">IF($J6="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J6),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J6)&amp;"|"&amp;$S6,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="N6" s="6">
+        <f>IF(ISNA(MATCH($D6&amp;"|"&amp;$W6,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D6&amp;"|"&amp;$W6,UserAccessCasePolicy!$W:$W,0))</f>
         <v>2</v>
       </c>
-      <c r="N6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N6" ca="1">IF($M6="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M6)&amp;"|"&amp;$R6,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>1</v>
-      </c>
       <c r="O6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O6" ca="1">IF($M6="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M6),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M6)&amp;"|"&amp;$R6,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O6" ca="1">IF($N6="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N6)&amp;"|"&amp;$S6,CaseTypeSetMember!$H:$H,0))))</f>
         <v>1</v>
       </c>
       <c r="P6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P6" ca="1">IF($M6="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M6),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M6)&amp;"|"&amp;$R6,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="Q6" t="s">
+        <f t="array" aca="1" ref="P6" ca="1">IF($N6="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N6),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N6)&amp;"|"&amp;$S6,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q6" ca="1">IF($N6="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N6),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N6)&amp;"|"&amp;$S6,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="R6" t="s">
         <v>716</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>119</v>
       </c>
-      <c r="S6" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R6,CaseType!$A:$A,0))</f>
+      <c r="T6" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S6,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T6" s="6" t="b">
-        <f>AND(IF($Z6="",TRUE,$R6=INDEX(CaseTypeCol!$B:$B,MATCH($Z6,CaseTypeCol!$A:$A,0))),IF($AG6="",TRUE,$R6=INDEX(CaseTypeCol!$B:$B,MATCH($AG6,CaseTypeCol!$A:$A,0))),IF($AN6="",TRUE,$R6=INDEX(CaseTypeCol!$B:$B,MATCH($AN6,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V6" t="s">
+      <c r="U6" s="6" t="b">
+        <f>AND(IF($AA6="",TRUE,$S6=INDEX(CaseTypeCol!$B:$B,MATCH($AA6,CaseTypeCol!$A:$A,0))),IF($AH6="",TRUE,$S6=INDEX(CaseTypeCol!$B:$B,MATCH($AH6,CaseTypeCol!$A:$A,0))),IF($AO6="",TRUE,$S6=INDEX(CaseTypeCol!$B:$B,MATCH($AO6,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W6" t="s">
         <v>11</v>
       </c>
-      <c r="W6" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V6,DataCollection!$A:$A,0))</f>
+      <c r="X6" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W6,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y6" s="14">
+      <c r="Z6" s="14">
         <v>36526</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AA6" t="s">
         <v>142</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AB6" t="s">
         <v>665</v>
       </c>
-      <c r="AB6" s="6" t="str">
-        <f>IF($Z6="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z6,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC6" s="6" t="str">
+        <f>IF($AA6="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA6,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC6" ca="1">IF($Z6="",TRUE,IF($I6="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I6)&amp;"|"&amp;$Z6,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AD6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD6" ca="1">IF($Z6="",TRUE,IF($I6="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I6)&amp;"|"&amp;$Z6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD6" ca="1">IF($AA6="",TRUE,IF($J6="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J6)&amp;"|"&amp;$AA6,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AE6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE6" ca="1">IF($Z6="",TRUE,IF($M6="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M6)&amp;"|"&amp;$Z6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE6" ca="1">IF($AA6="",TRUE,IF($J6="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J6)&amp;"|"&amp;$AA6,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AF6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF6" ca="1">IF($Z6="",TRUE,IF($M6="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M6)&amp;"|"&amp;$Z6,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AI6" s="6" t="str">
-        <f>IF($AG6="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG6,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF6" ca="1">IF($AA6="",TRUE,IF($N6="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N6)&amp;"|"&amp;$AA6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AG6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG6" ca="1">IF($AA6="",TRUE,IF($N6="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N6)&amp;"|"&amp;$AA6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AJ6" s="6" t="str">
+        <f>IF($AH6="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH6,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ6" ca="1">IF($AG6="",TRUE,IF($I6="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I6)&amp;"|"&amp;$AG6,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK6" ca="1">IF($AG6="",TRUE,IF($I6="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I6)&amp;"|"&amp;$AG6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK6" ca="1">IF($AH6="",TRUE,IF($J6="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J6)&amp;"|"&amp;$AH6,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL6" ca="1">IF($AG6="",TRUE,IF($M6="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M6)&amp;"|"&amp;$AG6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL6" ca="1">IF($AH6="",TRUE,IF($J6="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J6)&amp;"|"&amp;$AH6,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM6" ca="1">IF($AG6="",TRUE,IF($M6="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M6)&amp;"|"&amp;$AG6,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP6" s="6" t="str">
-        <f>IF($AN6="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN6,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM6" ca="1">IF($AH6="",TRUE,IF($N6="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N6)&amp;"|"&amp;$AH6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN6" ca="1">IF($AH6="",TRUE,IF($N6="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N6)&amp;"|"&amp;$AH6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ6" s="6" t="str">
+        <f>IF($AO6="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO6,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ6" ca="1">IF($AN6="",TRUE,IF($I6="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I6)&amp;"|"&amp;$AN6,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR6" ca="1">IF($AN6="",TRUE,IF($I6="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I6)&amp;"|"&amp;$AN6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR6" ca="1">IF($AO6="",TRUE,IF($J6="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J6)&amp;"|"&amp;$AO6,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS6" ca="1">IF($AN6="",TRUE,IF($M6="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M6)&amp;"|"&amp;$AN6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS6" ca="1">IF($AO6="",TRUE,IF($J6="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J6)&amp;"|"&amp;$AO6,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT6" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT6" ca="1">IF($AN6="",TRUE,IF($M6="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M6)&amp;"|"&amp;$AN6,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT6" ca="1">IF($AO6="",TRUE,IF($N6="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N6)&amp;"|"&amp;$AO6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU6" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU6" ca="1">IF($AO6="",TRUE,IF($N6="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N6)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N6)&amp;"|"&amp;$AO6,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="b">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
         <v>713</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>443</v>
       </c>
-      <c r="D7" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C7,User!$A:$A,0))</f>
+      <c r="E7" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D7,User!$A:$A,0))</f>
         <v>root1_1</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>723</v>
       </c>
-      <c r="F7" s="19" t="b">
+      <c r="G7" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="G7" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C7,User!$A:$A,0))</f>
+      <c r="H7" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D7,User!$A:$A,0))</f>
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
       </c>
-      <c r="H7" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C7,User!$A:$A,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I7" s="6">
-        <f>IF(ISNA(MATCH($G7&amp;"|"&amp;$V7,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G7&amp;"|"&amp;$V7,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I7" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D7,User!$A:$A,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J7" s="6">
+        <f>IF(ISNA(MATCH($H7&amp;"|"&amp;$W7,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H7&amp;"|"&amp;$W7,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v>2</v>
       </c>
-      <c r="J7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J7" ca="1">IF($I7="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I7)&amp;"|"&amp;$R7,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>1</v>
-      </c>
       <c r="K7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K7" ca="1">IF($I7="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I7),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I7)&amp;"|"&amp;$R7,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K7" ca="1">IF($J7="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J7)&amp;"|"&amp;$S7,CaseTypeSetMember!$H:$H,0))))</f>
         <v>1</v>
       </c>
       <c r="L7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L7" ca="1">IF($I7="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I7),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I7)&amp;"|"&amp;$R7,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="M7" s="6" t="str">
-        <f>IF(ISNA(MATCH($C7&amp;"|"&amp;$V7,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C7&amp;"|"&amp;$V7,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L7" ca="1">IF($J7="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J7),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J7)&amp;"|"&amp;$S7,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M7" ca="1">IF($J7="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J7),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J7)&amp;"|"&amp;$S7,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="N7" s="6" t="str">
+        <f>IF(ISNA(MATCH($D7&amp;"|"&amp;$W7,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D7&amp;"|"&amp;$W7,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N7" ca="1">IF($M7="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M7)&amp;"|"&amp;$R7,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O7" ca="1">IF($M7="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M7),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M7)&amp;"|"&amp;$R7,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O7" ca="1">IF($N7="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N7)&amp;"|"&amp;$S7,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P7" ca="1">IF($M7="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M7),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M7)&amp;"|"&amp;$R7,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q7" t="s">
+        <f t="array" aca="1" ref="P7" ca="1">IF($N7="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N7),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N7)&amp;"|"&amp;$S7,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q7" ca="1">IF($N7="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N7),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N7)&amp;"|"&amp;$S7,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R7" t="s">
         <v>717</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
         <v>119</v>
       </c>
-      <c r="S7" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R7,CaseType!$A:$A,0))</f>
+      <c r="T7" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S7,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T7" s="6" t="b">
-        <f>AND(IF($Z7="",TRUE,$R7=INDEX(CaseTypeCol!$B:$B,MATCH($Z7,CaseTypeCol!$A:$A,0))),IF($AG7="",TRUE,$R7=INDEX(CaseTypeCol!$B:$B,MATCH($AG7,CaseTypeCol!$A:$A,0))),IF($AN7="",TRUE,$R7=INDEX(CaseTypeCol!$B:$B,MATCH($AN7,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V7" t="s">
+      <c r="U7" s="6" t="b">
+        <f>AND(IF($AA7="",TRUE,$S7=INDEX(CaseTypeCol!$B:$B,MATCH($AA7,CaseTypeCol!$A:$A,0))),IF($AH7="",TRUE,$S7=INDEX(CaseTypeCol!$B:$B,MATCH($AH7,CaseTypeCol!$A:$A,0))),IF($AO7="",TRUE,$S7=INDEX(CaseTypeCol!$B:$B,MATCH($AO7,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W7" t="s">
         <v>11</v>
       </c>
-      <c r="W7" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V7,DataCollection!$A:$A,0))</f>
+      <c r="X7" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W7,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y7" s="14">
+      <c r="Z7" s="14">
         <v>36526</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AA7" t="s">
         <v>142</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="AB7" t="s">
         <v>665</v>
       </c>
-      <c r="AB7" s="6" t="str">
-        <f>IF($Z7="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z7,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC7" s="6" t="str">
+        <f>IF($AA7="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA7,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC7" ca="1">IF($Z7="",TRUE,IF($I7="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I7)&amp;"|"&amp;$Z7,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AD7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD7" ca="1">IF($Z7="",TRUE,IF($I7="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I7)&amp;"|"&amp;$Z7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD7" ca="1">IF($AA7="",TRUE,IF($J7="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J7)&amp;"|"&amp;$AA7,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AE7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE7" ca="1">IF($Z7="",TRUE,IF($M7="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M7)&amp;"|"&amp;$Z7,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
+        <f t="array" aca="1" ref="AE7" ca="1">IF($AA7="",TRUE,IF($J7="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J7)&amp;"|"&amp;$AA7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
       </c>
       <c r="AF7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF7" ca="1">IF($Z7="",TRUE,IF($M7="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M7)&amp;"|"&amp;$Z7,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI7" s="6" t="str">
-        <f>IF($AG7="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG7,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF7" ca="1">IF($AA7="",TRUE,IF($N7="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N7)&amp;"|"&amp;$AA7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG7" ca="1">IF($AA7="",TRUE,IF($N7="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N7)&amp;"|"&amp;$AA7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="6" t="str">
+        <f>IF($AH7="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH7,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ7" ca="1">IF($AG7="",TRUE,IF($I7="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I7)&amp;"|"&amp;$AG7,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK7" ca="1">IF($AG7="",TRUE,IF($I7="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I7)&amp;"|"&amp;$AG7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK7" ca="1">IF($AH7="",TRUE,IF($J7="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J7)&amp;"|"&amp;$AH7,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL7" ca="1">IF($AG7="",TRUE,IF($M7="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M7)&amp;"|"&amp;$AG7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL7" ca="1">IF($AH7="",TRUE,IF($J7="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J7)&amp;"|"&amp;$AH7,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM7" ca="1">IF($AG7="",TRUE,IF($M7="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M7)&amp;"|"&amp;$AG7,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP7" s="6" t="str">
-        <f>IF($AN7="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN7,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM7" ca="1">IF($AH7="",TRUE,IF($N7="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N7)&amp;"|"&amp;$AH7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN7" ca="1">IF($AH7="",TRUE,IF($N7="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N7)&amp;"|"&amp;$AH7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ7" s="6" t="str">
+        <f>IF($AO7="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO7,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ7" ca="1">IF($AN7="",TRUE,IF($I7="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I7)&amp;"|"&amp;$AN7,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR7" ca="1">IF($AN7="",TRUE,IF($I7="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I7)&amp;"|"&amp;$AN7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR7" ca="1">IF($AO7="",TRUE,IF($J7="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J7)&amp;"|"&amp;$AO7,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS7" ca="1">IF($AN7="",TRUE,IF($M7="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M7)&amp;"|"&amp;$AN7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS7" ca="1">IF($AO7="",TRUE,IF($J7="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J7)&amp;"|"&amp;$AO7,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT7" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT7" ca="1">IF($AN7="",TRUE,IF($M7="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M7)&amp;"|"&amp;$AN7,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT7" ca="1">IF($AO7="",TRUE,IF($N7="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N7)&amp;"|"&amp;$AO7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU7" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU7" ca="1">IF($AO7="",TRUE,IF($N7="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N7)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N7)&amp;"|"&amp;$AO7,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="b">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
         <v>714</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>445</v>
       </c>
-      <c r="D8" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C8,User!$A:$A,0))</f>
+      <c r="E8" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D8,User!$A:$A,0))</f>
         <v>app_admin1_1</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>723</v>
       </c>
-      <c r="F8" s="19" t="b">
+      <c r="G8" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="G8" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C8,User!$A:$A,0))</f>
+      <c r="H8" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D8,User!$A:$A,0))</f>
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
       </c>
-      <c r="H8" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C8,User!$A:$A,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I8" s="6">
-        <f>IF(ISNA(MATCH($G8&amp;"|"&amp;$V8,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G8&amp;"|"&amp;$V8,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I8" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D8,User!$A:$A,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J8" s="6">
+        <f>IF(ISNA(MATCH($H8&amp;"|"&amp;$W8,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H8&amp;"|"&amp;$W8,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v>2</v>
       </c>
-      <c r="J8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J8" ca="1">IF($I8="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I8)&amp;"|"&amp;$R8,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>1</v>
-      </c>
       <c r="K8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K8" ca="1">IF($I8="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I8),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I8)&amp;"|"&amp;$R8,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K8" ca="1">IF($J8="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J8)&amp;"|"&amp;$S8,CaseTypeSetMember!$H:$H,0))))</f>
         <v>1</v>
       </c>
       <c r="L8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L8" ca="1">IF($I8="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I8),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I8)&amp;"|"&amp;$R8,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="M8" s="6" t="str">
-        <f>IF(ISNA(MATCH($C8&amp;"|"&amp;$V8,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C8&amp;"|"&amp;$V8,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L8" ca="1">IF($J8="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J8),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J8)&amp;"|"&amp;$S8,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M8" ca="1">IF($J8="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J8),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J8)&amp;"|"&amp;$S8,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="N8" s="6" t="str">
+        <f>IF(ISNA(MATCH($D8&amp;"|"&amp;$W8,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D8&amp;"|"&amp;$W8,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N8" ca="1">IF($M8="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M8)&amp;"|"&amp;$R8,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O8" ca="1">IF($M8="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M8),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M8)&amp;"|"&amp;$R8,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O8" ca="1">IF($N8="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N8)&amp;"|"&amp;$S8,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P8" ca="1">IF($M8="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M8),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M8)&amp;"|"&amp;$R8,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q8" t="s">
+        <f t="array" aca="1" ref="P8" ca="1">IF($N8="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N8),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N8)&amp;"|"&amp;$S8,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q8" ca="1">IF($N8="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N8),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N8)&amp;"|"&amp;$S8,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R8" t="s">
         <v>718</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>119</v>
       </c>
-      <c r="S8" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R8,CaseType!$A:$A,0))</f>
+      <c r="T8" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S8,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T8" s="6" t="b">
-        <f>AND(IF($Z8="",TRUE,$R8=INDEX(CaseTypeCol!$B:$B,MATCH($Z8,CaseTypeCol!$A:$A,0))),IF($AG8="",TRUE,$R8=INDEX(CaseTypeCol!$B:$B,MATCH($AG8,CaseTypeCol!$A:$A,0))),IF($AN8="",TRUE,$R8=INDEX(CaseTypeCol!$B:$B,MATCH($AN8,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V8" t="s">
+      <c r="U8" s="6" t="b">
+        <f>AND(IF($AA8="",TRUE,$S8=INDEX(CaseTypeCol!$B:$B,MATCH($AA8,CaseTypeCol!$A:$A,0))),IF($AH8="",TRUE,$S8=INDEX(CaseTypeCol!$B:$B,MATCH($AH8,CaseTypeCol!$A:$A,0))),IF($AO8="",TRUE,$S8=INDEX(CaseTypeCol!$B:$B,MATCH($AO8,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W8" t="s">
         <v>11</v>
       </c>
-      <c r="W8" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V8,DataCollection!$A:$A,0))</f>
+      <c r="X8" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W8,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y8" s="14">
+      <c r="Z8" s="14">
         <v>36526</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="AA8" t="s">
         <v>142</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AB8" t="s">
         <v>665</v>
       </c>
-      <c r="AB8" s="6" t="str">
-        <f>IF($Z8="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z8,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC8" s="6" t="str">
+        <f>IF($AA8="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA8,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC8" ca="1">IF($Z8="",TRUE,IF($I8="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I8)&amp;"|"&amp;$Z8,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AD8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD8" ca="1">IF($Z8="",TRUE,IF($I8="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I8)&amp;"|"&amp;$Z8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD8" ca="1">IF($AA8="",TRUE,IF($J8="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J8)&amp;"|"&amp;$AA8,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AE8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE8" ca="1">IF($Z8="",TRUE,IF($M8="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M8)&amp;"|"&amp;$Z8,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
+        <f t="array" aca="1" ref="AE8" ca="1">IF($AA8="",TRUE,IF($J8="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J8)&amp;"|"&amp;$AA8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
       </c>
       <c r="AF8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF8" ca="1">IF($Z8="",TRUE,IF($M8="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M8)&amp;"|"&amp;$Z8,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI8" s="6" t="str">
-        <f>IF($AG8="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG8,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF8" ca="1">IF($AA8="",TRUE,IF($N8="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N8)&amp;"|"&amp;$AA8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG8" ca="1">IF($AA8="",TRUE,IF($N8="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N8)&amp;"|"&amp;$AA8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="6" t="str">
+        <f>IF($AH8="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH8,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ8" ca="1">IF($AG8="",TRUE,IF($I8="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I8)&amp;"|"&amp;$AG8,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK8" ca="1">IF($AG8="",TRUE,IF($I8="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I8)&amp;"|"&amp;$AG8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK8" ca="1">IF($AH8="",TRUE,IF($J8="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J8)&amp;"|"&amp;$AH8,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL8" ca="1">IF($AG8="",TRUE,IF($M8="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M8)&amp;"|"&amp;$AG8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL8" ca="1">IF($AH8="",TRUE,IF($J8="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J8)&amp;"|"&amp;$AH8,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM8" ca="1">IF($AG8="",TRUE,IF($M8="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M8)&amp;"|"&amp;$AG8,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP8" s="6" t="str">
-        <f>IF($AN8="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN8,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM8" ca="1">IF($AH8="",TRUE,IF($N8="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N8)&amp;"|"&amp;$AH8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN8" ca="1">IF($AH8="",TRUE,IF($N8="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N8)&amp;"|"&amp;$AH8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ8" s="6" t="str">
+        <f>IF($AO8="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO8,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ8" ca="1">IF($AN8="",TRUE,IF($I8="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I8)&amp;"|"&amp;$AN8,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR8" ca="1">IF($AN8="",TRUE,IF($I8="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I8)&amp;"|"&amp;$AN8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR8" ca="1">IF($AO8="",TRUE,IF($J8="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J8)&amp;"|"&amp;$AO8,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS8" ca="1">IF($AN8="",TRUE,IF($M8="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M8)&amp;"|"&amp;$AN8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS8" ca="1">IF($AO8="",TRUE,IF($J8="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J8)&amp;"|"&amp;$AO8,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT8" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT8" ca="1">IF($AN8="",TRUE,IF($M8="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M8)&amp;"|"&amp;$AN8,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT8" ca="1">IF($AO8="",TRUE,IF($N8="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N8)&amp;"|"&amp;$AO8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU8" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU8" ca="1">IF($AO8="",TRUE,IF($N8="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N8)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N8)&amp;"|"&amp;$AO8,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="b">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
         <v>610</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C9,User!$A:$A,0))</f>
+      <c r="E9" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D9,User!$A:$A,0))</f>
         <v>org_admin1_1</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>723</v>
       </c>
-      <c r="F9" s="19" t="b">
+      <c r="G9" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G9" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C9,User!$A:$A,0))</f>
+      <c r="H9" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D9,User!$A:$A,0))</f>
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
       </c>
-      <c r="H9" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C9,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="6">
-        <f>IF(ISNA(MATCH($G9&amp;"|"&amp;$V9,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G9&amp;"|"&amp;$V9,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I9" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D9,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="6">
+        <f>IF(ISNA(MATCH($H9&amp;"|"&amp;$W9,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H9&amp;"|"&amp;$W9,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v>2</v>
       </c>
-      <c r="J9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J9" ca="1">IF($I9="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I9)&amp;"|"&amp;$R9,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>1</v>
-      </c>
       <c r="K9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K9" ca="1">IF($I9="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I9),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I9)&amp;"|"&amp;$R9,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K9" ca="1">IF($J9="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J9)&amp;"|"&amp;$S9,CaseTypeSetMember!$H:$H,0))))</f>
         <v>1</v>
       </c>
       <c r="L9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L9" ca="1">IF($I9="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I9),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I9)&amp;"|"&amp;$R9,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="M9" s="6" t="str">
-        <f>IF(ISNA(MATCH($C9&amp;"|"&amp;$V9,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C9&amp;"|"&amp;$V9,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L9" ca="1">IF($J9="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J9),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J9)&amp;"|"&amp;$S9,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M9" ca="1">IF($J9="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J9),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J9)&amp;"|"&amp;$S9,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="N9" s="6" t="str">
+        <f>IF(ISNA(MATCH($D9&amp;"|"&amp;$W9,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D9&amp;"|"&amp;$W9,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N9" ca="1">IF($M9="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M9)&amp;"|"&amp;$R9,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O9" ca="1">IF($M9="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M9),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M9)&amp;"|"&amp;$R9,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O9" ca="1">IF($N9="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N9)&amp;"|"&amp;$S9,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P9" ca="1">IF($M9="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M9),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M9)&amp;"|"&amp;$R9,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q9" t="s">
+        <f t="array" aca="1" ref="P9" ca="1">IF($N9="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N9),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N9)&amp;"|"&amp;$S9,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q9" ca="1">IF($N9="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N9),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N9)&amp;"|"&amp;$S9,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R9" t="s">
         <v>636</v>
       </c>
-      <c r="R9" t="s">
+      <c r="S9" t="s">
         <v>119</v>
       </c>
-      <c r="S9" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R9,CaseType!$A:$A,0))</f>
+      <c r="T9" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S9,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T9" s="6" t="b">
-        <f>AND(IF($Z9="",TRUE,$R9=INDEX(CaseTypeCol!$B:$B,MATCH($Z9,CaseTypeCol!$A:$A,0))),IF($AG9="",TRUE,$R9=INDEX(CaseTypeCol!$B:$B,MATCH($AG9,CaseTypeCol!$A:$A,0))),IF($AN9="",TRUE,$R9=INDEX(CaseTypeCol!$B:$B,MATCH($AN9,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V9" t="s">
+      <c r="U9" s="6" t="b">
+        <f>AND(IF($AA9="",TRUE,$S9=INDEX(CaseTypeCol!$B:$B,MATCH($AA9,CaseTypeCol!$A:$A,0))),IF($AH9="",TRUE,$S9=INDEX(CaseTypeCol!$B:$B,MATCH($AH9,CaseTypeCol!$A:$A,0))),IF($AO9="",TRUE,$S9=INDEX(CaseTypeCol!$B:$B,MATCH($AO9,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W9" t="s">
         <v>11</v>
       </c>
-      <c r="W9" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V9,DataCollection!$A:$A,0))</f>
+      <c r="X9" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W9,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y9" s="14">
+      <c r="Z9" s="14">
         <v>36526</v>
       </c>
-      <c r="Z9" t="s">
+      <c r="AA9" t="s">
         <v>142</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AB9" t="s">
         <v>665</v>
       </c>
-      <c r="AB9" s="6" t="str">
-        <f>IF($Z9="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z9,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC9" s="6" t="str">
+        <f>IF($AA9="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA9,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC9" ca="1">IF($Z9="",TRUE,IF($I9="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I9)&amp;"|"&amp;$Z9,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AD9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD9" ca="1">IF($Z9="",TRUE,IF($I9="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I9)&amp;"|"&amp;$Z9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD9" ca="1">IF($AA9="",TRUE,IF($J9="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J9)&amp;"|"&amp;$AA9,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AE9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE9" ca="1">IF($Z9="",TRUE,IF($M9="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M9)&amp;"|"&amp;$Z9,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
+        <f t="array" aca="1" ref="AE9" ca="1">IF($AA9="",TRUE,IF($J9="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J9)&amp;"|"&amp;$AA9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
       </c>
       <c r="AF9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF9" ca="1">IF($Z9="",TRUE,IF($M9="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M9)&amp;"|"&amp;$Z9,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI9" s="6" t="str">
-        <f>IF($AG9="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG9,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF9" ca="1">IF($AA9="",TRUE,IF($N9="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N9)&amp;"|"&amp;$AA9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG9" ca="1">IF($AA9="",TRUE,IF($N9="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N9)&amp;"|"&amp;$AA9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="6" t="str">
+        <f>IF($AH9="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH9,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ9" ca="1">IF($AG9="",TRUE,IF($I9="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I9)&amp;"|"&amp;$AG9,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK9" ca="1">IF($AG9="",TRUE,IF($I9="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I9)&amp;"|"&amp;$AG9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK9" ca="1">IF($AH9="",TRUE,IF($J9="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J9)&amp;"|"&amp;$AH9,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL9" ca="1">IF($AG9="",TRUE,IF($M9="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M9)&amp;"|"&amp;$AG9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL9" ca="1">IF($AH9="",TRUE,IF($J9="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J9)&amp;"|"&amp;$AH9,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM9" ca="1">IF($AG9="",TRUE,IF($M9="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M9)&amp;"|"&amp;$AG9,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP9" s="6" t="str">
-        <f>IF($AN9="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN9,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM9" ca="1">IF($AH9="",TRUE,IF($N9="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N9)&amp;"|"&amp;$AH9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN9" ca="1">IF($AH9="",TRUE,IF($N9="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N9)&amp;"|"&amp;$AH9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ9" s="6" t="str">
+        <f>IF($AO9="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO9,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ9" ca="1">IF($AN9="",TRUE,IF($I9="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I9)&amp;"|"&amp;$AN9,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR9" ca="1">IF($AN9="",TRUE,IF($I9="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I9)&amp;"|"&amp;$AN9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR9" ca="1">IF($AO9="",TRUE,IF($J9="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J9)&amp;"|"&amp;$AO9,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS9" ca="1">IF($AN9="",TRUE,IF($M9="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M9)&amp;"|"&amp;$AN9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS9" ca="1">IF($AO9="",TRUE,IF($J9="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J9)&amp;"|"&amp;$AO9,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT9" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT9" ca="1">IF($AN9="",TRUE,IF($M9="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M9)&amp;"|"&amp;$AN9,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT9" ca="1">IF($AO9="",TRUE,IF($N9="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N9)&amp;"|"&amp;$AO9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU9" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU9" ca="1">IF($AO9="",TRUE,IF($N9="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N9)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N9)&amp;"|"&amp;$AO9,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="b">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
         <v>611</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C10,User!$A:$A,0))</f>
+      <c r="E10" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D10,User!$A:$A,0))</f>
         <v>org_admin2_1</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>723</v>
       </c>
-      <c r="F10" s="19" t="b">
+      <c r="G10" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G10" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C10,User!$A:$A,0))</f>
+      <c r="H10" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D10,User!$A:$A,0))</f>
         <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3</v>
       </c>
-      <c r="H10" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C10,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="6" t="str">
-        <f>IF(ISNA(MATCH($G10&amp;"|"&amp;$V10,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G10&amp;"|"&amp;$V10,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I10" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D10,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="6" t="str">
+        <f>IF(ISNA(MATCH($H10&amp;"|"&amp;$W10,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H10&amp;"|"&amp;$W10,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J10" ca="1">IF($I10="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I10)&amp;"|"&amp;$R10,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K10" ca="1">IF($I10="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I10),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I10)&amp;"|"&amp;$R10,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K10" ca="1">IF($J10="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J10)&amp;"|"&amp;$S10,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L10" ca="1">IF($I10="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I10),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I10)&amp;"|"&amp;$R10,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="6" t="str">
-        <f>IF(ISNA(MATCH($C10&amp;"|"&amp;$V10,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C10&amp;"|"&amp;$V10,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L10" ca="1">IF($J10="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J10),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J10)&amp;"|"&amp;$S10,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M10" ca="1">IF($J10="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J10),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J10)&amp;"|"&amp;$S10,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="6" t="str">
+        <f>IF(ISNA(MATCH($D10&amp;"|"&amp;$W10,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D10&amp;"|"&amp;$W10,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N10" ca="1">IF($M10="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M10)&amp;"|"&amp;$R10,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O10" ca="1">IF($M10="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M10),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M10)&amp;"|"&amp;$R10,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O10" ca="1">IF($N10="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N10)&amp;"|"&amp;$S10,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P10" ca="1">IF($M10="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M10),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M10)&amp;"|"&amp;$R10,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q10" t="s">
+        <f t="array" aca="1" ref="P10" ca="1">IF($N10="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N10),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N10)&amp;"|"&amp;$S10,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q10" ca="1">IF($N10="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N10),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N10)&amp;"|"&amp;$S10,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R10" t="s">
         <v>637</v>
       </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
         <v>119</v>
       </c>
-      <c r="S10" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R10,CaseType!$A:$A,0))</f>
+      <c r="T10" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S10,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T10" s="6" t="b">
-        <f>AND(IF($Z10="",TRUE,$R10=INDEX(CaseTypeCol!$B:$B,MATCH($Z10,CaseTypeCol!$A:$A,0))),IF($AG10="",TRUE,$R10=INDEX(CaseTypeCol!$B:$B,MATCH($AG10,CaseTypeCol!$A:$A,0))),IF($AN10="",TRUE,$R10=INDEX(CaseTypeCol!$B:$B,MATCH($AN10,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V10" t="s">
+      <c r="U10" s="6" t="b">
+        <f>AND(IF($AA10="",TRUE,$S10=INDEX(CaseTypeCol!$B:$B,MATCH($AA10,CaseTypeCol!$A:$A,0))),IF($AH10="",TRUE,$S10=INDEX(CaseTypeCol!$B:$B,MATCH($AH10,CaseTypeCol!$A:$A,0))),IF($AO10="",TRUE,$S10=INDEX(CaseTypeCol!$B:$B,MATCH($AO10,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W10" t="s">
         <v>11</v>
       </c>
-      <c r="W10" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V10,DataCollection!$A:$A,0))</f>
+      <c r="X10" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W10,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y10" s="14">
+      <c r="Z10" s="14">
         <v>36526</v>
       </c>
-      <c r="Z10" t="s">
+      <c r="AA10" t="s">
         <v>142</v>
       </c>
-      <c r="AA10" t="s">
+      <c r="AB10" t="s">
         <v>665</v>
       </c>
-      <c r="AB10" s="6" t="str">
-        <f>IF($Z10="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z10,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC10" s="6" t="str">
+        <f>IF($AA10="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA10,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC10" ca="1">IF($Z10="",TRUE,IF($I10="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I10)&amp;"|"&amp;$Z10,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD10" ca="1">IF($Z10="",TRUE,IF($I10="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I10)&amp;"|"&amp;$Z10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD10" ca="1">IF($AA10="",TRUE,IF($J10="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J10)&amp;"|"&amp;$AA10,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE10" ca="1">IF($Z10="",TRUE,IF($M10="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M10)&amp;"|"&amp;$Z10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE10" ca="1">IF($AA10="",TRUE,IF($J10="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J10)&amp;"|"&amp;$AA10,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF10" ca="1">IF($Z10="",TRUE,IF($M10="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M10)&amp;"|"&amp;$Z10,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI10" s="6" t="str">
-        <f>IF($AG10="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG10,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF10" ca="1">IF($AA10="",TRUE,IF($N10="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N10)&amp;"|"&amp;$AA10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG10" ca="1">IF($AA10="",TRUE,IF($N10="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N10)&amp;"|"&amp;$AA10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="6" t="str">
+        <f>IF($AH10="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH10,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ10" ca="1">IF($AG10="",TRUE,IF($I10="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I10)&amp;"|"&amp;$AG10,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK10" ca="1">IF($AG10="",TRUE,IF($I10="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I10)&amp;"|"&amp;$AG10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK10" ca="1">IF($AH10="",TRUE,IF($J10="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J10)&amp;"|"&amp;$AH10,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL10" ca="1">IF($AG10="",TRUE,IF($M10="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M10)&amp;"|"&amp;$AG10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL10" ca="1">IF($AH10="",TRUE,IF($J10="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J10)&amp;"|"&amp;$AH10,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM10" ca="1">IF($AG10="",TRUE,IF($M10="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M10)&amp;"|"&amp;$AG10,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP10" s="6" t="str">
-        <f>IF($AN10="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN10,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM10" ca="1">IF($AH10="",TRUE,IF($N10="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N10)&amp;"|"&amp;$AH10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN10" ca="1">IF($AH10="",TRUE,IF($N10="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N10)&amp;"|"&amp;$AH10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ10" s="6" t="str">
+        <f>IF($AO10="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO10,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ10" ca="1">IF($AN10="",TRUE,IF($I10="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I10)&amp;"|"&amp;$AN10,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR10" ca="1">IF($AN10="",TRUE,IF($I10="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I10)&amp;"|"&amp;$AN10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR10" ca="1">IF($AO10="",TRUE,IF($J10="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J10)&amp;"|"&amp;$AO10,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS10" ca="1">IF($AN10="",TRUE,IF($M10="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M10)&amp;"|"&amp;$AN10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS10" ca="1">IF($AO10="",TRUE,IF($J10="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J10)&amp;"|"&amp;$AO10,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT10" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT10" ca="1">IF($AN10="",TRUE,IF($M10="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M10)&amp;"|"&amp;$AN10,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT10" ca="1">IF($AO10="",TRUE,IF($N10="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N10)&amp;"|"&amp;$AO10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU10" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU10" ca="1">IF($AO10="",TRUE,IF($N10="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N10)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N10)&amp;"|"&amp;$AO10,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="b">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
         <v>612</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C11,User!$A:$A,0))</f>
+      <c r="E11" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D11,User!$A:$A,0))</f>
         <v>org_admin3_1</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>723</v>
       </c>
-      <c r="F11" s="19" t="b">
+      <c r="G11" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G11" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C11,User!$A:$A,0))</f>
+      <c r="H11" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D11,User!$A:$A,0))</f>
         <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037</v>
       </c>
-      <c r="H11" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C11,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="6" t="str">
-        <f>IF(ISNA(MATCH($G11&amp;"|"&amp;$V11,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G11&amp;"|"&amp;$V11,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I11" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D11,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="6" t="str">
+        <f>IF(ISNA(MATCH($H11&amp;"|"&amp;$W11,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H11&amp;"|"&amp;$W11,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J11" ca="1">IF($I11="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I11)&amp;"|"&amp;$R11,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K11" ca="1">IF($I11="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I11),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I11)&amp;"|"&amp;$R11,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K11" ca="1">IF($J11="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J11)&amp;"|"&amp;$S11,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L11" ca="1">IF($I11="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I11),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I11)&amp;"|"&amp;$R11,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="6" t="str">
-        <f>IF(ISNA(MATCH($C11&amp;"|"&amp;$V11,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C11&amp;"|"&amp;$V11,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L11" ca="1">IF($J11="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J11),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J11)&amp;"|"&amp;$S11,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M11" ca="1">IF($J11="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J11),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J11)&amp;"|"&amp;$S11,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="6" t="str">
+        <f>IF(ISNA(MATCH($D11&amp;"|"&amp;$W11,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D11&amp;"|"&amp;$W11,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N11" ca="1">IF($M11="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M11)&amp;"|"&amp;$R11,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O11" ca="1">IF($M11="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M11),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M11)&amp;"|"&amp;$R11,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O11" ca="1">IF($N11="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N11)&amp;"|"&amp;$S11,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P11" ca="1">IF($M11="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M11),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M11)&amp;"|"&amp;$R11,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q11" t="s">
+        <f t="array" aca="1" ref="P11" ca="1">IF($N11="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N11),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N11)&amp;"|"&amp;$S11,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q11" ca="1">IF($N11="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N11),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N11)&amp;"|"&amp;$S11,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R11" t="s">
         <v>638</v>
       </c>
-      <c r="R11" t="s">
+      <c r="S11" t="s">
         <v>119</v>
       </c>
-      <c r="S11" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R11,CaseType!$A:$A,0))</f>
+      <c r="T11" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S11,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T11" s="6" t="b">
-        <f>AND(IF($Z11="",TRUE,$R11=INDEX(CaseTypeCol!$B:$B,MATCH($Z11,CaseTypeCol!$A:$A,0))),IF($AG11="",TRUE,$R11=INDEX(CaseTypeCol!$B:$B,MATCH($AG11,CaseTypeCol!$A:$A,0))),IF($AN11="",TRUE,$R11=INDEX(CaseTypeCol!$B:$B,MATCH($AN11,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V11" t="s">
+      <c r="U11" s="6" t="b">
+        <f>AND(IF($AA11="",TRUE,$S11=INDEX(CaseTypeCol!$B:$B,MATCH($AA11,CaseTypeCol!$A:$A,0))),IF($AH11="",TRUE,$S11=INDEX(CaseTypeCol!$B:$B,MATCH($AH11,CaseTypeCol!$A:$A,0))),IF($AO11="",TRUE,$S11=INDEX(CaseTypeCol!$B:$B,MATCH($AO11,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W11" t="s">
         <v>11</v>
       </c>
-      <c r="W11" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V11,DataCollection!$A:$A,0))</f>
+      <c r="X11" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W11,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y11" s="14">
+      <c r="Z11" s="14">
         <v>36526</v>
       </c>
-      <c r="Z11" t="s">
+      <c r="AA11" t="s">
         <v>142</v>
       </c>
-      <c r="AA11" t="s">
+      <c r="AB11" t="s">
         <v>665</v>
       </c>
-      <c r="AB11" s="6" t="str">
-        <f>IF($Z11="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z11,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC11" s="6" t="str">
+        <f>IF($AA11="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA11,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC11" ca="1">IF($Z11="",TRUE,IF($I11="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I11)&amp;"|"&amp;$Z11,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD11" ca="1">IF($Z11="",TRUE,IF($I11="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I11)&amp;"|"&amp;$Z11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD11" ca="1">IF($AA11="",TRUE,IF($J11="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J11)&amp;"|"&amp;$AA11,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE11" ca="1">IF($Z11="",TRUE,IF($M11="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M11)&amp;"|"&amp;$Z11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE11" ca="1">IF($AA11="",TRUE,IF($J11="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J11)&amp;"|"&amp;$AA11,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF11" ca="1">IF($Z11="",TRUE,IF($M11="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M11)&amp;"|"&amp;$Z11,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI11" s="6" t="str">
-        <f>IF($AG11="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG11,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF11" ca="1">IF($AA11="",TRUE,IF($N11="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N11)&amp;"|"&amp;$AA11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG11" ca="1">IF($AA11="",TRUE,IF($N11="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N11)&amp;"|"&amp;$AA11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="6" t="str">
+        <f>IF($AH11="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH11,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ11" ca="1">IF($AG11="",TRUE,IF($I11="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I11)&amp;"|"&amp;$AG11,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK11" ca="1">IF($AG11="",TRUE,IF($I11="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I11)&amp;"|"&amp;$AG11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK11" ca="1">IF($AH11="",TRUE,IF($J11="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J11)&amp;"|"&amp;$AH11,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL11" ca="1">IF($AG11="",TRUE,IF($M11="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M11)&amp;"|"&amp;$AG11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL11" ca="1">IF($AH11="",TRUE,IF($J11="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J11)&amp;"|"&amp;$AH11,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM11" ca="1">IF($AG11="",TRUE,IF($M11="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M11)&amp;"|"&amp;$AG11,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP11" s="6" t="str">
-        <f>IF($AN11="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN11,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM11" ca="1">IF($AH11="",TRUE,IF($N11="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N11)&amp;"|"&amp;$AH11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN11" ca="1">IF($AH11="",TRUE,IF($N11="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N11)&amp;"|"&amp;$AH11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ11" s="6" t="str">
+        <f>IF($AO11="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO11,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ11" ca="1">IF($AN11="",TRUE,IF($I11="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I11)&amp;"|"&amp;$AN11,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR11" ca="1">IF($AN11="",TRUE,IF($I11="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I11)&amp;"|"&amp;$AN11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR11" ca="1">IF($AO11="",TRUE,IF($J11="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J11)&amp;"|"&amp;$AO11,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS11" ca="1">IF($AN11="",TRUE,IF($M11="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M11)&amp;"|"&amp;$AN11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS11" ca="1">IF($AO11="",TRUE,IF($J11="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J11)&amp;"|"&amp;$AO11,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT11" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT11" ca="1">IF($AN11="",TRUE,IF($M11="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M11)&amp;"|"&amp;$AN11,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT11" ca="1">IF($AO11="",TRUE,IF($N11="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N11)&amp;"|"&amp;$AO11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU11" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU11" ca="1">IF($AO11="",TRUE,IF($N11="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N11)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N11)&amp;"|"&amp;$AO11,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="b">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
         <v>613</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C12,User!$A:$A,0))</f>
+      <c r="E12" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D12,User!$A:$A,0))</f>
         <v>org_admin4_1</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>723</v>
       </c>
-      <c r="F12" s="19" t="b">
+      <c r="G12" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G12" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C12,User!$A:$A,0))</f>
+      <c r="H12" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D12,User!$A:$A,0))</f>
         <v>0195d18c-1c92-d419-4c71-a570f428499b</v>
       </c>
-      <c r="H12" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C12,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="6" t="str">
-        <f>IF(ISNA(MATCH($G12&amp;"|"&amp;$V12,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G12&amp;"|"&amp;$V12,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I12" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D12,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="6" t="str">
+        <f>IF(ISNA(MATCH($H12&amp;"|"&amp;$W12,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H12&amp;"|"&amp;$W12,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J12" ca="1">IF($I12="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I12)&amp;"|"&amp;$R12,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K12" ca="1">IF($I12="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I12),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I12)&amp;"|"&amp;$R12,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K12" ca="1">IF($J12="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J12)&amp;"|"&amp;$S12,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L12" ca="1">IF($I12="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I12),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I12)&amp;"|"&amp;$R12,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="6" t="str">
-        <f>IF(ISNA(MATCH($C12&amp;"|"&amp;$V12,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C12&amp;"|"&amp;$V12,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L12" ca="1">IF($J12="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J12),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J12)&amp;"|"&amp;$S12,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M12" ca="1">IF($J12="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J12),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J12)&amp;"|"&amp;$S12,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="6" t="str">
+        <f>IF(ISNA(MATCH($D12&amp;"|"&amp;$W12,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D12&amp;"|"&amp;$W12,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N12" ca="1">IF($M12="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M12)&amp;"|"&amp;$R12,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O12" ca="1">IF($M12="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M12),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M12)&amp;"|"&amp;$R12,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O12" ca="1">IF($N12="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N12)&amp;"|"&amp;$S12,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P12" ca="1">IF($M12="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M12),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M12)&amp;"|"&amp;$R12,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q12" t="s">
+        <f t="array" aca="1" ref="P12" ca="1">IF($N12="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N12),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N12)&amp;"|"&amp;$S12,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q12" ca="1">IF($N12="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N12),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N12)&amp;"|"&amp;$S12,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R12" t="s">
         <v>639</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
         <v>119</v>
       </c>
-      <c r="S12" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R12,CaseType!$A:$A,0))</f>
+      <c r="T12" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S12,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T12" s="6" t="b">
-        <f>AND(IF($Z12="",TRUE,$R12=INDEX(CaseTypeCol!$B:$B,MATCH($Z12,CaseTypeCol!$A:$A,0))),IF($AG12="",TRUE,$R12=INDEX(CaseTypeCol!$B:$B,MATCH($AG12,CaseTypeCol!$A:$A,0))),IF($AN12="",TRUE,$R12=INDEX(CaseTypeCol!$B:$B,MATCH($AN12,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V12" t="s">
+      <c r="U12" s="6" t="b">
+        <f>AND(IF($AA12="",TRUE,$S12=INDEX(CaseTypeCol!$B:$B,MATCH($AA12,CaseTypeCol!$A:$A,0))),IF($AH12="",TRUE,$S12=INDEX(CaseTypeCol!$B:$B,MATCH($AH12,CaseTypeCol!$A:$A,0))),IF($AO12="",TRUE,$S12=INDEX(CaseTypeCol!$B:$B,MATCH($AO12,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W12" t="s">
         <v>11</v>
       </c>
-      <c r="W12" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V12,DataCollection!$A:$A,0))</f>
+      <c r="X12" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W12,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y12" s="14">
+      <c r="Z12" s="14">
         <v>36526</v>
       </c>
-      <c r="Z12" t="s">
+      <c r="AA12" t="s">
         <v>142</v>
       </c>
-      <c r="AA12" t="s">
+      <c r="AB12" t="s">
         <v>665</v>
       </c>
-      <c r="AB12" s="6" t="str">
-        <f>IF($Z12="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z12,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC12" s="6" t="str">
+        <f>IF($AA12="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA12,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC12" ca="1">IF($Z12="",TRUE,IF($I12="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I12)&amp;"|"&amp;$Z12,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD12" ca="1">IF($Z12="",TRUE,IF($I12="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I12)&amp;"|"&amp;$Z12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD12" ca="1">IF($AA12="",TRUE,IF($J12="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J12)&amp;"|"&amp;$AA12,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE12" ca="1">IF($Z12="",TRUE,IF($M12="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M12)&amp;"|"&amp;$Z12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE12" ca="1">IF($AA12="",TRUE,IF($J12="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J12)&amp;"|"&amp;$AA12,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF12" ca="1">IF($Z12="",TRUE,IF($M12="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M12)&amp;"|"&amp;$Z12,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI12" s="6" t="str">
-        <f>IF($AG12="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG12,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF12" ca="1">IF($AA12="",TRUE,IF($N12="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N12)&amp;"|"&amp;$AA12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG12" ca="1">IF($AA12="",TRUE,IF($N12="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N12)&amp;"|"&amp;$AA12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="6" t="str">
+        <f>IF($AH12="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH12,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ12" ca="1">IF($AG12="",TRUE,IF($I12="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I12)&amp;"|"&amp;$AG12,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK12" ca="1">IF($AG12="",TRUE,IF($I12="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I12)&amp;"|"&amp;$AG12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK12" ca="1">IF($AH12="",TRUE,IF($J12="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J12)&amp;"|"&amp;$AH12,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL12" ca="1">IF($AG12="",TRUE,IF($M12="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M12)&amp;"|"&amp;$AG12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL12" ca="1">IF($AH12="",TRUE,IF($J12="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J12)&amp;"|"&amp;$AH12,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM12" ca="1">IF($AG12="",TRUE,IF($M12="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M12)&amp;"|"&amp;$AG12,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP12" s="6" t="str">
-        <f>IF($AN12="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN12,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM12" ca="1">IF($AH12="",TRUE,IF($N12="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N12)&amp;"|"&amp;$AH12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN12" ca="1">IF($AH12="",TRUE,IF($N12="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N12)&amp;"|"&amp;$AH12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ12" s="6" t="str">
+        <f>IF($AO12="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO12,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ12" ca="1">IF($AN12="",TRUE,IF($I12="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I12)&amp;"|"&amp;$AN12,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR12" ca="1">IF($AN12="",TRUE,IF($I12="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I12)&amp;"|"&amp;$AN12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR12" ca="1">IF($AO12="",TRUE,IF($J12="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J12)&amp;"|"&amp;$AO12,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS12" ca="1">IF($AN12="",TRUE,IF($M12="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M12)&amp;"|"&amp;$AN12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS12" ca="1">IF($AO12="",TRUE,IF($J12="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J12)&amp;"|"&amp;$AO12,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT12" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT12" ca="1">IF($AN12="",TRUE,IF($M12="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M12)&amp;"|"&amp;$AN12,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT12" ca="1">IF($AO12="",TRUE,IF($N12="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N12)&amp;"|"&amp;$AO12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU12" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU12" ca="1">IF($AO12="",TRUE,IF($N12="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N12)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N12)&amp;"|"&amp;$AO12,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
         <v>614</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C13,User!$A:$A,0))</f>
+      <c r="E13" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D13,User!$A:$A,0))</f>
         <v>org_admin5_1</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>723</v>
       </c>
-      <c r="F13" s="19" t="b">
+      <c r="G13" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G13" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C13,User!$A:$A,0))</f>
+      <c r="H13" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D13,User!$A:$A,0))</f>
         <v>0195d18c-1c93-02a2-6920-7e4dbfb73ce0</v>
       </c>
-      <c r="H13" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C13,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="6" t="str">
-        <f>IF(ISNA(MATCH($G13&amp;"|"&amp;$V13,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G13&amp;"|"&amp;$V13,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I13" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D13,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="6" t="str">
+        <f>IF(ISNA(MATCH($H13&amp;"|"&amp;$W13,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H13&amp;"|"&amp;$W13,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J13" ca="1">IF($I13="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I13)&amp;"|"&amp;$R13,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K13" ca="1">IF($I13="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I13),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I13)&amp;"|"&amp;$R13,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K13" ca="1">IF($J13="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J13)&amp;"|"&amp;$S13,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L13" ca="1">IF($I13="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I13),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I13)&amp;"|"&amp;$R13,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="6" t="str">
-        <f>IF(ISNA(MATCH($C13&amp;"|"&amp;$V13,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C13&amp;"|"&amp;$V13,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L13" ca="1">IF($J13="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J13),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J13)&amp;"|"&amp;$S13,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M13" ca="1">IF($J13="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J13),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J13)&amp;"|"&amp;$S13,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="6" t="str">
+        <f>IF(ISNA(MATCH($D13&amp;"|"&amp;$W13,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D13&amp;"|"&amp;$W13,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N13" ca="1">IF($M13="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M13)&amp;"|"&amp;$R13,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O13" ca="1">IF($M13="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M13),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M13)&amp;"|"&amp;$R13,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O13" ca="1">IF($N13="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N13)&amp;"|"&amp;$S13,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P13" ca="1">IF($M13="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M13),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M13)&amp;"|"&amp;$R13,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q13" t="s">
+        <f t="array" aca="1" ref="P13" ca="1">IF($N13="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N13),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N13)&amp;"|"&amp;$S13,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q13" ca="1">IF($N13="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N13),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N13)&amp;"|"&amp;$S13,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R13" t="s">
         <v>640</v>
       </c>
-      <c r="R13" t="s">
+      <c r="S13" t="s">
         <v>119</v>
       </c>
-      <c r="S13" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R13,CaseType!$A:$A,0))</f>
+      <c r="T13" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S13,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T13" s="6" t="b">
-        <f>AND(IF($Z13="",TRUE,$R13=INDEX(CaseTypeCol!$B:$B,MATCH($Z13,CaseTypeCol!$A:$A,0))),IF($AG13="",TRUE,$R13=INDEX(CaseTypeCol!$B:$B,MATCH($AG13,CaseTypeCol!$A:$A,0))),IF($AN13="",TRUE,$R13=INDEX(CaseTypeCol!$B:$B,MATCH($AN13,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V13" t="s">
+      <c r="U13" s="6" t="b">
+        <f>AND(IF($AA13="",TRUE,$S13=INDEX(CaseTypeCol!$B:$B,MATCH($AA13,CaseTypeCol!$A:$A,0))),IF($AH13="",TRUE,$S13=INDEX(CaseTypeCol!$B:$B,MATCH($AH13,CaseTypeCol!$A:$A,0))),IF($AO13="",TRUE,$S13=INDEX(CaseTypeCol!$B:$B,MATCH($AO13,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W13" t="s">
         <v>11</v>
       </c>
-      <c r="W13" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V13,DataCollection!$A:$A,0))</f>
+      <c r="X13" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W13,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y13" s="14">
+      <c r="Z13" s="14">
         <v>36526</v>
       </c>
-      <c r="Z13" t="s">
+      <c r="AA13" t="s">
         <v>142</v>
       </c>
-      <c r="AA13" t="s">
+      <c r="AB13" t="s">
         <v>665</v>
       </c>
-      <c r="AB13" s="6" t="str">
-        <f>IF($Z13="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z13,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC13" s="6" t="str">
+        <f>IF($AA13="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA13,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC13" ca="1">IF($Z13="",TRUE,IF($I13="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I13)&amp;"|"&amp;$Z13,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD13" ca="1">IF($Z13="",TRUE,IF($I13="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I13)&amp;"|"&amp;$Z13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD13" ca="1">IF($AA13="",TRUE,IF($J13="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J13)&amp;"|"&amp;$AA13,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE13" ca="1">IF($Z13="",TRUE,IF($M13="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M13)&amp;"|"&amp;$Z13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE13" ca="1">IF($AA13="",TRUE,IF($J13="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J13)&amp;"|"&amp;$AA13,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF13" ca="1">IF($Z13="",TRUE,IF($M13="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M13)&amp;"|"&amp;$Z13,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI13" s="6" t="str">
-        <f>IF($AG13="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG13,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF13" ca="1">IF($AA13="",TRUE,IF($N13="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N13)&amp;"|"&amp;$AA13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG13" ca="1">IF($AA13="",TRUE,IF($N13="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N13)&amp;"|"&amp;$AA13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6" t="str">
+        <f>IF($AH13="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH13,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ13" ca="1">IF($AG13="",TRUE,IF($I13="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I13)&amp;"|"&amp;$AG13,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK13" ca="1">IF($AG13="",TRUE,IF($I13="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I13)&amp;"|"&amp;$AG13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK13" ca="1">IF($AH13="",TRUE,IF($J13="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J13)&amp;"|"&amp;$AH13,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL13" ca="1">IF($AG13="",TRUE,IF($M13="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M13)&amp;"|"&amp;$AG13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL13" ca="1">IF($AH13="",TRUE,IF($J13="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J13)&amp;"|"&amp;$AH13,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM13" ca="1">IF($AG13="",TRUE,IF($M13="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M13)&amp;"|"&amp;$AG13,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP13" s="6" t="str">
-        <f>IF($AN13="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN13,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM13" ca="1">IF($AH13="",TRUE,IF($N13="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N13)&amp;"|"&amp;$AH13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN13" ca="1">IF($AH13="",TRUE,IF($N13="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N13)&amp;"|"&amp;$AH13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ13" s="6" t="str">
+        <f>IF($AO13="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO13,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ13" ca="1">IF($AN13="",TRUE,IF($I13="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I13)&amp;"|"&amp;$AN13,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR13" ca="1">IF($AN13="",TRUE,IF($I13="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I13)&amp;"|"&amp;$AN13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR13" ca="1">IF($AO13="",TRUE,IF($J13="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J13)&amp;"|"&amp;$AO13,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS13" ca="1">IF($AN13="",TRUE,IF($M13="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M13)&amp;"|"&amp;$AN13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS13" ca="1">IF($AO13="",TRUE,IF($J13="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J13)&amp;"|"&amp;$AO13,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT13" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT13" ca="1">IF($AN13="",TRUE,IF($M13="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M13)&amp;"|"&amp;$AN13,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT13" ca="1">IF($AO13="",TRUE,IF($N13="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N13)&amp;"|"&amp;$AO13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU13" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU13" ca="1">IF($AO13="",TRUE,IF($N13="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N13)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N13)&amp;"|"&amp;$AO13,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="b">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
         <v>615</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C14,User!$A:$A,0))</f>
+      <c r="E14" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D14,User!$A:$A,0))</f>
         <v>org_user1_1</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>723</v>
       </c>
-      <c r="F14" s="19" t="b">
+      <c r="G14" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="G14" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C14,User!$A:$A,0))</f>
+      <c r="H14" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D14,User!$A:$A,0))</f>
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
       </c>
-      <c r="H14" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C14,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="6">
-        <f>IF(ISNA(MATCH($G14&amp;"|"&amp;$V14,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G14&amp;"|"&amp;$V14,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I14" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D14,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="6">
+        <f>IF(ISNA(MATCH($H14&amp;"|"&amp;$W14,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H14&amp;"|"&amp;$W14,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v>2</v>
       </c>
-      <c r="J14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J14" ca="1">IF($I14="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I14)&amp;"|"&amp;$R14,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>1</v>
-      </c>
       <c r="K14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K14" ca="1">IF($I14="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I14),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I14)&amp;"|"&amp;$R14,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K14" ca="1">IF($J14="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J14)&amp;"|"&amp;$S14,CaseTypeSetMember!$H:$H,0))))</f>
         <v>1</v>
       </c>
       <c r="L14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L14" ca="1">IF($I14="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I14),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I14)&amp;"|"&amp;$R14,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="M14" s="6">
-        <f>IF(ISNA(MATCH($C14&amp;"|"&amp;$V14,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C14&amp;"|"&amp;$V14,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L14" ca="1">IF($J14="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J14),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J14)&amp;"|"&amp;$S14,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M14" ca="1">IF($J14="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J14),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J14)&amp;"|"&amp;$S14,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="N14" s="6">
+        <f>IF(ISNA(MATCH($D14&amp;"|"&amp;$W14,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D14&amp;"|"&amp;$W14,UserAccessCasePolicy!$W:$W,0))</f>
         <v>2</v>
       </c>
-      <c r="N14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N14" ca="1">IF($M14="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M14)&amp;"|"&amp;$R14,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>1</v>
-      </c>
       <c r="O14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O14" ca="1">IF($M14="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M14),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M14)&amp;"|"&amp;$R14,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O14" ca="1">IF($N14="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N14)&amp;"|"&amp;$S14,CaseTypeSetMember!$H:$H,0))))</f>
         <v>1</v>
       </c>
       <c r="P14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P14" ca="1">IF($M14="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M14),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M14)&amp;"|"&amp;$R14,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="Q14" t="s">
+        <f t="array" aca="1" ref="P14" ca="1">IF($N14="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N14),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N14)&amp;"|"&amp;$S14,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q14" ca="1">IF($N14="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N14),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N14)&amp;"|"&amp;$S14,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="R14" t="s">
         <v>641</v>
       </c>
-      <c r="R14" t="s">
+      <c r="S14" t="s">
         <v>119</v>
       </c>
-      <c r="S14" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R14,CaseType!$A:$A,0))</f>
+      <c r="T14" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S14,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T14" s="6" t="b">
-        <f>AND(IF($Z14="",TRUE,$R14=INDEX(CaseTypeCol!$B:$B,MATCH($Z14,CaseTypeCol!$A:$A,0))),IF($AG14="",TRUE,$R14=INDEX(CaseTypeCol!$B:$B,MATCH($AG14,CaseTypeCol!$A:$A,0))),IF($AN14="",TRUE,$R14=INDEX(CaseTypeCol!$B:$B,MATCH($AN14,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V14" t="s">
+      <c r="U14" s="6" t="b">
+        <f>AND(IF($AA14="",TRUE,$S14=INDEX(CaseTypeCol!$B:$B,MATCH($AA14,CaseTypeCol!$A:$A,0))),IF($AH14="",TRUE,$S14=INDEX(CaseTypeCol!$B:$B,MATCH($AH14,CaseTypeCol!$A:$A,0))),IF($AO14="",TRUE,$S14=INDEX(CaseTypeCol!$B:$B,MATCH($AO14,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W14" t="s">
         <v>11</v>
       </c>
-      <c r="W14" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V14,DataCollection!$A:$A,0))</f>
+      <c r="X14" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W14,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y14" s="14">
+      <c r="Z14" s="14">
         <v>36526</v>
       </c>
-      <c r="Z14" t="s">
+      <c r="AA14" t="s">
         <v>142</v>
       </c>
-      <c r="AA14" t="s">
+      <c r="AB14" t="s">
         <v>665</v>
       </c>
-      <c r="AB14" s="6" t="str">
-        <f>IF($Z14="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z14,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC14" s="6" t="str">
+        <f>IF($AA14="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA14,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC14" ca="1">IF($Z14="",TRUE,IF($I14="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I14)&amp;"|"&amp;$Z14,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AD14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD14" ca="1">IF($Z14="",TRUE,IF($I14="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I14)&amp;"|"&amp;$Z14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD14" ca="1">IF($AA14="",TRUE,IF($J14="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J14)&amp;"|"&amp;$AA14,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AE14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE14" ca="1">IF($Z14="",TRUE,IF($M14="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M14)&amp;"|"&amp;$Z14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE14" ca="1">IF($AA14="",TRUE,IF($J14="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J14)&amp;"|"&amp;$AA14,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AF14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF14" ca="1">IF($Z14="",TRUE,IF($M14="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M14)&amp;"|"&amp;$Z14,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AI14" s="6" t="str">
-        <f>IF($AG14="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG14,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF14" ca="1">IF($AA14="",TRUE,IF($N14="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N14)&amp;"|"&amp;$AA14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AG14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG14" ca="1">IF($AA14="",TRUE,IF($N14="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N14)&amp;"|"&amp;$AA14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AJ14" s="6" t="str">
+        <f>IF($AH14="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH14,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ14" ca="1">IF($AG14="",TRUE,IF($I14="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I14)&amp;"|"&amp;$AG14,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK14" ca="1">IF($AG14="",TRUE,IF($I14="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I14)&amp;"|"&amp;$AG14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK14" ca="1">IF($AH14="",TRUE,IF($J14="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J14)&amp;"|"&amp;$AH14,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL14" ca="1">IF($AG14="",TRUE,IF($M14="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M14)&amp;"|"&amp;$AG14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL14" ca="1">IF($AH14="",TRUE,IF($J14="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J14)&amp;"|"&amp;$AH14,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM14" ca="1">IF($AG14="",TRUE,IF($M14="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M14)&amp;"|"&amp;$AG14,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP14" s="6" t="str">
-        <f>IF($AN14="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN14,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM14" ca="1">IF($AH14="",TRUE,IF($N14="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N14)&amp;"|"&amp;$AH14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN14" ca="1">IF($AH14="",TRUE,IF($N14="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N14)&amp;"|"&amp;$AH14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ14" s="6" t="str">
+        <f>IF($AO14="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO14,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ14" ca="1">IF($AN14="",TRUE,IF($I14="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I14)&amp;"|"&amp;$AN14,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR14" ca="1">IF($AN14="",TRUE,IF($I14="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I14)&amp;"|"&amp;$AN14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR14" ca="1">IF($AO14="",TRUE,IF($J14="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J14)&amp;"|"&amp;$AO14,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS14" ca="1">IF($AN14="",TRUE,IF($M14="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M14)&amp;"|"&amp;$AN14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS14" ca="1">IF($AO14="",TRUE,IF($J14="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J14)&amp;"|"&amp;$AO14,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT14" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT14" ca="1">IF($AN14="",TRUE,IF($M14="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M14)&amp;"|"&amp;$AN14,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT14" ca="1">IF($AO14="",TRUE,IF($N14="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N14)&amp;"|"&amp;$AO14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU14" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU14" ca="1">IF($AO14="",TRUE,IF($N14="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N14)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N14)&amp;"|"&amp;$AO14,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
         <v>616</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C15,User!$A:$A,0))</f>
+      <c r="E15" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D15,User!$A:$A,0))</f>
         <v>org_user1_2</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>723</v>
       </c>
-      <c r="F15" s="19" t="b">
+      <c r="G15" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G15" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C15,User!$A:$A,0))</f>
+      <c r="H15" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D15,User!$A:$A,0))</f>
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
       </c>
-      <c r="H15" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C15,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="6">
-        <f>IF(ISNA(MATCH($G15&amp;"|"&amp;$V15,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G15&amp;"|"&amp;$V15,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I15" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D15,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="6">
+        <f>IF(ISNA(MATCH($H15&amp;"|"&amp;$W15,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H15&amp;"|"&amp;$W15,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v>2</v>
       </c>
-      <c r="J15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J15" ca="1">IF($I15="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I15)&amp;"|"&amp;$R15,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>1</v>
-      </c>
       <c r="K15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K15" ca="1">IF($I15="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I15),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I15)&amp;"|"&amp;$R15,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K15" ca="1">IF($J15="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J15)&amp;"|"&amp;$S15,CaseTypeSetMember!$H:$H,0))))</f>
         <v>1</v>
       </c>
       <c r="L15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L15" ca="1">IF($I15="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I15),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I15)&amp;"|"&amp;$R15,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="M15" s="6" t="str">
-        <f>IF(ISNA(MATCH($C15&amp;"|"&amp;$V15,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C15&amp;"|"&amp;$V15,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L15" ca="1">IF($J15="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J15),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J15)&amp;"|"&amp;$S15,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M15" ca="1">IF($J15="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J15),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J15)&amp;"|"&amp;$S15,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="N15" s="6" t="str">
+        <f>IF(ISNA(MATCH($D15&amp;"|"&amp;$W15,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D15&amp;"|"&amp;$W15,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N15" ca="1">IF($M15="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M15)&amp;"|"&amp;$R15,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O15" ca="1">IF($M15="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M15),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M15)&amp;"|"&amp;$R15,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O15" ca="1">IF($N15="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N15)&amp;"|"&amp;$S15,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P15" ca="1">IF($M15="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M15),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M15)&amp;"|"&amp;$R15,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" t="s">
+        <f t="array" aca="1" ref="P15" ca="1">IF($N15="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N15),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N15)&amp;"|"&amp;$S15,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q15" ca="1">IF($N15="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N15),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N15)&amp;"|"&amp;$S15,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R15" t="s">
         <v>642</v>
       </c>
-      <c r="R15" t="s">
+      <c r="S15" t="s">
         <v>119</v>
       </c>
-      <c r="S15" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R15,CaseType!$A:$A,0))</f>
+      <c r="T15" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S15,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T15" s="6" t="b">
-        <f>AND(IF($Z15="",TRUE,$R15=INDEX(CaseTypeCol!$B:$B,MATCH($Z15,CaseTypeCol!$A:$A,0))),IF($AG15="",TRUE,$R15=INDEX(CaseTypeCol!$B:$B,MATCH($AG15,CaseTypeCol!$A:$A,0))),IF($AN15="",TRUE,$R15=INDEX(CaseTypeCol!$B:$B,MATCH($AN15,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V15" t="s">
+      <c r="U15" s="6" t="b">
+        <f>AND(IF($AA15="",TRUE,$S15=INDEX(CaseTypeCol!$B:$B,MATCH($AA15,CaseTypeCol!$A:$A,0))),IF($AH15="",TRUE,$S15=INDEX(CaseTypeCol!$B:$B,MATCH($AH15,CaseTypeCol!$A:$A,0))),IF($AO15="",TRUE,$S15=INDEX(CaseTypeCol!$B:$B,MATCH($AO15,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W15" t="s">
         <v>11</v>
       </c>
-      <c r="W15" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V15,DataCollection!$A:$A,0))</f>
+      <c r="X15" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W15,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y15" s="14">
+      <c r="Z15" s="14">
         <v>36526</v>
       </c>
-      <c r="Z15" t="s">
+      <c r="AA15" t="s">
         <v>142</v>
       </c>
-      <c r="AA15" t="s">
+      <c r="AB15" t="s">
         <v>665</v>
       </c>
-      <c r="AB15" s="6" t="str">
-        <f>IF($Z15="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z15,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC15" s="6" t="str">
+        <f>IF($AA15="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA15,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC15" ca="1">IF($Z15="",TRUE,IF($I15="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I15)&amp;"|"&amp;$Z15,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AD15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD15" ca="1">IF($Z15="",TRUE,IF($I15="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I15)&amp;"|"&amp;$Z15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD15" ca="1">IF($AA15="",TRUE,IF($J15="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J15)&amp;"|"&amp;$AA15,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AE15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE15" ca="1">IF($Z15="",TRUE,IF($M15="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M15)&amp;"|"&amp;$Z15,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
+        <f t="array" aca="1" ref="AE15" ca="1">IF($AA15="",TRUE,IF($J15="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J15)&amp;"|"&amp;$AA15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
       </c>
       <c r="AF15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF15" ca="1">IF($Z15="",TRUE,IF($M15="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M15)&amp;"|"&amp;$Z15,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI15" s="6" t="str">
-        <f>IF($AG15="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG15,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF15" ca="1">IF($AA15="",TRUE,IF($N15="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N15)&amp;"|"&amp;$AA15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG15" ca="1">IF($AA15="",TRUE,IF($N15="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N15)&amp;"|"&amp;$AA15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="6" t="str">
+        <f>IF($AH15="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH15,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ15" ca="1">IF($AG15="",TRUE,IF($I15="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I15)&amp;"|"&amp;$AG15,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK15" ca="1">IF($AG15="",TRUE,IF($I15="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I15)&amp;"|"&amp;$AG15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK15" ca="1">IF($AH15="",TRUE,IF($J15="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J15)&amp;"|"&amp;$AH15,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL15" ca="1">IF($AG15="",TRUE,IF($M15="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M15)&amp;"|"&amp;$AG15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL15" ca="1">IF($AH15="",TRUE,IF($J15="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J15)&amp;"|"&amp;$AH15,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM15" ca="1">IF($AG15="",TRUE,IF($M15="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M15)&amp;"|"&amp;$AG15,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP15" s="6" t="str">
-        <f>IF($AN15="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN15,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM15" ca="1">IF($AH15="",TRUE,IF($N15="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N15)&amp;"|"&amp;$AH15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN15" ca="1">IF($AH15="",TRUE,IF($N15="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N15)&amp;"|"&amp;$AH15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ15" s="6" t="str">
+        <f>IF($AO15="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO15,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ15" ca="1">IF($AN15="",TRUE,IF($I15="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I15)&amp;"|"&amp;$AN15,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR15" ca="1">IF($AN15="",TRUE,IF($I15="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I15)&amp;"|"&amp;$AN15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR15" ca="1">IF($AO15="",TRUE,IF($J15="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J15)&amp;"|"&amp;$AO15,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS15" ca="1">IF($AN15="",TRUE,IF($M15="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M15)&amp;"|"&amp;$AN15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS15" ca="1">IF($AO15="",TRUE,IF($J15="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J15)&amp;"|"&amp;$AO15,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT15" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT15" ca="1">IF($AN15="",TRUE,IF($M15="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M15)&amp;"|"&amp;$AN15,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT15" ca="1">IF($AO15="",TRUE,IF($N15="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N15)&amp;"|"&amp;$AO15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU15" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU15" ca="1">IF($AO15="",TRUE,IF($N15="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N15)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N15)&amp;"|"&amp;$AO15,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="b">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
         <v>617</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C16,User!$A:$A,0))</f>
+      <c r="E16" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D16,User!$A:$A,0))</f>
         <v>org_user1_3</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>723</v>
       </c>
-      <c r="F16" s="19" t="b">
+      <c r="G16" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G16" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C16,User!$A:$A,0))</f>
+      <c r="H16" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D16,User!$A:$A,0))</f>
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
       </c>
-      <c r="H16" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C16,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="6">
-        <f>IF(ISNA(MATCH($G16&amp;"|"&amp;$V16,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G16&amp;"|"&amp;$V16,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I16" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D16,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="6">
+        <f>IF(ISNA(MATCH($H16&amp;"|"&amp;$W16,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H16&amp;"|"&amp;$W16,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v>2</v>
       </c>
-      <c r="J16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J16" ca="1">IF($I16="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I16)&amp;"|"&amp;$R16,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>1</v>
-      </c>
       <c r="K16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K16" ca="1">IF($I16="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I16),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I16)&amp;"|"&amp;$R16,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K16" ca="1">IF($J16="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J16)&amp;"|"&amp;$S16,CaseTypeSetMember!$H:$H,0))))</f>
         <v>1</v>
       </c>
       <c r="L16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L16" ca="1">IF($I16="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I16),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I16)&amp;"|"&amp;$R16,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="M16" s="6" t="str">
-        <f>IF(ISNA(MATCH($C16&amp;"|"&amp;$V16,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C16&amp;"|"&amp;$V16,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L16" ca="1">IF($J16="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J16),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J16)&amp;"|"&amp;$S16,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M16" ca="1">IF($J16="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J16),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J16)&amp;"|"&amp;$S16,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="N16" s="6" t="str">
+        <f>IF(ISNA(MATCH($D16&amp;"|"&amp;$W16,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D16&amp;"|"&amp;$W16,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N16" ca="1">IF($M16="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M16)&amp;"|"&amp;$R16,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O16" ca="1">IF($M16="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M16),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M16)&amp;"|"&amp;$R16,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O16" ca="1">IF($N16="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N16)&amp;"|"&amp;$S16,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P16" ca="1">IF($M16="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M16),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M16)&amp;"|"&amp;$R16,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" t="s">
+        <f t="array" aca="1" ref="P16" ca="1">IF($N16="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N16),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N16)&amp;"|"&amp;$S16,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q16" ca="1">IF($N16="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N16),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N16)&amp;"|"&amp;$S16,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R16" t="s">
         <v>643</v>
       </c>
-      <c r="R16" t="s">
+      <c r="S16" t="s">
         <v>119</v>
       </c>
-      <c r="S16" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R16,CaseType!$A:$A,0))</f>
+      <c r="T16" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S16,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T16" s="6" t="b">
-        <f>AND(IF($Z16="",TRUE,$R16=INDEX(CaseTypeCol!$B:$B,MATCH($Z16,CaseTypeCol!$A:$A,0))),IF($AG16="",TRUE,$R16=INDEX(CaseTypeCol!$B:$B,MATCH($AG16,CaseTypeCol!$A:$A,0))),IF($AN16="",TRUE,$R16=INDEX(CaseTypeCol!$B:$B,MATCH($AN16,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V16" t="s">
+      <c r="U16" s="6" t="b">
+        <f>AND(IF($AA16="",TRUE,$S16=INDEX(CaseTypeCol!$B:$B,MATCH($AA16,CaseTypeCol!$A:$A,0))),IF($AH16="",TRUE,$S16=INDEX(CaseTypeCol!$B:$B,MATCH($AH16,CaseTypeCol!$A:$A,0))),IF($AO16="",TRUE,$S16=INDEX(CaseTypeCol!$B:$B,MATCH($AO16,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W16" t="s">
         <v>11</v>
       </c>
-      <c r="W16" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V16,DataCollection!$A:$A,0))</f>
+      <c r="X16" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W16,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y16" s="14">
+      <c r="Z16" s="14">
         <v>36526</v>
       </c>
-      <c r="Z16" t="s">
+      <c r="AA16" t="s">
         <v>142</v>
       </c>
-      <c r="AA16" t="s">
+      <c r="AB16" t="s">
         <v>665</v>
       </c>
-      <c r="AB16" s="6" t="str">
-        <f>IF($Z16="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z16,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC16" s="6" t="str">
+        <f>IF($AA16="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA16,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC16" ca="1">IF($Z16="",TRUE,IF($I16="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I16)&amp;"|"&amp;$Z16,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AD16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD16" ca="1">IF($Z16="",TRUE,IF($I16="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I16)&amp;"|"&amp;$Z16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD16" ca="1">IF($AA16="",TRUE,IF($J16="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J16)&amp;"|"&amp;$AA16,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AE16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE16" ca="1">IF($Z16="",TRUE,IF($M16="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M16)&amp;"|"&amp;$Z16,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
+        <f t="array" aca="1" ref="AE16" ca="1">IF($AA16="",TRUE,IF($J16="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J16)&amp;"|"&amp;$AA16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
       </c>
       <c r="AF16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF16" ca="1">IF($Z16="",TRUE,IF($M16="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M16)&amp;"|"&amp;$Z16,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI16" s="6" t="str">
-        <f>IF($AG16="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG16,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF16" ca="1">IF($AA16="",TRUE,IF($N16="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N16)&amp;"|"&amp;$AA16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG16" ca="1">IF($AA16="",TRUE,IF($N16="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N16)&amp;"|"&amp;$AA16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="6" t="str">
+        <f>IF($AH16="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH16,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ16" ca="1">IF($AG16="",TRUE,IF($I16="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I16)&amp;"|"&amp;$AG16,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK16" ca="1">IF($AG16="",TRUE,IF($I16="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I16)&amp;"|"&amp;$AG16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK16" ca="1">IF($AH16="",TRUE,IF($J16="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J16)&amp;"|"&amp;$AH16,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL16" ca="1">IF($AG16="",TRUE,IF($M16="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M16)&amp;"|"&amp;$AG16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL16" ca="1">IF($AH16="",TRUE,IF($J16="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J16)&amp;"|"&amp;$AH16,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM16" ca="1">IF($AG16="",TRUE,IF($M16="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M16)&amp;"|"&amp;$AG16,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP16" s="6" t="str">
-        <f>IF($AN16="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN16,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM16" ca="1">IF($AH16="",TRUE,IF($N16="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N16)&amp;"|"&amp;$AH16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN16" ca="1">IF($AH16="",TRUE,IF($N16="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N16)&amp;"|"&amp;$AH16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ16" s="6" t="str">
+        <f>IF($AO16="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO16,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ16" ca="1">IF($AN16="",TRUE,IF($I16="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I16)&amp;"|"&amp;$AN16,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR16" ca="1">IF($AN16="",TRUE,IF($I16="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I16)&amp;"|"&amp;$AN16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR16" ca="1">IF($AO16="",TRUE,IF($J16="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J16)&amp;"|"&amp;$AO16,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS16" ca="1">IF($AN16="",TRUE,IF($M16="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M16)&amp;"|"&amp;$AN16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS16" ca="1">IF($AO16="",TRUE,IF($J16="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J16)&amp;"|"&amp;$AO16,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT16" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT16" ca="1">IF($AN16="",TRUE,IF($M16="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M16)&amp;"|"&amp;$AN16,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT16" ca="1">IF($AO16="",TRUE,IF($N16="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N16)&amp;"|"&amp;$AO16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU16" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU16" ca="1">IF($AO16="",TRUE,IF($N16="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N16)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N16)&amp;"|"&amp;$AO16,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="b">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
         <v>618</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C17,User!$A:$A,0))</f>
+      <c r="E17" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D17,User!$A:$A,0))</f>
         <v>org_user1_4</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>723</v>
       </c>
-      <c r="F17" s="19" t="b">
+      <c r="G17" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G17" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C17,User!$A:$A,0))</f>
+      <c r="H17" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D17,User!$A:$A,0))</f>
         <v>018d074d-ea0c-e942-07db-a3cc0ba1d653</v>
       </c>
-      <c r="H17" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C17,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="6">
-        <f>IF(ISNA(MATCH($G17&amp;"|"&amp;$V17,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G17&amp;"|"&amp;$V17,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I17" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D17,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="6">
+        <f>IF(ISNA(MATCH($H17&amp;"|"&amp;$W17,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H17&amp;"|"&amp;$W17,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v>2</v>
       </c>
-      <c r="J17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J17" ca="1">IF($I17="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I17)&amp;"|"&amp;$R17,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>1</v>
-      </c>
       <c r="K17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K17" ca="1">IF($I17="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I17),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I17)&amp;"|"&amp;$R17,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K17" ca="1">IF($J17="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J17)&amp;"|"&amp;$S17,CaseTypeSetMember!$H:$H,0))))</f>
         <v>1</v>
       </c>
       <c r="L17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L17" ca="1">IF($I17="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I17),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I17)&amp;"|"&amp;$R17,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="M17" s="6" t="str">
-        <f>IF(ISNA(MATCH($C17&amp;"|"&amp;$V17,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C17&amp;"|"&amp;$V17,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L17" ca="1">IF($J17="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J17),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J17)&amp;"|"&amp;$S17,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="M17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M17" ca="1">IF($J17="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J17),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J17)&amp;"|"&amp;$S17,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>1</v>
+      </c>
+      <c r="N17" s="6" t="str">
+        <f>IF(ISNA(MATCH($D17&amp;"|"&amp;$W17,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D17&amp;"|"&amp;$W17,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N17" ca="1">IF($M17="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M17)&amp;"|"&amp;$R17,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O17" ca="1">IF($M17="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M17),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M17)&amp;"|"&amp;$R17,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O17" ca="1">IF($N17="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N17)&amp;"|"&amp;$S17,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P17" ca="1">IF($M17="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M17),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M17)&amp;"|"&amp;$R17,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" t="s">
+        <f t="array" aca="1" ref="P17" ca="1">IF($N17="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N17),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N17)&amp;"|"&amp;$S17,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q17" ca="1">IF($N17="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N17),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N17)&amp;"|"&amp;$S17,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R17" t="s">
         <v>644</v>
       </c>
-      <c r="R17" t="s">
+      <c r="S17" t="s">
         <v>119</v>
       </c>
-      <c r="S17" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R17,CaseType!$A:$A,0))</f>
+      <c r="T17" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S17,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T17" s="6" t="b">
-        <f>AND(IF($Z17="",TRUE,$R17=INDEX(CaseTypeCol!$B:$B,MATCH($Z17,CaseTypeCol!$A:$A,0))),IF($AG17="",TRUE,$R17=INDEX(CaseTypeCol!$B:$B,MATCH($AG17,CaseTypeCol!$A:$A,0))),IF($AN17="",TRUE,$R17=INDEX(CaseTypeCol!$B:$B,MATCH($AN17,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V17" t="s">
+      <c r="U17" s="6" t="b">
+        <f>AND(IF($AA17="",TRUE,$S17=INDEX(CaseTypeCol!$B:$B,MATCH($AA17,CaseTypeCol!$A:$A,0))),IF($AH17="",TRUE,$S17=INDEX(CaseTypeCol!$B:$B,MATCH($AH17,CaseTypeCol!$A:$A,0))),IF($AO17="",TRUE,$S17=INDEX(CaseTypeCol!$B:$B,MATCH($AO17,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W17" t="s">
         <v>11</v>
       </c>
-      <c r="W17" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V17,DataCollection!$A:$A,0))</f>
+      <c r="X17" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W17,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y17" s="14">
+      <c r="Z17" s="14">
         <v>36526</v>
       </c>
-      <c r="Z17" t="s">
+      <c r="AA17" t="s">
         <v>142</v>
       </c>
-      <c r="AA17" t="s">
+      <c r="AB17" t="s">
         <v>665</v>
       </c>
-      <c r="AB17" s="6" t="str">
-        <f>IF($Z17="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z17,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC17" s="6" t="str">
+        <f>IF($AA17="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA17,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC17" ca="1">IF($Z17="",TRUE,IF($I17="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I17)&amp;"|"&amp;$Z17,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AD17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD17" ca="1">IF($Z17="",TRUE,IF($I17="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I17)&amp;"|"&amp;$Z17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD17" ca="1">IF($AA17="",TRUE,IF($J17="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J17)&amp;"|"&amp;$AA17,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AE17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE17" ca="1">IF($Z17="",TRUE,IF($M17="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M17)&amp;"|"&amp;$Z17,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
+        <f t="array" aca="1" ref="AE17" ca="1">IF($AA17="",TRUE,IF($J17="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J17)&amp;"|"&amp;$AA17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
       </c>
       <c r="AF17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF17" ca="1">IF($Z17="",TRUE,IF($M17="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M17)&amp;"|"&amp;$Z17,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI17" s="6" t="str">
-        <f>IF($AG17="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG17,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF17" ca="1">IF($AA17="",TRUE,IF($N17="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N17)&amp;"|"&amp;$AA17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG17" ca="1">IF($AA17="",TRUE,IF($N17="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N17)&amp;"|"&amp;$AA17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="6" t="str">
+        <f>IF($AH17="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH17,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ17" ca="1">IF($AG17="",TRUE,IF($I17="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I17)&amp;"|"&amp;$AG17,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK17" ca="1">IF($AG17="",TRUE,IF($I17="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I17)&amp;"|"&amp;$AG17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK17" ca="1">IF($AH17="",TRUE,IF($J17="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J17)&amp;"|"&amp;$AH17,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL17" ca="1">IF($AG17="",TRUE,IF($M17="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M17)&amp;"|"&amp;$AG17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL17" ca="1">IF($AH17="",TRUE,IF($J17="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J17)&amp;"|"&amp;$AH17,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM17" ca="1">IF($AG17="",TRUE,IF($M17="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M17)&amp;"|"&amp;$AG17,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP17" s="6" t="str">
-        <f>IF($AN17="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN17,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM17" ca="1">IF($AH17="",TRUE,IF($N17="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N17)&amp;"|"&amp;$AH17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN17" ca="1">IF($AH17="",TRUE,IF($N17="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N17)&amp;"|"&amp;$AH17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ17" s="6" t="str">
+        <f>IF($AO17="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO17,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ17" ca="1">IF($AN17="",TRUE,IF($I17="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I17)&amp;"|"&amp;$AN17,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR17" ca="1">IF($AN17="",TRUE,IF($I17="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I17)&amp;"|"&amp;$AN17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR17" ca="1">IF($AO17="",TRUE,IF($J17="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J17)&amp;"|"&amp;$AO17,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS17" ca="1">IF($AN17="",TRUE,IF($M17="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M17)&amp;"|"&amp;$AN17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS17" ca="1">IF($AO17="",TRUE,IF($J17="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J17)&amp;"|"&amp;$AO17,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT17" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT17" ca="1">IF($AN17="",TRUE,IF($M17="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M17)&amp;"|"&amp;$AN17,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT17" ca="1">IF($AO17="",TRUE,IF($N17="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N17)&amp;"|"&amp;$AO17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU17" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU17" ca="1">IF($AO17="",TRUE,IF($N17="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N17)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N17)&amp;"|"&amp;$AO17,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="b">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
         <v>619</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C18,User!$A:$A,0))</f>
+      <c r="E18" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D18,User!$A:$A,0))</f>
         <v>org_user2_1</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>723</v>
       </c>
-      <c r="F18" s="19" t="b">
+      <c r="G18" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G18" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C18,User!$A:$A,0))</f>
+      <c r="H18" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D18,User!$A:$A,0))</f>
         <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3</v>
       </c>
-      <c r="H18" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C18,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="6" t="str">
-        <f>IF(ISNA(MATCH($G18&amp;"|"&amp;$V18,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G18&amp;"|"&amp;$V18,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I18" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D18,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="6" t="str">
+        <f>IF(ISNA(MATCH($H18&amp;"|"&amp;$W18,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H18&amp;"|"&amp;$W18,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J18" ca="1">IF($I18="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I18)&amp;"|"&amp;$R18,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K18" ca="1">IF($I18="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I18),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I18)&amp;"|"&amp;$R18,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K18" ca="1">IF($J18="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J18)&amp;"|"&amp;$S18,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L18" ca="1">IF($I18="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I18),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I18)&amp;"|"&amp;$R18,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M18" s="6" t="str">
-        <f>IF(ISNA(MATCH($C18&amp;"|"&amp;$V18,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C18&amp;"|"&amp;$V18,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L18" ca="1">IF($J18="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J18),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J18)&amp;"|"&amp;$S18,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M18" ca="1">IF($J18="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J18),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J18)&amp;"|"&amp;$S18,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="6" t="str">
+        <f>IF(ISNA(MATCH($D18&amp;"|"&amp;$W18,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D18&amp;"|"&amp;$W18,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N18" ca="1">IF($M18="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M18)&amp;"|"&amp;$R18,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O18" ca="1">IF($M18="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M18),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M18)&amp;"|"&amp;$R18,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O18" ca="1">IF($N18="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N18)&amp;"|"&amp;$S18,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P18" ca="1">IF($M18="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M18),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M18)&amp;"|"&amp;$R18,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q18" t="s">
+        <f t="array" aca="1" ref="P18" ca="1">IF($N18="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N18),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N18)&amp;"|"&amp;$S18,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q18" ca="1">IF($N18="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N18),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N18)&amp;"|"&amp;$S18,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R18" t="s">
         <v>645</v>
       </c>
-      <c r="R18" t="s">
+      <c r="S18" t="s">
         <v>119</v>
       </c>
-      <c r="S18" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R18,CaseType!$A:$A,0))</f>
+      <c r="T18" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S18,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T18" s="6" t="b">
-        <f>AND(IF($Z18="",TRUE,$R18=INDEX(CaseTypeCol!$B:$B,MATCH($Z18,CaseTypeCol!$A:$A,0))),IF($AG18="",TRUE,$R18=INDEX(CaseTypeCol!$B:$B,MATCH($AG18,CaseTypeCol!$A:$A,0))),IF($AN18="",TRUE,$R18=INDEX(CaseTypeCol!$B:$B,MATCH($AN18,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V18" t="s">
+      <c r="U18" s="6" t="b">
+        <f>AND(IF($AA18="",TRUE,$S18=INDEX(CaseTypeCol!$B:$B,MATCH($AA18,CaseTypeCol!$A:$A,0))),IF($AH18="",TRUE,$S18=INDEX(CaseTypeCol!$B:$B,MATCH($AH18,CaseTypeCol!$A:$A,0))),IF($AO18="",TRUE,$S18=INDEX(CaseTypeCol!$B:$B,MATCH($AO18,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W18" t="s">
         <v>11</v>
       </c>
-      <c r="W18" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V18,DataCollection!$A:$A,0))</f>
+      <c r="X18" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W18,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y18" s="14">
+      <c r="Z18" s="14">
         <v>36526</v>
       </c>
-      <c r="Z18" t="s">
+      <c r="AA18" t="s">
         <v>142</v>
       </c>
-      <c r="AA18" t="s">
+      <c r="AB18" t="s">
         <v>665</v>
       </c>
-      <c r="AB18" s="6" t="str">
-        <f>IF($Z18="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z18,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC18" s="6" t="str">
+        <f>IF($AA18="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA18,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC18" ca="1">IF($Z18="",TRUE,IF($I18="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I18)&amp;"|"&amp;$Z18,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD18" ca="1">IF($Z18="",TRUE,IF($I18="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I18)&amp;"|"&amp;$Z18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD18" ca="1">IF($AA18="",TRUE,IF($J18="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J18)&amp;"|"&amp;$AA18,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE18" ca="1">IF($Z18="",TRUE,IF($M18="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M18)&amp;"|"&amp;$Z18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE18" ca="1">IF($AA18="",TRUE,IF($J18="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J18)&amp;"|"&amp;$AA18,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF18" ca="1">IF($Z18="",TRUE,IF($M18="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M18)&amp;"|"&amp;$Z18,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI18" s="6" t="str">
-        <f>IF($AG18="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG18,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF18" ca="1">IF($AA18="",TRUE,IF($N18="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N18)&amp;"|"&amp;$AA18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG18" ca="1">IF($AA18="",TRUE,IF($N18="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N18)&amp;"|"&amp;$AA18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="6" t="str">
+        <f>IF($AH18="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH18,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ18" ca="1">IF($AG18="",TRUE,IF($I18="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I18)&amp;"|"&amp;$AG18,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK18" ca="1">IF($AG18="",TRUE,IF($I18="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I18)&amp;"|"&amp;$AG18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK18" ca="1">IF($AH18="",TRUE,IF($J18="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J18)&amp;"|"&amp;$AH18,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL18" ca="1">IF($AG18="",TRUE,IF($M18="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M18)&amp;"|"&amp;$AG18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL18" ca="1">IF($AH18="",TRUE,IF($J18="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J18)&amp;"|"&amp;$AH18,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM18" ca="1">IF($AG18="",TRUE,IF($M18="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M18)&amp;"|"&amp;$AG18,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP18" s="6" t="str">
-        <f>IF($AN18="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN18,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM18" ca="1">IF($AH18="",TRUE,IF($N18="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N18)&amp;"|"&amp;$AH18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN18" ca="1">IF($AH18="",TRUE,IF($N18="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N18)&amp;"|"&amp;$AH18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ18" s="6" t="str">
+        <f>IF($AO18="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO18,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ18" ca="1">IF($AN18="",TRUE,IF($I18="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I18)&amp;"|"&amp;$AN18,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR18" ca="1">IF($AN18="",TRUE,IF($I18="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I18)&amp;"|"&amp;$AN18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR18" ca="1">IF($AO18="",TRUE,IF($J18="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J18)&amp;"|"&amp;$AO18,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS18" ca="1">IF($AN18="",TRUE,IF($M18="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M18)&amp;"|"&amp;$AN18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS18" ca="1">IF($AO18="",TRUE,IF($J18="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J18)&amp;"|"&amp;$AO18,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT18" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT18" ca="1">IF($AN18="",TRUE,IF($M18="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M18)&amp;"|"&amp;$AN18,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT18" ca="1">IF($AO18="",TRUE,IF($N18="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N18)&amp;"|"&amp;$AO18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU18" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU18" ca="1">IF($AO18="",TRUE,IF($N18="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N18)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N18)&amp;"|"&amp;$AO18,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="b">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
         <v>620</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C19,User!$A:$A,0))</f>
+      <c r="E19" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D19,User!$A:$A,0))</f>
         <v>org_user2_2</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>723</v>
       </c>
-      <c r="F19" s="19" t="b">
+      <c r="G19" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G19" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C19,User!$A:$A,0))</f>
+      <c r="H19" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D19,User!$A:$A,0))</f>
         <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3</v>
       </c>
-      <c r="H19" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C19,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="6" t="str">
-        <f>IF(ISNA(MATCH($G19&amp;"|"&amp;$V19,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G19&amp;"|"&amp;$V19,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I19" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D19,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="6" t="str">
+        <f>IF(ISNA(MATCH($H19&amp;"|"&amp;$W19,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H19&amp;"|"&amp;$W19,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J19" ca="1">IF($I19="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I19)&amp;"|"&amp;$R19,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K19" ca="1">IF($I19="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I19),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I19)&amp;"|"&amp;$R19,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K19" ca="1">IF($J19="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J19)&amp;"|"&amp;$S19,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L19" ca="1">IF($I19="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I19),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I19)&amp;"|"&amp;$R19,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="6" t="str">
-        <f>IF(ISNA(MATCH($C19&amp;"|"&amp;$V19,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C19&amp;"|"&amp;$V19,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L19" ca="1">IF($J19="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J19),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J19)&amp;"|"&amp;$S19,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M19" ca="1">IF($J19="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J19),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J19)&amp;"|"&amp;$S19,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="6" t="str">
+        <f>IF(ISNA(MATCH($D19&amp;"|"&amp;$W19,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D19&amp;"|"&amp;$W19,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N19" ca="1">IF($M19="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M19)&amp;"|"&amp;$R19,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O19" ca="1">IF($M19="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M19),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M19)&amp;"|"&amp;$R19,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O19" ca="1">IF($N19="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N19)&amp;"|"&amp;$S19,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P19" ca="1">IF($M19="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M19),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M19)&amp;"|"&amp;$R19,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q19" t="s">
+        <f t="array" aca="1" ref="P19" ca="1">IF($N19="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N19),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N19)&amp;"|"&amp;$S19,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q19" ca="1">IF($N19="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N19),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N19)&amp;"|"&amp;$S19,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R19" t="s">
         <v>646</v>
       </c>
-      <c r="R19" t="s">
+      <c r="S19" t="s">
         <v>119</v>
       </c>
-      <c r="S19" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R19,CaseType!$A:$A,0))</f>
+      <c r="T19" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S19,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T19" s="6" t="b">
-        <f>AND(IF($Z19="",TRUE,$R19=INDEX(CaseTypeCol!$B:$B,MATCH($Z19,CaseTypeCol!$A:$A,0))),IF($AG19="",TRUE,$R19=INDEX(CaseTypeCol!$B:$B,MATCH($AG19,CaseTypeCol!$A:$A,0))),IF($AN19="",TRUE,$R19=INDEX(CaseTypeCol!$B:$B,MATCH($AN19,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V19" t="s">
+      <c r="U19" s="6" t="b">
+        <f>AND(IF($AA19="",TRUE,$S19=INDEX(CaseTypeCol!$B:$B,MATCH($AA19,CaseTypeCol!$A:$A,0))),IF($AH19="",TRUE,$S19=INDEX(CaseTypeCol!$B:$B,MATCH($AH19,CaseTypeCol!$A:$A,0))),IF($AO19="",TRUE,$S19=INDEX(CaseTypeCol!$B:$B,MATCH($AO19,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W19" t="s">
         <v>11</v>
       </c>
-      <c r="W19" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V19,DataCollection!$A:$A,0))</f>
+      <c r="X19" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W19,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y19" s="14">
+      <c r="Z19" s="14">
         <v>36526</v>
       </c>
-      <c r="Z19" t="s">
+      <c r="AA19" t="s">
         <v>142</v>
       </c>
-      <c r="AA19" t="s">
+      <c r="AB19" t="s">
         <v>665</v>
       </c>
-      <c r="AB19" s="6" t="str">
-        <f>IF($Z19="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z19,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC19" s="6" t="str">
+        <f>IF($AA19="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA19,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC19" ca="1">IF($Z19="",TRUE,IF($I19="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I19)&amp;"|"&amp;$Z19,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD19" ca="1">IF($Z19="",TRUE,IF($I19="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I19)&amp;"|"&amp;$Z19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD19" ca="1">IF($AA19="",TRUE,IF($J19="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J19)&amp;"|"&amp;$AA19,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE19" ca="1">IF($Z19="",TRUE,IF($M19="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M19)&amp;"|"&amp;$Z19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE19" ca="1">IF($AA19="",TRUE,IF($J19="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J19)&amp;"|"&amp;$AA19,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF19" ca="1">IF($Z19="",TRUE,IF($M19="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M19)&amp;"|"&amp;$Z19,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI19" s="6" t="str">
-        <f>IF($AG19="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG19,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF19" ca="1">IF($AA19="",TRUE,IF($N19="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N19)&amp;"|"&amp;$AA19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG19" ca="1">IF($AA19="",TRUE,IF($N19="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N19)&amp;"|"&amp;$AA19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="6" t="str">
+        <f>IF($AH19="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH19,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ19" ca="1">IF($AG19="",TRUE,IF($I19="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I19)&amp;"|"&amp;$AG19,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK19" ca="1">IF($AG19="",TRUE,IF($I19="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I19)&amp;"|"&amp;$AG19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK19" ca="1">IF($AH19="",TRUE,IF($J19="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J19)&amp;"|"&amp;$AH19,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL19" ca="1">IF($AG19="",TRUE,IF($M19="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M19)&amp;"|"&amp;$AG19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL19" ca="1">IF($AH19="",TRUE,IF($J19="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J19)&amp;"|"&amp;$AH19,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM19" ca="1">IF($AG19="",TRUE,IF($M19="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M19)&amp;"|"&amp;$AG19,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP19" s="6" t="str">
-        <f>IF($AN19="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN19,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM19" ca="1">IF($AH19="",TRUE,IF($N19="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N19)&amp;"|"&amp;$AH19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN19" ca="1">IF($AH19="",TRUE,IF($N19="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N19)&amp;"|"&amp;$AH19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ19" s="6" t="str">
+        <f>IF($AO19="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO19,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ19" ca="1">IF($AN19="",TRUE,IF($I19="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I19)&amp;"|"&amp;$AN19,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR19" ca="1">IF($AN19="",TRUE,IF($I19="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I19)&amp;"|"&amp;$AN19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR19" ca="1">IF($AO19="",TRUE,IF($J19="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J19)&amp;"|"&amp;$AO19,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS19" ca="1">IF($AN19="",TRUE,IF($M19="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M19)&amp;"|"&amp;$AN19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS19" ca="1">IF($AO19="",TRUE,IF($J19="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J19)&amp;"|"&amp;$AO19,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT19" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT19" ca="1">IF($AN19="",TRUE,IF($M19="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M19)&amp;"|"&amp;$AN19,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT19" ca="1">IF($AO19="",TRUE,IF($N19="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N19)&amp;"|"&amp;$AO19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU19" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU19" ca="1">IF($AO19="",TRUE,IF($N19="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N19)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N19)&amp;"|"&amp;$AO19,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="b">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
         <v>621</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C20,User!$A:$A,0))</f>
+      <c r="E20" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D20,User!$A:$A,0))</f>
         <v>org_user2_3</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>723</v>
       </c>
-      <c r="F20" s="19" t="b">
+      <c r="G20" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G20" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C20,User!$A:$A,0))</f>
+      <c r="H20" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D20,User!$A:$A,0))</f>
         <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3</v>
       </c>
-      <c r="H20" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C20,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="6" t="str">
-        <f>IF(ISNA(MATCH($G20&amp;"|"&amp;$V20,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G20&amp;"|"&amp;$V20,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I20" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D20,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="6" t="str">
+        <f>IF(ISNA(MATCH($H20&amp;"|"&amp;$W20,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H20&amp;"|"&amp;$W20,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J20" ca="1">IF($I20="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I20)&amp;"|"&amp;$R20,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K20" ca="1">IF($I20="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I20),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I20)&amp;"|"&amp;$R20,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K20" ca="1">IF($J20="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J20)&amp;"|"&amp;$S20,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L20" ca="1">IF($I20="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I20),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I20)&amp;"|"&amp;$R20,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M20" s="6" t="str">
-        <f>IF(ISNA(MATCH($C20&amp;"|"&amp;$V20,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C20&amp;"|"&amp;$V20,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L20" ca="1">IF($J20="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J20),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J20)&amp;"|"&amp;$S20,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M20" ca="1">IF($J20="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J20),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J20)&amp;"|"&amp;$S20,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="6" t="str">
+        <f>IF(ISNA(MATCH($D20&amp;"|"&amp;$W20,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D20&amp;"|"&amp;$W20,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N20" ca="1">IF($M20="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M20)&amp;"|"&amp;$R20,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O20" ca="1">IF($M20="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M20),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M20)&amp;"|"&amp;$R20,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O20" ca="1">IF($N20="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N20)&amp;"|"&amp;$S20,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P20" ca="1">IF($M20="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M20),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M20)&amp;"|"&amp;$R20,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q20" t="s">
+        <f t="array" aca="1" ref="P20" ca="1">IF($N20="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N20),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N20)&amp;"|"&amp;$S20,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q20" ca="1">IF($N20="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N20),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N20)&amp;"|"&amp;$S20,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R20" t="s">
         <v>647</v>
       </c>
-      <c r="R20" t="s">
+      <c r="S20" t="s">
         <v>119</v>
       </c>
-      <c r="S20" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R20,CaseType!$A:$A,0))</f>
+      <c r="T20" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S20,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T20" s="6" t="b">
-        <f>AND(IF($Z20="",TRUE,$R20=INDEX(CaseTypeCol!$B:$B,MATCH($Z20,CaseTypeCol!$A:$A,0))),IF($AG20="",TRUE,$R20=INDEX(CaseTypeCol!$B:$B,MATCH($AG20,CaseTypeCol!$A:$A,0))),IF($AN20="",TRUE,$R20=INDEX(CaseTypeCol!$B:$B,MATCH($AN20,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V20" t="s">
+      <c r="U20" s="6" t="b">
+        <f>AND(IF($AA20="",TRUE,$S20=INDEX(CaseTypeCol!$B:$B,MATCH($AA20,CaseTypeCol!$A:$A,0))),IF($AH20="",TRUE,$S20=INDEX(CaseTypeCol!$B:$B,MATCH($AH20,CaseTypeCol!$A:$A,0))),IF($AO20="",TRUE,$S20=INDEX(CaseTypeCol!$B:$B,MATCH($AO20,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W20" t="s">
         <v>11</v>
       </c>
-      <c r="W20" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V20,DataCollection!$A:$A,0))</f>
+      <c r="X20" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W20,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y20" s="14">
+      <c r="Z20" s="14">
         <v>36526</v>
       </c>
-      <c r="Z20" t="s">
+      <c r="AA20" t="s">
         <v>142</v>
       </c>
-      <c r="AA20" t="s">
+      <c r="AB20" t="s">
         <v>665</v>
       </c>
-      <c r="AB20" s="6" t="str">
-        <f>IF($Z20="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z20,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC20" s="6" t="str">
+        <f>IF($AA20="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA20,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC20" ca="1">IF($Z20="",TRUE,IF($I20="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I20)&amp;"|"&amp;$Z20,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD20" ca="1">IF($Z20="",TRUE,IF($I20="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I20)&amp;"|"&amp;$Z20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD20" ca="1">IF($AA20="",TRUE,IF($J20="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J20)&amp;"|"&amp;$AA20,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE20" ca="1">IF($Z20="",TRUE,IF($M20="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M20)&amp;"|"&amp;$Z20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE20" ca="1">IF($AA20="",TRUE,IF($J20="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J20)&amp;"|"&amp;$AA20,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF20" ca="1">IF($Z20="",TRUE,IF($M20="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M20)&amp;"|"&amp;$Z20,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI20" s="6" t="str">
-        <f>IF($AG20="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG20,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF20" ca="1">IF($AA20="",TRUE,IF($N20="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N20)&amp;"|"&amp;$AA20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG20" ca="1">IF($AA20="",TRUE,IF($N20="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N20)&amp;"|"&amp;$AA20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="6" t="str">
+        <f>IF($AH20="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH20,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ20" ca="1">IF($AG20="",TRUE,IF($I20="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I20)&amp;"|"&amp;$AG20,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK20" ca="1">IF($AG20="",TRUE,IF($I20="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I20)&amp;"|"&amp;$AG20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK20" ca="1">IF($AH20="",TRUE,IF($J20="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J20)&amp;"|"&amp;$AH20,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL20" ca="1">IF($AG20="",TRUE,IF($M20="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M20)&amp;"|"&amp;$AG20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL20" ca="1">IF($AH20="",TRUE,IF($J20="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J20)&amp;"|"&amp;$AH20,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM20" ca="1">IF($AG20="",TRUE,IF($M20="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M20)&amp;"|"&amp;$AG20,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP20" s="6" t="str">
-        <f>IF($AN20="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN20,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM20" ca="1">IF($AH20="",TRUE,IF($N20="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N20)&amp;"|"&amp;$AH20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN20" ca="1">IF($AH20="",TRUE,IF($N20="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N20)&amp;"|"&amp;$AH20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ20" s="6" t="str">
+        <f>IF($AO20="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO20,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ20" ca="1">IF($AN20="",TRUE,IF($I20="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I20)&amp;"|"&amp;$AN20,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR20" ca="1">IF($AN20="",TRUE,IF($I20="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I20)&amp;"|"&amp;$AN20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR20" ca="1">IF($AO20="",TRUE,IF($J20="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J20)&amp;"|"&amp;$AO20,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS20" ca="1">IF($AN20="",TRUE,IF($M20="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M20)&amp;"|"&amp;$AN20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS20" ca="1">IF($AO20="",TRUE,IF($J20="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J20)&amp;"|"&amp;$AO20,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT20" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT20" ca="1">IF($AN20="",TRUE,IF($M20="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M20)&amp;"|"&amp;$AN20,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT20" ca="1">IF($AO20="",TRUE,IF($N20="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N20)&amp;"|"&amp;$AO20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU20" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU20" ca="1">IF($AO20="",TRUE,IF($N20="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N20)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N20)&amp;"|"&amp;$AO20,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="b">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
         <v>622</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C21,User!$A:$A,0))</f>
+      <c r="E21" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D21,User!$A:$A,0))</f>
         <v>org_user2_4</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>723</v>
       </c>
-      <c r="F21" s="19" t="b">
+      <c r="G21" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G21" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C21,User!$A:$A,0))</f>
+      <c r="H21" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D21,User!$A:$A,0))</f>
         <v>0195d18c-1c92-0ed4-2e94-b4f66d82baf3</v>
       </c>
-      <c r="H21" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C21,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="6" t="str">
-        <f>IF(ISNA(MATCH($G21&amp;"|"&amp;$V21,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G21&amp;"|"&amp;$V21,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I21" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D21,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="6" t="str">
+        <f>IF(ISNA(MATCH($H21&amp;"|"&amp;$W21,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H21&amp;"|"&amp;$W21,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J21" ca="1">IF($I21="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I21)&amp;"|"&amp;$R21,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K21" ca="1">IF($I21="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I21),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I21)&amp;"|"&amp;$R21,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K21" ca="1">IF($J21="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J21)&amp;"|"&amp;$S21,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L21" ca="1">IF($I21="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I21),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I21)&amp;"|"&amp;$R21,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M21" s="6" t="str">
-        <f>IF(ISNA(MATCH($C21&amp;"|"&amp;$V21,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C21&amp;"|"&amp;$V21,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L21" ca="1">IF($J21="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J21),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J21)&amp;"|"&amp;$S21,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M21" ca="1">IF($J21="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J21),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J21)&amp;"|"&amp;$S21,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N21" s="6" t="str">
+        <f>IF(ISNA(MATCH($D21&amp;"|"&amp;$W21,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D21&amp;"|"&amp;$W21,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N21" ca="1">IF($M21="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M21)&amp;"|"&amp;$R21,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O21" ca="1">IF($M21="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M21),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M21)&amp;"|"&amp;$R21,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O21" ca="1">IF($N21="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N21)&amp;"|"&amp;$S21,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P21" ca="1">IF($M21="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M21),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M21)&amp;"|"&amp;$R21,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q21" t="s">
+        <f t="array" aca="1" ref="P21" ca="1">IF($N21="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N21),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N21)&amp;"|"&amp;$S21,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q21" ca="1">IF($N21="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N21),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N21)&amp;"|"&amp;$S21,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R21" t="s">
         <v>648</v>
       </c>
-      <c r="R21" t="s">
+      <c r="S21" t="s">
         <v>119</v>
       </c>
-      <c r="S21" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R21,CaseType!$A:$A,0))</f>
+      <c r="T21" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S21,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T21" s="6" t="b">
-        <f>AND(IF($Z21="",TRUE,$R21=INDEX(CaseTypeCol!$B:$B,MATCH($Z21,CaseTypeCol!$A:$A,0))),IF($AG21="",TRUE,$R21=INDEX(CaseTypeCol!$B:$B,MATCH($AG21,CaseTypeCol!$A:$A,0))),IF($AN21="",TRUE,$R21=INDEX(CaseTypeCol!$B:$B,MATCH($AN21,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V21" t="s">
+      <c r="U21" s="6" t="b">
+        <f>AND(IF($AA21="",TRUE,$S21=INDEX(CaseTypeCol!$B:$B,MATCH($AA21,CaseTypeCol!$A:$A,0))),IF($AH21="",TRUE,$S21=INDEX(CaseTypeCol!$B:$B,MATCH($AH21,CaseTypeCol!$A:$A,0))),IF($AO21="",TRUE,$S21=INDEX(CaseTypeCol!$B:$B,MATCH($AO21,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W21" t="s">
         <v>11</v>
       </c>
-      <c r="W21" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V21,DataCollection!$A:$A,0))</f>
+      <c r="X21" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W21,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y21" s="14">
+      <c r="Z21" s="14">
         <v>36526</v>
       </c>
-      <c r="Z21" t="s">
+      <c r="AA21" t="s">
         <v>142</v>
       </c>
-      <c r="AA21" t="s">
+      <c r="AB21" t="s">
         <v>665</v>
       </c>
-      <c r="AB21" s="6" t="str">
-        <f>IF($Z21="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z21,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC21" s="6" t="str">
+        <f>IF($AA21="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA21,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC21" ca="1">IF($Z21="",TRUE,IF($I21="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I21)&amp;"|"&amp;$Z21,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD21" ca="1">IF($Z21="",TRUE,IF($I21="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I21)&amp;"|"&amp;$Z21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD21" ca="1">IF($AA21="",TRUE,IF($J21="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J21)&amp;"|"&amp;$AA21,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE21" ca="1">IF($Z21="",TRUE,IF($M21="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M21)&amp;"|"&amp;$Z21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE21" ca="1">IF($AA21="",TRUE,IF($J21="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J21)&amp;"|"&amp;$AA21,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF21" ca="1">IF($Z21="",TRUE,IF($M21="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M21)&amp;"|"&amp;$Z21,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI21" s="6" t="str">
-        <f>IF($AG21="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG21,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF21" ca="1">IF($AA21="",TRUE,IF($N21="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N21)&amp;"|"&amp;$AA21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG21" ca="1">IF($AA21="",TRUE,IF($N21="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N21)&amp;"|"&amp;$AA21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="6" t="str">
+        <f>IF($AH21="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH21,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ21" ca="1">IF($AG21="",TRUE,IF($I21="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I21)&amp;"|"&amp;$AG21,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK21" ca="1">IF($AG21="",TRUE,IF($I21="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I21)&amp;"|"&amp;$AG21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK21" ca="1">IF($AH21="",TRUE,IF($J21="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J21)&amp;"|"&amp;$AH21,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL21" ca="1">IF($AG21="",TRUE,IF($M21="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M21)&amp;"|"&amp;$AG21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL21" ca="1">IF($AH21="",TRUE,IF($J21="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J21)&amp;"|"&amp;$AH21,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM21" ca="1">IF($AG21="",TRUE,IF($M21="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M21)&amp;"|"&amp;$AG21,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP21" s="6" t="str">
-        <f>IF($AN21="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN21,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM21" ca="1">IF($AH21="",TRUE,IF($N21="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N21)&amp;"|"&amp;$AH21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN21" ca="1">IF($AH21="",TRUE,IF($N21="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N21)&amp;"|"&amp;$AH21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ21" s="6" t="str">
+        <f>IF($AO21="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO21,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ21" ca="1">IF($AN21="",TRUE,IF($I21="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I21)&amp;"|"&amp;$AN21,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR21" ca="1">IF($AN21="",TRUE,IF($I21="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I21)&amp;"|"&amp;$AN21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR21" ca="1">IF($AO21="",TRUE,IF($J21="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J21)&amp;"|"&amp;$AO21,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS21" ca="1">IF($AN21="",TRUE,IF($M21="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M21)&amp;"|"&amp;$AN21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS21" ca="1">IF($AO21="",TRUE,IF($J21="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J21)&amp;"|"&amp;$AO21,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT21" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT21" ca="1">IF($AN21="",TRUE,IF($M21="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M21)&amp;"|"&amp;$AN21,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT21" ca="1">IF($AO21="",TRUE,IF($N21="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N21)&amp;"|"&amp;$AO21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU21" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU21" ca="1">IF($AO21="",TRUE,IF($N21="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N21)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N21)&amp;"|"&amp;$AO21,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="b">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
         <v>623</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C22,User!$A:$A,0))</f>
+      <c r="E22" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D22,User!$A:$A,0))</f>
         <v>org_user3_1</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>723</v>
       </c>
-      <c r="F22" s="19" t="b">
+      <c r="G22" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G22" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C22,User!$A:$A,0))</f>
+      <c r="H22" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D22,User!$A:$A,0))</f>
         <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037</v>
       </c>
-      <c r="H22" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C22,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I22" s="6" t="str">
-        <f>IF(ISNA(MATCH($G22&amp;"|"&amp;$V22,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G22&amp;"|"&amp;$V22,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I22" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D22,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="6" t="str">
+        <f>IF(ISNA(MATCH($H22&amp;"|"&amp;$W22,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H22&amp;"|"&amp;$W22,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J22" ca="1">IF($I22="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I22)&amp;"|"&amp;$R22,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K22" ca="1">IF($I22="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I22),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I22)&amp;"|"&amp;$R22,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K22" ca="1">IF($J22="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J22)&amp;"|"&amp;$S22,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L22" ca="1">IF($I22="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I22),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I22)&amp;"|"&amp;$R22,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M22" s="6" t="str">
-        <f>IF(ISNA(MATCH($C22&amp;"|"&amp;$V22,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C22&amp;"|"&amp;$V22,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L22" ca="1">IF($J22="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J22),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J22)&amp;"|"&amp;$S22,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M22" ca="1">IF($J22="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J22),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J22)&amp;"|"&amp;$S22,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="6" t="str">
+        <f>IF(ISNA(MATCH($D22&amp;"|"&amp;$W22,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D22&amp;"|"&amp;$W22,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N22" ca="1">IF($M22="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M22)&amp;"|"&amp;$R22,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O22" ca="1">IF($M22="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M22),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M22)&amp;"|"&amp;$R22,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O22" ca="1">IF($N22="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N22)&amp;"|"&amp;$S22,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P22" ca="1">IF($M22="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M22),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M22)&amp;"|"&amp;$R22,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q22" t="s">
+        <f t="array" aca="1" ref="P22" ca="1">IF($N22="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N22),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N22)&amp;"|"&amp;$S22,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q22" ca="1">IF($N22="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N22),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N22)&amp;"|"&amp;$S22,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R22" t="s">
         <v>649</v>
       </c>
-      <c r="R22" t="s">
+      <c r="S22" t="s">
         <v>119</v>
       </c>
-      <c r="S22" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R22,CaseType!$A:$A,0))</f>
+      <c r="T22" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S22,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T22" s="6" t="b">
-        <f>AND(IF($Z22="",TRUE,$R22=INDEX(CaseTypeCol!$B:$B,MATCH($Z22,CaseTypeCol!$A:$A,0))),IF($AG22="",TRUE,$R22=INDEX(CaseTypeCol!$B:$B,MATCH($AG22,CaseTypeCol!$A:$A,0))),IF($AN22="",TRUE,$R22=INDEX(CaseTypeCol!$B:$B,MATCH($AN22,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V22" t="s">
+      <c r="U22" s="6" t="b">
+        <f>AND(IF($AA22="",TRUE,$S22=INDEX(CaseTypeCol!$B:$B,MATCH($AA22,CaseTypeCol!$A:$A,0))),IF($AH22="",TRUE,$S22=INDEX(CaseTypeCol!$B:$B,MATCH($AH22,CaseTypeCol!$A:$A,0))),IF($AO22="",TRUE,$S22=INDEX(CaseTypeCol!$B:$B,MATCH($AO22,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W22" t="s">
         <v>11</v>
       </c>
-      <c r="W22" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V22,DataCollection!$A:$A,0))</f>
+      <c r="X22" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W22,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y22" s="14">
+      <c r="Z22" s="14">
         <v>36526</v>
       </c>
-      <c r="Z22" t="s">
+      <c r="AA22" t="s">
         <v>142</v>
       </c>
-      <c r="AA22" t="s">
+      <c r="AB22" t="s">
         <v>665</v>
       </c>
-      <c r="AB22" s="6" t="str">
-        <f>IF($Z22="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z22,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC22" s="6" t="str">
+        <f>IF($AA22="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA22,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC22" ca="1">IF($Z22="",TRUE,IF($I22="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I22)&amp;"|"&amp;$Z22,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD22" ca="1">IF($Z22="",TRUE,IF($I22="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I22)&amp;"|"&amp;$Z22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD22" ca="1">IF($AA22="",TRUE,IF($J22="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J22)&amp;"|"&amp;$AA22,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE22" ca="1">IF($Z22="",TRUE,IF($M22="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M22)&amp;"|"&amp;$Z22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE22" ca="1">IF($AA22="",TRUE,IF($J22="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J22)&amp;"|"&amp;$AA22,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF22" ca="1">IF($Z22="",TRUE,IF($M22="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M22)&amp;"|"&amp;$Z22,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI22" s="6" t="str">
-        <f>IF($AG22="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG22,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF22" ca="1">IF($AA22="",TRUE,IF($N22="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N22)&amp;"|"&amp;$AA22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG22" ca="1">IF($AA22="",TRUE,IF($N22="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N22)&amp;"|"&amp;$AA22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="6" t="str">
+        <f>IF($AH22="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH22,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ22" ca="1">IF($AG22="",TRUE,IF($I22="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I22)&amp;"|"&amp;$AG22,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK22" ca="1">IF($AG22="",TRUE,IF($I22="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I22)&amp;"|"&amp;$AG22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK22" ca="1">IF($AH22="",TRUE,IF($J22="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J22)&amp;"|"&amp;$AH22,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL22" ca="1">IF($AG22="",TRUE,IF($M22="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M22)&amp;"|"&amp;$AG22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL22" ca="1">IF($AH22="",TRUE,IF($J22="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J22)&amp;"|"&amp;$AH22,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM22" ca="1">IF($AG22="",TRUE,IF($M22="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M22)&amp;"|"&amp;$AG22,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP22" s="6" t="str">
-        <f>IF($AN22="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN22,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM22" ca="1">IF($AH22="",TRUE,IF($N22="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N22)&amp;"|"&amp;$AH22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN22" ca="1">IF($AH22="",TRUE,IF($N22="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N22)&amp;"|"&amp;$AH22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ22" s="6" t="str">
+        <f>IF($AO22="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO22,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ22" ca="1">IF($AN22="",TRUE,IF($I22="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I22)&amp;"|"&amp;$AN22,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR22" ca="1">IF($AN22="",TRUE,IF($I22="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I22)&amp;"|"&amp;$AN22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR22" ca="1">IF($AO22="",TRUE,IF($J22="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J22)&amp;"|"&amp;$AO22,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS22" ca="1">IF($AN22="",TRUE,IF($M22="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M22)&amp;"|"&amp;$AN22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS22" ca="1">IF($AO22="",TRUE,IF($J22="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J22)&amp;"|"&amp;$AO22,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT22" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT22" ca="1">IF($AN22="",TRUE,IF($M22="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M22)&amp;"|"&amp;$AN22,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT22" ca="1">IF($AO22="",TRUE,IF($N22="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N22)&amp;"|"&amp;$AO22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU22" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU22" ca="1">IF($AO22="",TRUE,IF($N22="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N22)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N22)&amp;"|"&amp;$AO22,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
         <v>624</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C23,User!$A:$A,0))</f>
+      <c r="E23" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D23,User!$A:$A,0))</f>
         <v>org_user3_2</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>723</v>
       </c>
-      <c r="F23" s="19" t="b">
+      <c r="G23" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G23" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C23,User!$A:$A,0))</f>
+      <c r="H23" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D23,User!$A:$A,0))</f>
         <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037</v>
       </c>
-      <c r="H23" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C23,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="6" t="str">
-        <f>IF(ISNA(MATCH($G23&amp;"|"&amp;$V23,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G23&amp;"|"&amp;$V23,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I23" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D23,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="6" t="str">
+        <f>IF(ISNA(MATCH($H23&amp;"|"&amp;$W23,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H23&amp;"|"&amp;$W23,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J23" ca="1">IF($I23="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I23)&amp;"|"&amp;$R23,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K23" ca="1">IF($I23="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I23),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I23)&amp;"|"&amp;$R23,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K23" ca="1">IF($J23="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J23)&amp;"|"&amp;$S23,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L23" ca="1">IF($I23="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I23),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I23)&amp;"|"&amp;$R23,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M23" s="6" t="str">
-        <f>IF(ISNA(MATCH($C23&amp;"|"&amp;$V23,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C23&amp;"|"&amp;$V23,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L23" ca="1">IF($J23="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J23),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J23)&amp;"|"&amp;$S23,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M23" ca="1">IF($J23="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J23),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J23)&amp;"|"&amp;$S23,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N23" s="6" t="str">
+        <f>IF(ISNA(MATCH($D23&amp;"|"&amp;$W23,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D23&amp;"|"&amp;$W23,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N23" ca="1">IF($M23="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M23)&amp;"|"&amp;$R23,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O23" ca="1">IF($M23="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M23),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M23)&amp;"|"&amp;$R23,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O23" ca="1">IF($N23="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N23)&amp;"|"&amp;$S23,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P23" ca="1">IF($M23="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M23),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M23)&amp;"|"&amp;$R23,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q23" t="s">
+        <f t="array" aca="1" ref="P23" ca="1">IF($N23="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N23),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N23)&amp;"|"&amp;$S23,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q23" ca="1">IF($N23="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N23),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N23)&amp;"|"&amp;$S23,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R23" t="s">
         <v>650</v>
       </c>
-      <c r="R23" t="s">
+      <c r="S23" t="s">
         <v>119</v>
       </c>
-      <c r="S23" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R23,CaseType!$A:$A,0))</f>
+      <c r="T23" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S23,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T23" s="6" t="b">
-        <f>AND(IF($Z23="",TRUE,$R23=INDEX(CaseTypeCol!$B:$B,MATCH($Z23,CaseTypeCol!$A:$A,0))),IF($AG23="",TRUE,$R23=INDEX(CaseTypeCol!$B:$B,MATCH($AG23,CaseTypeCol!$A:$A,0))),IF($AN23="",TRUE,$R23=INDEX(CaseTypeCol!$B:$B,MATCH($AN23,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V23" t="s">
+      <c r="U23" s="6" t="b">
+        <f>AND(IF($AA23="",TRUE,$S23=INDEX(CaseTypeCol!$B:$B,MATCH($AA23,CaseTypeCol!$A:$A,0))),IF($AH23="",TRUE,$S23=INDEX(CaseTypeCol!$B:$B,MATCH($AH23,CaseTypeCol!$A:$A,0))),IF($AO23="",TRUE,$S23=INDEX(CaseTypeCol!$B:$B,MATCH($AO23,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W23" t="s">
         <v>11</v>
       </c>
-      <c r="W23" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V23,DataCollection!$A:$A,0))</f>
+      <c r="X23" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W23,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y23" s="14">
+      <c r="Z23" s="14">
         <v>36526</v>
       </c>
-      <c r="Z23" t="s">
+      <c r="AA23" t="s">
         <v>142</v>
       </c>
-      <c r="AA23" t="s">
+      <c r="AB23" t="s">
         <v>665</v>
       </c>
-      <c r="AB23" s="6" t="str">
-        <f>IF($Z23="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z23,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC23" s="6" t="str">
+        <f>IF($AA23="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA23,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC23" ca="1">IF($Z23="",TRUE,IF($I23="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I23)&amp;"|"&amp;$Z23,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD23" ca="1">IF($Z23="",TRUE,IF($I23="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I23)&amp;"|"&amp;$Z23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD23" ca="1">IF($AA23="",TRUE,IF($J23="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J23)&amp;"|"&amp;$AA23,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE23" ca="1">IF($Z23="",TRUE,IF($M23="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M23)&amp;"|"&amp;$Z23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE23" ca="1">IF($AA23="",TRUE,IF($J23="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J23)&amp;"|"&amp;$AA23,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF23" ca="1">IF($Z23="",TRUE,IF($M23="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M23)&amp;"|"&amp;$Z23,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI23" s="6" t="str">
-        <f>IF($AG23="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG23,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF23" ca="1">IF($AA23="",TRUE,IF($N23="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N23)&amp;"|"&amp;$AA23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG23" ca="1">IF($AA23="",TRUE,IF($N23="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N23)&amp;"|"&amp;$AA23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="6" t="str">
+        <f>IF($AH23="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH23,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ23" ca="1">IF($AG23="",TRUE,IF($I23="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I23)&amp;"|"&amp;$AG23,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK23" ca="1">IF($AG23="",TRUE,IF($I23="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I23)&amp;"|"&amp;$AG23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK23" ca="1">IF($AH23="",TRUE,IF($J23="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J23)&amp;"|"&amp;$AH23,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL23" ca="1">IF($AG23="",TRUE,IF($M23="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M23)&amp;"|"&amp;$AG23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL23" ca="1">IF($AH23="",TRUE,IF($J23="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J23)&amp;"|"&amp;$AH23,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM23" ca="1">IF($AG23="",TRUE,IF($M23="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M23)&amp;"|"&amp;$AG23,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP23" s="6" t="str">
-        <f>IF($AN23="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN23,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM23" ca="1">IF($AH23="",TRUE,IF($N23="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N23)&amp;"|"&amp;$AH23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN23" ca="1">IF($AH23="",TRUE,IF($N23="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N23)&amp;"|"&amp;$AH23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ23" s="6" t="str">
+        <f>IF($AO23="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO23,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ23" ca="1">IF($AN23="",TRUE,IF($I23="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I23)&amp;"|"&amp;$AN23,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR23" ca="1">IF($AN23="",TRUE,IF($I23="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I23)&amp;"|"&amp;$AN23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR23" ca="1">IF($AO23="",TRUE,IF($J23="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J23)&amp;"|"&amp;$AO23,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS23" ca="1">IF($AN23="",TRUE,IF($M23="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M23)&amp;"|"&amp;$AN23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS23" ca="1">IF($AO23="",TRUE,IF($J23="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J23)&amp;"|"&amp;$AO23,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT23" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT23" ca="1">IF($AN23="",TRUE,IF($M23="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M23)&amp;"|"&amp;$AN23,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT23" ca="1">IF($AO23="",TRUE,IF($N23="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N23)&amp;"|"&amp;$AO23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU23" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU23" ca="1">IF($AO23="",TRUE,IF($N23="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N23)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N23)&amp;"|"&amp;$AO23,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="b">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
         <v>625</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C24,User!$A:$A,0))</f>
+      <c r="E24" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D24,User!$A:$A,0))</f>
         <v>org_user3_3</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>723</v>
       </c>
-      <c r="F24" s="19" t="b">
+      <c r="G24" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G24" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C24,User!$A:$A,0))</f>
+      <c r="H24" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D24,User!$A:$A,0))</f>
         <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037</v>
       </c>
-      <c r="H24" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C24,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="6" t="str">
-        <f>IF(ISNA(MATCH($G24&amp;"|"&amp;$V24,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G24&amp;"|"&amp;$V24,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I24" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D24,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="6" t="str">
+        <f>IF(ISNA(MATCH($H24&amp;"|"&amp;$W24,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H24&amp;"|"&amp;$W24,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J24" ca="1">IF($I24="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I24)&amp;"|"&amp;$R24,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K24" ca="1">IF($I24="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I24),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I24)&amp;"|"&amp;$R24,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K24" ca="1">IF($J24="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J24)&amp;"|"&amp;$S24,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L24" ca="1">IF($I24="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I24),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I24)&amp;"|"&amp;$R24,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M24" s="6" t="str">
-        <f>IF(ISNA(MATCH($C24&amp;"|"&amp;$V24,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C24&amp;"|"&amp;$V24,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L24" ca="1">IF($J24="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J24),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J24)&amp;"|"&amp;$S24,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M24" ca="1">IF($J24="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J24),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J24)&amp;"|"&amp;$S24,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="6" t="str">
+        <f>IF(ISNA(MATCH($D24&amp;"|"&amp;$W24,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D24&amp;"|"&amp;$W24,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N24" ca="1">IF($M24="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M24)&amp;"|"&amp;$R24,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O24" ca="1">IF($M24="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M24),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M24)&amp;"|"&amp;$R24,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O24" ca="1">IF($N24="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N24)&amp;"|"&amp;$S24,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P24" ca="1">IF($M24="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M24),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M24)&amp;"|"&amp;$R24,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q24" t="s">
+        <f t="array" aca="1" ref="P24" ca="1">IF($N24="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N24),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N24)&amp;"|"&amp;$S24,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q24" ca="1">IF($N24="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N24),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N24)&amp;"|"&amp;$S24,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R24" t="s">
         <v>651</v>
       </c>
-      <c r="R24" t="s">
+      <c r="S24" t="s">
         <v>119</v>
       </c>
-      <c r="S24" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R24,CaseType!$A:$A,0))</f>
+      <c r="T24" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S24,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T24" s="6" t="b">
-        <f>AND(IF($Z24="",TRUE,$R24=INDEX(CaseTypeCol!$B:$B,MATCH($Z24,CaseTypeCol!$A:$A,0))),IF($AG24="",TRUE,$R24=INDEX(CaseTypeCol!$B:$B,MATCH($AG24,CaseTypeCol!$A:$A,0))),IF($AN24="",TRUE,$R24=INDEX(CaseTypeCol!$B:$B,MATCH($AN24,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V24" t="s">
+      <c r="U24" s="6" t="b">
+        <f>AND(IF($AA24="",TRUE,$S24=INDEX(CaseTypeCol!$B:$B,MATCH($AA24,CaseTypeCol!$A:$A,0))),IF($AH24="",TRUE,$S24=INDEX(CaseTypeCol!$B:$B,MATCH($AH24,CaseTypeCol!$A:$A,0))),IF($AO24="",TRUE,$S24=INDEX(CaseTypeCol!$B:$B,MATCH($AO24,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W24" t="s">
         <v>11</v>
       </c>
-      <c r="W24" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V24,DataCollection!$A:$A,0))</f>
+      <c r="X24" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W24,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y24" s="14">
+      <c r="Z24" s="14">
         <v>36526</v>
       </c>
-      <c r="Z24" t="s">
+      <c r="AA24" t="s">
         <v>142</v>
       </c>
-      <c r="AA24" t="s">
+      <c r="AB24" t="s">
         <v>665</v>
       </c>
-      <c r="AB24" s="6" t="str">
-        <f>IF($Z24="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z24,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC24" s="6" t="str">
+        <f>IF($AA24="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA24,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC24" ca="1">IF($Z24="",TRUE,IF($I24="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I24)&amp;"|"&amp;$Z24,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD24" ca="1">IF($Z24="",TRUE,IF($I24="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I24)&amp;"|"&amp;$Z24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD24" ca="1">IF($AA24="",TRUE,IF($J24="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J24)&amp;"|"&amp;$AA24,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE24" ca="1">IF($Z24="",TRUE,IF($M24="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M24)&amp;"|"&amp;$Z24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE24" ca="1">IF($AA24="",TRUE,IF($J24="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J24)&amp;"|"&amp;$AA24,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF24" ca="1">IF($Z24="",TRUE,IF($M24="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M24)&amp;"|"&amp;$Z24,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI24" s="6" t="str">
-        <f>IF($AG24="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG24,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF24" ca="1">IF($AA24="",TRUE,IF($N24="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N24)&amp;"|"&amp;$AA24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG24" ca="1">IF($AA24="",TRUE,IF($N24="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N24)&amp;"|"&amp;$AA24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="6" t="str">
+        <f>IF($AH24="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH24,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ24" ca="1">IF($AG24="",TRUE,IF($I24="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I24)&amp;"|"&amp;$AG24,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK24" ca="1">IF($AG24="",TRUE,IF($I24="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I24)&amp;"|"&amp;$AG24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK24" ca="1">IF($AH24="",TRUE,IF($J24="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J24)&amp;"|"&amp;$AH24,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL24" ca="1">IF($AG24="",TRUE,IF($M24="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M24)&amp;"|"&amp;$AG24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL24" ca="1">IF($AH24="",TRUE,IF($J24="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J24)&amp;"|"&amp;$AH24,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM24" ca="1">IF($AG24="",TRUE,IF($M24="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M24)&amp;"|"&amp;$AG24,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP24" s="6" t="str">
-        <f>IF($AN24="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN24,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM24" ca="1">IF($AH24="",TRUE,IF($N24="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N24)&amp;"|"&amp;$AH24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN24" ca="1">IF($AH24="",TRUE,IF($N24="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N24)&amp;"|"&amp;$AH24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ24" s="6" t="str">
+        <f>IF($AO24="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO24,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ24" ca="1">IF($AN24="",TRUE,IF($I24="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I24)&amp;"|"&amp;$AN24,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR24" ca="1">IF($AN24="",TRUE,IF($I24="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I24)&amp;"|"&amp;$AN24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR24" ca="1">IF($AO24="",TRUE,IF($J24="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J24)&amp;"|"&amp;$AO24,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS24" ca="1">IF($AN24="",TRUE,IF($M24="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M24)&amp;"|"&amp;$AN24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS24" ca="1">IF($AO24="",TRUE,IF($J24="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J24)&amp;"|"&amp;$AO24,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT24" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT24" ca="1">IF($AN24="",TRUE,IF($M24="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M24)&amp;"|"&amp;$AN24,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT24" ca="1">IF($AO24="",TRUE,IF($N24="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N24)&amp;"|"&amp;$AO24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU24" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU24" ca="1">IF($AO24="",TRUE,IF($N24="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N24)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N24)&amp;"|"&amp;$AO24,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="b">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
         <v>626</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C25,User!$A:$A,0))</f>
+      <c r="E25" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D25,User!$A:$A,0))</f>
         <v>org_user3_4</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>723</v>
       </c>
-      <c r="F25" s="19" t="b">
+      <c r="G25" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G25" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C25,User!$A:$A,0))</f>
+      <c r="H25" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D25,User!$A:$A,0))</f>
         <v>0195d18c-1c92-52b3-93e0-43dc1f2aa037</v>
       </c>
-      <c r="H25" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C25,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="6" t="str">
-        <f>IF(ISNA(MATCH($G25&amp;"|"&amp;$V25,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G25&amp;"|"&amp;$V25,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I25" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D25,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="6" t="str">
+        <f>IF(ISNA(MATCH($H25&amp;"|"&amp;$W25,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H25&amp;"|"&amp;$W25,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J25" ca="1">IF($I25="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I25)&amp;"|"&amp;$R25,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K25" ca="1">IF($I25="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I25),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I25)&amp;"|"&amp;$R25,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K25" ca="1">IF($J25="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J25)&amp;"|"&amp;$S25,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L25" ca="1">IF($I25="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I25),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I25)&amp;"|"&amp;$R25,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M25" s="6" t="str">
-        <f>IF(ISNA(MATCH($C25&amp;"|"&amp;$V25,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C25&amp;"|"&amp;$V25,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L25" ca="1">IF($J25="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J25),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J25)&amp;"|"&amp;$S25,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M25" ca="1">IF($J25="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J25),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J25)&amp;"|"&amp;$S25,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N25" s="6" t="str">
+        <f>IF(ISNA(MATCH($D25&amp;"|"&amp;$W25,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D25&amp;"|"&amp;$W25,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N25" ca="1">IF($M25="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M25)&amp;"|"&amp;$R25,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O25" ca="1">IF($M25="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M25),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M25)&amp;"|"&amp;$R25,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O25" ca="1">IF($N25="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N25)&amp;"|"&amp;$S25,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P25" ca="1">IF($M25="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M25),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M25)&amp;"|"&amp;$R25,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q25" t="s">
+        <f t="array" aca="1" ref="P25" ca="1">IF($N25="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N25),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N25)&amp;"|"&amp;$S25,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q25" ca="1">IF($N25="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N25),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N25)&amp;"|"&amp;$S25,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R25" t="s">
         <v>652</v>
       </c>
-      <c r="R25" t="s">
+      <c r="S25" t="s">
         <v>119</v>
       </c>
-      <c r="S25" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R25,CaseType!$A:$A,0))</f>
+      <c r="T25" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S25,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T25" s="6" t="b">
-        <f>AND(IF($Z25="",TRUE,$R25=INDEX(CaseTypeCol!$B:$B,MATCH($Z25,CaseTypeCol!$A:$A,0))),IF($AG25="",TRUE,$R25=INDEX(CaseTypeCol!$B:$B,MATCH($AG25,CaseTypeCol!$A:$A,0))),IF($AN25="",TRUE,$R25=INDEX(CaseTypeCol!$B:$B,MATCH($AN25,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V25" t="s">
+      <c r="U25" s="6" t="b">
+        <f>AND(IF($AA25="",TRUE,$S25=INDEX(CaseTypeCol!$B:$B,MATCH($AA25,CaseTypeCol!$A:$A,0))),IF($AH25="",TRUE,$S25=INDEX(CaseTypeCol!$B:$B,MATCH($AH25,CaseTypeCol!$A:$A,0))),IF($AO25="",TRUE,$S25=INDEX(CaseTypeCol!$B:$B,MATCH($AO25,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W25" t="s">
         <v>11</v>
       </c>
-      <c r="W25" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V25,DataCollection!$A:$A,0))</f>
+      <c r="X25" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W25,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y25" s="14">
+      <c r="Z25" s="14">
         <v>36526</v>
       </c>
-      <c r="Z25" t="s">
+      <c r="AA25" t="s">
         <v>142</v>
       </c>
-      <c r="AA25" t="s">
+      <c r="AB25" t="s">
         <v>665</v>
       </c>
-      <c r="AB25" s="6" t="str">
-        <f>IF($Z25="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z25,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC25" s="6" t="str">
+        <f>IF($AA25="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA25,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC25" ca="1">IF($Z25="",TRUE,IF($I25="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I25)&amp;"|"&amp;$Z25,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD25" ca="1">IF($Z25="",TRUE,IF($I25="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I25)&amp;"|"&amp;$Z25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD25" ca="1">IF($AA25="",TRUE,IF($J25="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J25)&amp;"|"&amp;$AA25,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE25" ca="1">IF($Z25="",TRUE,IF($M25="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M25)&amp;"|"&amp;$Z25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE25" ca="1">IF($AA25="",TRUE,IF($J25="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J25)&amp;"|"&amp;$AA25,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF25" ca="1">IF($Z25="",TRUE,IF($M25="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M25)&amp;"|"&amp;$Z25,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI25" s="6" t="str">
-        <f>IF($AG25="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG25,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF25" ca="1">IF($AA25="",TRUE,IF($N25="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N25)&amp;"|"&amp;$AA25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG25" ca="1">IF($AA25="",TRUE,IF($N25="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N25)&amp;"|"&amp;$AA25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="6" t="str">
+        <f>IF($AH25="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH25,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ25" ca="1">IF($AG25="",TRUE,IF($I25="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I25)&amp;"|"&amp;$AG25,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK25" ca="1">IF($AG25="",TRUE,IF($I25="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I25)&amp;"|"&amp;$AG25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK25" ca="1">IF($AH25="",TRUE,IF($J25="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J25)&amp;"|"&amp;$AH25,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL25" ca="1">IF($AG25="",TRUE,IF($M25="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M25)&amp;"|"&amp;$AG25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL25" ca="1">IF($AH25="",TRUE,IF($J25="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J25)&amp;"|"&amp;$AH25,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM25" ca="1">IF($AG25="",TRUE,IF($M25="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M25)&amp;"|"&amp;$AG25,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP25" s="6" t="str">
-        <f>IF($AN25="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN25,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM25" ca="1">IF($AH25="",TRUE,IF($N25="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N25)&amp;"|"&amp;$AH25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN25" ca="1">IF($AH25="",TRUE,IF($N25="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N25)&amp;"|"&amp;$AH25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ25" s="6" t="str">
+        <f>IF($AO25="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO25,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ25" ca="1">IF($AN25="",TRUE,IF($I25="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I25)&amp;"|"&amp;$AN25,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR25" ca="1">IF($AN25="",TRUE,IF($I25="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I25)&amp;"|"&amp;$AN25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR25" ca="1">IF($AO25="",TRUE,IF($J25="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J25)&amp;"|"&amp;$AO25,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS25" ca="1">IF($AN25="",TRUE,IF($M25="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M25)&amp;"|"&amp;$AN25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS25" ca="1">IF($AO25="",TRUE,IF($J25="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J25)&amp;"|"&amp;$AO25,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT25" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT25" ca="1">IF($AN25="",TRUE,IF($M25="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M25)&amp;"|"&amp;$AN25,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT25" ca="1">IF($AO25="",TRUE,IF($N25="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N25)&amp;"|"&amp;$AO25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU25" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU25" ca="1">IF($AO25="",TRUE,IF($N25="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N25)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N25)&amp;"|"&amp;$AO25,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="b">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
         <v>627</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C26,User!$A:$A,0))</f>
+      <c r="E26" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D26,User!$A:$A,0))</f>
         <v>org_user4_1</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>723</v>
       </c>
-      <c r="F26" s="19" t="b">
+      <c r="G26" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G26" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C26,User!$A:$A,0))</f>
+      <c r="H26" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D26,User!$A:$A,0))</f>
         <v>0195d18c-1c92-d419-4c71-a570f428499b</v>
       </c>
-      <c r="H26" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C26,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="6" t="str">
-        <f>IF(ISNA(MATCH($G26&amp;"|"&amp;$V26,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G26&amp;"|"&amp;$V26,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I26" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D26,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="6" t="str">
+        <f>IF(ISNA(MATCH($H26&amp;"|"&amp;$W26,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H26&amp;"|"&amp;$W26,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J26" ca="1">IF($I26="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I26)&amp;"|"&amp;$R26,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K26" ca="1">IF($I26="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I26),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I26)&amp;"|"&amp;$R26,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K26" ca="1">IF($J26="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J26)&amp;"|"&amp;$S26,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L26" ca="1">IF($I26="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I26),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I26)&amp;"|"&amp;$R26,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M26" s="6" t="str">
-        <f>IF(ISNA(MATCH($C26&amp;"|"&amp;$V26,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C26&amp;"|"&amp;$V26,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L26" ca="1">IF($J26="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J26),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J26)&amp;"|"&amp;$S26,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M26" ca="1">IF($J26="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J26),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J26)&amp;"|"&amp;$S26,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N26" s="6" t="str">
+        <f>IF(ISNA(MATCH($D26&amp;"|"&amp;$W26,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D26&amp;"|"&amp;$W26,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N26" ca="1">IF($M26="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M26)&amp;"|"&amp;$R26,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O26" ca="1">IF($M26="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M26),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M26)&amp;"|"&amp;$R26,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O26" ca="1">IF($N26="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N26)&amp;"|"&amp;$S26,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P26" ca="1">IF($M26="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M26),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M26)&amp;"|"&amp;$R26,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q26" t="s">
+        <f t="array" aca="1" ref="P26" ca="1">IF($N26="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N26),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N26)&amp;"|"&amp;$S26,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q26" ca="1">IF($N26="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N26),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N26)&amp;"|"&amp;$S26,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R26" t="s">
         <v>653</v>
       </c>
-      <c r="R26" t="s">
+      <c r="S26" t="s">
         <v>119</v>
       </c>
-      <c r="S26" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R26,CaseType!$A:$A,0))</f>
+      <c r="T26" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S26,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T26" s="6" t="b">
-        <f>AND(IF($Z26="",TRUE,$R26=INDEX(CaseTypeCol!$B:$B,MATCH($Z26,CaseTypeCol!$A:$A,0))),IF($AG26="",TRUE,$R26=INDEX(CaseTypeCol!$B:$B,MATCH($AG26,CaseTypeCol!$A:$A,0))),IF($AN26="",TRUE,$R26=INDEX(CaseTypeCol!$B:$B,MATCH($AN26,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V26" t="s">
+      <c r="U26" s="6" t="b">
+        <f>AND(IF($AA26="",TRUE,$S26=INDEX(CaseTypeCol!$B:$B,MATCH($AA26,CaseTypeCol!$A:$A,0))),IF($AH26="",TRUE,$S26=INDEX(CaseTypeCol!$B:$B,MATCH($AH26,CaseTypeCol!$A:$A,0))),IF($AO26="",TRUE,$S26=INDEX(CaseTypeCol!$B:$B,MATCH($AO26,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W26" t="s">
         <v>11</v>
       </c>
-      <c r="W26" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V26,DataCollection!$A:$A,0))</f>
+      <c r="X26" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W26,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y26" s="14">
+      <c r="Z26" s="14">
         <v>36526</v>
       </c>
-      <c r="Z26" t="s">
+      <c r="AA26" t="s">
         <v>142</v>
       </c>
-      <c r="AA26" t="s">
+      <c r="AB26" t="s">
         <v>665</v>
       </c>
-      <c r="AB26" s="6" t="str">
-        <f>IF($Z26="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z26,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC26" s="6" t="str">
+        <f>IF($AA26="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA26,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC26" ca="1">IF($Z26="",TRUE,IF($I26="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I26)&amp;"|"&amp;$Z26,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD26" ca="1">IF($Z26="",TRUE,IF($I26="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I26)&amp;"|"&amp;$Z26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD26" ca="1">IF($AA26="",TRUE,IF($J26="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J26)&amp;"|"&amp;$AA26,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE26" ca="1">IF($Z26="",TRUE,IF($M26="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M26)&amp;"|"&amp;$Z26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE26" ca="1">IF($AA26="",TRUE,IF($J26="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J26)&amp;"|"&amp;$AA26,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF26" ca="1">IF($Z26="",TRUE,IF($M26="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M26)&amp;"|"&amp;$Z26,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI26" s="6" t="str">
-        <f>IF($AG26="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG26,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF26" ca="1">IF($AA26="",TRUE,IF($N26="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N26)&amp;"|"&amp;$AA26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG26" ca="1">IF($AA26="",TRUE,IF($N26="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N26)&amp;"|"&amp;$AA26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="6" t="str">
+        <f>IF($AH26="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH26,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ26" ca="1">IF($AG26="",TRUE,IF($I26="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I26)&amp;"|"&amp;$AG26,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK26" ca="1">IF($AG26="",TRUE,IF($I26="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I26)&amp;"|"&amp;$AG26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK26" ca="1">IF($AH26="",TRUE,IF($J26="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J26)&amp;"|"&amp;$AH26,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL26" ca="1">IF($AG26="",TRUE,IF($M26="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M26)&amp;"|"&amp;$AG26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL26" ca="1">IF($AH26="",TRUE,IF($J26="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J26)&amp;"|"&amp;$AH26,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM26" ca="1">IF($AG26="",TRUE,IF($M26="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M26)&amp;"|"&amp;$AG26,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP26" s="6" t="str">
-        <f>IF($AN26="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN26,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM26" ca="1">IF($AH26="",TRUE,IF($N26="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N26)&amp;"|"&amp;$AH26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN26" ca="1">IF($AH26="",TRUE,IF($N26="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N26)&amp;"|"&amp;$AH26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ26" s="6" t="str">
+        <f>IF($AO26="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO26,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ26" ca="1">IF($AN26="",TRUE,IF($I26="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I26)&amp;"|"&amp;$AN26,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR26" ca="1">IF($AN26="",TRUE,IF($I26="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I26)&amp;"|"&amp;$AN26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR26" ca="1">IF($AO26="",TRUE,IF($J26="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J26)&amp;"|"&amp;$AO26,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS26" ca="1">IF($AN26="",TRUE,IF($M26="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M26)&amp;"|"&amp;$AN26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS26" ca="1">IF($AO26="",TRUE,IF($J26="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J26)&amp;"|"&amp;$AO26,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT26" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT26" ca="1">IF($AN26="",TRUE,IF($M26="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M26)&amp;"|"&amp;$AN26,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT26" ca="1">IF($AO26="",TRUE,IF($N26="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N26)&amp;"|"&amp;$AO26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU26" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU26" ca="1">IF($AO26="",TRUE,IF($N26="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N26)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N26)&amp;"|"&amp;$AO26,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="b">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
         <v>628</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C27,User!$A:$A,0))</f>
+      <c r="E27" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D27,User!$A:$A,0))</f>
         <v>org_user4_2</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>723</v>
       </c>
-      <c r="F27" s="19" t="b">
+      <c r="G27" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G27" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C27,User!$A:$A,0))</f>
+      <c r="H27" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D27,User!$A:$A,0))</f>
         <v>0195d18c-1c92-d419-4c71-a570f428499b</v>
       </c>
-      <c r="H27" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C27,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="6" t="str">
-        <f>IF(ISNA(MATCH($G27&amp;"|"&amp;$V27,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G27&amp;"|"&amp;$V27,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I27" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D27,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="6" t="str">
+        <f>IF(ISNA(MATCH($H27&amp;"|"&amp;$W27,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H27&amp;"|"&amp;$W27,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J27" ca="1">IF($I27="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I27)&amp;"|"&amp;$R27,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K27" ca="1">IF($I27="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I27),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I27)&amp;"|"&amp;$R27,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K27" ca="1">IF($J27="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J27)&amp;"|"&amp;$S27,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L27" ca="1">IF($I27="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I27),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I27)&amp;"|"&amp;$R27,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M27" s="6" t="str">
-        <f>IF(ISNA(MATCH($C27&amp;"|"&amp;$V27,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C27&amp;"|"&amp;$V27,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L27" ca="1">IF($J27="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J27),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J27)&amp;"|"&amp;$S27,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M27" ca="1">IF($J27="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J27),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J27)&amp;"|"&amp;$S27,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="6" t="str">
+        <f>IF(ISNA(MATCH($D27&amp;"|"&amp;$W27,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D27&amp;"|"&amp;$W27,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N27" ca="1">IF($M27="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M27)&amp;"|"&amp;$R27,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O27" ca="1">IF($M27="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M27),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M27)&amp;"|"&amp;$R27,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O27" ca="1">IF($N27="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N27)&amp;"|"&amp;$S27,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P27" ca="1">IF($M27="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M27),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M27)&amp;"|"&amp;$R27,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q27" t="s">
+        <f t="array" aca="1" ref="P27" ca="1">IF($N27="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N27),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N27)&amp;"|"&amp;$S27,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q27" ca="1">IF($N27="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N27),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N27)&amp;"|"&amp;$S27,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R27" t="s">
         <v>654</v>
       </c>
-      <c r="R27" t="s">
+      <c r="S27" t="s">
         <v>119</v>
       </c>
-      <c r="S27" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R27,CaseType!$A:$A,0))</f>
+      <c r="T27" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S27,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T27" s="6" t="b">
-        <f>AND(IF($Z27="",TRUE,$R27=INDEX(CaseTypeCol!$B:$B,MATCH($Z27,CaseTypeCol!$A:$A,0))),IF($AG27="",TRUE,$R27=INDEX(CaseTypeCol!$B:$B,MATCH($AG27,CaseTypeCol!$A:$A,0))),IF($AN27="",TRUE,$R27=INDEX(CaseTypeCol!$B:$B,MATCH($AN27,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V27" t="s">
+      <c r="U27" s="6" t="b">
+        <f>AND(IF($AA27="",TRUE,$S27=INDEX(CaseTypeCol!$B:$B,MATCH($AA27,CaseTypeCol!$A:$A,0))),IF($AH27="",TRUE,$S27=INDEX(CaseTypeCol!$B:$B,MATCH($AH27,CaseTypeCol!$A:$A,0))),IF($AO27="",TRUE,$S27=INDEX(CaseTypeCol!$B:$B,MATCH($AO27,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W27" t="s">
         <v>11</v>
       </c>
-      <c r="W27" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V27,DataCollection!$A:$A,0))</f>
+      <c r="X27" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W27,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y27" s="14">
+      <c r="Z27" s="14">
         <v>36526</v>
       </c>
-      <c r="Z27" t="s">
+      <c r="AA27" t="s">
         <v>142</v>
       </c>
-      <c r="AA27" t="s">
+      <c r="AB27" t="s">
         <v>665</v>
       </c>
-      <c r="AB27" s="6" t="str">
-        <f>IF($Z27="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z27,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC27" s="6" t="str">
+        <f>IF($AA27="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA27,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC27" ca="1">IF($Z27="",TRUE,IF($I27="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I27)&amp;"|"&amp;$Z27,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD27" ca="1">IF($Z27="",TRUE,IF($I27="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I27)&amp;"|"&amp;$Z27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD27" ca="1">IF($AA27="",TRUE,IF($J27="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J27)&amp;"|"&amp;$AA27,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE27" ca="1">IF($Z27="",TRUE,IF($M27="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M27)&amp;"|"&amp;$Z27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE27" ca="1">IF($AA27="",TRUE,IF($J27="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J27)&amp;"|"&amp;$AA27,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF27" ca="1">IF($Z27="",TRUE,IF($M27="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M27)&amp;"|"&amp;$Z27,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI27" s="6" t="str">
-        <f>IF($AG27="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG27,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF27" ca="1">IF($AA27="",TRUE,IF($N27="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N27)&amp;"|"&amp;$AA27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG27" ca="1">IF($AA27="",TRUE,IF($N27="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N27)&amp;"|"&amp;$AA27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="6" t="str">
+        <f>IF($AH27="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH27,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ27" ca="1">IF($AG27="",TRUE,IF($I27="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I27)&amp;"|"&amp;$AG27,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK27" ca="1">IF($AG27="",TRUE,IF($I27="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I27)&amp;"|"&amp;$AG27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK27" ca="1">IF($AH27="",TRUE,IF($J27="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J27)&amp;"|"&amp;$AH27,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL27" ca="1">IF($AG27="",TRUE,IF($M27="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M27)&amp;"|"&amp;$AG27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL27" ca="1">IF($AH27="",TRUE,IF($J27="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J27)&amp;"|"&amp;$AH27,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM27" ca="1">IF($AG27="",TRUE,IF($M27="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M27)&amp;"|"&amp;$AG27,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP27" s="6" t="str">
-        <f>IF($AN27="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN27,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM27" ca="1">IF($AH27="",TRUE,IF($N27="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N27)&amp;"|"&amp;$AH27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN27" ca="1">IF($AH27="",TRUE,IF($N27="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N27)&amp;"|"&amp;$AH27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ27" s="6" t="str">
+        <f>IF($AO27="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO27,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ27" ca="1">IF($AN27="",TRUE,IF($I27="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I27)&amp;"|"&amp;$AN27,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR27" ca="1">IF($AN27="",TRUE,IF($I27="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I27)&amp;"|"&amp;$AN27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR27" ca="1">IF($AO27="",TRUE,IF($J27="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J27)&amp;"|"&amp;$AO27,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS27" ca="1">IF($AN27="",TRUE,IF($M27="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M27)&amp;"|"&amp;$AN27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS27" ca="1">IF($AO27="",TRUE,IF($J27="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J27)&amp;"|"&amp;$AO27,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT27" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT27" ca="1">IF($AN27="",TRUE,IF($M27="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M27)&amp;"|"&amp;$AN27,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT27" ca="1">IF($AO27="",TRUE,IF($N27="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N27)&amp;"|"&amp;$AO27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU27" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU27" ca="1">IF($AO27="",TRUE,IF($N27="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N27)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N27)&amp;"|"&amp;$AO27,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="b">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
         <v>629</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C28,User!$A:$A,0))</f>
+      <c r="E28" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D28,User!$A:$A,0))</f>
         <v>org_user4_3</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>723</v>
       </c>
-      <c r="F28" s="19" t="b">
+      <c r="G28" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G28" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C28,User!$A:$A,0))</f>
+      <c r="H28" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D28,User!$A:$A,0))</f>
         <v>0195d18c-1c92-d419-4c71-a570f428499b</v>
       </c>
-      <c r="H28" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C28,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="6" t="str">
-        <f>IF(ISNA(MATCH($G28&amp;"|"&amp;$V28,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G28&amp;"|"&amp;$V28,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I28" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D28,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="6" t="str">
+        <f>IF(ISNA(MATCH($H28&amp;"|"&amp;$W28,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H28&amp;"|"&amp;$W28,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J28" ca="1">IF($I28="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I28)&amp;"|"&amp;$R28,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K28" ca="1">IF($I28="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I28),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I28)&amp;"|"&amp;$R28,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K28" ca="1">IF($J28="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J28)&amp;"|"&amp;$S28,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L28" ca="1">IF($I28="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I28),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I28)&amp;"|"&amp;$R28,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M28" s="6" t="str">
-        <f>IF(ISNA(MATCH($C28&amp;"|"&amp;$V28,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C28&amp;"|"&amp;$V28,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L28" ca="1">IF($J28="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J28),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J28)&amp;"|"&amp;$S28,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M28" ca="1">IF($J28="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J28),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J28)&amp;"|"&amp;$S28,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N28" s="6" t="str">
+        <f>IF(ISNA(MATCH($D28&amp;"|"&amp;$W28,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D28&amp;"|"&amp;$W28,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N28" ca="1">IF($M28="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M28)&amp;"|"&amp;$R28,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O28" ca="1">IF($M28="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M28),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M28)&amp;"|"&amp;$R28,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O28" ca="1">IF($N28="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N28)&amp;"|"&amp;$S28,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P28" ca="1">IF($M28="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M28),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M28)&amp;"|"&amp;$R28,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q28" t="s">
+        <f t="array" aca="1" ref="P28" ca="1">IF($N28="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N28),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N28)&amp;"|"&amp;$S28,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q28" ca="1">IF($N28="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N28),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N28)&amp;"|"&amp;$S28,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R28" t="s">
         <v>655</v>
       </c>
-      <c r="R28" t="s">
+      <c r="S28" t="s">
         <v>119</v>
       </c>
-      <c r="S28" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R28,CaseType!$A:$A,0))</f>
+      <c r="T28" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S28,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T28" s="6" t="b">
-        <f>AND(IF($Z28="",TRUE,$R28=INDEX(CaseTypeCol!$B:$B,MATCH($Z28,CaseTypeCol!$A:$A,0))),IF($AG28="",TRUE,$R28=INDEX(CaseTypeCol!$B:$B,MATCH($AG28,CaseTypeCol!$A:$A,0))),IF($AN28="",TRUE,$R28=INDEX(CaseTypeCol!$B:$B,MATCH($AN28,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V28" t="s">
+      <c r="U28" s="6" t="b">
+        <f>AND(IF($AA28="",TRUE,$S28=INDEX(CaseTypeCol!$B:$B,MATCH($AA28,CaseTypeCol!$A:$A,0))),IF($AH28="",TRUE,$S28=INDEX(CaseTypeCol!$B:$B,MATCH($AH28,CaseTypeCol!$A:$A,0))),IF($AO28="",TRUE,$S28=INDEX(CaseTypeCol!$B:$B,MATCH($AO28,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W28" t="s">
         <v>11</v>
       </c>
-      <c r="W28" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V28,DataCollection!$A:$A,0))</f>
+      <c r="X28" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W28,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y28" s="14">
+      <c r="Z28" s="14">
         <v>36526</v>
       </c>
-      <c r="Z28" t="s">
+      <c r="AA28" t="s">
         <v>142</v>
       </c>
-      <c r="AA28" t="s">
+      <c r="AB28" t="s">
         <v>665</v>
       </c>
-      <c r="AB28" s="6" t="str">
-        <f>IF($Z28="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z28,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC28" s="6" t="str">
+        <f>IF($AA28="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA28,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC28" ca="1">IF($Z28="",TRUE,IF($I28="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I28)&amp;"|"&amp;$Z28,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD28" ca="1">IF($Z28="",TRUE,IF($I28="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I28)&amp;"|"&amp;$Z28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD28" ca="1">IF($AA28="",TRUE,IF($J28="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J28)&amp;"|"&amp;$AA28,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE28" ca="1">IF($Z28="",TRUE,IF($M28="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M28)&amp;"|"&amp;$Z28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE28" ca="1">IF($AA28="",TRUE,IF($J28="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J28)&amp;"|"&amp;$AA28,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF28" ca="1">IF($Z28="",TRUE,IF($M28="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M28)&amp;"|"&amp;$Z28,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI28" s="6" t="str">
-        <f>IF($AG28="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG28,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF28" ca="1">IF($AA28="",TRUE,IF($N28="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N28)&amp;"|"&amp;$AA28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG28" ca="1">IF($AA28="",TRUE,IF($N28="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N28)&amp;"|"&amp;$AA28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="6" t="str">
+        <f>IF($AH28="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH28,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ28" ca="1">IF($AG28="",TRUE,IF($I28="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I28)&amp;"|"&amp;$AG28,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK28" ca="1">IF($AG28="",TRUE,IF($I28="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I28)&amp;"|"&amp;$AG28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK28" ca="1">IF($AH28="",TRUE,IF($J28="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J28)&amp;"|"&amp;$AH28,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL28" ca="1">IF($AG28="",TRUE,IF($M28="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M28)&amp;"|"&amp;$AG28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL28" ca="1">IF($AH28="",TRUE,IF($J28="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J28)&amp;"|"&amp;$AH28,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM28" ca="1">IF($AG28="",TRUE,IF($M28="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M28)&amp;"|"&amp;$AG28,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP28" s="6" t="str">
-        <f>IF($AN28="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN28,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM28" ca="1">IF($AH28="",TRUE,IF($N28="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N28)&amp;"|"&amp;$AH28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN28" ca="1">IF($AH28="",TRUE,IF($N28="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N28)&amp;"|"&amp;$AH28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ28" s="6" t="str">
+        <f>IF($AO28="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO28,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ28" ca="1">IF($AN28="",TRUE,IF($I28="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I28)&amp;"|"&amp;$AN28,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR28" ca="1">IF($AN28="",TRUE,IF($I28="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I28)&amp;"|"&amp;$AN28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR28" ca="1">IF($AO28="",TRUE,IF($J28="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J28)&amp;"|"&amp;$AO28,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS28" ca="1">IF($AN28="",TRUE,IF($M28="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M28)&amp;"|"&amp;$AN28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS28" ca="1">IF($AO28="",TRUE,IF($J28="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J28)&amp;"|"&amp;$AO28,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT28" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT28" ca="1">IF($AN28="",TRUE,IF($M28="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M28)&amp;"|"&amp;$AN28,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT28" ca="1">IF($AO28="",TRUE,IF($N28="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N28)&amp;"|"&amp;$AO28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU28" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU28" ca="1">IF($AO28="",TRUE,IF($N28="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N28)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N28)&amp;"|"&amp;$AO28,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="b">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
         <v>630</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C29,User!$A:$A,0))</f>
+      <c r="E29" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D29,User!$A:$A,0))</f>
         <v>org_user4_4</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>723</v>
       </c>
-      <c r="F29" s="19" t="b">
+      <c r="G29" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G29" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C29,User!$A:$A,0))</f>
+      <c r="H29" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D29,User!$A:$A,0))</f>
         <v>0195d18c-1c92-d419-4c71-a570f428499b</v>
       </c>
-      <c r="H29" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C29,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="6" t="str">
-        <f>IF(ISNA(MATCH($G29&amp;"|"&amp;$V29,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G29&amp;"|"&amp;$V29,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I29" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D29,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="6" t="str">
+        <f>IF(ISNA(MATCH($H29&amp;"|"&amp;$W29,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H29&amp;"|"&amp;$W29,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J29" ca="1">IF($I29="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I29)&amp;"|"&amp;$R29,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K29" ca="1">IF($I29="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I29),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I29)&amp;"|"&amp;$R29,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K29" ca="1">IF($J29="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J29)&amp;"|"&amp;$S29,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L29" ca="1">IF($I29="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I29),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I29)&amp;"|"&amp;$R29,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M29" s="6" t="str">
-        <f>IF(ISNA(MATCH($C29&amp;"|"&amp;$V29,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C29&amp;"|"&amp;$V29,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L29" ca="1">IF($J29="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J29),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J29)&amp;"|"&amp;$S29,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M29" ca="1">IF($J29="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J29),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J29)&amp;"|"&amp;$S29,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N29" s="6" t="str">
+        <f>IF(ISNA(MATCH($D29&amp;"|"&amp;$W29,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D29&amp;"|"&amp;$W29,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N29" ca="1">IF($M29="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M29)&amp;"|"&amp;$R29,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O29" ca="1">IF($M29="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M29),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M29)&amp;"|"&amp;$R29,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O29" ca="1">IF($N29="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N29)&amp;"|"&amp;$S29,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P29" ca="1">IF($M29="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M29),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M29)&amp;"|"&amp;$R29,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q29" t="s">
+        <f t="array" aca="1" ref="P29" ca="1">IF($N29="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N29),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N29)&amp;"|"&amp;$S29,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q29" ca="1">IF($N29="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N29),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N29)&amp;"|"&amp;$S29,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R29" t="s">
         <v>656</v>
       </c>
-      <c r="R29" t="s">
+      <c r="S29" t="s">
         <v>119</v>
       </c>
-      <c r="S29" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R29,CaseType!$A:$A,0))</f>
+      <c r="T29" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S29,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T29" s="6" t="b">
-        <f>AND(IF($Z29="",TRUE,$R29=INDEX(CaseTypeCol!$B:$B,MATCH($Z29,CaseTypeCol!$A:$A,0))),IF($AG29="",TRUE,$R29=INDEX(CaseTypeCol!$B:$B,MATCH($AG29,CaseTypeCol!$A:$A,0))),IF($AN29="",TRUE,$R29=INDEX(CaseTypeCol!$B:$B,MATCH($AN29,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V29" t="s">
+      <c r="U29" s="6" t="b">
+        <f>AND(IF($AA29="",TRUE,$S29=INDEX(CaseTypeCol!$B:$B,MATCH($AA29,CaseTypeCol!$A:$A,0))),IF($AH29="",TRUE,$S29=INDEX(CaseTypeCol!$B:$B,MATCH($AH29,CaseTypeCol!$A:$A,0))),IF($AO29="",TRUE,$S29=INDEX(CaseTypeCol!$B:$B,MATCH($AO29,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W29" t="s">
         <v>11</v>
       </c>
-      <c r="W29" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V29,DataCollection!$A:$A,0))</f>
+      <c r="X29" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W29,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y29" s="14">
+      <c r="Z29" s="14">
         <v>36526</v>
       </c>
-      <c r="Z29" t="s">
+      <c r="AA29" t="s">
         <v>142</v>
       </c>
-      <c r="AA29" t="s">
+      <c r="AB29" t="s">
         <v>665</v>
       </c>
-      <c r="AB29" s="6" t="str">
-        <f>IF($Z29="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z29,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC29" s="6" t="str">
+        <f>IF($AA29="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA29,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC29" ca="1">IF($Z29="",TRUE,IF($I29="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I29)&amp;"|"&amp;$Z29,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD29" ca="1">IF($Z29="",TRUE,IF($I29="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I29)&amp;"|"&amp;$Z29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD29" ca="1">IF($AA29="",TRUE,IF($J29="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J29)&amp;"|"&amp;$AA29,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE29" ca="1">IF($Z29="",TRUE,IF($M29="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M29)&amp;"|"&amp;$Z29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE29" ca="1">IF($AA29="",TRUE,IF($J29="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J29)&amp;"|"&amp;$AA29,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF29" ca="1">IF($Z29="",TRUE,IF($M29="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M29)&amp;"|"&amp;$Z29,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI29" s="6" t="str">
-        <f>IF($AG29="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG29,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF29" ca="1">IF($AA29="",TRUE,IF($N29="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N29)&amp;"|"&amp;$AA29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG29" ca="1">IF($AA29="",TRUE,IF($N29="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N29)&amp;"|"&amp;$AA29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="6" t="str">
+        <f>IF($AH29="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH29,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ29" ca="1">IF($AG29="",TRUE,IF($I29="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I29)&amp;"|"&amp;$AG29,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK29" ca="1">IF($AG29="",TRUE,IF($I29="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I29)&amp;"|"&amp;$AG29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK29" ca="1">IF($AH29="",TRUE,IF($J29="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J29)&amp;"|"&amp;$AH29,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL29" ca="1">IF($AG29="",TRUE,IF($M29="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M29)&amp;"|"&amp;$AG29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL29" ca="1">IF($AH29="",TRUE,IF($J29="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J29)&amp;"|"&amp;$AH29,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM29" ca="1">IF($AG29="",TRUE,IF($M29="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M29)&amp;"|"&amp;$AG29,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP29" s="6" t="str">
-        <f>IF($AN29="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN29,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM29" ca="1">IF($AH29="",TRUE,IF($N29="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N29)&amp;"|"&amp;$AH29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN29" ca="1">IF($AH29="",TRUE,IF($N29="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N29)&amp;"|"&amp;$AH29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ29" s="6" t="str">
+        <f>IF($AO29="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO29,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ29" ca="1">IF($AN29="",TRUE,IF($I29="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I29)&amp;"|"&amp;$AN29,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR29" ca="1">IF($AN29="",TRUE,IF($I29="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I29)&amp;"|"&amp;$AN29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR29" ca="1">IF($AO29="",TRUE,IF($J29="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J29)&amp;"|"&amp;$AO29,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS29" ca="1">IF($AN29="",TRUE,IF($M29="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M29)&amp;"|"&amp;$AN29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS29" ca="1">IF($AO29="",TRUE,IF($J29="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J29)&amp;"|"&amp;$AO29,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT29" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT29" ca="1">IF($AN29="",TRUE,IF($M29="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M29)&amp;"|"&amp;$AN29,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT29" ca="1">IF($AO29="",TRUE,IF($N29="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N29)&amp;"|"&amp;$AO29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU29" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU29" ca="1">IF($AO29="",TRUE,IF($N29="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N29)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N29)&amp;"|"&amp;$AO29,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="b">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
         <v>631</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C30,User!$A:$A,0))</f>
+      <c r="E30" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D30,User!$A:$A,0))</f>
         <v>org_user5_1</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>723</v>
       </c>
-      <c r="F30" s="19" t="b">
+      <c r="G30" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G30" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C30,User!$A:$A,0))</f>
+      <c r="H30" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D30,User!$A:$A,0))</f>
         <v>0195d18c-1c93-02a2-6920-7e4dbfb73ce0</v>
       </c>
-      <c r="H30" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C30,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I30" s="6" t="str">
-        <f>IF(ISNA(MATCH($G30&amp;"|"&amp;$V30,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G30&amp;"|"&amp;$V30,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I30" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D30,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="6" t="str">
+        <f>IF(ISNA(MATCH($H30&amp;"|"&amp;$W30,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H30&amp;"|"&amp;$W30,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J30" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J30" ca="1">IF($I30="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I30)&amp;"|"&amp;$R30,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K30" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K30" ca="1">IF($I30="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I30),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I30)&amp;"|"&amp;$R30,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K30" ca="1">IF($J30="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J30)&amp;"|"&amp;$S30,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L30" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L30" ca="1">IF($I30="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I30),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I30)&amp;"|"&amp;$R30,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M30" s="6" t="str">
-        <f>IF(ISNA(MATCH($C30&amp;"|"&amp;$V30,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C30&amp;"|"&amp;$V30,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L30" ca="1">IF($J30="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J30),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J30)&amp;"|"&amp;$S30,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M30" ca="1">IF($J30="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J30),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J30)&amp;"|"&amp;$S30,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N30" s="6" t="str">
+        <f>IF(ISNA(MATCH($D30&amp;"|"&amp;$W30,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D30&amp;"|"&amp;$W30,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N30" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N30" ca="1">IF($M30="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M30)&amp;"|"&amp;$R30,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O30" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O30" ca="1">IF($M30="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M30),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M30)&amp;"|"&amp;$R30,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O30" ca="1">IF($N30="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N30)&amp;"|"&amp;$S30,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P30" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P30" ca="1">IF($M30="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M30),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M30)&amp;"|"&amp;$R30,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q30" t="s">
+        <f t="array" aca="1" ref="P30" ca="1">IF($N30="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N30),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N30)&amp;"|"&amp;$S30,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q30" ca="1">IF($N30="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N30),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N30)&amp;"|"&amp;$S30,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R30" t="s">
         <v>657</v>
       </c>
-      <c r="R30" t="s">
+      <c r="S30" t="s">
         <v>119</v>
       </c>
-      <c r="S30" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R30,CaseType!$A:$A,0))</f>
+      <c r="T30" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S30,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T30" s="6" t="b">
-        <f>AND(IF($Z30="",TRUE,$R30=INDEX(CaseTypeCol!$B:$B,MATCH($Z30,CaseTypeCol!$A:$A,0))),IF($AG30="",TRUE,$R30=INDEX(CaseTypeCol!$B:$B,MATCH($AG30,CaseTypeCol!$A:$A,0))),IF($AN30="",TRUE,$R30=INDEX(CaseTypeCol!$B:$B,MATCH($AN30,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V30" t="s">
+      <c r="U30" s="6" t="b">
+        <f>AND(IF($AA30="",TRUE,$S30=INDEX(CaseTypeCol!$B:$B,MATCH($AA30,CaseTypeCol!$A:$A,0))),IF($AH30="",TRUE,$S30=INDEX(CaseTypeCol!$B:$B,MATCH($AH30,CaseTypeCol!$A:$A,0))),IF($AO30="",TRUE,$S30=INDEX(CaseTypeCol!$B:$B,MATCH($AO30,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W30" t="s">
         <v>11</v>
       </c>
-      <c r="W30" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V30,DataCollection!$A:$A,0))</f>
+      <c r="X30" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W30,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y30" s="14">
+      <c r="Z30" s="14">
         <v>36526</v>
       </c>
-      <c r="Z30" t="s">
+      <c r="AA30" t="s">
         <v>142</v>
       </c>
-      <c r="AA30" t="s">
+      <c r="AB30" t="s">
         <v>665</v>
       </c>
-      <c r="AB30" s="6" t="str">
-        <f>IF($Z30="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z30,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC30" s="6" t="str">
+        <f>IF($AA30="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA30,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC30" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC30" ca="1">IF($Z30="",TRUE,IF($I30="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I30)&amp;"|"&amp;$Z30,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD30" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD30" ca="1">IF($Z30="",TRUE,IF($I30="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I30)&amp;"|"&amp;$Z30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD30" ca="1">IF($AA30="",TRUE,IF($J30="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J30)&amp;"|"&amp;$AA30,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE30" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE30" ca="1">IF($Z30="",TRUE,IF($M30="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M30)&amp;"|"&amp;$Z30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE30" ca="1">IF($AA30="",TRUE,IF($J30="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J30)&amp;"|"&amp;$AA30,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF30" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF30" ca="1">IF($Z30="",TRUE,IF($M30="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M30)&amp;"|"&amp;$Z30,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI30" s="6" t="str">
-        <f>IF($AG30="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG30,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF30" ca="1">IF($AA30="",TRUE,IF($N30="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N30)&amp;"|"&amp;$AA30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG30" ca="1">IF($AA30="",TRUE,IF($N30="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N30)&amp;"|"&amp;$AA30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="6" t="str">
+        <f>IF($AH30="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH30,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ30" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ30" ca="1">IF($AG30="",TRUE,IF($I30="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I30)&amp;"|"&amp;$AG30,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK30" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK30" ca="1">IF($AG30="",TRUE,IF($I30="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I30)&amp;"|"&amp;$AG30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK30" ca="1">IF($AH30="",TRUE,IF($J30="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J30)&amp;"|"&amp;$AH30,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL30" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL30" ca="1">IF($AG30="",TRUE,IF($M30="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M30)&amp;"|"&amp;$AG30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL30" ca="1">IF($AH30="",TRUE,IF($J30="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J30)&amp;"|"&amp;$AH30,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM30" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM30" ca="1">IF($AG30="",TRUE,IF($M30="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M30)&amp;"|"&amp;$AG30,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP30" s="6" t="str">
-        <f>IF($AN30="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN30,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM30" ca="1">IF($AH30="",TRUE,IF($N30="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N30)&amp;"|"&amp;$AH30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN30" ca="1">IF($AH30="",TRUE,IF($N30="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N30)&amp;"|"&amp;$AH30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ30" s="6" t="str">
+        <f>IF($AO30="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO30,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ30" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ30" ca="1">IF($AN30="",TRUE,IF($I30="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I30)&amp;"|"&amp;$AN30,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR30" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR30" ca="1">IF($AN30="",TRUE,IF($I30="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I30)&amp;"|"&amp;$AN30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR30" ca="1">IF($AO30="",TRUE,IF($J30="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J30)&amp;"|"&amp;$AO30,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS30" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS30" ca="1">IF($AN30="",TRUE,IF($M30="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M30)&amp;"|"&amp;$AN30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS30" ca="1">IF($AO30="",TRUE,IF($J30="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J30)&amp;"|"&amp;$AO30,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT30" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT30" ca="1">IF($AN30="",TRUE,IF($M30="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M30)&amp;"|"&amp;$AN30,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT30" ca="1">IF($AO30="",TRUE,IF($N30="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N30)&amp;"|"&amp;$AO30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU30" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU30" ca="1">IF($AO30="",TRUE,IF($N30="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N30)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N30)&amp;"|"&amp;$AO30,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="b">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
         <v>632</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>36</v>
       </c>
-      <c r="D31" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C31,User!$A:$A,0))</f>
+      <c r="E31" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D31,User!$A:$A,0))</f>
         <v>org_user5_2</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>723</v>
       </c>
-      <c r="F31" s="19" t="b">
+      <c r="G31" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G31" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C31,User!$A:$A,0))</f>
+      <c r="H31" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D31,User!$A:$A,0))</f>
         <v>0195d18c-1c93-02a2-6920-7e4dbfb73ce0</v>
       </c>
-      <c r="H31" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C31,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I31" s="6" t="str">
-        <f>IF(ISNA(MATCH($G31&amp;"|"&amp;$V31,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G31&amp;"|"&amp;$V31,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I31" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D31,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="6" t="str">
+        <f>IF(ISNA(MATCH($H31&amp;"|"&amp;$W31,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H31&amp;"|"&amp;$W31,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J31" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J31" ca="1">IF($I31="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I31)&amp;"|"&amp;$R31,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K31" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K31" ca="1">IF($I31="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I31),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I31)&amp;"|"&amp;$R31,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K31" ca="1">IF($J31="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J31)&amp;"|"&amp;$S31,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L31" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L31" ca="1">IF($I31="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I31),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I31)&amp;"|"&amp;$R31,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M31" s="6" t="str">
-        <f>IF(ISNA(MATCH($C31&amp;"|"&amp;$V31,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C31&amp;"|"&amp;$V31,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L31" ca="1">IF($J31="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J31),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J31)&amp;"|"&amp;$S31,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M31" ca="1">IF($J31="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J31),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J31)&amp;"|"&amp;$S31,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="6" t="str">
+        <f>IF(ISNA(MATCH($D31&amp;"|"&amp;$W31,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D31&amp;"|"&amp;$W31,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N31" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N31" ca="1">IF($M31="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M31)&amp;"|"&amp;$R31,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O31" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O31" ca="1">IF($M31="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M31),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M31)&amp;"|"&amp;$R31,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O31" ca="1">IF($N31="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N31)&amp;"|"&amp;$S31,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P31" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P31" ca="1">IF($M31="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M31),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M31)&amp;"|"&amp;$R31,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q31" t="s">
+        <f t="array" aca="1" ref="P31" ca="1">IF($N31="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N31),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N31)&amp;"|"&amp;$S31,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q31" ca="1">IF($N31="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N31),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N31)&amp;"|"&amp;$S31,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R31" t="s">
         <v>658</v>
       </c>
-      <c r="R31" t="s">
+      <c r="S31" t="s">
         <v>119</v>
       </c>
-      <c r="S31" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R31,CaseType!$A:$A,0))</f>
+      <c r="T31" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S31,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T31" s="6" t="b">
-        <f>AND(IF($Z31="",TRUE,$R31=INDEX(CaseTypeCol!$B:$B,MATCH($Z31,CaseTypeCol!$A:$A,0))),IF($AG31="",TRUE,$R31=INDEX(CaseTypeCol!$B:$B,MATCH($AG31,CaseTypeCol!$A:$A,0))),IF($AN31="",TRUE,$R31=INDEX(CaseTypeCol!$B:$B,MATCH($AN31,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V31" t="s">
+      <c r="U31" s="6" t="b">
+        <f>AND(IF($AA31="",TRUE,$S31=INDEX(CaseTypeCol!$B:$B,MATCH($AA31,CaseTypeCol!$A:$A,0))),IF($AH31="",TRUE,$S31=INDEX(CaseTypeCol!$B:$B,MATCH($AH31,CaseTypeCol!$A:$A,0))),IF($AO31="",TRUE,$S31=INDEX(CaseTypeCol!$B:$B,MATCH($AO31,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W31" t="s">
         <v>11</v>
       </c>
-      <c r="W31" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V31,DataCollection!$A:$A,0))</f>
+      <c r="X31" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W31,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y31" s="14">
+      <c r="Z31" s="14">
         <v>36526</v>
       </c>
-      <c r="Z31" t="s">
+      <c r="AA31" t="s">
         <v>142</v>
       </c>
-      <c r="AA31" t="s">
+      <c r="AB31" t="s">
         <v>665</v>
       </c>
-      <c r="AB31" s="6" t="str">
-        <f>IF($Z31="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z31,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC31" s="6" t="str">
+        <f>IF($AA31="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA31,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC31" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC31" ca="1">IF($Z31="",TRUE,IF($I31="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I31)&amp;"|"&amp;$Z31,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD31" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD31" ca="1">IF($Z31="",TRUE,IF($I31="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I31)&amp;"|"&amp;$Z31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD31" ca="1">IF($AA31="",TRUE,IF($J31="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J31)&amp;"|"&amp;$AA31,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE31" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE31" ca="1">IF($Z31="",TRUE,IF($M31="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M31)&amp;"|"&amp;$Z31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE31" ca="1">IF($AA31="",TRUE,IF($J31="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J31)&amp;"|"&amp;$AA31,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF31" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF31" ca="1">IF($Z31="",TRUE,IF($M31="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M31)&amp;"|"&amp;$Z31,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI31" s="6" t="str">
-        <f>IF($AG31="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG31,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF31" ca="1">IF($AA31="",TRUE,IF($N31="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N31)&amp;"|"&amp;$AA31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG31" ca="1">IF($AA31="",TRUE,IF($N31="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N31)&amp;"|"&amp;$AA31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="6" t="str">
+        <f>IF($AH31="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH31,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ31" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ31" ca="1">IF($AG31="",TRUE,IF($I31="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I31)&amp;"|"&amp;$AG31,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK31" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK31" ca="1">IF($AG31="",TRUE,IF($I31="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I31)&amp;"|"&amp;$AG31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK31" ca="1">IF($AH31="",TRUE,IF($J31="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J31)&amp;"|"&amp;$AH31,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL31" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL31" ca="1">IF($AG31="",TRUE,IF($M31="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M31)&amp;"|"&amp;$AG31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL31" ca="1">IF($AH31="",TRUE,IF($J31="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J31)&amp;"|"&amp;$AH31,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM31" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM31" ca="1">IF($AG31="",TRUE,IF($M31="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M31)&amp;"|"&amp;$AG31,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP31" s="6" t="str">
-        <f>IF($AN31="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN31,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM31" ca="1">IF($AH31="",TRUE,IF($N31="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N31)&amp;"|"&amp;$AH31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN31" ca="1">IF($AH31="",TRUE,IF($N31="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N31)&amp;"|"&amp;$AH31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ31" s="6" t="str">
+        <f>IF($AO31="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO31,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ31" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ31" ca="1">IF($AN31="",TRUE,IF($I31="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I31)&amp;"|"&amp;$AN31,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR31" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR31" ca="1">IF($AN31="",TRUE,IF($I31="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I31)&amp;"|"&amp;$AN31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR31" ca="1">IF($AO31="",TRUE,IF($J31="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J31)&amp;"|"&amp;$AO31,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS31" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS31" ca="1">IF($AN31="",TRUE,IF($M31="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M31)&amp;"|"&amp;$AN31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS31" ca="1">IF($AO31="",TRUE,IF($J31="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J31)&amp;"|"&amp;$AO31,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT31" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT31" ca="1">IF($AN31="",TRUE,IF($M31="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M31)&amp;"|"&amp;$AN31,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT31" ca="1">IF($AO31="",TRUE,IF($N31="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N31)&amp;"|"&amp;$AO31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU31" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU31" ca="1">IF($AO31="",TRUE,IF($N31="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N31)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N31)&amp;"|"&amp;$AO31,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="b">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
         <v>633</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>37</v>
       </c>
-      <c r="D32" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C32,User!$A:$A,0))</f>
+      <c r="E32" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D32,User!$A:$A,0))</f>
         <v>org_user5_3</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>723</v>
       </c>
-      <c r="F32" s="19" t="b">
+      <c r="G32" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G32" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C32,User!$A:$A,0))</f>
+      <c r="H32" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D32,User!$A:$A,0))</f>
         <v>0195d18c-1c93-02a2-6920-7e4dbfb73ce0</v>
       </c>
-      <c r="H32" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C32,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I32" s="6" t="str">
-        <f>IF(ISNA(MATCH($G32&amp;"|"&amp;$V32,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G32&amp;"|"&amp;$V32,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I32" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D32,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="6" t="str">
+        <f>IF(ISNA(MATCH($H32&amp;"|"&amp;$W32,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H32&amp;"|"&amp;$W32,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J32" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J32" ca="1">IF($I32="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I32)&amp;"|"&amp;$R32,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K32" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K32" ca="1">IF($I32="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I32),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I32)&amp;"|"&amp;$R32,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K32" ca="1">IF($J32="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J32)&amp;"|"&amp;$S32,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L32" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L32" ca="1">IF($I32="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I32),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I32)&amp;"|"&amp;$R32,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M32" s="6" t="str">
-        <f>IF(ISNA(MATCH($C32&amp;"|"&amp;$V32,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C32&amp;"|"&amp;$V32,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L32" ca="1">IF($J32="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J32),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J32)&amp;"|"&amp;$S32,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M32" ca="1">IF($J32="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J32),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J32)&amp;"|"&amp;$S32,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N32" s="6" t="str">
+        <f>IF(ISNA(MATCH($D32&amp;"|"&amp;$W32,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D32&amp;"|"&amp;$W32,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N32" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N32" ca="1">IF($M32="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M32)&amp;"|"&amp;$R32,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O32" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O32" ca="1">IF($M32="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M32),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M32)&amp;"|"&amp;$R32,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O32" ca="1">IF($N32="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N32)&amp;"|"&amp;$S32,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P32" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P32" ca="1">IF($M32="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M32),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M32)&amp;"|"&amp;$R32,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q32" t="s">
+        <f t="array" aca="1" ref="P32" ca="1">IF($N32="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N32),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N32)&amp;"|"&amp;$S32,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q32" ca="1">IF($N32="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N32),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N32)&amp;"|"&amp;$S32,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R32" t="s">
         <v>659</v>
       </c>
-      <c r="R32" t="s">
+      <c r="S32" t="s">
         <v>119</v>
       </c>
-      <c r="S32" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R32,CaseType!$A:$A,0))</f>
+      <c r="T32" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S32,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T32" s="6" t="b">
-        <f>AND(IF($Z32="",TRUE,$R32=INDEX(CaseTypeCol!$B:$B,MATCH($Z32,CaseTypeCol!$A:$A,0))),IF($AG32="",TRUE,$R32=INDEX(CaseTypeCol!$B:$B,MATCH($AG32,CaseTypeCol!$A:$A,0))),IF($AN32="",TRUE,$R32=INDEX(CaseTypeCol!$B:$B,MATCH($AN32,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V32" t="s">
+      <c r="U32" s="6" t="b">
+        <f>AND(IF($AA32="",TRUE,$S32=INDEX(CaseTypeCol!$B:$B,MATCH($AA32,CaseTypeCol!$A:$A,0))),IF($AH32="",TRUE,$S32=INDEX(CaseTypeCol!$B:$B,MATCH($AH32,CaseTypeCol!$A:$A,0))),IF($AO32="",TRUE,$S32=INDEX(CaseTypeCol!$B:$B,MATCH($AO32,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W32" t="s">
         <v>11</v>
       </c>
-      <c r="W32" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V32,DataCollection!$A:$A,0))</f>
+      <c r="X32" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W32,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y32" s="14">
+      <c r="Z32" s="14">
         <v>36526</v>
       </c>
-      <c r="Z32" t="s">
+      <c r="AA32" t="s">
         <v>142</v>
       </c>
-      <c r="AA32" t="s">
+      <c r="AB32" t="s">
         <v>665</v>
       </c>
-      <c r="AB32" s="6" t="str">
-        <f>IF($Z32="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z32,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC32" s="6" t="str">
+        <f>IF($AA32="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA32,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC32" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC32" ca="1">IF($Z32="",TRUE,IF($I32="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I32)&amp;"|"&amp;$Z32,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD32" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD32" ca="1">IF($Z32="",TRUE,IF($I32="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I32)&amp;"|"&amp;$Z32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD32" ca="1">IF($AA32="",TRUE,IF($J32="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J32)&amp;"|"&amp;$AA32,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE32" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE32" ca="1">IF($Z32="",TRUE,IF($M32="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M32)&amp;"|"&amp;$Z32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE32" ca="1">IF($AA32="",TRUE,IF($J32="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J32)&amp;"|"&amp;$AA32,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF32" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF32" ca="1">IF($Z32="",TRUE,IF($M32="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M32)&amp;"|"&amp;$Z32,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI32" s="6" t="str">
-        <f>IF($AG32="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG32,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF32" ca="1">IF($AA32="",TRUE,IF($N32="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N32)&amp;"|"&amp;$AA32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG32" ca="1">IF($AA32="",TRUE,IF($N32="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N32)&amp;"|"&amp;$AA32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="6" t="str">
+        <f>IF($AH32="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH32,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ32" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ32" ca="1">IF($AG32="",TRUE,IF($I32="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I32)&amp;"|"&amp;$AG32,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK32" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK32" ca="1">IF($AG32="",TRUE,IF($I32="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I32)&amp;"|"&amp;$AG32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK32" ca="1">IF($AH32="",TRUE,IF($J32="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J32)&amp;"|"&amp;$AH32,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL32" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL32" ca="1">IF($AG32="",TRUE,IF($M32="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M32)&amp;"|"&amp;$AG32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL32" ca="1">IF($AH32="",TRUE,IF($J32="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J32)&amp;"|"&amp;$AH32,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM32" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM32" ca="1">IF($AG32="",TRUE,IF($M32="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M32)&amp;"|"&amp;$AG32,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP32" s="6" t="str">
-        <f>IF($AN32="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN32,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM32" ca="1">IF($AH32="",TRUE,IF($N32="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N32)&amp;"|"&amp;$AH32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN32" ca="1">IF($AH32="",TRUE,IF($N32="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N32)&amp;"|"&amp;$AH32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ32" s="6" t="str">
+        <f>IF($AO32="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO32,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ32" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ32" ca="1">IF($AN32="",TRUE,IF($I32="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I32)&amp;"|"&amp;$AN32,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR32" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR32" ca="1">IF($AN32="",TRUE,IF($I32="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I32)&amp;"|"&amp;$AN32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR32" ca="1">IF($AO32="",TRUE,IF($J32="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J32)&amp;"|"&amp;$AO32,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS32" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS32" ca="1">IF($AN32="",TRUE,IF($M32="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M32)&amp;"|"&amp;$AN32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS32" ca="1">IF($AO32="",TRUE,IF($J32="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J32)&amp;"|"&amp;$AO32,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT32" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT32" ca="1">IF($AN32="",TRUE,IF($M32="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M32)&amp;"|"&amp;$AN32,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="array" aca="1" ref="AT32" ca="1">IF($AO32="",TRUE,IF($N32="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N32)&amp;"|"&amp;$AO32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU32" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU32" ca="1">IF($AO32="",TRUE,IF($N32="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N32)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N32)&amp;"|"&amp;$AO32,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="b">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
         <v>634</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="6" t="str">
-        <f>INDEX(User!$C:$C,MATCH($C33,User!$A:$A,0))</f>
+      <c r="E33" s="6" t="str">
+        <f>INDEX(User!$C:$C,MATCH($D33,User!$A:$A,0))</f>
         <v>org_user5_4</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>723</v>
       </c>
-      <c r="F33" s="19" t="b">
+      <c r="G33" s="19" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="G33" s="6" t="str">
-        <f>INDEX(User!$F:$F,MATCH($C33,User!$A:$A,0))</f>
+      <c r="H33" s="6" t="str">
+        <f>INDEX(User!$F:$F,MATCH($D33,User!$A:$A,0))</f>
         <v>0195d18c-1c93-02a2-6920-7e4dbfb73ce0</v>
       </c>
-      <c r="H33" s="6" t="b">
-        <f>INDEX(User!$L:$L,MATCH($C33,User!$A:$A,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I33" s="6" t="str">
-        <f>IF(ISNA(MATCH($G33&amp;"|"&amp;$V33,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($G33&amp;"|"&amp;$V33,OrganizationAccessCasePolicy!$V:$V,0))</f>
+      <c r="I33" s="6" t="b">
+        <f>INDEX(User!$L:$L,MATCH($D33,User!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="6" t="str">
+        <f>IF(ISNA(MATCH($H33&amp;"|"&amp;$W33,OrganizationAccessCasePolicy!$V:$V,0)),"",MATCH($H33&amp;"|"&amp;$W33,OrganizationAccessCasePolicy!$V:$V,0))</f>
         <v/>
       </c>
-      <c r="J33" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="J33" ca="1">IF($I33="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I33)&amp;"|"&amp;$R33,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="K33" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="K33" ca="1">IF($I33="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$I33),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I33)&amp;"|"&amp;$R33,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="K33" ca="1">IF($J33="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J33)&amp;"|"&amp;$S33,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="L33" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="L33" ca="1">IF($I33="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$I33),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$I33)&amp;"|"&amp;$R33,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="M33" s="6" t="str">
-        <f>IF(ISNA(MATCH($C33&amp;"|"&amp;$V33,UserAccessCasePolicy!$W:$W,0)),"",MATCH($C33&amp;"|"&amp;$V33,UserAccessCasePolicy!$W:$W,0))</f>
+        <f t="array" aca="1" ref="L33" ca="1">IF($J33="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!H"&amp;$J33),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J33)&amp;"|"&amp;$S33,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="M33" ca="1">IF($J33="",FALSE,AND(INDIRECT("OrganizationAccessCasePolicy!I"&amp;$J33),NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!D"&amp;$J33)&amp;"|"&amp;$S33,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="N33" s="6" t="str">
+        <f>IF(ISNA(MATCH($D33&amp;"|"&amp;$W33,UserAccessCasePolicy!$W:$W,0)),"",MATCH($D33&amp;"|"&amp;$W33,UserAccessCasePolicy!$W:$W,0))</f>
         <v/>
       </c>
-      <c r="N33" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="N33" ca="1">IF($M33="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M33)&amp;"|"&amp;$R33,CaseTypeSetMember!$H:$H,0))))</f>
-        <v>0</v>
-      </c>
       <c r="O33" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="O33" ca="1">IF($M33="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$M33),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M33)&amp;"|"&amp;$R33,CaseTypeSetMember!$H:$H,0)))))</f>
+        <f t="array" aca="1" ref="O33" ca="1">IF($N33="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N33)&amp;"|"&amp;$S33,CaseTypeSetMember!$H:$H,0))))</f>
         <v>0</v>
       </c>
       <c r="P33" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="P33" ca="1">IF($M33="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$M33),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$M33)&amp;"|"&amp;$R33,CaseTypeSetMember!$H:$H,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="Q33" t="s">
+        <f t="array" aca="1" ref="P33" ca="1">IF($N33="",FALSE,AND(INDIRECT("UserAccessCasePolicy!G"&amp;$N33),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N33)&amp;"|"&amp;$S33,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="Q33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="Q33" ca="1">IF($N33="",FALSE,AND(INDIRECT("UserAccessCasePolicy!H"&amp;$N33),NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!D"&amp;$N33)&amp;"|"&amp;$S33,CaseTypeSetMember!$H:$H,0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="R33" t="s">
         <v>660</v>
       </c>
-      <c r="R33" t="s">
+      <c r="S33" t="s">
         <v>119</v>
       </c>
-      <c r="S33" s="6" t="str">
-        <f>INDEX(CaseType!$B:$B,MATCH($R33,CaseType!$A:$A,0))</f>
+      <c r="T33" s="6" t="str">
+        <f>INDEX(CaseType!$B:$B,MATCH($S33,CaseType!$A:$A,0))</f>
         <v>case_type1</v>
       </c>
-      <c r="T33" s="6" t="b">
-        <f>AND(IF($Z33="",TRUE,$R33=INDEX(CaseTypeCol!$B:$B,MATCH($Z33,CaseTypeCol!$A:$A,0))),IF($AG33="",TRUE,$R33=INDEX(CaseTypeCol!$B:$B,MATCH($AG33,CaseTypeCol!$A:$A,0))),IF($AN33="",TRUE,$R33=INDEX(CaseTypeCol!$B:$B,MATCH($AN33,CaseTypeCol!$A:$A,0))))</f>
-        <v>1</v>
-      </c>
-      <c r="V33" t="s">
+      <c r="U33" s="6" t="b">
+        <f>AND(IF($AA33="",TRUE,$S33=INDEX(CaseTypeCol!$B:$B,MATCH($AA33,CaseTypeCol!$A:$A,0))),IF($AH33="",TRUE,$S33=INDEX(CaseTypeCol!$B:$B,MATCH($AH33,CaseTypeCol!$A:$A,0))),IF($AO33="",TRUE,$S33=INDEX(CaseTypeCol!$B:$B,MATCH($AO33,CaseTypeCol!$A:$A,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="W33" t="s">
         <v>11</v>
       </c>
-      <c r="W33" s="6" t="str">
-        <f>INDEX(DataCollection!$B:$B,MATCH($V33,DataCollection!$A:$A,0))</f>
+      <c r="X33" s="6" t="str">
+        <f>INDEX(DataCollection!$B:$B,MATCH($W33,DataCollection!$A:$A,0))</f>
         <v>data_collection1</v>
       </c>
-      <c r="Y33" s="14">
+      <c r="Z33" s="14">
         <v>36526</v>
       </c>
-      <c r="Z33" t="s">
+      <c r="AA33" t="s">
         <v>142</v>
       </c>
-      <c r="AA33" t="s">
+      <c r="AB33" t="s">
         <v>665</v>
       </c>
-      <c r="AB33" s="6" t="str">
-        <f>IF($Z33="","",INDEX(CaseTypeCol!$G:$G,MATCH($Z33,CaseTypeCol!$A:$A,0)))</f>
+      <c r="AC33" s="6" t="str">
+        <f>IF($AA33="","",INDEX(CaseTypeCol!$G:$G,MATCH($AA33,CaseTypeCol!$A:$A,0)))</f>
         <v>case_type1_dim1_1_text</v>
       </c>
-      <c r="AC33" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AC33" ca="1">IF($Z33="",TRUE,IF($I33="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I33)&amp;"|"&amp;$Z33,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
       <c r="AD33" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AD33" ca="1">IF($Z33="",TRUE,IF($I33="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I33)&amp;"|"&amp;$Z33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AD33" ca="1">IF($AA33="",TRUE,IF($J33="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J33)&amp;"|"&amp;$AA33,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AE33" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AE33" ca="1">IF($Z33="",TRUE,IF($M33="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M33)&amp;"|"&amp;$Z33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AE33" ca="1">IF($AA33="",TRUE,IF($J33="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J33)&amp;"|"&amp;$AA33,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>0</v>
       </c>
       <c r="AF33" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AF33" ca="1">IF($Z33="",TRUE,IF($M33="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M33)&amp;"|"&amp;$Z33,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>0</v>
-      </c>
-      <c r="AI33" s="6" t="str">
-        <f>IF($AG33="","",INDEX(CaseTypeCol!$G:$G,MATCH($AG33,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AF33" ca="1">IF($AA33="",TRUE,IF($N33="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N33)&amp;"|"&amp;$AA33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AG33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AG33" ca="1">IF($AA33="",TRUE,IF($N33="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N33)&amp;"|"&amp;$AA33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="6" t="str">
+        <f>IF($AH33="","",INDEX(CaseTypeCol!$G:$G,MATCH($AH33,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AJ33" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AJ33" ca="1">IF($AG33="",TRUE,IF($I33="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I33)&amp;"|"&amp;$AG33,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AK33" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AK33" ca="1">IF($AG33="",TRUE,IF($I33="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I33)&amp;"|"&amp;$AG33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AK33" ca="1">IF($AH33="",TRUE,IF($J33="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J33)&amp;"|"&amp;$AH33,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AL33" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AL33" ca="1">IF($AG33="",TRUE,IF($M33="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M33)&amp;"|"&amp;$AG33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AL33" ca="1">IF($AH33="",TRUE,IF($J33="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J33)&amp;"|"&amp;$AH33,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AM33" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AM33" ca="1">IF($AG33="",TRUE,IF($M33="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M33)&amp;"|"&amp;$AG33,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
-      <c r="AP33" s="6" t="str">
-        <f>IF($AN33="","",INDEX(CaseTypeCol!$G:$G,MATCH($AN33,CaseTypeCol!$A:$A,0)))</f>
+        <f t="array" aca="1" ref="AM33" ca="1">IF($AH33="",TRUE,IF($N33="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N33)&amp;"|"&amp;$AH33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AN33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AN33" ca="1">IF($AH33="",TRUE,IF($N33="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N33)&amp;"|"&amp;$AH33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AQ33" s="6" t="str">
+        <f>IF($AO33="","",INDEX(CaseTypeCol!$G:$G,MATCH($AO33,CaseTypeCol!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="AQ33" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AQ33" ca="1">IF($AN33="",TRUE,IF($I33="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$I33)&amp;"|"&amp;$AN33,CaseTypeColSetMember!$H:$H,0))))))</f>
-        <v>1</v>
-      </c>
       <c r="AR33" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AR33" ca="1">IF($AN33="",TRUE,IF($I33="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$I33)&amp;"|"&amp;$AN33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AR33" ca="1">IF($AO33="",TRUE,IF($J33="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!J"&amp;$J33)&amp;"|"&amp;$AO33,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AS33" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AS33" ca="1">IF($AN33="",TRUE,IF($M33="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$M33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$M33)&amp;"|"&amp;$AN33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AS33" ca="1">IF($AO33="",TRUE,IF($J33="",FALSE,IF(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("OrganizationAccessCasePolicy!L"&amp;$J33)&amp;"|"&amp;$AO33,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
       <c r="AT33" s="6" t="b" cm="1">
-        <f t="array" aca="1" ref="AT33" ca="1">IF($AN33="",TRUE,IF($M33="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$M33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$M33)&amp;"|"&amp;$AN33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <f t="array" aca="1" ref="AT33" ca="1">IF($AO33="",TRUE,IF($N33="",FALSE,IF(INDIRECT("UserAccessCasePolicy!I"&amp;$N33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!I"&amp;$N33)&amp;"|"&amp;$AO33,CaseTypeColSetMember!$H:$H,0))))))</f>
+        <v>1</v>
+      </c>
+      <c r="AU33" s="6" t="b" cm="1">
+        <f t="array" aca="1" ref="AU33" ca="1">IF($AO33="",TRUE,IF($N33="",FALSE,IF(INDIRECT("UserAccessCasePolicy!K"&amp;$N33)="",FALSE,NOT(ISNA(MATCH(INDIRECT("UserAccessCasePolicy!K"&amp;$N33)&amp;"|"&amp;$AO33,CaseTypeColSetMember!$H:$H,0))))))</f>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AU33" xr:uid="{8E0C7C33-6768-4AAE-A57E-F80585DED472}"/>
+  <autoFilter ref="A1:AV33" xr:uid="{8E0C7C33-6768-4AAE-A57E-F80585DED472}"/>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="T2:T33">
+  <conditionalFormatting sqref="U2:U33">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>T2=FALSE</formula>
+      <formula>U2=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
